--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A91897-9D80-4BC1-B6B9-766599B41B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845AD921-642C-47C7-B0E2-6977CC2E961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="COMPUTER" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$438</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$445</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1205">
   <si>
     <t>INDICE</t>
   </si>
@@ -3553,9 +3553,6 @@
     <t>E.M. ANDRE GOMES</t>
   </si>
   <si>
-    <t xml:space="preserve"> E.M. MARGARIDA TRINDADE</t>
-  </si>
-  <si>
     <t>E.M. TONINHO SERRA</t>
   </si>
   <si>
@@ -3613,7 +3610,49 @@
     <t>E.M.B. SUELI AMARAL</t>
   </si>
   <si>
-    <t>E.M. AGOSTINHO FRAMSCESCHI</t>
+    <t>E.M. AGOSTINHO FRANSCESCHI</t>
+  </si>
+  <si>
+    <t>EPSON WORKFORCE PRO WF-C5890 </t>
+  </si>
+  <si>
+    <t>EPSON WORKFORCE PRO WF-C5899 </t>
+  </si>
+  <si>
+    <t>XBJZ043814</t>
+  </si>
+  <si>
+    <t>INSTALADA GABINETE SEDUC 24/02/2026;</t>
+  </si>
+  <si>
+    <t>SESAU - REGULAÇÃO RECEPCAO</t>
+  </si>
+  <si>
+    <t>E.M. MARGARIDA TRINDADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E.M. DR. FABIO SIQUEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTALADA 20/10/2025 SEDUC GABINETE; </t>
+  </si>
+  <si>
+    <t>XBJZ043818</t>
+  </si>
+  <si>
+    <t>XBJZ029723</t>
+  </si>
+  <si>
+    <t>XBJZ029718</t>
+  </si>
+  <si>
+    <t>XBJZ043841</t>
+  </si>
+  <si>
+    <t>XC75036979</t>
+  </si>
+  <si>
+    <t>XC75047651</t>
   </si>
 </sst>
 </file>
@@ -3679,7 +3718,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3740,6 +3779,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3787,7 +3832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3924,6 +3969,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4145,6 +4196,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4170,16 +4231,6 @@
       <fill>
         <patternFill>
           <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4554,8 +4605,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J438" tableType="queryTable" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
-  <autoFilter ref="A1:J438" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J445" tableType="queryTable" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A1:J445" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -4906,14 +4957,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
-  <dimension ref="A1:J438"/>
+  <dimension ref="A1:J445"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="36.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -5636,7 +5687,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -7150,7 +7201,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -8059,10 +8110,10 @@
         <v>206</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>667</v>
+        <v>1195</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -9015,7 +9066,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9079,7 +9130,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9239,7 +9290,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9547,16 +9598,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>719</v>
+        <v>696</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>720</v>
+      <c r="D149" s="5" t="s">
+        <v>815</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>714</v>
+        <v>364</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>387</v>
@@ -9564,14 +9615,14 @@
       <c r="G149" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H149" s="15">
-        <v>45918</v>
+      <c r="H149" s="9">
+        <v>45939</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>722</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -9579,31 +9630,31 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>696</v>
+        <v>256</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>364</v>
+        <v>257</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H150" s="9">
-        <v>45939</v>
+        <v>45698</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>1027</v>
+        <v>258</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -9611,13 +9662,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>256</v>
+        <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>257</v>
+      <c r="D151" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>23</v>
@@ -9629,13 +9680,13 @@
         <v>14</v>
       </c>
       <c r="H151" s="9">
-        <v>45698</v>
+        <v>45729</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>258</v>
+        <v>590</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -9649,9 +9700,9 @@
         <v>11</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E152" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E152" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F152" s="1" t="s">
@@ -9661,13 +9712,13 @@
         <v>14</v>
       </c>
       <c r="H152" s="9">
-        <v>45729</v>
+        <v>45643</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>590</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -9680,10 +9731,10 @@
       <c r="C153" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E153" s="1" t="s">
+      <c r="D153" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E153" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F153" s="1" t="s">
@@ -9693,13 +9744,13 @@
         <v>14</v>
       </c>
       <c r="H153" s="9">
-        <v>45643</v>
+        <v>45667</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>1186</v>
+        <v>263</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -9713,25 +9764,25 @@
         <v>11</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>723</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H154" s="9">
-        <v>45667</v>
+      <c r="H154" s="6">
+        <v>45932</v>
       </c>
       <c r="I154" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J154" s="3" t="s">
-        <v>263</v>
+      <c r="J154" s="7" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -9745,25 +9796,25 @@
         <v>11</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F155" s="4" t="s">
-        <v>723</v>
+        <v>364</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>959</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H155" s="6">
-        <v>45932</v>
+      <c r="H155" s="9">
+        <v>45959</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="J155" s="7" t="s">
-        <v>1002</v>
+        <v>721</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -9776,26 +9827,23 @@
       <c r="C156" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E156" s="4" t="s">
-        <v>364</v>
+      <c r="D156" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>959</v>
+        <v>267</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H156" s="9">
-        <v>45959</v>
+        <v>45787</v>
       </c>
       <c r="I156" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="J156" s="3" t="s">
-        <v>958</v>
+        <v>618</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -9808,20 +9856,20 @@
       <c r="C157" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D157" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E157" s="1" t="s">
+      <c r="D157" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H157" s="9">
-        <v>45787</v>
+        <v>45636</v>
       </c>
       <c r="I157" s="4" t="s">
         <v>618</v>
@@ -9832,26 +9880,24 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>10</v>
+        <v>233</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E158" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F158" s="1" t="s">
-        <v>269</v>
+      <c r="F158" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H158" s="9">
-        <v>45636</v>
-      </c>
+      <c r="H158" s="4"/>
       <c r="I158" s="4" t="s">
         <v>618</v>
       </c>
@@ -9861,26 +9907,31 @@
         <v>158</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D159" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F159" s="4" t="s">
-        <v>271</v>
+      <c r="D159" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H159" s="4"/>
+      <c r="H159" s="9">
+        <v>45698</v>
+      </c>
       <c r="I159" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -9888,31 +9939,28 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>23</v>
+      <c r="D160" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>667</v>
+        <v>276</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H160" s="9">
-        <v>45698</v>
+        <v>45813</v>
       </c>
       <c r="I160" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="J160" s="3" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -9920,92 +9968,95 @@
         <v>160</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>276</v>
+        <v>32</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H161" s="9">
-        <v>45813</v>
+        <v>32</v>
+      </c>
+      <c r="H161" s="6">
+        <v>45646</v>
       </c>
       <c r="I161" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>669</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="4">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>277</v>
+      <c r="B162" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F162" s="4" t="s">
-        <v>25</v>
+        <v>279</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H162" s="6">
-        <v>45646</v>
+        <v>45652</v>
       </c>
       <c r="I162" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J162" s="3" t="s">
-        <v>669</v>
+      <c r="J162" s="7" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="4">
         <v>162</v>
       </c>
-      <c r="B163" s="5" t="s">
-        <v>61</v>
+      <c r="B163" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>23</v>
+        <v>281</v>
+      </c>
+      <c r="E163" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>66</v>
+        <v>718</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H163" s="6">
-        <v>45652</v>
+      <c r="H163" s="9">
+        <v>45706</v>
       </c>
       <c r="I163" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J163" s="7" t="s">
-        <v>280</v>
+      <c r="J163" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -10013,31 +10064,31 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E164" s="4" t="s">
+      <c r="D164" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>718</v>
+        <v>285</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H164" s="9">
-        <v>45706</v>
+        <v>45813</v>
       </c>
       <c r="I164" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J164" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -10045,31 +10096,28 @@
         <v>164</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="G165" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G165" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H165" s="9">
-        <v>45813</v>
+        <v>45653</v>
       </c>
       <c r="I165" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="J165" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -10077,25 +10125,25 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>287</v>
+        <v>10</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G166" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G166" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="9">
-        <v>45653</v>
+        <v>45623</v>
       </c>
       <c r="I166" s="4" t="s">
         <v>618</v>
@@ -10105,61 +10153,58 @@
       <c r="A167" s="4">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>10</v>
+      <c r="B167" s="5" t="s">
+        <v>193</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E167" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E167" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F167" s="1" t="s">
-        <v>290</v>
+      <c r="F167" s="4" t="s">
+        <v>658</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H167" s="9">
-        <v>45623</v>
+      <c r="H167" s="6">
+        <v>45845</v>
       </c>
       <c r="I167" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="4">
         <v>167</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F168" s="4" t="s">
-        <v>658</v>
+      <c r="D168" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H168" s="6">
-        <v>45845</v>
-      </c>
       <c r="I168" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="J168" s="3" t="s">
-        <v>659</v>
+        <v>721</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -10173,81 +10218,84 @@
         <v>88</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>194</v>
+        <v>897</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>195</v>
+        <v>1062</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I169" s="4" t="s">
-        <v>721</v>
-      </c>
+      <c r="H169" s="23">
+        <v>46018</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="J169" s="24"/>
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="4">
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>193</v>
+        <v>249</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>897</v>
+        <v>293</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>1059</v>
+        <v>80</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1062</v>
+        <v>294</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H170" s="23">
-        <v>46018</v>
-      </c>
-      <c r="I170" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="J170" s="24"/>
+      <c r="H170" s="9">
+        <v>45653</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J170" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="4">
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>249</v>
+        <v>296</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>80</v>
+        <v>1059</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>294</v>
+        <v>1063</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H171" s="9">
-        <v>45653</v>
+        <v>45855</v>
       </c>
       <c r="I171" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="J171" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -10255,15 +10303,15 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E172" s="4" t="s">
         <v>1059</v>
       </c>
       <c r="F172" s="1" t="s">
@@ -10284,25 +10332,25 @@
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>34</v>
+        <v>299</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D173" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>1059</v>
+      <c r="D173" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1063</v>
+        <v>668</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H173" s="9">
-        <v>45855</v>
+        <v>45687</v>
       </c>
       <c r="I173" s="4" t="s">
         <v>618</v>
@@ -10319,7 +10367,7 @@
         <v>11</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>23</v>
@@ -10348,7 +10396,7 @@
         <v>11</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>23</v>
@@ -10377,7 +10425,7 @@
         <v>11</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>23</v>
@@ -10406,7 +10454,7 @@
         <v>11</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>23</v>
@@ -10435,7 +10483,7 @@
         <v>11</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>23</v>
@@ -10464,7 +10512,7 @@
         <v>11</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>23</v>
@@ -10493,7 +10541,7 @@
         <v>11</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>23</v>
@@ -10522,7 +10570,7 @@
         <v>11</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>23</v>
@@ -10551,7 +10599,7 @@
         <v>11</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>23</v>
@@ -10580,7 +10628,7 @@
         <v>11</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>23</v>
@@ -10609,7 +10657,7 @@
         <v>11</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>23</v>
@@ -10638,7 +10686,7 @@
         <v>11</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>23</v>
@@ -10667,7 +10715,7 @@
         <v>11</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>23</v>
@@ -10696,7 +10744,7 @@
         <v>11</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>23</v>
@@ -10725,7 +10773,7 @@
         <v>11</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>23</v>
@@ -10754,7 +10802,7 @@
         <v>11</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>23</v>
@@ -10783,7 +10831,7 @@
         <v>11</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>23</v>
@@ -10812,7 +10860,7 @@
         <v>11</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>23</v>
@@ -10841,7 +10889,7 @@
         <v>11</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>23</v>
@@ -10870,7 +10918,7 @@
         <v>11</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>23</v>
@@ -10893,21 +10941,21 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="G194" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G194" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H194" s="9">
@@ -10928,7 +10976,7 @@
         <v>11</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>23</v>
@@ -10936,92 +10984,95 @@
       <c r="F195" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G195" s="2" t="s">
+      <c r="G195" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H195" s="9">
-        <v>45687</v>
+        <v>45652</v>
       </c>
       <c r="I195" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="4">
         <v>195</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>321</v>
+      <c r="B196" s="3" t="s">
+        <v>325</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F196" s="1" t="s">
-        <v>66</v>
+        <v>326</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>1061</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H196" s="9">
-        <v>45652</v>
+      <c r="H196" s="6">
+        <v>45826</v>
       </c>
       <c r="I196" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J196" s="3" t="s">
-        <v>324</v>
+      <c r="J196" s="7" t="s">
+        <v>649</v>
       </c>
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="4">
         <v>196</v>
       </c>
-      <c r="B197" s="3" t="s">
-        <v>325</v>
+      <c r="B197" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>326</v>
+      <c r="D197" s="5" t="s">
+        <v>327</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>1059</v>
+        <v>23</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>1061</v>
+        <v>25</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H197" s="6">
-        <v>45826</v>
+        <v>45795</v>
       </c>
       <c r="I197" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J197" s="7" t="s">
-        <v>649</v>
+      <c r="J197" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="4">
         <v>197</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>111</v>
+      <c r="B198" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>327</v>
+        <v>998</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11033,13 +11084,13 @@
         <v>14</v>
       </c>
       <c r="H198" s="6">
-        <v>45795</v>
+        <v>45823</v>
       </c>
       <c r="I198" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>655</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -11053,57 +11104,57 @@
         <v>11</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>998</v>
+        <v>328</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>23</v>
+        <v>1059</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>25</v>
+        <v>1061</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="6">
-        <v>45823</v>
+        <v>45832</v>
       </c>
       <c r="I199" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J199" s="3" t="s">
-        <v>1087</v>
+      <c r="J199" s="7" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="4">
         <v>199</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>69</v>
+      <c r="B200" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F200" s="4" t="s">
-        <v>1061</v>
+        <v>19</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>1197</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H200" s="6">
-        <v>45832</v>
+      <c r="H200" s="9">
+        <v>45649</v>
       </c>
       <c r="I200" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J200" s="7" t="s">
-        <v>636</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -11117,13 +11168,13 @@
         <v>11</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="E201" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E201" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1171</v>
+        <v>1156</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11134,8 +11185,8 @@
       <c r="I201" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J201" s="7" t="s">
-        <v>331</v>
+      <c r="J201" s="8" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -11143,63 +11194,63 @@
         <v>201</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>1156</v>
+        <v>66</v>
       </c>
       <c r="G202" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H202" s="9">
-        <v>45649</v>
+      <c r="H202" s="6">
+        <v>45652</v>
       </c>
       <c r="I202" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J202" s="8" t="s">
-        <v>1152</v>
+      <c r="J202" s="7" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="4">
         <v>202</v>
       </c>
-      <c r="B203" s="3" t="s">
-        <v>61</v>
+      <c r="B203" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D203" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>23</v>
+      <c r="D203" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>66</v>
+        <v>604</v>
       </c>
       <c r="G203" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H203" s="6">
-        <v>45652</v>
+      <c r="H203" s="9">
+        <v>45714</v>
       </c>
       <c r="I203" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J203" s="7" t="s">
-        <v>334</v>
+      <c r="J203" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -11207,31 +11258,31 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E204" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="G204" s="5" t="s">
-        <v>14</v>
+        <v>1171</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="H204" s="9">
-        <v>45714</v>
+        <v>45707</v>
       </c>
       <c r="I204" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>336</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -11245,25 +11296,25 @@
         <v>11</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>19</v>
+        <v>337</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>1172</v>
+        <v>667</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H205" s="9">
-        <v>45707</v>
+        <v>45960</v>
       </c>
       <c r="I205" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1050</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -11271,31 +11322,31 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E206" s="4" t="s">
-        <v>23</v>
+        <v>338</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="G206" s="2" t="s">
-        <v>32</v>
+        <v>1196</v>
+      </c>
+      <c r="G206" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H206" s="9">
-        <v>45960</v>
+        <v>45653</v>
       </c>
       <c r="I206" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>1127</v>
+        <v>339</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -11309,25 +11360,25 @@
         <v>11</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>25</v>
+        <v>1172</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H207" s="9">
-        <v>45653</v>
+        <v>45873</v>
       </c>
       <c r="I207" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>339</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -11340,26 +11391,26 @@
       <c r="C208" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D208" s="2" t="s">
-        <v>340</v>
+      <c r="D208" s="5" t="s">
+        <v>341</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H208" s="9">
-        <v>45873</v>
+        <v>45936</v>
       </c>
       <c r="I208" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>1161</v>
+        <v>775</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -11373,25 +11424,25 @@
         <v>11</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1167</v>
+        <v>667</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H209" s="9">
-        <v>45936</v>
+        <v>45942</v>
       </c>
       <c r="I209" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>775</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -11404,72 +11455,72 @@
       <c r="C210" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D210" s="5" t="s">
-        <v>342</v>
+      <c r="D210" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>667</v>
+        <v>953</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H210" s="9">
-        <v>45942</v>
+        <v>45652</v>
       </c>
       <c r="I210" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1139</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="A211" s="4">
         <v>210</v>
       </c>
-      <c r="B211" s="2" t="s">
+      <c r="B211" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>953</v>
+        <v>25</v>
       </c>
       <c r="G211" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H211" s="9">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="I211" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>1015</v>
+        <v>345</v>
       </c>
     </row>
     <row r="212" spans="1:10">
       <c r="A212" s="4">
         <v>211</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>23</v>
@@ -11481,13 +11532,13 @@
         <v>14</v>
       </c>
       <c r="H212" s="9">
-        <v>45653</v>
+        <v>45652</v>
       </c>
       <c r="I212" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -11501,7 +11552,7 @@
         <v>11</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>23</v>
@@ -11513,13 +11564,13 @@
         <v>14</v>
       </c>
       <c r="H213" s="9">
-        <v>45652</v>
+        <v>45622</v>
       </c>
       <c r="I213" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>347</v>
+        <v>630</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -11533,7 +11584,7 @@
         <v>11</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>23</v>
@@ -11545,13 +11596,13 @@
         <v>14</v>
       </c>
       <c r="H214" s="9">
-        <v>45622</v>
+        <v>45649</v>
       </c>
       <c r="I214" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>630</v>
+        <v>350</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -11565,7 +11616,7 @@
         <v>11</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>23</v>
@@ -11577,13 +11628,13 @@
         <v>14</v>
       </c>
       <c r="H215" s="9">
-        <v>45649</v>
+        <v>45652</v>
       </c>
       <c r="I215" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>350</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -11597,25 +11648,25 @@
         <v>11</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>25</v>
+        <v>1162</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H216" s="9">
-        <v>45652</v>
+        <v>45932</v>
       </c>
       <c r="I216" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -11629,25 +11680,25 @@
         <v>11</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>1162</v>
+        <v>25</v>
       </c>
       <c r="G217" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H217" s="9">
-        <v>45932</v>
+        <v>45652</v>
       </c>
       <c r="I217" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J217" s="3" t="s">
-        <v>1164</v>
+        <v>354</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -11661,25 +11712,25 @@
         <v>11</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>25</v>
+        <v>1179</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H218" s="9">
-        <v>45652</v>
+        <v>45933</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>354</v>
+        <v>772</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -11693,25 +11744,25 @@
         <v>11</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E219" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E219" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H219" s="9">
-        <v>45933</v>
+        <v>45870</v>
       </c>
       <c r="I219" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>772</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -11724,26 +11775,26 @@
       <c r="C220" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D220" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E220" s="4" t="s">
-        <v>19</v>
+      <c r="D220" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1182</v>
+        <v>25</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H220" s="9">
-        <v>45870</v>
+        <v>45636</v>
       </c>
       <c r="I220" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1016</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -11756,8 +11807,8 @@
       <c r="C221" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D221" s="17" t="s">
-        <v>357</v>
+      <c r="D221" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>23</v>
@@ -11769,13 +11820,13 @@
         <v>14</v>
       </c>
       <c r="H221" s="9">
-        <v>45636</v>
+        <v>45652</v>
       </c>
       <c r="I221" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J221" s="3" t="s">
-        <v>1036</v>
+        <v>359</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -11789,25 +11840,25 @@
         <v>11</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F222" s="1" t="s">
-        <v>25</v>
+      <c r="F222" s="4" t="s">
+        <v>667</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H222" s="9">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="I222" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J222" s="3" t="s">
-        <v>359</v>
+        <v>608</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -11815,31 +11866,31 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F223" s="4" t="s">
-        <v>667</v>
+        <v>361</v>
+      </c>
+      <c r="E223" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>909</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H223" s="9">
-        <v>45649</v>
+        <v>45775</v>
       </c>
       <c r="I223" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>608</v>
+        <v>910</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -11847,31 +11898,31 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E224" s="4" t="s">
-        <v>71</v>
+        <v>362</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>909</v>
+        <v>25</v>
       </c>
       <c r="G224" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H224" s="9">
-        <v>45775</v>
+        <v>45667</v>
       </c>
       <c r="I224" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>910</v>
+        <v>363</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -11879,31 +11930,31 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D225" s="2" t="s">
-        <v>362</v>
+      <c r="D225" s="5" t="s">
+        <v>928</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>25</v>
+        <v>929</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H225" s="9">
-        <v>45667</v>
+        <v>45791</v>
       </c>
       <c r="I225" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>363</v>
+        <v>930</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -11911,31 +11962,31 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D226" s="5" t="s">
-        <v>928</v>
+      <c r="D226" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>929</v>
+        <v>25</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H226" s="9">
-        <v>45791</v>
+        <v>45819</v>
       </c>
       <c r="I226" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>930</v>
+        <v>629</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -11949,25 +12000,25 @@
         <v>11</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>25</v>
+        <v>1155</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H227" s="9">
-        <v>45819</v>
+        <v>45930</v>
       </c>
       <c r="I227" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>629</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -11981,25 +12032,25 @@
         <v>11</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1155</v>
+        <v>25</v>
       </c>
       <c r="G228" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H228" s="9">
-        <v>45930</v>
+        <v>45652</v>
       </c>
       <c r="I228" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>1154</v>
+        <v>368</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -12012,26 +12063,26 @@
       <c r="C229" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D229" s="2" t="s">
-        <v>367</v>
+      <c r="D229" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>25</v>
+        <v>1190</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H229" s="9">
-        <v>45652</v>
+      <c r="H229" s="6">
+        <v>45955</v>
       </c>
       <c r="I229" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J229" s="3" t="s">
-        <v>368</v>
+      <c r="J229" s="7" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -12045,28 +12096,28 @@
         <v>11</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="E230" s="1" t="s">
-        <v>19</v>
+        <v>370</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1191</v>
+        <v>667</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H230" s="6">
-        <v>45955</v>
+        <v>45665</v>
       </c>
       <c r="I230" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J230" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="15.6">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12077,28 +12128,28 @@
         <v>11</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="E231" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F231" s="1" t="s">
-        <v>667</v>
+        <v>372</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F231" s="50" t="s">
+        <v>1151</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H231" s="6">
-        <v>45665</v>
+        <v>46055</v>
       </c>
       <c r="I231" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="15.6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -12108,90 +12159,90 @@
       <c r="C232" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D232" s="5" t="s">
-        <v>372</v>
+      <c r="D232" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F232" s="50" t="s">
-        <v>1151</v>
+      <c r="F232" s="1" t="s">
+        <v>1180</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H232" s="6">
-        <v>46055</v>
+      <c r="H232" s="9">
+        <v>44127</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="J232" s="7" t="s">
-        <v>1150</v>
+        <v>721</v>
+      </c>
+      <c r="J232" s="3" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="233" spans="1:10">
       <c r="A233" s="4">
         <v>232</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="51" t="s">
         <v>34</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H233" s="9">
-        <v>44127</v>
+        <v>45870</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>1140</v>
+        <v>677</v>
       </c>
     </row>
     <row r="234" spans="1:10">
       <c r="A234" s="4">
         <v>233</v>
       </c>
-      <c r="B234" s="51" t="s">
+      <c r="B234" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>374</v>
+      <c r="D234" s="5" t="s">
+        <v>375</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F234" s="1" t="s">
+      <c r="F234" s="41" t="s">
         <v>1174</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H234" s="9">
-        <v>45870</v>
+      <c r="H234" s="6">
+        <v>46085</v>
       </c>
       <c r="I234" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J234" s="3" t="s">
-        <v>677</v>
+      <c r="J234" s="8" t="s">
+        <v>1157</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12199,31 +12250,31 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>34</v>
+        <v>376</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D235" s="5" t="s">
-        <v>375</v>
+      <c r="D235" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F235" s="41" t="s">
-        <v>1175</v>
-      </c>
-      <c r="G235" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H235" s="6">
-        <v>46085</v>
+        <v>364</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="G235" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H235" s="15">
+        <v>45705</v>
       </c>
       <c r="I235" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1157</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12231,32 +12282,30 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>376</v>
+        <v>595</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D236" s="14" t="s">
-        <v>377</v>
+      <c r="D236" s="2" t="s">
+        <v>617</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>364</v>
+        <v>1059</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>868</v>
-      </c>
-      <c r="G236" s="14" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G236" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H236" s="15">
-        <v>45705</v>
+        <v>45797</v>
       </c>
       <c r="I236" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J236" s="8" t="s">
-        <v>1118</v>
-      </c>
+      <c r="J236" s="20"/>
     </row>
     <row r="237" spans="1:10">
       <c r="A237" s="4">
@@ -12265,59 +12314,61 @@
       <c r="B237" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="C237" s="1" t="s">
+      <c r="C237" s="13" t="s">
         <v>11</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="E237" s="1" t="s">
-        <v>1059</v>
+        <v>596</v>
+      </c>
+      <c r="E237" s="33" t="s">
+        <v>949</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="G237" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="G237" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H237" s="15">
-        <v>45797</v>
+        <v>45744</v>
       </c>
       <c r="I237" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J237" s="20"/>
+      <c r="J237" s="8" t="s">
+        <v>950</v>
+      </c>
     </row>
     <row r="238" spans="1:10">
       <c r="A238" s="4">
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C238" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E238" s="33" t="s">
-        <v>949</v>
+        <v>379</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="G238" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="H238" s="15">
-        <v>45744</v>
+        <v>687</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H238" s="9">
+        <v>45652</v>
       </c>
       <c r="I238" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J238" s="8" t="s">
-        <v>950</v>
+      <c r="J238" s="3" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -12331,25 +12382,25 @@
         <v>11</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E239" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E239" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>687</v>
+        <v>371</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H239" s="9">
-        <v>45652</v>
+        <v>45870</v>
       </c>
       <c r="I239" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -12363,25 +12414,25 @@
         <v>11</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E240" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F240" s="1" t="s">
-        <v>371</v>
+        <v>381</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>1012</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H240" s="9">
-        <v>45870</v>
+        <v>45917</v>
       </c>
       <c r="I240" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>676</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -12389,31 +12440,31 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>378</v>
+        <v>1064</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G241" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
+      </c>
+      <c r="E241" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="H241" s="9">
-        <v>45917</v>
+        <v>45624</v>
       </c>
       <c r="I241" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>1014</v>
+        <v>382</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -12421,31 +12472,28 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>1064</v>
+        <v>383</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E242" s="4" t="s">
-        <v>19</v>
+        <v>384</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1176</v>
+        <v>25</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H242" s="9">
-        <v>45624</v>
+        <v>45653</v>
       </c>
       <c r="I242" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="J242" s="3" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -12453,28 +12501,31 @@
         <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>23</v>
+        <v>949</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G243" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="G243" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H243" s="9">
-        <v>45653</v>
+        <v>45940</v>
       </c>
       <c r="I243" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J243" s="3" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -12482,31 +12533,31 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>385</v>
+        <v>277</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D244" s="2" t="s">
-        <v>386</v>
+      <c r="D244" s="10" t="s">
+        <v>825</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>949</v>
+        <v>32</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>869</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="H244" s="9">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="I244" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>870</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -12514,31 +12565,31 @@
         <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>277</v>
+        <v>388</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D245" s="10" t="s">
-        <v>825</v>
+        <v>11</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G245" s="2" t="s">
-        <v>32</v>
+      <c r="G245" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H245" s="9">
-        <v>45941</v>
+        <v>45705</v>
       </c>
       <c r="I245" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>1057</v>
+        <v>390</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -12546,60 +12597,60 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>388</v>
+        <v>28</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>23</v>
+        <v>1069</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G246" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H246" s="9">
-        <v>45705</v>
+        <v>392</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="I246" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J246" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="4">
         <v>246</v>
       </c>
-      <c r="B247" s="2" t="s">
+      <c r="B247" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>391</v>
+      <c r="D247" s="10" t="s">
+        <v>744</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>1069</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G247" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="H247" s="9">
+        <v>45638</v>
+      </c>
       <c r="I247" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J247" s="3" t="s">
-        <v>393</v>
+        <v>594</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -12613,13 +12664,13 @@
         <v>11</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>744</v>
+        <v>395</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>1069</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="G248" s="2" t="s">
         <v>32</v>
@@ -12629,9 +12680,6 @@
       </c>
       <c r="I248" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="J248" s="3" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -12645,22 +12693,22 @@
         <v>11</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>1069</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G249" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H249" s="9">
-        <v>45638</v>
-      </c>
       <c r="I249" s="4" t="s">
         <v>618</v>
+      </c>
+      <c r="J249" s="3" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -12668,28 +12716,31 @@
         <v>249</v>
       </c>
       <c r="B250" s="10" t="s">
-        <v>28</v>
+        <v>277</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D250" s="10" t="s">
-        <v>397</v>
+        <v>88</v>
+      </c>
+      <c r="D250" s="35" t="s">
+        <v>951</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>1069</v>
+        <v>32</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>398</v>
+        <v>25</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>32</v>
+        <v>14</v>
+      </c>
+      <c r="H250" s="15">
+        <v>45797</v>
       </c>
       <c r="I250" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>399</v>
+        <v>952</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -12702,8 +12753,8 @@
       <c r="C251" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D251" s="35" t="s">
-        <v>951</v>
+      <c r="D251" s="10" t="s">
+        <v>400</v>
       </c>
       <c r="E251" s="1" t="s">
         <v>32</v>
@@ -12711,49 +12762,49 @@
       <c r="F251" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G251" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H251" s="15">
-        <v>45797</v>
+      <c r="G251" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H251" s="9">
+        <v>45952</v>
       </c>
       <c r="I251" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>952</v>
+        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="4">
         <v>251</v>
       </c>
-      <c r="B252" s="10" t="s">
-        <v>277</v>
+      <c r="B252" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D252" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E252" s="1" t="s">
-        <v>32</v>
+      <c r="D252" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E252" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>25</v>
+        <v>610</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H252" s="9">
-        <v>45952</v>
+        <v>45775</v>
       </c>
       <c r="I252" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>925</v>
+        <v>605</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -12761,31 +12812,31 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E253" s="4" t="s">
-        <v>19</v>
+        <v>402</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H253" s="9">
-        <v>45775</v>
+        <v>45622</v>
       </c>
       <c r="I253" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>605</v>
+        <v>403</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -12793,31 +12844,31 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>642</v>
+        <v>25</v>
       </c>
       <c r="G254" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H254" s="9">
-        <v>45622</v>
+        <v>45652</v>
       </c>
       <c r="I254" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -12825,31 +12876,31 @@
         <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G255" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H255" s="9">
-        <v>45652</v>
+        <v>45632</v>
       </c>
       <c r="I255" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -12863,25 +12914,25 @@
         <v>11</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H256" s="9">
-        <v>45632</v>
+        <v>45797</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>408</v>
+        <v>712</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -12895,7 +12946,7 @@
         <v>11</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>32</v>
@@ -12907,13 +12958,13 @@
         <v>14</v>
       </c>
       <c r="H257" s="9">
-        <v>45797</v>
+        <v>45624</v>
       </c>
       <c r="I257" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J257" s="3" t="s">
-        <v>712</v>
+        <v>647</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -12927,25 +12978,25 @@
         <v>11</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G258" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H258" s="9">
-        <v>45624</v>
+        <v>43971</v>
       </c>
       <c r="I258" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -12958,26 +13009,26 @@
       <c r="C259" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D259" s="2" t="s">
-        <v>411</v>
+      <c r="D259" s="17" t="s">
+        <v>412</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G259" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H259" s="9">
-        <v>43971</v>
+        <v>45797</v>
       </c>
       <c r="I259" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J259" s="3" t="s">
-        <v>648</v>
+        <v>413</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -12985,16 +13036,16 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>406</v>
+        <v>34</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D260" s="17" t="s">
-        <v>412</v>
+      <c r="D260" s="2" t="s">
+        <v>414</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>25</v>
@@ -13003,13 +13054,13 @@
         <v>14</v>
       </c>
       <c r="H260" s="9">
-        <v>45797</v>
+        <v>45652</v>
       </c>
       <c r="I260" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>413</v>
+        <v>692</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -13023,25 +13074,25 @@
         <v>11</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>23</v>
+        <v>415</v>
+      </c>
+      <c r="E261" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>25</v>
+        <v>1189</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H261" s="9">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="I261" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>692</v>
+        <v>416</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -13049,31 +13100,31 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>34</v>
+        <v>417</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E262" s="4" t="s">
-        <v>19</v>
+        <v>418</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1190</v>
+        <v>25</v>
       </c>
       <c r="G262" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H262" s="9">
-        <v>45649</v>
+        <v>45762</v>
       </c>
       <c r="I262" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>416</v>
+        <v>614</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -13081,16 +13132,16 @@
         <v>262</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>25</v>
@@ -13099,13 +13150,13 @@
         <v>14</v>
       </c>
       <c r="H263" s="9">
-        <v>45762</v>
+        <v>45653</v>
       </c>
       <c r="I263" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J263" s="3" t="s">
-        <v>614</v>
+        <v>421</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -13113,31 +13164,31 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>419</v>
+        <v>251</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F264" s="1" t="s">
-        <v>25</v>
+        <v>1059</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>1088</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H264" s="9">
-        <v>45653</v>
+        <v>45698</v>
       </c>
       <c r="I264" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -13145,31 +13196,31 @@
         <v>264</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>251</v>
+        <v>101</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F265" s="4" t="s">
-        <v>1088</v>
+        <v>23</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H265" s="9">
-        <v>45698</v>
+        <v>45813</v>
       </c>
       <c r="I265" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -13177,31 +13228,31 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="G266" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G266" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H266" s="9">
-        <v>45813</v>
+        <v>45652</v>
       </c>
       <c r="I266" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J266" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -13209,13 +13260,13 @@
         <v>266</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>23</v>
@@ -13227,45 +13278,45 @@
         <v>14</v>
       </c>
       <c r="H267" s="9">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="I267" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J267" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="268" spans="1:10">
       <c r="A268" s="4">
         <v>267</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>61</v>
+      <c r="B268" s="31" t="s">
+        <v>431</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D268" s="2" t="s">
-        <v>429</v>
+      <c r="D268" s="5" t="s">
+        <v>432</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>25</v>
+        <v>602</v>
       </c>
       <c r="G268" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H268" s="9">
-        <v>45653</v>
+        <v>45763</v>
       </c>
       <c r="I268" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J268" s="3" t="s">
-        <v>430</v>
+        <v>603</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -13278,26 +13329,26 @@
       <c r="C269" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D269" s="5" t="s">
-        <v>432</v>
+      <c r="D269" s="2" t="s">
+        <v>433</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>602</v>
+        <v>1184</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H269" s="9">
-        <v>45763</v>
+        <v>45590</v>
       </c>
       <c r="I269" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>603</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -13311,25 +13362,25 @@
         <v>11</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>364</v>
+        <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1185</v>
+        <v>329</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H270" s="9">
-        <v>45590</v>
+        <v>45832</v>
       </c>
       <c r="I270" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J270" s="3" t="s">
-        <v>1184</v>
+        <v>597</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -13343,25 +13394,25 @@
         <v>11</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>329</v>
+        <v>437</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H271" s="9">
-        <v>45832</v>
+        <v>45590</v>
       </c>
       <c r="I271" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J271" s="3" t="s">
-        <v>597</v>
+        <v>435</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -13375,25 +13426,25 @@
         <v>11</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H272" s="9">
-        <v>45590</v>
+        <v>45588</v>
       </c>
       <c r="I272" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J272" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -13407,13 +13458,13 @@
         <v>11</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>439</v>
+        <v>628</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13425,7 +13476,7 @@
         <v>618</v>
       </c>
       <c r="J273" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -13439,25 +13490,25 @@
         <v>11</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>628</v>
+        <v>444</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H274" s="9">
-        <v>45588</v>
+        <v>45594</v>
       </c>
       <c r="I274" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J274" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -13471,13 +13522,13 @@
         <v>11</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E275" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13503,13 +13554,13 @@
         <v>11</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E276" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>447</v>
+        <v>1080</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13535,13 +13586,13 @@
         <v>11</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E277" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13567,25 +13618,25 @@
         <v>11</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1081</v>
+        <v>451</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H278" s="9">
-        <v>45594</v>
+        <v>45596</v>
       </c>
       <c r="I278" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J278" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -13599,13 +13650,13 @@
         <v>11</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>451</v>
+        <v>622</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13617,7 +13668,7 @@
         <v>618</v>
       </c>
       <c r="J279" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -13631,13 +13682,13 @@
         <v>11</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>622</v>
+        <v>456</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13649,7 +13700,7 @@
         <v>618</v>
       </c>
       <c r="J280" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -13663,25 +13714,25 @@
         <v>11</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H281" s="9">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="I281" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J281" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -13695,13 +13746,13 @@
         <v>11</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13727,13 +13778,13 @@
         <v>11</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>461</v>
+        <v>1109</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13742,10 +13793,10 @@
         <v>45597</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>459</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -13759,13 +13810,13 @@
         <v>11</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1109</v>
+        <v>464</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13774,10 +13825,10 @@
         <v>45597</v>
       </c>
       <c r="I284" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J284" s="3" t="s">
-        <v>1110</v>
+        <v>459</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -13790,26 +13841,26 @@
       <c r="C285" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D285" s="2" t="s">
-        <v>463</v>
+      <c r="D285" s="36" t="s">
+        <v>465</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F285" s="1" t="s">
-        <v>464</v>
+      <c r="F285" s="4" t="s">
+        <v>466</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H285" s="9">
-        <v>45597</v>
+        <v>45603</v>
       </c>
       <c r="I285" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J285" s="3" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -13822,14 +13873,14 @@
       <c r="C286" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D286" s="36" t="s">
-        <v>465</v>
+      <c r="D286" s="2" t="s">
+        <v>468</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F286" s="4" t="s">
-        <v>466</v>
+      <c r="F286" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -13855,25 +13906,25 @@
         <v>11</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E287" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F287" s="1" t="s">
-        <v>469</v>
+      <c r="F287" s="4" t="s">
+        <v>471</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H287" s="9">
-        <v>45603</v>
+        <v>45604</v>
       </c>
       <c r="I287" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J287" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -13886,26 +13937,26 @@
       <c r="C288" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>470</v>
+      <c r="D288" s="5" t="s">
+        <v>474</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F288" s="4" t="s">
-        <v>471</v>
+        <v>364</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H288" s="9">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="I288" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J288" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -13919,13 +13970,13 @@
         <v>11</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E289" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>14</v>
@@ -13951,13 +14002,13 @@
         <v>11</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E290" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>14</v>
@@ -13983,25 +14034,25 @@
         <v>11</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G291" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H291" s="9">
-        <v>45607</v>
+        <v>45614</v>
       </c>
       <c r="I291" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J291" s="3" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -14015,13 +14066,13 @@
         <v>11</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G292" s="2" t="s">
         <v>14</v>
@@ -14047,25 +14098,25 @@
         <v>11</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G293" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H293" s="9">
-        <v>45614</v>
+        <v>45615</v>
       </c>
       <c r="I293" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J293" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -14079,13 +14130,13 @@
         <v>11</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G294" s="2" t="s">
         <v>14</v>
@@ -14111,13 +14162,13 @@
         <v>11</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>14</v>
@@ -14143,25 +14194,25 @@
         <v>11</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G296" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H296" s="9">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="I296" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J296" s="3" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -14175,13 +14226,13 @@
         <v>11</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>494</v>
+        <v>613</v>
       </c>
       <c r="G297" s="2" t="s">
         <v>14</v>
@@ -14193,7 +14244,7 @@
         <v>618</v>
       </c>
       <c r="J297" s="3" t="s">
-        <v>495</v>
+        <v>619</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -14207,25 +14258,25 @@
         <v>11</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>613</v>
+        <v>498</v>
       </c>
       <c r="G298" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H298" s="9">
-        <v>45617</v>
+        <v>45618</v>
       </c>
       <c r="I298" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J298" s="3" t="s">
-        <v>619</v>
+        <v>499</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -14239,25 +14290,25 @@
         <v>11</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G299" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H299" s="9">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="I299" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J299" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -14271,13 +14322,13 @@
         <v>11</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G300" s="2" t="s">
         <v>14</v>
@@ -14302,26 +14353,26 @@
       <c r="C301" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D301" s="5" t="s">
-        <v>503</v>
+      <c r="D301" s="2" t="s">
+        <v>505</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>504</v>
+        <v>940</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H301" s="9">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="I301" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J301" s="3" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -14335,13 +14386,13 @@
         <v>11</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E302" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>940</v>
+        <v>511</v>
       </c>
       <c r="G302" s="2" t="s">
         <v>14</v>
@@ -14353,7 +14404,7 @@
         <v>618</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>506</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -14367,13 +14418,13 @@
         <v>11</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E303" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>511</v>
+        <v>932</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -14385,7 +14436,7 @@
         <v>618</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>1091</v>
+        <v>885</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -14399,25 +14450,25 @@
         <v>11</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>932</v>
+        <v>638</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H304" s="9">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="I304" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>885</v>
+        <v>639</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -14431,25 +14482,25 @@
         <v>11</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>638</v>
+        <v>761</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H305" s="9">
-        <v>45621</v>
+        <v>45622</v>
       </c>
       <c r="I305" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>639</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -14463,25 +14514,25 @@
         <v>11</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>761</v>
+        <v>513</v>
       </c>
       <c r="G306" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H306" s="9">
-        <v>45622</v>
+        <v>44543</v>
       </c>
       <c r="I306" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J306" s="3" t="s">
-        <v>1104</v>
+        <v>514</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -14495,25 +14546,25 @@
         <v>11</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G307" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H307" s="9">
-        <v>44543</v>
+        <v>45635</v>
       </c>
       <c r="I307" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -14527,25 +14578,25 @@
         <v>11</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H308" s="9">
-        <v>45635</v>
+        <v>44539</v>
       </c>
       <c r="I308" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -14559,25 +14610,25 @@
         <v>11</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>519</v>
+        <v>437</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H309" s="9">
-        <v>44539</v>
+        <v>45645</v>
       </c>
       <c r="I309" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -14591,13 +14642,13 @@
         <v>11</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>437</v>
+        <v>524</v>
       </c>
       <c r="G310" s="2" t="s">
         <v>14</v>
@@ -14623,25 +14674,25 @@
         <v>11</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>524</v>
+        <v>673</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H311" s="9">
-        <v>45645</v>
+        <v>45867</v>
       </c>
       <c r="I311" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>522</v>
+        <v>674</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -14655,25 +14706,25 @@
         <v>11</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>673</v>
+        <v>528</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H312" s="9">
-        <v>45867</v>
+        <v>45664</v>
       </c>
       <c r="I312" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J312" s="3" t="s">
-        <v>674</v>
+        <v>529</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -14687,13 +14738,13 @@
         <v>11</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>14</v>
@@ -14719,13 +14770,13 @@
         <v>11</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G314" s="2" t="s">
         <v>14</v>
@@ -14751,25 +14802,25 @@
         <v>11</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H315" s="9">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="I315" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -14783,25 +14834,25 @@
         <v>11</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E316" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>535</v>
+        <v>653</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H316" s="9">
-        <v>45667</v>
+        <v>45842</v>
       </c>
       <c r="I316" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>536</v>
+        <v>654</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -14815,25 +14866,25 @@
         <v>11</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E317" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>653</v>
+        <v>621</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H317" s="9">
-        <v>45842</v>
+        <v>45702</v>
       </c>
       <c r="I317" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>654</v>
+        <v>539</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -14847,13 +14898,13 @@
         <v>11</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E318" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>621</v>
+        <v>541</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -14879,13 +14930,13 @@
         <v>11</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -14897,7 +14948,7 @@
         <v>618</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -14911,25 +14962,25 @@
         <v>11</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H320" s="9">
-        <v>45702</v>
+        <v>45705</v>
       </c>
       <c r="I320" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="321" spans="1:10">
@@ -14943,25 +14994,25 @@
         <v>11</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>545</v>
+        <v>581</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>546</v>
+        <v>582</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H321" s="9">
-        <v>45705</v>
+        <v>45726</v>
       </c>
       <c r="I321" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J321" s="3" t="s">
-        <v>547</v>
+        <v>583</v>
       </c>
     </row>
     <row r="322" spans="1:10">
@@ -14975,13 +15026,13 @@
         <v>11</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15007,13 +15058,13 @@
         <v>11</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15039,25 +15090,25 @@
         <v>11</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>586</v>
+        <v>253</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H324" s="9">
-        <v>45726</v>
+        <v>45653</v>
       </c>
       <c r="I324" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J324" s="3" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="325" spans="1:10">
@@ -15071,25 +15122,25 @@
         <v>11</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>253</v>
+        <v>626</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H325" s="9">
-        <v>45653</v>
+        <v>45817</v>
       </c>
       <c r="I325" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J325" s="3" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -15103,25 +15154,25 @@
         <v>11</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H326" s="9">
-        <v>45817</v>
+        <v>45653</v>
       </c>
       <c r="I326" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J326" s="3" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -15135,25 +15186,25 @@
         <v>11</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H327" s="9">
-        <v>45653</v>
+        <v>45838</v>
       </c>
       <c r="I327" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -15167,13 +15218,13 @@
         <v>11</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15185,7 +15236,7 @@
         <v>618</v>
       </c>
       <c r="J328" s="3" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -15199,25 +15250,25 @@
         <v>11</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H329" s="9">
-        <v>45838</v>
+        <v>45842</v>
       </c>
       <c r="I329" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J329" s="3" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -15231,25 +15282,25 @@
         <v>11</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H330" s="9">
-        <v>45842</v>
+        <v>45852</v>
       </c>
       <c r="I330" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J330" s="3" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -15263,25 +15314,25 @@
         <v>11</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>663</v>
+        <v>942</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H331" s="9">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="I331" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J331" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -15295,25 +15346,25 @@
         <v>11</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>942</v>
+        <v>623</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H332" s="9">
-        <v>45853</v>
+        <v>45870</v>
       </c>
       <c r="I332" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J332" s="3" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -15327,13 +15378,13 @@
         <v>11</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F333" s="1" t="s">
-        <v>623</v>
+      <c r="F333" s="4" t="s">
+        <v>683</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15345,7 +15396,7 @@
         <v>618</v>
       </c>
       <c r="J333" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -15359,25 +15410,25 @@
         <v>11</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F334" s="4" t="s">
-        <v>683</v>
+      <c r="F334" s="1" t="s">
+        <v>690</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H334" s="9">
-        <v>45870</v>
+        <v>45876</v>
       </c>
       <c r="I334" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J334" s="3" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -15391,25 +15442,25 @@
         <v>11</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>690</v>
+        <v>709</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H335" s="9">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="I335" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -15423,13 +15474,13 @@
         <v>11</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15441,7 +15492,7 @@
         <v>618</v>
       </c>
       <c r="J336" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -15455,25 +15506,25 @@
         <v>11</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H337" s="9">
-        <v>45884</v>
+        <v>45653</v>
       </c>
       <c r="I337" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J337" s="3" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -15487,25 +15538,25 @@
         <v>11</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>697</v>
+        <v>745</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H338" s="9">
-        <v>45653</v>
+        <v>45929</v>
       </c>
       <c r="I338" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>698</v>
+        <v>747</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -15519,25 +15570,25 @@
         <v>11</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H339" s="9">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="I339" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -15551,13 +15602,13 @@
         <v>11</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -15569,7 +15620,7 @@
         <v>618</v>
       </c>
       <c r="J340" s="3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -15583,25 +15634,25 @@
         <v>11</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H341" s="9">
-        <v>45931</v>
+        <v>40452</v>
       </c>
       <c r="I341" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -15615,25 +15666,25 @@
         <v>11</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H342" s="9">
-        <v>40452</v>
+        <v>45932</v>
       </c>
       <c r="I342" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J342" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -15647,57 +15698,57 @@
         <v>11</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>762</v>
+        <v>660</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>760</v>
+        <v>657</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H343" s="9">
-        <v>45932</v>
+        <v>45653</v>
       </c>
       <c r="I343" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J343" s="3" t="s">
-        <v>759</v>
+        <v>661</v>
       </c>
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="4">
         <v>343</v>
       </c>
-      <c r="B344" s="31" t="s">
+      <c r="B344" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="C344" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D344" s="2" t="s">
-        <v>660</v>
+      <c r="C344" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D344" s="37" t="s">
+        <v>473</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>13</v>
+        <v>364</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="G344" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H344" s="9">
-        <v>45653</v>
+        <v>599</v>
+      </c>
+      <c r="G344" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H344" s="15">
+        <v>45604</v>
       </c>
       <c r="I344" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J344" s="3" t="s">
-        <v>661</v>
+        <v>600</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -15710,90 +15761,90 @@
       <c r="C345" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D345" s="37" t="s">
-        <v>473</v>
+      <c r="D345" s="2" t="s">
+        <v>601</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>599</v>
+        <v>1111</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
       </c>
       <c r="H345" s="15">
-        <v>45604</v>
+        <v>45768</v>
       </c>
       <c r="I345" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>600</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="4">
         <v>345</v>
       </c>
-      <c r="B346" s="32" t="s">
-        <v>431</v>
-      </c>
-      <c r="C346" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="D346" s="2" t="s">
-        <v>601</v>
+      <c r="B346" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="D346" s="14">
+        <v>22011316</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G346" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="G346" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H346" s="15">
-        <v>45768</v>
+        <v>45933</v>
       </c>
       <c r="I346" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>1112</v>
+        <v>766</v>
       </c>
     </row>
     <row r="347" spans="1:10">
       <c r="A347" s="4">
         <v>346</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>764</v>
+      <c r="B347" s="30" t="s">
+        <v>431</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="D347" s="14">
-        <v>22011316</v>
+        <v>11</v>
+      </c>
+      <c r="D347" s="38" t="s">
+        <v>783</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>228</v>
+        <v>526</v>
       </c>
       <c r="G347" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H347" s="15">
-        <v>45933</v>
+      <c r="H347" s="9">
+        <v>45937</v>
       </c>
       <c r="I347" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>766</v>
+        <v>810</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -15807,13 +15858,13 @@
         <v>11</v>
       </c>
       <c r="D348" s="38" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>526</v>
+        <v>81</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -15825,7 +15876,7 @@
         <v>618</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -15839,13 +15890,13 @@
         <v>11</v>
       </c>
       <c r="D349" s="38" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>81</v>
+        <v>809</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -15871,25 +15922,25 @@
         <v>11</v>
       </c>
       <c r="D350" s="38" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>809</v>
+        <v>941</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H350" s="9">
-        <v>45937</v>
+      <c r="H350" s="23">
+        <v>45939</v>
       </c>
       <c r="I350" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -15903,13 +15954,13 @@
         <v>11</v>
       </c>
       <c r="D351" s="38" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>941</v>
+        <v>749</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -15921,7 +15972,7 @@
         <v>618</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -15935,25 +15986,25 @@
         <v>11</v>
       </c>
       <c r="D352" s="38" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>749</v>
+        <v>856</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H352" s="23">
-        <v>45939</v>
+        <v>45942</v>
       </c>
       <c r="I352" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>813</v>
+        <v>858</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -15967,25 +16018,25 @@
         <v>11</v>
       </c>
       <c r="D353" s="38" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>856</v>
+        <v>25</v>
       </c>
       <c r="G353" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H353" s="23">
-        <v>45942</v>
+        <v>45946</v>
       </c>
       <c r="I353" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>858</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -15999,25 +16050,25 @@
         <v>11</v>
       </c>
       <c r="D354" s="38" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>25</v>
+        <v>892</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H354" s="23">
-        <v>45946</v>
+      <c r="H354" s="9">
+        <v>45947</v>
       </c>
       <c r="I354" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>1058</v>
+        <v>972</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -16031,25 +16082,25 @@
         <v>11</v>
       </c>
       <c r="D355" s="38" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H355" s="9">
-        <v>45947</v>
+      <c r="H355" s="23">
+        <v>45946</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>972</v>
+        <v>894</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -16063,25 +16114,25 @@
         <v>11</v>
       </c>
       <c r="D356" s="38" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>889</v>
+        <v>879</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H356" s="23">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="I356" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -16095,25 +16146,25 @@
         <v>11</v>
       </c>
       <c r="D357" s="38" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>879</v>
+        <v>748</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H357" s="23">
-        <v>45945</v>
+        <v>45942</v>
       </c>
       <c r="I357" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>880</v>
+        <v>859</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -16127,25 +16178,25 @@
         <v>11</v>
       </c>
       <c r="D358" s="38" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>748</v>
+        <v>890</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H358" s="23">
-        <v>45942</v>
+        <v>45946</v>
       </c>
       <c r="I358" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>859</v>
+        <v>893</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -16159,13 +16210,13 @@
         <v>11</v>
       </c>
       <c r="D359" s="38" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>14</v>
@@ -16177,7 +16228,7 @@
         <v>618</v>
       </c>
       <c r="J359" s="3" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -16191,25 +16242,25 @@
         <v>11</v>
       </c>
       <c r="D360" s="38" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>887</v>
+        <v>855</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H360" s="23">
-        <v>45946</v>
+        <v>45942</v>
       </c>
       <c r="I360" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>888</v>
+        <v>860</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -16223,25 +16274,25 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>855</v>
+        <v>1041</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H361" s="23">
-        <v>45942</v>
+        <v>45945</v>
       </c>
       <c r="I361" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>860</v>
+        <v>960</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -16255,25 +16306,25 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>790</v>
+        <v>978</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>1041</v>
+        <v>526</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H362" s="23">
-        <v>45945</v>
+        <v>46036</v>
       </c>
       <c r="I362" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>960</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -16287,25 +16338,25 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>526</v>
+        <v>1026</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H363" s="23">
-        <v>46036</v>
+        <v>45968</v>
       </c>
       <c r="I363" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -16319,25 +16370,25 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H364" s="23">
-        <v>45968</v>
+        <v>45994</v>
       </c>
       <c r="I364" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>1083</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -16351,25 +16402,25 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H365" s="23">
-        <v>45994</v>
+        <v>45968</v>
       </c>
       <c r="I365" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -16383,13 +16434,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1033</v>
+        <v>1010</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16398,10 +16449,10 @@
         <v>45968</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1034</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -16415,13 +16466,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16433,7 +16484,7 @@
         <v>721</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -16447,13 +16498,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16462,10 +16513,10 @@
         <v>45968</v>
       </c>
       <c r="I368" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -16479,13 +16530,13 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>999</v>
+        <v>875</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16494,10 +16545,10 @@
         <v>45968</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>1000</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -16511,13 +16562,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>875</v>
+        <v>988</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -16529,7 +16580,7 @@
         <v>721</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>1009</v>
+        <v>987</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -16543,57 +16594,57 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>988</v>
+        <v>763</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H371" s="23">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="I371" s="4" t="s">
         <v>721</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="372" spans="1:10">
       <c r="A372" s="4">
         <v>371</v>
       </c>
-      <c r="B372" s="30" t="s">
-        <v>431</v>
+      <c r="B372" s="25" t="s">
+        <v>792</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>990</v>
+        <v>793</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>763</v>
+        <v>1149</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H372" s="23">
-        <v>45971</v>
+        <v>45945</v>
       </c>
       <c r="I372" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>991</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -16607,13 +16658,13 @@
         <v>88</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>71</v>
+        <v>364</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1149</v>
+        <v>599</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -16625,7 +16676,7 @@
         <v>618</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1103</v>
+        <v>957</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -16639,13 +16690,13 @@
         <v>88</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>599</v>
+        <v>1153</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -16657,7 +16708,7 @@
         <v>618</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>957</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -16671,25 +16722,25 @@
         <v>88</v>
       </c>
       <c r="D375" s="38" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>1153</v>
+        <v>939</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H375" s="23">
-        <v>45945</v>
+        <v>45992</v>
       </c>
       <c r="I375" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>1183</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -16703,26 +16754,24 @@
         <v>88</v>
       </c>
       <c r="D376" s="38" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>939</v>
+        <v>816</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H376" s="23">
-        <v>45992</v>
+        <v>45945</v>
       </c>
       <c r="I376" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J376" s="3" t="s">
-        <v>1025</v>
-      </c>
+      <c r="J376" s="24"/>
     </row>
     <row r="377" spans="1:10">
       <c r="A377" s="4">
@@ -16734,25 +16783,27 @@
       <c r="C377" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D377" s="38" t="s">
-        <v>797</v>
+      <c r="D377" s="39" t="s">
+        <v>798</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H377" s="23">
-        <v>45945</v>
+        <v>45941</v>
       </c>
       <c r="I377" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J377" s="24"/>
+      <c r="J377" s="3" t="s">
+        <v>819</v>
+      </c>
     </row>
     <row r="378" spans="1:10">
       <c r="A378" s="4">
@@ -16764,27 +16815,25 @@
       <c r="C378" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D378" s="39" t="s">
-        <v>798</v>
+      <c r="D378" s="38" t="s">
+        <v>799</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H378" s="23">
-        <v>45941</v>
+        <v>45945</v>
       </c>
       <c r="I378" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J378" s="3" t="s">
-        <v>819</v>
-      </c>
+      <c r="J378" s="24"/>
     </row>
     <row r="379" spans="1:10">
       <c r="A379" s="4">
@@ -16797,7 +16846,7 @@
         <v>88</v>
       </c>
       <c r="D379" s="38" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>23</v>
@@ -16826,25 +16875,27 @@
       <c r="C380" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D380" s="38" t="s">
-        <v>800</v>
+      <c r="D380" s="39" t="s">
+        <v>801</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>23</v>
+        <v>364</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H380" s="23">
-        <v>45945</v>
+        <v>45941</v>
       </c>
       <c r="I380" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J380" s="24"/>
+      <c r="J380" s="3" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="381" spans="1:10">
       <c r="A381" s="4">
@@ -16857,13 +16908,13 @@
         <v>88</v>
       </c>
       <c r="D381" s="39" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -16875,7 +16926,7 @@
         <v>618</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -16888,26 +16939,26 @@
       <c r="C382" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D382" s="39" t="s">
-        <v>802</v>
+      <c r="D382" s="38" t="s">
+        <v>803</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>364</v>
+        <v>23</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>814</v>
+        <v>667</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H382" s="23">
-        <v>45941</v>
+        <v>45952</v>
       </c>
       <c r="I382" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>824</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -16921,19 +16972,19 @@
         <v>88</v>
       </c>
       <c r="D383" s="38" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>19</v>
+        <v>1059</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>911</v>
+        <v>1060</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H383" s="23">
-        <v>45952</v>
+        <v>45950</v>
       </c>
       <c r="I383" s="4" t="s">
         <v>618</v>
@@ -16953,89 +17004,89 @@
         <v>88</v>
       </c>
       <c r="D384" s="38" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>1059</v>
+        <v>71</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>1060</v>
+        <v>253</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H384" s="23">
-        <v>45950</v>
+        <v>45996</v>
       </c>
       <c r="I384" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>912</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="385" spans="1:10">
       <c r="A385" s="4">
         <v>384</v>
       </c>
-      <c r="B385" s="25" t="s">
+      <c r="B385" s="26" t="s">
         <v>792</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D385" s="38" t="s">
-        <v>805</v>
+      <c r="D385" s="39" t="s">
+        <v>806</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>71</v>
+        <v>364</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>253</v>
+        <v>822</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H385" s="23">
-        <v>45996</v>
+      <c r="H385" s="9">
+        <v>45941</v>
       </c>
       <c r="I385" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>1048</v>
+        <v>823</v>
       </c>
     </row>
     <row r="386" spans="1:10">
       <c r="A386" s="4">
         <v>385</v>
       </c>
-      <c r="B386" s="26" t="s">
-        <v>792</v>
+      <c r="B386" s="27" t="s">
+        <v>40</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D386" s="39" t="s">
-        <v>806</v>
+        <v>11</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>886</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>364</v>
+        <v>13</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>822</v>
+        <v>98</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H386" s="9">
-        <v>45941</v>
+      <c r="H386" s="23">
+        <v>45946</v>
       </c>
       <c r="I386" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>823</v>
+        <v>896</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -17049,25 +17100,25 @@
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>886</v>
+        <v>922</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>98</v>
+        <v>1188</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H387" s="23">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="I387" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>896</v>
+        <v>956</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -17081,25 +17132,25 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>922</v>
+        <v>955</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1189</v>
+        <v>667</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H388" s="23">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="I388" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>956</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17113,25 +17164,25 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>955</v>
+        <v>971</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>667</v>
+        <v>1082</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H389" s="23">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1008</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17145,25 +17196,25 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>971</v>
+        <v>1119</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>1082</v>
+        <v>685</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H390" s="23">
-        <v>45960</v>
+        <v>45945</v>
       </c>
       <c r="I390" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1076</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -17177,13 +17228,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>685</v>
+        <v>72</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17195,7 +17246,7 @@
         <v>618</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1132</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -17209,13 +17260,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>72</v>
+        <v>1123</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17227,7 +17278,7 @@
         <v>618</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17241,13 +17292,13 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1123</v>
+        <v>637</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17259,7 +17310,7 @@
         <v>618</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17273,13 +17324,13 @@
         <v>11</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>637</v>
+        <v>989</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17291,39 +17342,39 @@
         <v>618</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="395" spans="1:10">
       <c r="A395" s="4">
         <v>394</v>
       </c>
-      <c r="B395" s="27" t="s">
-        <v>40</v>
+      <c r="B395" s="28" t="s">
+        <v>817</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D395" s="2" t="s">
-        <v>1130</v>
+      <c r="D395" s="5" t="s">
+        <v>832</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>71</v>
+        <v>364</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>989</v>
+        <v>834</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H395" s="23">
-        <v>45945</v>
+        <v>45940</v>
       </c>
       <c r="I395" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J395" s="3" t="s">
-        <v>1131</v>
+        <v>847</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -17337,13 +17388,13 @@
         <v>11</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>14</v>
@@ -17354,7 +17405,7 @@
       <c r="I396" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J396" s="3" t="s">
+      <c r="J396" s="24" t="s">
         <v>847</v>
       </c>
     </row>
@@ -17369,13 +17420,13 @@
         <v>11</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>14</v>
@@ -17386,8 +17437,8 @@
       <c r="I397" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J397" s="24" t="s">
-        <v>847</v>
+      <c r="J397" s="3" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -17401,25 +17452,25 @@
         <v>11</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H398" s="23">
-        <v>45940</v>
+        <v>45939</v>
       </c>
       <c r="I398" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J398" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -17433,13 +17484,13 @@
         <v>11</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>14</v>
@@ -17450,7 +17501,7 @@
       <c r="I399" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J399" s="3" t="s">
+      <c r="J399" s="24" t="s">
         <v>850</v>
       </c>
     </row>
@@ -17465,25 +17516,25 @@
         <v>11</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H400" s="23">
-        <v>45939</v>
+        <v>45938</v>
       </c>
       <c r="I400" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J400" s="24" t="s">
-        <v>850</v>
+      <c r="J400" s="3" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -17497,13 +17548,13 @@
         <v>11</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>14</v>
@@ -17515,7 +17566,7 @@
         <v>618</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -17529,25 +17580,25 @@
         <v>11</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>843</v>
+        <v>862</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H402" s="23">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="I402" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -17561,13 +17612,13 @@
         <v>11</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
@@ -17579,7 +17630,7 @@
         <v>618</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -17593,25 +17644,25 @@
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>863</v>
+        <v>1017</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>864</v>
+        <v>1018</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H404" s="23">
-        <v>45939</v>
+        <v>45985</v>
       </c>
       <c r="I404" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>866</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -17625,25 +17676,25 @@
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H405" s="23">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="I405" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -17657,25 +17708,25 @@
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H406" s="23">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="I406" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1030</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -17689,13 +17740,13 @@
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17707,7 +17758,7 @@
         <v>618</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -17721,57 +17772,57 @@
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H408" s="23">
-        <v>45996</v>
+        <v>45985</v>
       </c>
       <c r="I408" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>1047</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="409" spans="1:10">
       <c r="A409" s="4">
         <v>408</v>
       </c>
-      <c r="B409" s="28" t="s">
-        <v>817</v>
+      <c r="B409" s="29" t="s">
+        <v>818</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>1072</v>
+        <v>826</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>1073</v>
+        <v>828</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H409" s="23">
-        <v>45985</v>
+        <v>45940</v>
       </c>
       <c r="I409" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J409" s="3" t="s">
-        <v>1108</v>
+        <v>849</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -17785,13 +17836,13 @@
         <v>11</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>14</v>
@@ -17803,7 +17854,7 @@
         <v>618</v>
       </c>
       <c r="J410" s="3" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -17817,13 +17868,13 @@
         <v>11</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>14</v>
@@ -17835,7 +17886,7 @@
         <v>618</v>
       </c>
       <c r="J411" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -17849,25 +17900,25 @@
         <v>11</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>827</v>
+        <v>876</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>831</v>
+        <v>877</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H412" s="23">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="I412" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -17881,25 +17932,25 @@
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>876</v>
+        <v>902</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>877</v>
+        <v>903</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H413" s="23">
-        <v>45945</v>
+        <v>45950</v>
       </c>
       <c r="I413" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>878</v>
+        <v>918</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -17913,13 +17964,13 @@
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>14</v>
@@ -17931,7 +17982,7 @@
         <v>618</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -17945,25 +17996,25 @@
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H415" s="23">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="I415" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -17977,13 +18028,13 @@
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -17995,7 +18046,7 @@
         <v>618</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -18009,25 +18060,25 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>917</v>
+        <v>943</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>916</v>
+        <v>610</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H417" s="23">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="I417" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>921</v>
+        <v>965</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -18041,25 +18092,25 @@
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>943</v>
+        <v>1021</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>610</v>
+        <v>1004</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H418" s="23">
-        <v>45960</v>
+        <v>45992</v>
       </c>
       <c r="I418" s="4" t="s">
-        <v>721</v>
+        <v>618</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>965</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -18073,13 +18124,13 @@
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18091,7 +18142,7 @@
         <v>618</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -18105,25 +18156,25 @@
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1023</v>
+        <v>1038</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>1005</v>
+        <v>1040</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H420" s="23">
-        <v>45992</v>
+        <v>45975</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>1024</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -18137,13 +18188,13 @@
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18155,7 +18206,7 @@
         <v>618</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -18169,13 +18220,13 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18187,7 +18238,7 @@
         <v>618</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -18201,25 +18252,25 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1054</v>
+        <v>1077</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1055</v>
+        <v>1078</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H423" s="23">
-        <v>45975</v>
+        <v>46001</v>
       </c>
       <c r="I423" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1056</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -18233,25 +18284,25 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1077</v>
+        <v>1094</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1078</v>
+        <v>1003</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H424" s="23">
-        <v>46001</v>
+        <v>46036</v>
       </c>
       <c r="I424" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1079</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -18265,25 +18316,25 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1003</v>
+        <v>1035</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H425" s="23">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="I425" s="4" t="s">
-        <v>618</v>
+        <v>721</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -18297,26 +18348,24 @@
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1035</v>
+        <v>1102</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H426" s="23">
-        <v>46037</v>
+        <v>46001</v>
       </c>
       <c r="I426" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="J426" s="3" t="s">
-        <v>1098</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="J426" s="24"/>
     </row>
     <row r="427" spans="1:10">
       <c r="A427" s="4">
@@ -18329,43 +18378,45 @@
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>1102</v>
+        <v>891</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H427" s="23">
-        <v>46001</v>
+        <v>46041</v>
       </c>
       <c r="I427" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J427" s="24"/>
+      <c r="J427" s="3" t="s">
+        <v>1106</v>
+      </c>
     </row>
     <row r="428" spans="1:10">
       <c r="A428" s="4">
         <v>427</v>
       </c>
-      <c r="B428" s="29" t="s">
-        <v>818</v>
+      <c r="B428" s="40" t="s">
+        <v>944</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>1105</v>
+        <v>945</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
@@ -18377,7 +18428,7 @@
         <v>618</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18391,25 +18442,25 @@
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>857</v>
+        <v>973</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H429" s="23">
-        <v>46041</v>
+        <v>45957</v>
       </c>
       <c r="I429" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1107</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18423,25 +18474,25 @@
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>364</v>
+        <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>973</v>
+        <v>1089</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H430" s="23">
-        <v>45957</v>
+        <v>46034</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1141</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18455,25 +18506,25 @@
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>947</v>
+        <v>1125</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>1089</v>
+        <v>811</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H431" s="23">
-        <v>46034</v>
+        <v>45957</v>
       </c>
       <c r="I431" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1090</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18487,57 +18538,57 @@
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>1125</v>
+        <v>948</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>811</v>
+        <v>934</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H432" s="23">
-        <v>45957</v>
+        <v>46036</v>
       </c>
       <c r="I432" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1126</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="433" spans="1:10">
       <c r="A433" s="4">
         <v>432</v>
       </c>
-      <c r="B433" s="40" t="s">
-        <v>944</v>
+      <c r="B433" s="31" t="s">
+        <v>927</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D433" s="5" t="s">
-        <v>948</v>
+      <c r="D433" s="2" t="s">
+        <v>1115</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>934</v>
+        <v>773</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H433" s="23">
-        <v>46036</v>
+        <v>45950</v>
       </c>
       <c r="I433" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1096</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -18551,13 +18602,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>773</v>
+        <v>836</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
@@ -18569,7 +18620,7 @@
         <v>618</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -18583,25 +18634,25 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1113</v>
+        <v>1133</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>836</v>
+        <v>1137</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H435" s="23">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="I435" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1114</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -18615,25 +18666,25 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H436" s="23">
-        <v>45952</v>
+        <v>46048</v>
       </c>
       <c r="I436" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -18647,89 +18698,289 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H437" s="23">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="I437" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="438" spans="1:10">
       <c r="A438" s="4">
         <v>437</v>
       </c>
-      <c r="B438" s="31" t="s">
-        <v>927</v>
+      <c r="B438" s="53" t="s">
+        <v>719</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1142</v>
+        <v>720</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>364</v>
+        <v>714</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>1147</v>
+        <v>387</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H438" s="23">
-        <v>46050</v>
+      <c r="H438" s="15">
+        <v>45918</v>
       </c>
       <c r="I438" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1143</v>
-      </c>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10">
+      <c r="A439" s="4">
+        <v>438</v>
+      </c>
+      <c r="B439" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F439" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="G439" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H439" s="23">
+        <v>45712</v>
+      </c>
+      <c r="I439" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J439" s="3" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
+      <c r="A440" s="4">
+        <v>439</v>
+      </c>
+      <c r="B440" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E440" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F440" s="52"/>
+      <c r="G440" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H440" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I440" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J440" s="24"/>
+    </row>
+    <row r="441" spans="1:10">
+      <c r="A441" s="4">
+        <v>440</v>
+      </c>
+      <c r="B441" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E441" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F441" s="52"/>
+      <c r="G441" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H441" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I441" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J441" s="24"/>
+    </row>
+    <row r="442" spans="1:10">
+      <c r="A442" s="4">
+        <v>441</v>
+      </c>
+      <c r="B442" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E442" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F442" s="52"/>
+      <c r="G442" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H442" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I442" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J442" s="24"/>
+    </row>
+    <row r="443" spans="1:10">
+      <c r="A443" s="4">
+        <v>442</v>
+      </c>
+      <c r="B443" s="53" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E443" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F443" s="52"/>
+      <c r="G443" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H443" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I443" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J443" s="24"/>
+    </row>
+    <row r="444" spans="1:10">
+      <c r="A444" s="4">
+        <v>443</v>
+      </c>
+      <c r="B444" s="53" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E444" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F444" s="52"/>
+      <c r="G444" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H444" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I444" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J444" s="24"/>
+    </row>
+    <row r="445" spans="1:10">
+      <c r="A445" s="4">
+        <v>444</v>
+      </c>
+      <c r="B445" s="53" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E445" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F445" s="52"/>
+      <c r="G445" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H445" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I445" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J445" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="duplicateValues" dxfId="26" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D347">
-    <cfRule type="duplicateValues" dxfId="25" priority="80"/>
+  <conditionalFormatting sqref="D246">
+    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D247">
-    <cfRule type="duplicateValues" dxfId="24" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+  <conditionalFormatting sqref="D344">
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D345">
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+  <conditionalFormatting sqref="D345:D346">
+    <cfRule type="duplicateValues" dxfId="21" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D346:D347">
-    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+  <conditionalFormatting sqref="D438 D2:D346">
+    <cfRule type="duplicateValues" dxfId="20" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E237 G195 E239:E1048576">
+  <conditionalFormatting sqref="E1:E236 G194 E238:E1048576">
     <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E345:E347">
+  <conditionalFormatting sqref="E344:E346">
     <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F231 F233:F234 F236:F1048576">
+  <conditionalFormatting sqref="F1:F230 F232:F233 F235:F1048576">
     <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
@@ -18743,7 +18994,7 @@
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F345">
+  <conditionalFormatting sqref="F344">
     <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845AD921-642C-47C7-B0E2-6977CC2E961A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33536121-BB0C-43C9-A92D-76A2C791B4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1207">
   <si>
     <t>INDICE</t>
   </si>
@@ -2776,9 +2776,6 @@
     <t>SEDUC - GABINETE</t>
   </si>
   <si>
-    <t>INSTALADA 20/10/2025 SEDUC GABINETE;</t>
-  </si>
-  <si>
     <t>ESTAVA NO PLANEJAMENTO - PMA; MANCHANDO FOLHAS; ESTAVA CASA DO EMPREENDEDOR; INSTALADA MORADA DO RECOMEÇO 22/10/2025;</t>
   </si>
   <si>
@@ -3148,9 +3145,6 @@
     <t>UBS - MORRO GRANDE</t>
   </si>
   <si>
-    <t>RETIRADA COM INFESTAÇÃO DE FORMIGA DENTRO DA IMPRESSORA 06/01/2025; DARCY RIBEIRO 03/12/2025;</t>
-  </si>
-  <si>
     <t>NAIR VALADARES</t>
   </si>
   <si>
@@ -3220,9 +3214,6 @@
     <t xml:space="preserve">OPERACIONAL </t>
   </si>
   <si>
-    <t>SOLAGOS - ADM</t>
-  </si>
-  <si>
     <t>COMSERVE - ITA</t>
   </si>
   <si>
@@ -3634,9 +3625,6 @@
     <t xml:space="preserve"> E.M. DR. FABIO SIQUEIRA</t>
   </si>
   <si>
-    <t xml:space="preserve">INSTALADA 20/10/2025 SEDUC GABINETE; </t>
-  </si>
-  <si>
     <t>XBJZ043818</t>
   </si>
   <si>
@@ -3653,13 +3641,31 @@
   </si>
   <si>
     <t>XC75047651</t>
+  </si>
+  <si>
+    <t>E.M. NEDIR PAULO B. ROSA</t>
+  </si>
+  <si>
+    <t>RETIRADA COM INFESTAÇÃO DE FORMIGA DENTRO DA IMPRESSORA 06/01/2025; DARCY RIBEIRO 03/12/2025; INSTALADA ESCOLA NEDIR PAULO B. ROSA 26/02/2026;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M. PASTOR ALCEBIADES </t>
+  </si>
+  <si>
+    <t>INSTALADA 20/10/2025 SEDUC GABINETE; INSTALADA ESCOLA PASTOR ALCEBIDES F. DE MENDONÇA 26/02/2026;</t>
+  </si>
+  <si>
+    <t>E.M. JOAO AUGUSTO CHAVES</t>
+  </si>
+  <si>
+    <t>INSTALADA 20/10/2025 SOLAGOS ADM; INSTALADA JOAO AUGUSTO CHAVES 26/02/2026;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3832,7 +3838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3975,6 +3981,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4958,7 +4967,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J445"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4973,7 +4982,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5005,7 +5014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5037,7 +5046,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5069,7 +5078,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5101,7 +5110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5133,7 +5142,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5165,7 +5174,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5197,7 +5206,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5229,7 +5238,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5259,7 +5268,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5289,12 +5298,12 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5318,15 +5327,15 @@
         <v>618</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5353,7 +5362,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5385,7 +5394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5402,7 +5411,7 @@
         <v>364</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5414,10 +5423,10 @@
         <v>618</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5449,7 +5458,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5478,7 +5487,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5510,7 +5519,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5527,7 +5536,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -5542,7 +5551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5574,7 +5583,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5591,7 +5600,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5603,10 +5612,10 @@
         <v>618</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -5638,7 +5647,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5655,7 +5664,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5667,10 +5676,10 @@
         <v>618</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -5687,7 +5696,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -5702,7 +5711,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5734,7 +5743,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5766,7 +5775,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5795,7 +5804,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5824,7 +5833,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5856,7 +5865,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -5885,10 +5894,10 @@
         <v>618</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -5920,7 +5929,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -5952,7 +5961,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -5984,7 +5993,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6016,7 +6025,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6048,7 +6057,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6080,7 +6089,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6094,10 +6103,10 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>14</v>
@@ -6109,10 +6118,10 @@
         <v>618</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6141,7 +6150,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6173,7 +6182,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6205,7 +6214,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6237,7 +6246,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6269,7 +6278,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6301,7 +6310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6333,7 +6342,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6365,7 +6374,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6394,7 +6403,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6426,7 +6435,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6458,7 +6467,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6490,7 +6499,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6519,7 +6528,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6548,7 +6557,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6580,12 +6589,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6612,12 +6621,12 @@
         <v>693</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6644,12 +6653,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6661,7 +6670,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6676,7 +6685,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -6705,7 +6714,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -6734,7 +6743,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -6763,7 +6772,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -6792,7 +6801,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -6821,7 +6830,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -6850,7 +6859,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -6882,7 +6891,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -6914,7 +6923,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -6943,7 +6952,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -6975,7 +6984,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7004,7 +7013,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7033,7 +7042,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7062,7 +7071,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7091,7 +7100,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7123,7 +7132,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7155,7 +7164,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7184,7 +7193,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7201,7 +7210,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7213,10 +7222,10 @@
         <v>618</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7248,7 +7257,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7280,7 +7289,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7309,7 +7318,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7341,7 +7350,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7373,7 +7382,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7405,7 +7414,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7437,7 +7446,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7451,7 +7460,7 @@
         <v>730</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7469,7 +7478,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7483,7 +7492,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7501,7 +7510,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7515,7 +7524,7 @@
         <v>731</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7527,7 +7536,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7541,7 +7550,7 @@
         <v>732</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7553,7 +7562,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7567,7 +7576,7 @@
         <v>733</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7579,7 +7588,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7593,7 +7602,7 @@
         <v>734</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7611,7 +7620,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -7625,7 +7634,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7643,7 +7652,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -7657,7 +7666,7 @@
         <v>735</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7675,7 +7684,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -7689,7 +7698,7 @@
         <v>736</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7707,7 +7716,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -7721,7 +7730,7 @@
         <v>737</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7736,7 +7745,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -7765,10 +7774,10 @@
         <v>618</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -7782,7 +7791,7 @@
         <v>739</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7800,7 +7809,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -7814,7 +7823,7 @@
         <v>740</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7826,7 +7835,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -7840,7 +7849,7 @@
         <v>741</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -7852,7 +7861,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -7866,7 +7875,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -7881,10 +7890,10 @@
         <v>618</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -7895,10 +7904,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -7913,7 +7922,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -7942,7 +7951,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -7971,7 +7980,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8000,7 +8009,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8032,7 +8041,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8064,7 +8073,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8096,7 +8105,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8113,7 +8122,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8125,10 +8134,10 @@
         <v>618</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8160,7 +8169,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8192,7 +8201,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8224,7 +8233,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8256,7 +8265,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8288,7 +8297,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8299,7 +8308,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8316,7 +8325,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8348,7 +8357,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8380,7 +8389,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8412,7 +8421,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8444,7 +8453,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8476,7 +8485,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8508,7 +8517,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8540,7 +8549,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8572,7 +8581,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -8604,7 +8613,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -8636,7 +8645,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -8668,7 +8677,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -8700,7 +8709,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -8732,7 +8741,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -8764,7 +8773,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8793,7 +8802,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8825,7 +8834,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -8857,7 +8866,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -8874,7 +8883,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8889,7 +8898,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -8903,10 +8912,10 @@
         <v>743</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>32</v>
@@ -8921,7 +8930,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -8953,7 +8962,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -8985,7 +8994,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -8999,10 +9008,10 @@
         <v>234</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9017,7 +9026,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9049,7 +9058,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9066,7 +9075,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9081,7 +9090,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9098,7 +9107,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9110,10 +9119,10 @@
         <v>618</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9130,7 +9139,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9145,7 +9154,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9174,10 +9183,10 @@
         <v>618</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9191,10 +9200,10 @@
         <v>241</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>667</v>
+        <v>1187</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9209,7 +9218,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9226,7 +9235,7 @@
         <v>19</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>14</v>
@@ -9241,7 +9250,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9258,7 +9267,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9270,10 +9279,10 @@
         <v>618</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9290,7 +9299,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9302,10 +9311,10 @@
         <v>618</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9337,7 +9346,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9366,10 +9375,10 @@
         <v>618</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9401,7 +9410,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9418,7 +9427,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9430,10 +9439,10 @@
         <v>618</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9444,13 +9453,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9462,10 +9471,10 @@
         <v>618</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9482,7 +9491,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9497,7 +9506,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9529,7 +9538,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9561,7 +9570,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9593,7 +9602,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -9622,10 +9631,10 @@
         <v>618</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9657,7 +9666,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -9689,7 +9698,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9718,10 +9727,10 @@
         <v>618</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -9753,7 +9762,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -9782,10 +9791,10 @@
         <v>618</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -9802,7 +9811,7 @@
         <v>364</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -9814,10 +9823,10 @@
         <v>721</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -9846,7 +9855,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -9875,7 +9884,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -9902,7 +9911,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -9934,7 +9943,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -9963,7 +9972,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -9995,7 +10004,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10027,7 +10036,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10059,7 +10068,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10091,7 +10100,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10120,7 +10129,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10149,7 +10158,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10181,7 +10190,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10195,7 +10204,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10207,7 +10216,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10221,10 +10230,10 @@
         <v>897</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F169" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10237,7 +10246,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10269,7 +10278,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10283,10 +10292,10 @@
         <v>297</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10298,7 +10307,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10312,10 +10321,10 @@
         <v>298</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -10327,7 +10336,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10356,7 +10365,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10385,7 +10394,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10414,7 +10423,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10443,7 +10452,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10472,7 +10481,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10501,7 +10510,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10530,7 +10539,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -10559,7 +10568,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -10588,7 +10597,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10617,7 +10626,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -10646,7 +10655,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -10675,7 +10684,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -10704,7 +10713,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -10733,7 +10742,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -10762,7 +10771,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -10791,7 +10800,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -10820,7 +10829,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -10849,7 +10858,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -10878,7 +10887,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -10907,7 +10916,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -10936,7 +10945,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -10965,7 +10974,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -10997,7 +11006,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11011,10 +11020,10 @@
         <v>326</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11029,7 +11038,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11061,7 +11070,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11072,7 +11081,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11090,10 +11099,10 @@
         <v>618</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11107,10 +11116,10 @@
         <v>328</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11125,7 +11134,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -11142,7 +11151,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11157,7 +11166,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -11174,7 +11183,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11186,10 +11195,10 @@
         <v>618</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11221,7 +11230,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -11253,7 +11262,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -11264,13 +11273,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11282,10 +11291,10 @@
         <v>618</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11314,10 +11323,10 @@
         <v>618</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11331,10 +11340,10 @@
         <v>338</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>1196</v>
+        <v>667</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>14</v>
@@ -11349,7 +11358,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -11366,7 +11375,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11378,10 +11387,10 @@
         <v>618</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -11398,7 +11407,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11413,7 +11422,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11442,10 +11451,10 @@
         <v>618</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11462,7 +11471,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
@@ -11474,10 +11483,10 @@
         <v>618</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11509,7 +11518,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -11541,7 +11550,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -11573,7 +11582,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -11605,7 +11614,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -11634,10 +11643,10 @@
         <v>618</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -11654,7 +11663,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11666,10 +11675,10 @@
         <v>618</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -11701,7 +11710,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -11718,7 +11727,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11733,7 +11742,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -11750,7 +11759,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11762,10 +11771,10 @@
         <v>618</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -11775,14 +11784,14 @@
       <c r="C220" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D220" s="17" t="s">
+      <c r="D220" s="54" t="s">
         <v>357</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>25</v>
+        <v>1201</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11794,10 +11803,10 @@
         <v>618</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -11829,7 +11838,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -11861,7 +11870,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -11893,7 +11902,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -11925,7 +11934,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -11936,13 +11945,13 @@
         <v>11</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>14</v>
@@ -11954,10 +11963,10 @@
         <v>618</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -11989,7 +11998,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -12006,7 +12015,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12018,10 +12027,10 @@
         <v>618</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -12053,7 +12062,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -12067,10 +12076,10 @@
         <v>369</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1190</v>
+        <v>667</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12082,10 +12091,10 @@
         <v>618</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -12099,10 +12108,10 @@
         <v>370</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>667</v>
+        <v>1193</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12117,7 +12126,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15.6">
+    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12134,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12146,10 +12155,10 @@
         <v>618</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -12166,7 +12175,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12178,10 +12187,10 @@
         <v>721</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -12198,7 +12207,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12213,7 +12222,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -12230,7 +12239,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12242,10 +12251,10 @@
         <v>618</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -12274,10 +12283,10 @@
         <v>618</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12291,10 +12300,10 @@
         <v>617</v>
       </c>
       <c r="E236" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F236" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12307,7 +12316,7 @@
       </c>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12321,7 +12330,7 @@
         <v>596</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>670</v>
@@ -12336,10 +12345,10 @@
         <v>618</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -12371,7 +12380,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -12403,7 +12412,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12420,7 +12429,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12432,15 +12441,15 @@
         <v>618</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12452,7 +12461,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12467,7 +12476,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -12496,7 +12505,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -12510,7 +12519,7 @@
         <v>386</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>869</v>
@@ -12528,7 +12537,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12557,10 +12566,10 @@
         <v>618</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -12592,7 +12601,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -12606,7 +12615,7 @@
         <v>391</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>392</v>
@@ -12621,7 +12630,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -12635,7 +12644,7 @@
         <v>744</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>394</v>
@@ -12653,7 +12662,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -12667,7 +12676,7 @@
         <v>395</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>396</v>
@@ -12682,7 +12691,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -12696,7 +12705,7 @@
         <v>397</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>398</v>
@@ -12711,7 +12720,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12722,7 +12731,7 @@
         <v>88</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -12740,10 +12749,10 @@
         <v>618</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -12772,10 +12781,10 @@
         <v>618</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -12807,7 +12816,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12839,7 +12848,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -12871,7 +12880,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -12903,7 +12912,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -12935,7 +12944,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -12967,7 +12976,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -12999,7 +13008,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13031,7 +13040,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13063,7 +13072,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13080,7 +13089,7 @@
         <v>19</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>14</v>
@@ -13095,7 +13104,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13127,7 +13136,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13159,7 +13168,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -13173,10 +13182,10 @@
         <v>422</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13191,7 +13200,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -13223,7 +13232,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13255,7 +13264,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13287,7 +13296,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13319,7 +13328,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13336,7 +13345,7 @@
         <v>364</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13348,10 +13357,10 @@
         <v>618</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13383,7 +13392,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13415,7 +13424,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13447,7 +13456,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13479,7 +13488,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13511,7 +13520,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13543,7 +13552,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13560,7 +13569,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13575,7 +13584,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13592,7 +13601,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13607,7 +13616,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13639,7 +13648,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13671,7 +13680,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13703,7 +13712,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13735,7 +13744,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13767,7 +13776,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13784,7 +13793,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13796,10 +13805,10 @@
         <v>721</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13831,7 +13840,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13863,7 +13872,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -13895,7 +13904,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -13927,7 +13936,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -13959,7 +13968,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -13991,7 +14000,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14023,7 +14032,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14055,7 +14064,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14087,7 +14096,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14119,7 +14128,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14151,7 +14160,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14183,7 +14192,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14215,7 +14224,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14247,7 +14256,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14279,7 +14288,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14311,7 +14320,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14343,7 +14352,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14360,7 +14369,7 @@
         <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -14375,7 +14384,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14404,10 +14413,10 @@
         <v>618</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14424,7 +14433,7 @@
         <v>80</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -14439,7 +14448,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14471,7 +14480,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14500,10 +14509,10 @@
         <v>618</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14535,7 +14544,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14567,7 +14576,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -14599,7 +14608,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -14631,7 +14640,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -14663,7 +14672,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14695,7 +14704,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -14727,7 +14736,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -14759,7 +14768,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -14791,7 +14800,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14823,7 +14832,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14855,7 +14864,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -14887,7 +14896,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -14919,7 +14928,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -14951,7 +14960,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -14983,7 +14992,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15015,7 +15024,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15047,7 +15056,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15079,7 +15088,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15111,7 +15120,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15143,7 +15152,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15175,7 +15184,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15207,7 +15216,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15239,7 +15248,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15271,7 +15280,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15303,7 +15312,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15320,7 +15329,7 @@
         <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -15335,7 +15344,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15367,7 +15376,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15399,7 +15408,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15431,7 +15440,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15463,7 +15472,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15495,7 +15504,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15527,7 +15536,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15559,7 +15568,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15591,7 +15600,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15623,7 +15632,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15655,7 +15664,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15687,7 +15696,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15719,7 +15728,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -15751,7 +15760,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15768,7 +15777,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15780,10 +15789,10 @@
         <v>618</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -15815,7 +15824,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -15847,7 +15856,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -15879,7 +15888,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -15911,7 +15920,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -15928,7 +15937,7 @@
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -15943,7 +15952,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -15975,7 +15984,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16007,7 +16016,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16036,10 +16045,10 @@
         <v>618</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="354" spans="1:10">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16068,10 +16077,10 @@
         <v>618</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="355" spans="1:10">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16103,7 +16112,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16135,7 +16144,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16167,7 +16176,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16199,7 +16208,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16231,7 +16240,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16263,7 +16272,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16280,7 +16289,7 @@
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
@@ -16292,10 +16301,10 @@
         <v>618</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16306,7 +16315,7 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
@@ -16324,10 +16333,10 @@
         <v>618</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16338,13 +16347,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -16356,10 +16365,10 @@
         <v>618</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16370,13 +16379,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16388,10 +16397,10 @@
         <v>618</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16402,13 +16411,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16420,10 +16429,10 @@
         <v>618</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16434,13 +16443,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16452,10 +16461,10 @@
         <v>721</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16466,13 +16475,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16484,10 +16493,10 @@
         <v>721</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16498,13 +16507,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16516,10 +16525,10 @@
         <v>618</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16530,7 +16539,7 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>80</v>
@@ -16548,10 +16557,10 @@
         <v>721</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16562,13 +16571,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -16580,10 +16589,10 @@
         <v>721</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -16594,7 +16603,7 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>80</v>
@@ -16612,10 +16621,10 @@
         <v>721</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16632,7 +16641,7 @@
         <v>71</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -16644,10 +16653,10 @@
         <v>618</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16676,10 +16685,10 @@
         <v>618</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -16696,7 +16705,7 @@
         <v>19</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -16708,10 +16717,10 @@
         <v>618</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -16728,7 +16737,7 @@
         <v>80</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
@@ -16740,10 +16749,10 @@
         <v>618</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16773,7 +16782,7 @@
       </c>
       <c r="J376" s="24"/>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16805,7 +16814,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -16835,7 +16844,7 @@
       </c>
       <c r="J378" s="24"/>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -16865,7 +16874,7 @@
       </c>
       <c r="J379" s="24"/>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -16897,7 +16906,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -16929,7 +16938,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -16943,10 +16952,10 @@
         <v>803</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>667</v>
+        <v>1203</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -16958,10 +16967,10 @@
         <v>618</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -16975,10 +16984,10 @@
         <v>804</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>1059</v>
+        <v>19</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1060</v>
+        <v>1205</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -16990,10 +16999,10 @@
         <v>618</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17022,10 +17031,10 @@
         <v>618</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17057,7 +17066,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -17089,7 +17098,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17100,13 +17109,13 @@
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
@@ -17118,10 +17127,10 @@
         <v>618</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17132,7 +17141,7 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>23</v>
@@ -17150,10 +17159,10 @@
         <v>618</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17164,13 +17173,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17182,10 +17191,10 @@
         <v>721</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17196,7 +17205,7 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
@@ -17214,10 +17223,10 @@
         <v>618</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17228,7 +17237,7 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
@@ -17246,10 +17255,10 @@
         <v>618</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17260,13 +17269,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17278,10 +17287,10 @@
         <v>618</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17292,7 +17301,7 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
@@ -17310,10 +17319,10 @@
         <v>618</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17324,13 +17333,13 @@
         <v>11</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17342,10 +17351,10 @@
         <v>618</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="395" spans="1:10">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17377,7 +17386,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17409,7 +17418,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17441,7 +17450,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17473,7 +17482,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17505,7 +17514,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17537,7 +17546,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -17569,7 +17578,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17601,7 +17610,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17633,7 +17642,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17644,13 +17653,13 @@
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -17662,10 +17671,10 @@
         <v>618</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17676,13 +17685,13 @@
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17694,10 +17703,10 @@
         <v>618</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17708,13 +17717,13 @@
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -17726,10 +17735,10 @@
         <v>618</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="407" spans="1:10">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -17740,13 +17749,13 @@
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17758,10 +17767,10 @@
         <v>618</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -17772,13 +17781,13 @@
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
@@ -17790,10 +17799,10 @@
         <v>618</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="409" spans="1:10">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -17825,7 +17834,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -17857,7 +17866,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -17889,7 +17898,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -17921,7 +17930,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -17950,10 +17959,10 @@
         <v>618</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -17982,10 +17991,10 @@
         <v>618</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -17996,13 +18005,13 @@
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
@@ -18014,10 +18023,10 @@
         <v>618</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18028,13 +18037,13 @@
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -18046,10 +18055,10 @@
         <v>618</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18060,7 +18069,7 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>19</v>
@@ -18078,10 +18087,10 @@
         <v>721</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18092,13 +18101,13 @@
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -18110,10 +18119,10 @@
         <v>618</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="419" spans="1:10">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18124,13 +18133,13 @@
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18142,10 +18151,10 @@
         <v>618</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18156,13 +18165,13 @@
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18174,10 +18183,10 @@
         <v>618</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18188,13 +18197,13 @@
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18206,10 +18215,10 @@
         <v>618</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18220,13 +18229,13 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18238,10 +18247,10 @@
         <v>618</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18252,13 +18261,13 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -18270,10 +18279,10 @@
         <v>618</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18284,13 +18293,13 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -18302,10 +18311,10 @@
         <v>618</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18316,13 +18325,13 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18334,10 +18343,10 @@
         <v>721</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18348,13 +18357,13 @@
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -18367,7 +18376,7 @@
       </c>
       <c r="J426" s="24"/>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18378,7 +18387,7 @@
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>80</v>
@@ -18396,21 +18405,21 @@
         <v>618</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>427</v>
       </c>
       <c r="B428" s="40" t="s">
+        <v>943</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428" s="5" t="s">
         <v>944</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D428" s="5" t="s">
-        <v>945</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>80</v>
@@ -18428,27 +18437,27 @@
         <v>618</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>428</v>
       </c>
       <c r="B429" s="40" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18460,27 +18469,27 @@
         <v>618</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>429</v>
       </c>
       <c r="B430" s="40" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18492,21 +18501,21 @@
         <v>618</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>430</v>
       </c>
       <c r="B431" s="40" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>71</v>
@@ -18524,27 +18533,27 @@
         <v>618</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>431</v>
       </c>
       <c r="B432" s="40" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>14</v>
@@ -18556,21 +18565,21 @@
         <v>618</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>432</v>
       </c>
       <c r="B433" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>364</v>
@@ -18588,21 +18597,21 @@
         <v>618</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>433</v>
       </c>
       <c r="B434" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>364</v>
@@ -18620,27 +18629,27 @@
         <v>618</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>434</v>
       </c>
       <c r="B435" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18652,27 +18661,27 @@
         <v>618</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>435</v>
       </c>
       <c r="B436" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18684,27 +18693,27 @@
         <v>618</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>436</v>
       </c>
       <c r="B437" s="31" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
@@ -18716,10 +18725,10 @@
         <v>618</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>437</v>
       </c>
@@ -18751,18 +18760,18 @@
         <v>722</v>
       </c>
     </row>
-    <row r="439" spans="1:10">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>19</v>
@@ -18780,21 +18789,21 @@
         <v>618</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18811,18 +18820,18 @@
       </c>
       <c r="J440" s="24"/>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18839,18 +18848,18 @@
       </c>
       <c r="J441" s="24"/>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -18867,18 +18876,18 @@
       </c>
       <c r="J442" s="24"/>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>23</v>
@@ -18895,18 +18904,18 @@
       </c>
       <c r="J443" s="24"/>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>23</v>
@@ -18923,18 +18932,18 @@
       </c>
       <c r="J444" s="24"/>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>23</v>
@@ -19013,7 +19022,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -19022,7 +19031,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>548</v>
       </c>
@@ -19042,127 +19051,127 @@
         <v>552</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>991</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>992</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="C3" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>992</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>993</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>993</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>994</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C5" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>994</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>995</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>995</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>996</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="42" t="s">
+        <v>960</v>
+      </c>
+      <c r="B7" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="C7" s="42" t="s">
         <v>962</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>996</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>963</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>997</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>964</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>553</v>
       </c>
@@ -19179,7 +19188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>553</v>
       </c>
@@ -19196,7 +19205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>553</v>
       </c>
@@ -19213,7 +19222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>553</v>
       </c>
@@ -19230,7 +19239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>553</v>
       </c>
@@ -19247,7 +19256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>553</v>
       </c>
@@ -19264,7 +19273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>553</v>
       </c>
@@ -19281,7 +19290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>553</v>
       </c>
@@ -19298,7 +19307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>553</v>
       </c>
@@ -19315,7 +19324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>553</v>
       </c>
@@ -19332,7 +19341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>553</v>
       </c>
@@ -19349,7 +19358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>553</v>
       </c>
@@ -19366,7 +19375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>553</v>
       </c>
@@ -19383,7 +19392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>558</v>
       </c>
@@ -19403,7 +19412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>558</v>
       </c>
@@ -19423,7 +19432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>558</v>
       </c>
@@ -19443,7 +19452,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>558</v>
       </c>
@@ -19463,7 +19472,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>558</v>
       </c>
@@ -19483,7 +19492,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>558</v>
       </c>
@@ -19503,7 +19512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>558</v>
       </c>
@@ -19523,7 +19532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>571</v>
       </c>
@@ -19543,7 +19552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>575</v>
       </c>
@@ -19563,7 +19572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>577</v>
       </c>
@@ -19583,7 +19592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>577</v>
       </c>
@@ -19603,7 +19612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>571</v>
       </c>
@@ -19635,7 +19644,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -19652,7 +19661,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19684,7 +19693,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -19716,7 +19725,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -19748,7 +19757,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -19780,7 +19789,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -19812,7 +19821,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -19844,7 +19853,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -19876,7 +19885,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -19908,7 +19917,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -19940,7 +19949,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -19972,7 +19981,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -20004,7 +20013,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -20036,7 +20045,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -20068,7 +20077,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -20100,7 +20109,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -20132,7 +20141,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -20164,7 +20173,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -20196,7 +20205,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -20228,7 +20237,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -20260,7 +20269,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -20292,7 +20301,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -20324,7 +20333,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -20356,7 +20365,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -20388,7 +20397,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -20420,7 +20429,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -20450,7 +20459,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -20480,7 +20489,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -20510,7 +20519,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -20540,7 +20549,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -20570,7 +20579,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -20600,7 +20609,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -20630,7 +20639,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -20660,7 +20669,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -20690,7 +20699,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -20720,7 +20729,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -20750,7 +20759,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -20780,7 +20789,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -20810,7 +20819,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -20840,7 +20849,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -20870,7 +20879,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -20900,7 +20909,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -20930,7 +20939,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -20959,7 +20968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -20991,15 +21000,15 @@
         <v>884</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>965</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>966</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>967</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
@@ -21020,18 +21029,18 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>965</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>966</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>967</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -21052,15 +21061,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -21081,15 +21090,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -21110,15 +21119,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="18">
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -21139,15 +21148,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -21168,15 +21177,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -21197,18 +21206,18 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -21217,7 +21226,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -21229,21 +21238,21 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>937</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>938</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>71</v>
@@ -21261,110 +21270,110 @@
         <v>618</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="18"/>
       <c r="B53" s="21"/>
       <c r="C53" s="49"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33536121-BB0C-43C9-A92D-76A2C791B4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102E5F73-F235-4B3F-B758-87B7E1A33FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="COMPUTER" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$445</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$488</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1208">
   <si>
     <t>INDICE</t>
   </si>
@@ -2842,9 +2842,6 @@
     <t>SESAU - DEJUR</t>
   </si>
   <si>
-    <t>ESTAVA NO ITBI - PAÇO; TROCA DE FUSÃO ROLETES 23/10/2025; INSTALADA SESAU 24/10/2025;</t>
-  </si>
-  <si>
     <t>FRAGMENTADORA PSX12-06</t>
   </si>
   <si>
@@ -3659,13 +3656,19 @@
   </si>
   <si>
     <t>INSTALADA 20/10/2025 SOLAGOS ADM; INSTALADA JOAO AUGUSTO CHAVES 26/02/2026;</t>
+  </si>
+  <si>
+    <t>PAM - ESPACO DA MULHER</t>
+  </si>
+  <si>
+    <t>ESTAVA NO ITBI - PAÇO; TROCA DE FUSÃO ROLETES 23/10/2025; INSTALADA SESAU 24/10/2025; INSTALADA PAM ESPACO DA MULHER 27/02/2026;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3724,7 +3727,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3791,6 +3794,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3838,7 +3847,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3977,13 +3986,14 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4614,8 +4624,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J445" tableType="queryTable" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
-  <autoFilter ref="A1:J445" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J488" tableType="queryTable" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A1:J488" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -4966,8 +4976,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
-  <dimension ref="A1:J445"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J488"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -4982,7 +4992,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5014,7 +5024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5046,7 +5056,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5078,7 +5088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5110,7 +5120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5142,7 +5152,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5174,7 +5184,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5206,7 +5216,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5238,7 +5248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5268,7 +5278,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5298,12 +5308,12 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5327,15 +5337,15 @@
         <v>618</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5362,7 +5372,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5394,7 +5404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5411,7 +5421,7 @@
         <v>364</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5423,10 +5433,10 @@
         <v>618</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5458,7 +5468,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5487,7 +5497,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5519,7 +5529,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5536,7 +5546,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -5551,7 +5561,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5583,7 +5593,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5600,7 +5610,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5612,10 +5622,10 @@
         <v>618</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -5647,7 +5657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5664,7 +5674,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5676,10 +5686,10 @@
         <v>618</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -5696,7 +5706,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -5711,7 +5721,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5743,7 +5753,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5775,7 +5785,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5804,7 +5814,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5833,7 +5843,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5865,7 +5875,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -5894,10 +5904,10 @@
         <v>618</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -5961,7 +5971,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -5993,7 +6003,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6025,7 +6035,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6057,7 +6067,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6089,7 +6099,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6103,7 +6113,7 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>922</v>
@@ -6121,7 +6131,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6150,7 +6160,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6182,7 +6192,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6214,7 +6224,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6246,7 +6256,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6278,7 +6288,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6310,7 +6320,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6342,7 +6352,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6374,7 +6384,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6403,7 +6413,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6435,7 +6445,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6467,7 +6477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6499,7 +6509,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6528,7 +6538,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6557,7 +6567,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6589,12 +6599,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6621,12 +6631,12 @@
         <v>693</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6653,12 +6663,12 @@
         <v>694</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6670,7 +6680,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6685,7 +6695,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -6714,7 +6724,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -6743,7 +6753,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -6772,7 +6782,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -6801,7 +6811,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -6830,7 +6840,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -6859,7 +6869,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -6891,7 +6901,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -6923,7 +6933,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -6952,7 +6962,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -6984,7 +6994,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7013,7 +7023,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7042,7 +7052,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7071,7 +7081,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7100,7 +7110,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7132,7 +7142,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7164,7 +7174,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7193,7 +7203,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7210,7 +7220,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7225,7 +7235,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7257,7 +7267,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7289,7 +7299,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7318,7 +7328,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7350,7 +7360,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7382,7 +7392,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7414,7 +7424,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7446,7 +7456,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7460,7 +7470,7 @@
         <v>730</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7478,7 +7488,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7492,7 +7502,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7510,7 +7520,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7524,7 +7534,7 @@
         <v>731</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7536,7 +7546,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7550,7 +7560,7 @@
         <v>732</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7562,7 +7572,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7576,7 +7586,7 @@
         <v>733</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7588,7 +7598,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7602,7 +7612,7 @@
         <v>734</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7620,7 +7630,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -7634,7 +7644,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7652,7 +7662,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -7666,7 +7676,7 @@
         <v>735</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7684,7 +7694,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -7698,7 +7708,7 @@
         <v>736</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7716,7 +7726,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -7730,7 +7740,7 @@
         <v>737</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7745,7 +7755,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -7774,10 +7784,10 @@
         <v>618</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -7791,7 +7801,7 @@
         <v>739</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7809,7 +7819,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -7823,7 +7833,7 @@
         <v>740</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7835,7 +7845,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -7849,7 +7859,7 @@
         <v>741</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -7861,7 +7871,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -7875,7 +7885,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -7893,7 +7903,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -7904,10 +7914,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -7922,7 +7932,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -7951,7 +7961,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -7980,7 +7990,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8009,7 +8019,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8041,7 +8051,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8073,7 +8083,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8105,7 +8115,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8122,7 +8132,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8134,10 +8144,10 @@
         <v>618</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8169,7 +8179,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8201,7 +8211,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8233,7 +8243,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8265,7 +8275,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8297,7 +8307,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8308,7 +8318,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8325,7 +8335,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8357,7 +8367,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8389,7 +8399,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8421,7 +8431,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8453,7 +8463,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8485,7 +8495,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8517,7 +8527,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8549,7 +8559,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8581,7 +8591,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -8613,7 +8623,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -8645,7 +8655,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -8677,7 +8687,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -8709,7 +8719,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -8741,7 +8751,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -8773,7 +8783,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8802,7 +8812,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8834,7 +8844,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -8866,7 +8876,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -8883,7 +8893,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8898,7 +8908,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -8912,10 +8922,10 @@
         <v>743</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>32</v>
@@ -8930,7 +8940,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -8962,7 +8972,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -8994,7 +9004,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9008,10 +9018,10 @@
         <v>234</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9026,7 +9036,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9058,7 +9068,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9075,7 +9085,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9090,7 +9100,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9107,7 +9117,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9119,10 +9129,10 @@
         <v>618</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9139,7 +9149,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9154,7 +9164,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9168,25 +9178,25 @@
         <v>240</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>667</v>
+        <v>1206</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H135" s="9">
-        <v>45954</v>
+        <v>46080</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9203,7 +9213,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9218,7 +9228,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9235,7 +9245,7 @@
         <v>19</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>14</v>
@@ -9250,7 +9260,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9267,7 +9277,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9279,10 +9289,10 @@
         <v>618</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9299,7 +9309,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9314,7 +9324,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9346,7 +9356,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9375,10 +9385,10 @@
         <v>618</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9410,7 +9420,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9427,7 +9437,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9439,10 +9449,10 @@
         <v>618</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9453,13 +9463,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9471,10 +9481,10 @@
         <v>618</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9491,7 +9501,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9506,7 +9516,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9538,7 +9548,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9570,7 +9580,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9602,7 +9612,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -9631,10 +9641,10 @@
         <v>618</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9666,7 +9676,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -9698,7 +9708,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9727,10 +9737,10 @@
         <v>618</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -9762,7 +9772,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -9791,10 +9801,10 @@
         <v>618</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -9811,7 +9821,7 @@
         <v>364</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -9823,10 +9833,10 @@
         <v>721</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -9855,7 +9865,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -9884,7 +9894,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -9911,7 +9921,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -9943,7 +9953,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -9972,7 +9982,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10004,7 +10014,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10036,7 +10046,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10068,7 +10078,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10100,7 +10110,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10129,7 +10139,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10158,7 +10168,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10190,7 +10200,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10204,7 +10214,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10216,7 +10226,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10230,10 +10240,10 @@
         <v>897</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10246,7 +10256,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10278,7 +10288,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10292,10 +10302,10 @@
         <v>297</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10307,7 +10317,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10321,10 +10331,10 @@
         <v>298</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -10336,7 +10346,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10365,7 +10375,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10394,7 +10404,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10423,7 +10433,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10452,7 +10462,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10481,7 +10491,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10510,7 +10520,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10539,7 +10549,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -10568,7 +10578,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -10597,7 +10607,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10626,7 +10636,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -10655,7 +10665,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -10684,7 +10694,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -10713,7 +10723,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -10742,7 +10752,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -10771,7 +10781,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -10800,7 +10810,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -10829,7 +10839,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -10858,7 +10868,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -10887,7 +10897,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -10916,7 +10926,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -10945,7 +10955,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -10974,7 +10984,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -11006,7 +11016,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11020,10 +11030,10 @@
         <v>326</v>
       </c>
       <c r="E196" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F196" s="4" t="s">
         <v>1057</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>1058</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11038,7 +11048,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11070,7 +11080,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11081,7 +11091,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11099,10 +11109,10 @@
         <v>618</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11116,10 +11126,10 @@
         <v>328</v>
       </c>
       <c r="E199" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F199" s="4" t="s">
         <v>1057</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>1058</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11134,7 +11144,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -11151,7 +11161,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11166,7 +11176,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -11183,7 +11193,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11195,10 +11205,10 @@
         <v>618</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11230,7 +11240,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -11262,7 +11272,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -11273,13 +11283,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11291,10 +11301,10 @@
         <v>618</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11323,10 +11333,10 @@
         <v>618</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11358,7 +11368,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -11375,7 +11385,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11387,10 +11397,10 @@
         <v>618</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -11407,7 +11417,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11422,7 +11432,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11451,10 +11461,10 @@
         <v>618</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11471,7 +11481,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
@@ -11483,10 +11493,10 @@
         <v>618</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11518,7 +11528,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -11550,7 +11560,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -11582,7 +11592,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -11614,7 +11624,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -11643,10 +11653,10 @@
         <v>618</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -11663,7 +11673,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11675,10 +11685,10 @@
         <v>618</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -11710,7 +11720,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -11727,7 +11737,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11742,7 +11752,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -11759,7 +11769,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11771,10 +11781,10 @@
         <v>618</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -11784,14 +11794,14 @@
       <c r="C220" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D220" s="54" t="s">
+      <c r="D220" s="2" t="s">
         <v>357</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11803,10 +11813,10 @@
         <v>618</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -11838,7 +11848,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -11870,7 +11880,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -11902,7 +11912,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -11934,7 +11944,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -11966,7 +11976,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -11998,7 +12008,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -12015,7 +12025,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12027,10 +12037,10 @@
         <v>618</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -12062,7 +12072,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -12094,7 +12104,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -12111,7 +12121,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12126,7 +12136,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" ht="15.6">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12143,7 +12153,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12155,10 +12165,10 @@
         <v>618</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -12175,7 +12185,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12187,10 +12197,10 @@
         <v>721</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -12207,7 +12217,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12222,7 +12232,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -12239,7 +12249,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12251,10 +12261,10 @@
         <v>618</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -12283,10 +12293,10 @@
         <v>618</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12300,10 +12310,10 @@
         <v>617</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12316,7 +12326,7 @@
       </c>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12330,7 +12340,7 @@
         <v>596</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>670</v>
@@ -12345,10 +12355,10 @@
         <v>618</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -12380,7 +12390,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -12412,7 +12422,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12429,7 +12439,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12441,15 +12451,15 @@
         <v>618</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
       <c r="A241" s="4">
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12461,7 +12471,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12476,7 +12486,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -12505,7 +12515,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -12519,7 +12529,7 @@
         <v>386</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>869</v>
@@ -12537,7 +12547,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12566,10 +12576,10 @@
         <v>618</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -12601,7 +12611,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -12615,7 +12625,7 @@
         <v>391</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>392</v>
@@ -12630,7 +12640,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -12644,7 +12654,7 @@
         <v>744</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>394</v>
@@ -12662,7 +12672,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -12676,7 +12686,7 @@
         <v>395</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>396</v>
@@ -12691,7 +12701,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -12705,7 +12715,7 @@
         <v>397</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>398</v>
@@ -12720,7 +12730,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12731,7 +12741,7 @@
         <v>88</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -12749,10 +12759,10 @@
         <v>618</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -12784,7 +12794,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -12816,7 +12826,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12848,7 +12858,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -12880,7 +12890,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -12912,7 +12922,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -12944,7 +12954,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -12976,7 +12986,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -13008,7 +13018,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13040,7 +13050,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13072,7 +13082,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13089,7 +13099,7 @@
         <v>19</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>14</v>
@@ -13104,7 +13114,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13136,7 +13146,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13168,7 +13178,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -13182,10 +13192,10 @@
         <v>422</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13200,7 +13210,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -13232,7 +13242,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13264,7 +13274,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13296,7 +13306,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13328,7 +13338,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13345,7 +13355,7 @@
         <v>364</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13357,10 +13367,10 @@
         <v>618</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13392,7 +13402,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13424,7 +13434,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13456,7 +13466,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13488,7 +13498,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13520,7 +13530,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13552,7 +13562,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13569,7 +13579,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13584,7 +13594,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13601,7 +13611,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13616,7 +13626,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13648,7 +13658,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13680,7 +13690,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13712,7 +13722,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13744,7 +13754,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13776,7 +13786,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13793,7 +13803,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13805,10 +13815,10 @@
         <v>721</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13840,7 +13850,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13872,7 +13882,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -13904,7 +13914,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -13936,7 +13946,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -13968,7 +13978,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -14000,7 +14010,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14032,7 +14042,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14064,7 +14074,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14096,7 +14106,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14128,7 +14138,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14160,7 +14170,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14192,7 +14202,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14224,7 +14234,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14256,7 +14266,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14288,7 +14298,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14320,7 +14330,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14352,7 +14362,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14369,7 +14379,7 @@
         <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -14384,7 +14394,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14413,10 +14423,10 @@
         <v>618</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14448,7 +14458,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14480,7 +14490,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14509,10 +14519,10 @@
         <v>618</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14544,7 +14554,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14576,7 +14586,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -14608,7 +14618,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -14640,7 +14650,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -14672,7 +14682,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14704,7 +14714,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -14736,7 +14746,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -14768,7 +14778,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -14800,7 +14810,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14832,7 +14842,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14864,7 +14874,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -14896,7 +14906,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -14928,7 +14938,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -14960,7 +14970,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -14992,7 +15002,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15024,7 +15034,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15056,7 +15066,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15088,7 +15098,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15120,7 +15130,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15152,7 +15162,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15184,7 +15194,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15216,7 +15226,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15248,7 +15258,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15280,7 +15290,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15312,7 +15322,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15329,7 +15339,7 @@
         <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -15344,7 +15354,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15376,7 +15386,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15408,7 +15418,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15440,7 +15450,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15472,7 +15482,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15504,7 +15514,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15536,7 +15546,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15568,7 +15578,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15600,7 +15610,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15632,7 +15642,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15664,7 +15674,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15696,7 +15706,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15728,7 +15738,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -15760,7 +15770,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15777,7 +15787,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15789,10 +15799,10 @@
         <v>618</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -15824,7 +15834,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -15856,7 +15866,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -15888,7 +15898,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -15920,7 +15930,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -15937,7 +15947,7 @@
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -15952,7 +15962,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -15984,7 +15994,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16016,7 +16026,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16045,10 +16055,10 @@
         <v>618</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16077,10 +16087,10 @@
         <v>618</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="355" spans="1:10">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16112,7 +16122,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16144,7 +16154,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16176,7 +16186,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16208,7 +16218,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16240,7 +16250,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16272,7 +16282,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16289,7 +16299,7 @@
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
@@ -16301,10 +16311,10 @@
         <v>618</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16315,7 +16325,7 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
@@ -16333,10 +16343,10 @@
         <v>618</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16347,13 +16357,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -16365,10 +16375,10 @@
         <v>618</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16379,13 +16389,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16397,10 +16407,10 @@
         <v>618</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16411,13 +16421,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16429,10 +16439,10 @@
         <v>618</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16443,13 +16453,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16461,10 +16471,10 @@
         <v>721</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16475,13 +16485,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16493,10 +16503,10 @@
         <v>721</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16507,13 +16517,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16525,10 +16535,10 @@
         <v>618</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16539,7 +16549,7 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>80</v>
@@ -16557,10 +16567,10 @@
         <v>721</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16571,13 +16581,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -16589,10 +16599,10 @@
         <v>721</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -16603,7 +16613,7 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>80</v>
@@ -16621,10 +16631,10 @@
         <v>721</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16641,7 +16651,7 @@
         <v>71</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -16653,10 +16663,10 @@
         <v>618</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16685,10 +16695,10 @@
         <v>618</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -16705,7 +16715,7 @@
         <v>19</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -16717,10 +16727,10 @@
         <v>618</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -16737,7 +16747,7 @@
         <v>80</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
@@ -16749,10 +16759,10 @@
         <v>618</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16782,7 +16792,7 @@
       </c>
       <c r="J376" s="24"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16814,7 +16824,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:10">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -16844,7 +16854,7 @@
       </c>
       <c r="J378" s="24"/>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:10">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -16874,7 +16884,7 @@
       </c>
       <c r="J379" s="24"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -16906,7 +16916,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -16938,7 +16948,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:10">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -16955,7 +16965,7 @@
         <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -16967,10 +16977,10 @@
         <v>618</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -16987,7 +16997,7 @@
         <v>19</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -16999,10 +17009,10 @@
         <v>618</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17031,10 +17041,10 @@
         <v>618</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17066,7 +17076,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -17098,7 +17108,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17115,7 +17125,7 @@
         <v>19</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
@@ -17127,10 +17137,10 @@
         <v>618</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17141,7 +17151,7 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>23</v>
@@ -17159,10 +17169,10 @@
         <v>618</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17173,13 +17183,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17191,10 +17201,10 @@
         <v>721</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17205,7 +17215,7 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
@@ -17223,10 +17233,10 @@
         <v>618</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17237,7 +17247,7 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
@@ -17255,10 +17265,10 @@
         <v>618</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17269,13 +17279,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17287,10 +17297,10 @@
         <v>618</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17301,7 +17311,7 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
@@ -17319,10 +17329,10 @@
         <v>618</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17333,13 +17343,13 @@
         <v>11</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17351,10 +17361,10 @@
         <v>618</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="395" spans="1:10">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17386,7 +17396,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17418,7 +17428,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17450,7 +17460,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17482,7 +17492,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17514,7 +17524,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17546,7 +17556,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -17578,7 +17588,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17610,7 +17620,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17642,7 +17652,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17653,13 +17663,13 @@
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -17671,10 +17681,10 @@
         <v>618</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17685,13 +17695,13 @@
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17703,10 +17713,10 @@
         <v>618</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17717,13 +17727,13 @@
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -17735,10 +17745,10 @@
         <v>618</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -17749,13 +17759,13 @@
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17767,10 +17777,10 @@
         <v>618</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -17781,13 +17791,13 @@
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
@@ -17799,10 +17809,10 @@
         <v>618</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="409" spans="1:10">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -17834,7 +17844,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -17866,7 +17876,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -17898,7 +17908,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -17930,7 +17940,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -17962,7 +17972,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -17994,7 +18004,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18026,7 +18036,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18058,7 +18068,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18069,7 +18079,7 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>19</v>
@@ -18087,10 +18097,10 @@
         <v>721</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18101,13 +18111,13 @@
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -18119,10 +18129,10 @@
         <v>618</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18133,13 +18143,13 @@
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18151,10 +18161,10 @@
         <v>618</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18165,13 +18175,13 @@
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18183,10 +18193,10 @@
         <v>618</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18197,13 +18207,13 @@
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18215,10 +18225,10 @@
         <v>618</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18229,13 +18239,13 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18247,10 +18257,10 @@
         <v>618</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18261,13 +18271,13 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -18279,10 +18289,10 @@
         <v>618</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18293,13 +18303,13 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -18311,10 +18321,10 @@
         <v>618</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18325,13 +18335,13 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18343,10 +18353,10 @@
         <v>721</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18357,13 +18367,13 @@
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -18376,7 +18386,7 @@
       </c>
       <c r="J426" s="24"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18387,7 +18397,7 @@
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>80</v>
@@ -18405,21 +18415,21 @@
         <v>618</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
       <c r="A428" s="4">
         <v>427</v>
       </c>
       <c r="B428" s="40" t="s">
+        <v>942</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428" s="5" t="s">
         <v>943</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D428" s="5" t="s">
-        <v>944</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>80</v>
@@ -18437,27 +18447,27 @@
         <v>618</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10">
       <c r="A429" s="4">
         <v>428</v>
       </c>
       <c r="B429" s="40" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18469,27 +18479,27 @@
         <v>618</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
       <c r="A430" s="4">
         <v>429</v>
       </c>
       <c r="B430" s="40" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18501,21 +18511,21 @@
         <v>618</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10">
       <c r="A431" s="4">
         <v>430</v>
       </c>
       <c r="B431" s="40" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>71</v>
@@ -18533,21 +18543,21 @@
         <v>618</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10">
       <c r="A432" s="4">
         <v>431</v>
       </c>
       <c r="B432" s="40" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>80</v>
@@ -18565,10 +18575,10 @@
         <v>618</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -18579,7 +18589,7 @@
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>364</v>
@@ -18597,10 +18607,10 @@
         <v>618</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -18611,7 +18621,7 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>364</v>
@@ -18629,10 +18639,10 @@
         <v>618</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -18643,13 +18653,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18661,10 +18671,10 @@
         <v>618</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -18675,13 +18685,13 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18693,10 +18703,10 @@
         <v>618</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -18707,13 +18717,13 @@
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
@@ -18725,14 +18735,14 @@
         <v>618</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10">
       <c r="A438" s="4">
         <v>437</v>
       </c>
-      <c r="B438" s="53" t="s">
+      <c r="B438" s="52" t="s">
         <v>719</v>
       </c>
       <c r="C438" s="1" t="s">
@@ -18760,18 +18770,18 @@
         <v>722</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:10">
       <c r="A439" s="4">
         <v>438</v>
       </c>
-      <c r="B439" s="53" t="s">
-        <v>1188</v>
+      <c r="B439" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>19</v>
@@ -18789,26 +18799,28 @@
         <v>618</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="440" spans="1:10">
       <c r="A440" s="4">
         <v>439</v>
       </c>
-      <c r="B440" s="53" t="s">
-        <v>1188</v>
+      <c r="B440" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F440" s="52"/>
+      <c r="F440" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G440" s="2" t="s">
         <v>32</v>
       </c>
@@ -18820,23 +18832,25 @@
       </c>
       <c r="J440" s="24"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10">
       <c r="A441" s="4">
         <v>440</v>
       </c>
-      <c r="B441" s="53" t="s">
-        <v>1188</v>
+      <c r="B441" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F441" s="52"/>
+      <c r="F441" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G441" s="2" t="s">
         <v>32</v>
       </c>
@@ -18848,23 +18862,25 @@
       </c>
       <c r="J441" s="24"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10">
       <c r="A442" s="4">
         <v>441</v>
       </c>
-      <c r="B442" s="53" t="s">
-        <v>1188</v>
+      <c r="B442" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F442" s="52"/>
+      <c r="F442" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G442" s="2" t="s">
         <v>32</v>
       </c>
@@ -18876,23 +18892,25 @@
       </c>
       <c r="J442" s="24"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10">
       <c r="A443" s="4">
         <v>442</v>
       </c>
-      <c r="B443" s="53" t="s">
-        <v>1188</v>
+      <c r="B443" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F443" s="52"/>
+      <c r="F443" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
       </c>
@@ -18904,23 +18922,25 @@
       </c>
       <c r="J443" s="24"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10">
       <c r="A444" s="4">
         <v>443</v>
       </c>
-      <c r="B444" s="53" t="s">
-        <v>1189</v>
+      <c r="B444" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1199</v>
+        <v>573</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F444" s="52"/>
+      <c r="F444" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
       </c>
@@ -18932,23 +18952,25 @@
       </c>
       <c r="J444" s="24"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10">
       <c r="A445" s="4">
         <v>444</v>
       </c>
-      <c r="B445" s="53" t="s">
-        <v>1189</v>
+      <c r="B445" s="55" t="s">
+        <v>1187</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1200</v>
+        <v>573</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F445" s="52"/>
+      <c r="F445" s="1" t="s">
+        <v>667</v>
+      </c>
       <c r="G445" s="2" t="s">
         <v>32</v>
       </c>
@@ -18959,6 +18981,1296 @@
         <v>618</v>
       </c>
       <c r="J445" s="24"/>
+    </row>
+    <row r="446" spans="1:10">
+      <c r="A446" s="4">
+        <v>445</v>
+      </c>
+      <c r="B446" s="55" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E446" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F446" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G446" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H446" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I446" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J446" s="54"/>
+    </row>
+    <row r="447" spans="1:10">
+      <c r="A447" s="4">
+        <v>446</v>
+      </c>
+      <c r="B447" s="55" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E447" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F447" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G447" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H447" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I447" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J447" s="54"/>
+    </row>
+    <row r="448" spans="1:10">
+      <c r="A448" s="4">
+        <v>447</v>
+      </c>
+      <c r="B448" s="55" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E448" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F448" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G448" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H448" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I448" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J448" s="54"/>
+    </row>
+    <row r="449" spans="1:10">
+      <c r="A449" s="4">
+        <v>448</v>
+      </c>
+      <c r="B449" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E449" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F449" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G449" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H449" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I449" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J449" s="54"/>
+    </row>
+    <row r="450" spans="1:10">
+      <c r="A450" s="4">
+        <v>449</v>
+      </c>
+      <c r="B450" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E450" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F450" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G450" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H450" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I450" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J450" s="54"/>
+    </row>
+    <row r="451" spans="1:10">
+      <c r="A451" s="4">
+        <v>450</v>
+      </c>
+      <c r="B451" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E451" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F451" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G451" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H451" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I451" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J451" s="54"/>
+    </row>
+    <row r="452" spans="1:10">
+      <c r="A452" s="4">
+        <v>451</v>
+      </c>
+      <c r="B452" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E452" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F452" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G452" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H452" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I452" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J452" s="54"/>
+    </row>
+    <row r="453" spans="1:10">
+      <c r="A453" s="4">
+        <v>452</v>
+      </c>
+      <c r="B453" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E453" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F453" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G453" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H453" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I453" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J453" s="54"/>
+    </row>
+    <row r="454" spans="1:10">
+      <c r="A454" s="4">
+        <v>453</v>
+      </c>
+      <c r="B454" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C454" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E454" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F454" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G454" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H454" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I454" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J454" s="54"/>
+    </row>
+    <row r="455" spans="1:10">
+      <c r="A455" s="4">
+        <v>454</v>
+      </c>
+      <c r="B455" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C455" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E455" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F455" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G455" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H455" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I455" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J455" s="54"/>
+    </row>
+    <row r="456" spans="1:10">
+      <c r="A456" s="4">
+        <v>455</v>
+      </c>
+      <c r="B456" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E456" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F456" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G456" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H456" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I456" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J456" s="54"/>
+    </row>
+    <row r="457" spans="1:10">
+      <c r="A457" s="4">
+        <v>456</v>
+      </c>
+      <c r="B457" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E457" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F457" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G457" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H457" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I457" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J457" s="54"/>
+    </row>
+    <row r="458" spans="1:10">
+      <c r="A458" s="4">
+        <v>457</v>
+      </c>
+      <c r="B458" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E458" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F458" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G458" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H458" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I458" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J458" s="54"/>
+    </row>
+    <row r="459" spans="1:10">
+      <c r="A459" s="4">
+        <v>458</v>
+      </c>
+      <c r="B459" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E459" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F459" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G459" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H459" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I459" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J459" s="54"/>
+    </row>
+    <row r="460" spans="1:10">
+      <c r="A460" s="4">
+        <v>459</v>
+      </c>
+      <c r="B460" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E460" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F460" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G460" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H460" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I460" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J460" s="54"/>
+    </row>
+    <row r="461" spans="1:10">
+      <c r="A461" s="4">
+        <v>460</v>
+      </c>
+      <c r="B461" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C461" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E461" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F461" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G461" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H461" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I461" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J461" s="54"/>
+    </row>
+    <row r="462" spans="1:10">
+      <c r="A462" s="4">
+        <v>461</v>
+      </c>
+      <c r="B462" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E462" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F462" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G462" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H462" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I462" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J462" s="54"/>
+    </row>
+    <row r="463" spans="1:10">
+      <c r="A463" s="4">
+        <v>462</v>
+      </c>
+      <c r="B463" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E463" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F463" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G463" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H463" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I463" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J463" s="54"/>
+    </row>
+    <row r="464" spans="1:10">
+      <c r="A464" s="4">
+        <v>463</v>
+      </c>
+      <c r="B464" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E464" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F464" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G464" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H464" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I464" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J464" s="54"/>
+    </row>
+    <row r="465" spans="1:10">
+      <c r="A465" s="4">
+        <v>464</v>
+      </c>
+      <c r="B465" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E465" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F465" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G465" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H465" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I465" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J465" s="54"/>
+    </row>
+    <row r="466" spans="1:10">
+      <c r="A466" s="4">
+        <v>465</v>
+      </c>
+      <c r="B466" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E466" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F466" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G466" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H466" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I466" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J466" s="54"/>
+    </row>
+    <row r="467" spans="1:10">
+      <c r="A467" s="4">
+        <v>466</v>
+      </c>
+      <c r="B467" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E467" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F467" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G467" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H467" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I467" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J467" s="54"/>
+    </row>
+    <row r="468" spans="1:10">
+      <c r="A468" s="4">
+        <v>467</v>
+      </c>
+      <c r="B468" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E468" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F468" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G468" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H468" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I468" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J468" s="54"/>
+    </row>
+    <row r="469" spans="1:10">
+      <c r="A469" s="4">
+        <v>468</v>
+      </c>
+      <c r="B469" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E469" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F469" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G469" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H469" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I469" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J469" s="54"/>
+    </row>
+    <row r="470" spans="1:10">
+      <c r="A470" s="4">
+        <v>469</v>
+      </c>
+      <c r="B470" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E470" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F470" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G470" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H470" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I470" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J470" s="54"/>
+    </row>
+    <row r="471" spans="1:10">
+      <c r="A471" s="4">
+        <v>470</v>
+      </c>
+      <c r="B471" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E471" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F471" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G471" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H471" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I471" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J471" s="54"/>
+    </row>
+    <row r="472" spans="1:10">
+      <c r="A472" s="4">
+        <v>471</v>
+      </c>
+      <c r="B472" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C472" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E472" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F472" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G472" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H472" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I472" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J472" s="54"/>
+    </row>
+    <row r="473" spans="1:10">
+      <c r="A473" s="4">
+        <v>472</v>
+      </c>
+      <c r="B473" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E473" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F473" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G473" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H473" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I473" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J473" s="54"/>
+    </row>
+    <row r="474" spans="1:10">
+      <c r="A474" s="4">
+        <v>473</v>
+      </c>
+      <c r="B474" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E474" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F474" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G474" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H474" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I474" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J474" s="54"/>
+    </row>
+    <row r="475" spans="1:10">
+      <c r="A475" s="4">
+        <v>474</v>
+      </c>
+      <c r="B475" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E475" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F475" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G475" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H475" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I475" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J475" s="54"/>
+    </row>
+    <row r="476" spans="1:10">
+      <c r="A476" s="4">
+        <v>475</v>
+      </c>
+      <c r="B476" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E476" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F476" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G476" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H476" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I476" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J476" s="54"/>
+    </row>
+    <row r="477" spans="1:10">
+      <c r="A477" s="4">
+        <v>476</v>
+      </c>
+      <c r="B477" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D477" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E477" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F477" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G477" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H477" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I477" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J477" s="54"/>
+    </row>
+    <row r="478" spans="1:10">
+      <c r="A478" s="4">
+        <v>477</v>
+      </c>
+      <c r="B478" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D478" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E478" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F478" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G478" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H478" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I478" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J478" s="54"/>
+    </row>
+    <row r="479" spans="1:10">
+      <c r="A479" s="4">
+        <v>478</v>
+      </c>
+      <c r="B479" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D479" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E479" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F479" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G479" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H479" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I479" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J479" s="54"/>
+    </row>
+    <row r="480" spans="1:10">
+      <c r="A480" s="4">
+        <v>479</v>
+      </c>
+      <c r="B480" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D480" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E480" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F480" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G480" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H480" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I480" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J480" s="54"/>
+    </row>
+    <row r="481" spans="1:10">
+      <c r="A481" s="4">
+        <v>480</v>
+      </c>
+      <c r="B481" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D481" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E481" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F481" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G481" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H481" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I481" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J481" s="54"/>
+    </row>
+    <row r="482" spans="1:10">
+      <c r="A482" s="4">
+        <v>481</v>
+      </c>
+      <c r="B482" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D482" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E482" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F482" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G482" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H482" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I482" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J482" s="54"/>
+    </row>
+    <row r="483" spans="1:10">
+      <c r="A483" s="4">
+        <v>482</v>
+      </c>
+      <c r="B483" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D483" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E483" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F483" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G483" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H483" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I483" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J483" s="54"/>
+    </row>
+    <row r="484" spans="1:10">
+      <c r="A484" s="4">
+        <v>483</v>
+      </c>
+      <c r="B484" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D484" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E484" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F484" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G484" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H484" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I484" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J484" s="54"/>
+    </row>
+    <row r="485" spans="1:10">
+      <c r="A485" s="4">
+        <v>484</v>
+      </c>
+      <c r="B485" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C485" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D485" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E485" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F485" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G485" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H485" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I485" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J485" s="54"/>
+    </row>
+    <row r="486" spans="1:10">
+      <c r="A486" s="4">
+        <v>485</v>
+      </c>
+      <c r="B486" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C486" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D486" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E486" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F486" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G486" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H486" s="53">
+        <v>46081</v>
+      </c>
+      <c r="I486" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J486" s="54"/>
+    </row>
+    <row r="487" spans="1:10">
+      <c r="A487" s="4">
+        <v>486</v>
+      </c>
+      <c r="B487" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D487" s="2" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E487" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F487" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G487" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H487" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I487" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J487" s="24"/>
+    </row>
+    <row r="488" spans="1:10">
+      <c r="A488" s="4">
+        <v>487</v>
+      </c>
+      <c r="B488" s="52" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C488" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D488" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E488" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F488" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="G488" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H488" s="23">
+        <v>46063</v>
+      </c>
+      <c r="I488" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="J488" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -19022,7 +20334,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -19031,7 +20343,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>548</v>
       </c>
@@ -19051,127 +20363,127 @@
         <v>552</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>990</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>991</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="C3" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>991</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>992</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>992</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>993</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C5" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>993</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>994</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>994</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>995</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
+        <v>959</v>
+      </c>
+      <c r="B7" s="42" t="s">
         <v>960</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="C7" s="42" t="s">
         <v>961</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>995</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>962</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>996</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>963</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>553</v>
       </c>
@@ -19188,7 +20500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>553</v>
       </c>
@@ -19205,7 +20517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>553</v>
       </c>
@@ -19222,7 +20534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>553</v>
       </c>
@@ -19239,7 +20551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>553</v>
       </c>
@@ -19256,7 +20568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>553</v>
       </c>
@@ -19273,7 +20585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>553</v>
       </c>
@@ -19290,7 +20602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>553</v>
       </c>
@@ -19307,7 +20619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>553</v>
       </c>
@@ -19324,7 +20636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>553</v>
       </c>
@@ -19341,7 +20653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>553</v>
       </c>
@@ -19358,7 +20670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>553</v>
       </c>
@@ -19375,7 +20687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>553</v>
       </c>
@@ -19392,7 +20704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>558</v>
       </c>
@@ -19412,7 +20724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>558</v>
       </c>
@@ -19432,7 +20744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>558</v>
       </c>
@@ -19452,7 +20764,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>558</v>
       </c>
@@ -19472,7 +20784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>558</v>
       </c>
@@ -19492,7 +20804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>558</v>
       </c>
@@ -19512,7 +20824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>558</v>
       </c>
@@ -19532,7 +20844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>571</v>
       </c>
@@ -19552,7 +20864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>575</v>
       </c>
@@ -19572,7 +20884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>577</v>
       </c>
@@ -19592,7 +20904,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>577</v>
       </c>
@@ -19612,7 +20924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>571</v>
       </c>
@@ -19644,7 +20956,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -19661,7 +20973,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -19693,7 +21005,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -19725,7 +21037,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -19757,7 +21069,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -19789,7 +21101,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -19821,7 +21133,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -19853,7 +21165,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -19885,7 +21197,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -19917,7 +21229,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -19949,7 +21261,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -19981,7 +21293,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -20013,7 +21325,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -20045,7 +21357,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -20077,7 +21389,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -20109,7 +21421,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -20141,7 +21453,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -20173,7 +21485,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -20205,7 +21517,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -20237,7 +21549,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -20269,7 +21581,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -20301,7 +21613,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -20333,7 +21645,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -20365,7 +21677,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -20397,7 +21709,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -20429,7 +21741,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -20459,7 +21771,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -20489,7 +21801,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -20519,7 +21831,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -20549,7 +21861,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -20579,7 +21891,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -20609,7 +21921,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -20639,7 +21951,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -20669,7 +21981,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -20699,7 +22011,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -20729,7 +22041,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -20759,7 +22071,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -20789,7 +22101,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -20819,7 +22131,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -20849,7 +22161,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -20879,7 +22191,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -20909,7 +22221,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -20939,7 +22251,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -20968,7 +22280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -21000,15 +22312,15 @@
         <v>884</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="33">
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>964</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>965</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>966</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
@@ -21029,18 +22341,18 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="18">
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>964</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>965</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>966</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -21061,15 +22373,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="18">
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -21090,15 +22402,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="18">
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -21119,15 +22431,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="18">
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -21148,15 +22460,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="18">
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -21177,15 +22489,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="18">
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -21206,18 +22518,18 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="18">
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -21226,7 +22538,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -21238,21 +22550,21 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="3" customFormat="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>937</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>71</v>
@@ -21270,110 +22582,110 @@
         <v>618</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="18"/>
       <c r="B53" s="21"/>
       <c r="C53" s="49"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102E5F73-F235-4B3F-B758-87B7E1A33FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4084E8-90E7-4062-ADD9-1FC274FA46A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1209">
   <si>
     <t>INDICE</t>
   </si>
@@ -2176,9 +2176,6 @@
     <t>ESTAVA NO PAÇO - RECURSOS HUMANOS; PROBLEMA IMPRESSÃO EM BRACO FOI PARA WP;  QUEBROU BARRA DE LEDE RETIRADA DO PAÇO 02/05/2025 PAÇO; IMPRESSORA INSTALADA NO FME ARRAIAL DO CABO 11/09/2025;</t>
   </si>
   <si>
-    <t>INSTALAÇÃO FEITA EM 10/09/2024 - DISTRIVISA; RETIRADA FME ARRAIAL DO CABO PARA MANUTENÇÃO 11/09/2025;</t>
-  </si>
-  <si>
     <t xml:space="preserve">PC I5 Mon.22POL Nobreak 600 </t>
   </si>
   <si>
@@ -2812,9 +2809,6 @@
     <t>INSTALADA NO GABINETE DA SECRETARIA DA FAZENDA 21/10/2025;</t>
   </si>
   <si>
-    <t>RETIRADA DO GABINETE DA SEC. DA FAZENDA PROBLEMAS DE FAZENDA 22/10/2025;</t>
-  </si>
-  <si>
     <t>INSTALADA NA SECRETARIA DE OBRAS ITA;</t>
   </si>
   <si>
@@ -3662,6 +3656,15 @@
   </si>
   <si>
     <t>ESTAVA NO ITBI - PAÇO; TROCA DE FUSÃO ROLETES 23/10/2025; INSTALADA SESAU 24/10/2025; INSTALADA PAM ESPACO DA MULHER 27/02/2026;</t>
+  </si>
+  <si>
+    <t>RETIRADA DO GABINETE DA SEC. DA FAZENDA PROBLEMAS DE FUSAO 22/10/2025;  FUSAO REPARADA NA WP E DISPONIVEL NA SOLAGOS 03/03/2026;</t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO FEITA EM 10/09/2024 - DISTRIVISA; RETIRADA FME ARRAIAL DO CABO PARA MANUTENÇÃO 11/09/2025; MANUTENÇÃO FEITA NA WP E DISPONIVEL NA SOLAGOS 03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAM - SALA02 - TRIAGEM </t>
   </si>
 </sst>
 </file>
@@ -3847,7 +3850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3989,10 +3992,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -5041,7 +5040,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -5053,7 +5052,7 @@
         <v>618</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5073,7 +5072,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -5137,7 +5136,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -5313,7 +5312,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5337,7 +5336,7 @@
         <v>618</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5345,7 +5344,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5357,7 +5356,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -5369,7 +5368,7 @@
         <v>618</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5383,7 +5382,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>19</v>
@@ -5421,7 +5420,7 @@
         <v>364</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5433,7 +5432,7 @@
         <v>618</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5447,7 +5446,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>19</v>
@@ -5546,7 +5545,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -5610,7 +5609,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5622,7 +5621,7 @@
         <v>618</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5674,7 +5673,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5686,7 +5685,7 @@
         <v>618</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5706,7 +5705,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -5904,7 +5903,7 @@
         <v>618</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6020,7 +6019,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -6113,10 +6112,10 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>14</v>
@@ -6128,7 +6127,7 @@
         <v>618</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6285,7 +6284,7 @@
         <v>618</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -6604,7 +6603,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6636,7 +6635,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6668,7 +6667,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6680,7 +6679,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6692,7 +6691,7 @@
         <v>618</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6706,7 +6705,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>23</v>
@@ -7185,7 +7184,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>23</v>
@@ -7220,7 +7219,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7232,7 +7231,7 @@
         <v>618</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7467,10 +7466,10 @@
         <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7502,7 +7501,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7531,10 +7530,10 @@
         <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7557,10 +7556,10 @@
         <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7583,10 +7582,10 @@
         <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7609,10 +7608,10 @@
         <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7644,7 +7643,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7673,10 +7672,10 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7705,10 +7704,10 @@
         <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7737,10 +7736,10 @@
         <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7766,7 +7765,7 @@
         <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>23</v>
@@ -7784,7 +7783,7 @@
         <v>618</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -7798,10 +7797,10 @@
         <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7830,10 +7829,10 @@
         <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7856,10 +7855,10 @@
         <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -7885,7 +7884,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -7900,7 +7899,7 @@
         <v>618</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -7914,10 +7913,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -8132,7 +8131,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8144,7 +8143,7 @@
         <v>618</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -8318,7 +8317,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8887,13 +8886,13 @@
         <v>11</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8919,13 +8918,13 @@
         <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>32</v>
@@ -9018,10 +9017,10 @@
         <v>234</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9065,7 +9064,7 @@
         <v>618</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -9085,7 +9084,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9117,7 +9116,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9129,7 +9128,7 @@
         <v>618</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9149,7 +9148,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9158,10 +9157,10 @@
         <v>45936</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -9181,7 +9180,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9193,7 +9192,7 @@
         <v>618</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9213,7 +9212,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9225,7 +9224,7 @@
         <v>618</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -9242,10 +9241,10 @@
         <v>242</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1166</v>
+        <v>25</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>14</v>
@@ -9277,7 +9276,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9289,7 +9288,7 @@
         <v>618</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -9309,7 +9308,7 @@
         <v>19</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9321,7 +9320,7 @@
         <v>618</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9385,7 +9384,7 @@
         <v>618</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -9437,7 +9436,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9449,7 +9448,7 @@
         <v>618</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -9463,13 +9462,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9481,7 +9480,7 @@
         <v>618</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -9501,7 +9500,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9623,7 +9622,7 @@
         <v>88</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>364</v>
@@ -9641,7 +9640,7 @@
         <v>618</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -9737,7 +9736,7 @@
         <v>618</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -9789,7 +9788,7 @@
         <v>13</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>14</v>
@@ -9801,7 +9800,7 @@
         <v>618</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -9821,7 +9820,7 @@
         <v>364</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -9830,10 +9829,10 @@
         <v>45959</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -10063,7 +10062,7 @@
         <v>13</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G163" s="5" t="s">
         <v>14</v>
@@ -10214,7 +10213,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10223,7 +10222,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -10237,13 +10236,13 @@
         <v>88</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F169" s="1" t="s">
         <v>1056</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10302,10 +10301,10 @@
         <v>297</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10331,10 +10330,10 @@
         <v>298</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -11030,10 +11029,10 @@
         <v>326</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11091,7 +11090,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11109,7 +11108,7 @@
         <v>618</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -11126,10 +11125,10 @@
         <v>328</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11161,7 +11160,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11193,7 +11192,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11205,7 +11204,7 @@
         <v>618</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -11283,13 +11282,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11301,7 +11300,7 @@
         <v>618</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -11333,7 +11332,7 @@
         <v>618</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -11385,7 +11384,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11397,7 +11396,7 @@
         <v>618</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -11417,7 +11416,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11429,7 +11428,7 @@
         <v>618</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -11446,10 +11445,10 @@
         <v>342</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>667</v>
+        <v>1208</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11461,7 +11460,7 @@
         <v>618</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -11481,7 +11480,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
@@ -11493,7 +11492,7 @@
         <v>618</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -11653,7 +11652,7 @@
         <v>618</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -11673,7 +11672,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11685,7 +11684,7 @@
         <v>618</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -11737,7 +11736,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11746,10 +11745,10 @@
         <v>45933</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -11769,7 +11768,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11781,7 +11780,7 @@
         <v>618</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -11801,7 +11800,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11813,7 +11812,7 @@
         <v>618</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -11862,10 +11861,10 @@
         <v>360</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>667</v>
+        <v>1164</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -11897,7 +11896,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -11909,7 +11908,7 @@
         <v>618</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -11955,13 +11954,13 @@
         <v>11</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>14</v>
@@ -11973,7 +11972,7 @@
         <v>618</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -12025,7 +12024,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12037,7 +12036,7 @@
         <v>618</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -12101,7 +12100,7 @@
         <v>618</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -12121,7 +12120,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12153,7 +12152,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12165,7 +12164,7 @@
         <v>618</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -12185,7 +12184,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12194,10 +12193,10 @@
         <v>44127</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -12217,7 +12216,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12249,7 +12248,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12261,7 +12260,7 @@
         <v>618</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12281,7 +12280,7 @@
         <v>364</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G235" s="14" t="s">
         <v>14</v>
@@ -12293,7 +12292,7 @@
         <v>618</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12310,10 +12309,10 @@
         <v>617</v>
       </c>
       <c r="E236" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F236" s="1" t="s">
         <v>1056</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12340,7 +12339,7 @@
         <v>596</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>670</v>
@@ -12355,7 +12354,7 @@
         <v>618</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -12439,7 +12438,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12451,7 +12450,7 @@
         <v>618</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -12459,7 +12458,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12471,7 +12470,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12529,10 +12528,10 @@
         <v>386</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -12544,7 +12543,7 @@
         <v>618</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -12558,7 +12557,7 @@
         <v>88</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>32</v>
@@ -12576,7 +12575,7 @@
         <v>618</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -12625,7 +12624,7 @@
         <v>391</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>392</v>
@@ -12651,10 +12650,10 @@
         <v>11</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>394</v>
@@ -12686,7 +12685,7 @@
         <v>395</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>396</v>
@@ -12715,7 +12714,7 @@
         <v>397</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>398</v>
@@ -12741,7 +12740,7 @@
         <v>88</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -12759,7 +12758,7 @@
         <v>618</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -12776,22 +12775,22 @@
         <v>400</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>25</v>
+        <v>667</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>32</v>
       </c>
       <c r="H251" s="9">
-        <v>45952</v>
+        <v>46084</v>
       </c>
       <c r="I251" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>924</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -12936,22 +12935,22 @@
         <v>409</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>25</v>
+        <v>667</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H256" s="9">
-        <v>45797</v>
+        <v>46084</v>
       </c>
       <c r="I256" s="4" t="s">
         <v>618</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>712</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -13099,7 +13098,7 @@
         <v>19</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>14</v>
@@ -13192,10 +13191,10 @@
         <v>422</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13355,7 +13354,7 @@
         <v>364</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13367,7 +13366,7 @@
         <v>618</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -13579,7 +13578,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13611,7 +13610,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13803,7 +13802,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13812,10 +13811,10 @@
         <v>45597</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -14379,7 +14378,7 @@
         <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -14423,7 +14422,7 @@
         <v>618</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -14443,7 +14442,7 @@
         <v>80</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -14455,7 +14454,7 @@
         <v>618</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -14507,7 +14506,7 @@
         <v>80</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>14</v>
@@ -14519,7 +14518,7 @@
         <v>618</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -15339,7 +15338,7 @@
         <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -15557,13 +15556,13 @@
         <v>11</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -15575,7 +15574,7 @@
         <v>618</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -15589,13 +15588,13 @@
         <v>11</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -15607,7 +15606,7 @@
         <v>618</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -15621,13 +15620,13 @@
         <v>11</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -15639,7 +15638,7 @@
         <v>618</v>
       </c>
       <c r="J340" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -15653,13 +15652,13 @@
         <v>11</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -15671,7 +15670,7 @@
         <v>618</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -15685,13 +15684,13 @@
         <v>11</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -15703,7 +15702,7 @@
         <v>618</v>
       </c>
       <c r="J342" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -15787,7 +15786,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15799,7 +15798,7 @@
         <v>618</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -15807,10 +15806,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C346" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>765</v>
       </c>
       <c r="D346" s="14">
         <v>22011316</v>
@@ -15831,7 +15830,7 @@
         <v>618</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -15845,7 +15844,7 @@
         <v>11</v>
       </c>
       <c r="D347" s="38" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>80</v>
@@ -15863,7 +15862,7 @@
         <v>618</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -15877,7 +15876,7 @@
         <v>11</v>
       </c>
       <c r="D348" s="38" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>80</v>
@@ -15895,7 +15894,7 @@
         <v>618</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -15909,13 +15908,13 @@
         <v>11</v>
       </c>
       <c r="D349" s="38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -15927,7 +15926,7 @@
         <v>618</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -15941,13 +15940,13 @@
         <v>11</v>
       </c>
       <c r="D350" s="38" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -15959,7 +15958,7 @@
         <v>618</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -15973,13 +15972,13 @@
         <v>11</v>
       </c>
       <c r="D351" s="38" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -15991,7 +15990,7 @@
         <v>618</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -16005,13 +16004,13 @@
         <v>11</v>
       </c>
       <c r="D352" s="38" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -16023,7 +16022,7 @@
         <v>618</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -16037,7 +16036,7 @@
         <v>11</v>
       </c>
       <c r="D353" s="38" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>32</v>
@@ -16055,7 +16054,7 @@
         <v>618</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -16069,13 +16068,13 @@
         <v>11</v>
       </c>
       <c r="D354" s="38" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -16087,7 +16086,7 @@
         <v>618</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -16101,13 +16100,13 @@
         <v>11</v>
       </c>
       <c r="D355" s="38" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -16119,7 +16118,7 @@
         <v>618</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -16133,13 +16132,13 @@
         <v>11</v>
       </c>
       <c r="D356" s="38" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -16151,7 +16150,7 @@
         <v>618</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -16165,13 +16164,13 @@
         <v>11</v>
       </c>
       <c r="D357" s="38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>14</v>
@@ -16183,7 +16182,7 @@
         <v>618</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -16197,13 +16196,13 @@
         <v>11</v>
       </c>
       <c r="D358" s="38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>14</v>
@@ -16215,7 +16214,7 @@
         <v>618</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -16229,13 +16228,13 @@
         <v>11</v>
       </c>
       <c r="D359" s="38" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>14</v>
@@ -16247,7 +16246,7 @@
         <v>618</v>
       </c>
       <c r="J359" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -16261,13 +16260,13 @@
         <v>11</v>
       </c>
       <c r="D360" s="38" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
@@ -16279,7 +16278,7 @@
         <v>618</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -16293,13 +16292,13 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
@@ -16311,7 +16310,7 @@
         <v>618</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -16325,7 +16324,7 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
@@ -16343,7 +16342,7 @@
         <v>618</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -16357,13 +16356,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -16375,7 +16374,7 @@
         <v>618</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -16389,13 +16388,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16407,7 +16406,7 @@
         <v>618</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -16421,13 +16420,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16439,7 +16438,7 @@
         <v>618</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -16453,13 +16452,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16468,10 +16467,10 @@
         <v>45968</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -16485,13 +16484,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16500,10 +16499,10 @@
         <v>45968</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -16517,13 +16516,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16535,7 +16534,7 @@
         <v>618</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -16549,13 +16548,13 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16564,10 +16563,10 @@
         <v>45968</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -16581,13 +16580,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -16596,10 +16595,10 @@
         <v>45968</v>
       </c>
       <c r="I370" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -16613,13 +16612,13 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16628,10 +16627,10 @@
         <v>45971</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -16639,19 +16638,19 @@
         <v>371</v>
       </c>
       <c r="B372" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -16663,7 +16662,7 @@
         <v>618</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -16671,13 +16670,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>364</v>
@@ -16695,7 +16694,7 @@
         <v>618</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -16703,19 +16702,19 @@
         <v>373</v>
       </c>
       <c r="B374" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -16727,7 +16726,7 @@
         <v>618</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -16735,19 +16734,19 @@
         <v>374</v>
       </c>
       <c r="B375" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D375" s="38" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
@@ -16759,7 +16758,7 @@
         <v>618</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -16767,19 +16766,19 @@
         <v>375</v>
       </c>
       <c r="B376" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D376" s="38" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>14</v>
@@ -16797,19 +16796,19 @@
         <v>376</v>
       </c>
       <c r="B377" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D377" s="39" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
@@ -16821,7 +16820,7 @@
         <v>618</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -16829,19 +16828,19 @@
         <v>377</v>
       </c>
       <c r="B378" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D378" s="38" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16859,19 +16858,19 @@
         <v>378</v>
       </c>
       <c r="B379" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D379" s="38" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>14</v>
@@ -16889,19 +16888,19 @@
         <v>379</v>
       </c>
       <c r="B380" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D380" s="39" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>14</v>
@@ -16913,7 +16912,7 @@
         <v>618</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -16921,19 +16920,19 @@
         <v>380</v>
       </c>
       <c r="B381" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D381" s="39" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -16945,7 +16944,7 @@
         <v>618</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -16953,19 +16952,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D382" s="38" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -16977,7 +16976,7 @@
         <v>618</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -16985,19 +16984,19 @@
         <v>382</v>
       </c>
       <c r="B383" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D383" s="38" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17009,7 +17008,7 @@
         <v>618</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -17017,13 +17016,13 @@
         <v>383</v>
       </c>
       <c r="B384" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D384" s="38" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>71</v>
@@ -17041,7 +17040,7 @@
         <v>618</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -17049,19 +17048,19 @@
         <v>384</v>
       </c>
       <c r="B385" s="26" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D385" s="39" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>14</v>
@@ -17073,7 +17072,7 @@
         <v>618</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -17087,7 +17086,7 @@
         <v>11</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>13</v>
@@ -17105,7 +17104,7 @@
         <v>618</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -17119,13 +17118,13 @@
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
@@ -17137,7 +17136,7 @@
         <v>618</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -17151,7 +17150,7 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>23</v>
@@ -17169,7 +17168,7 @@
         <v>618</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17183,13 +17182,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17198,10 +17197,10 @@
         <v>45960</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17215,7 +17214,7 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
@@ -17233,7 +17232,7 @@
         <v>618</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -17247,7 +17246,7 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
@@ -17265,7 +17264,7 @@
         <v>618</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -17279,13 +17278,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17297,7 +17296,7 @@
         <v>618</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17311,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
@@ -17329,7 +17328,7 @@
         <v>618</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17343,13 +17342,13 @@
         <v>11</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17361,7 +17360,7 @@
         <v>618</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -17369,19 +17368,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>14</v>
@@ -17393,7 +17392,7 @@
         <v>618</v>
       </c>
       <c r="J395" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -17401,19 +17400,19 @@
         <v>395</v>
       </c>
       <c r="B396" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>14</v>
@@ -17425,7 +17424,7 @@
         <v>618</v>
       </c>
       <c r="J396" s="24" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -17433,19 +17432,19 @@
         <v>396</v>
       </c>
       <c r="B397" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>14</v>
@@ -17457,7 +17456,7 @@
         <v>618</v>
       </c>
       <c r="J397" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -17465,19 +17464,19 @@
         <v>397</v>
       </c>
       <c r="B398" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>14</v>
@@ -17489,7 +17488,7 @@
         <v>618</v>
       </c>
       <c r="J398" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -17497,19 +17496,19 @@
         <v>398</v>
       </c>
       <c r="B399" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>14</v>
@@ -17521,7 +17520,7 @@
         <v>618</v>
       </c>
       <c r="J399" s="24" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -17529,19 +17528,19 @@
         <v>399</v>
       </c>
       <c r="B400" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>14</v>
@@ -17553,7 +17552,7 @@
         <v>618</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -17561,19 +17560,19 @@
         <v>400</v>
       </c>
       <c r="B401" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>14</v>
@@ -17585,7 +17584,7 @@
         <v>618</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -17593,19 +17592,19 @@
         <v>401</v>
       </c>
       <c r="B402" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>14</v>
@@ -17617,7 +17616,7 @@
         <v>618</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -17625,19 +17624,19 @@
         <v>402</v>
       </c>
       <c r="B403" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
@@ -17649,7 +17648,7 @@
         <v>618</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -17657,19 +17656,19 @@
         <v>403</v>
       </c>
       <c r="B404" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -17681,7 +17680,7 @@
         <v>618</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -17689,19 +17688,19 @@
         <v>404</v>
       </c>
       <c r="B405" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17713,7 +17712,7 @@
         <v>618</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -17721,19 +17720,19 @@
         <v>405</v>
       </c>
       <c r="B406" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -17745,7 +17744,7 @@
         <v>618</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -17753,19 +17752,19 @@
         <v>406</v>
       </c>
       <c r="B407" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17777,7 +17776,7 @@
         <v>618</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -17785,19 +17784,19 @@
         <v>407</v>
       </c>
       <c r="B408" s="28" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
@@ -17809,7 +17808,7 @@
         <v>618</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -17817,19 +17816,19 @@
         <v>408</v>
       </c>
       <c r="B409" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>14</v>
@@ -17841,7 +17840,7 @@
         <v>618</v>
       </c>
       <c r="J409" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -17849,19 +17848,19 @@
         <v>409</v>
       </c>
       <c r="B410" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>14</v>
@@ -17873,7 +17872,7 @@
         <v>618</v>
       </c>
       <c r="J410" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -17881,19 +17880,19 @@
         <v>410</v>
       </c>
       <c r="B411" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>14</v>
@@ -17905,7 +17904,7 @@
         <v>618</v>
       </c>
       <c r="J411" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -17913,19 +17912,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>14</v>
@@ -17937,7 +17936,7 @@
         <v>618</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -17945,19 +17944,19 @@
         <v>412</v>
       </c>
       <c r="B413" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>14</v>
@@ -17969,7 +17968,7 @@
         <v>618</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -17977,19 +17976,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>14</v>
@@ -18001,7 +18000,7 @@
         <v>618</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -18009,19 +18008,19 @@
         <v>414</v>
       </c>
       <c r="B415" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
@@ -18033,7 +18032,7 @@
         <v>618</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -18041,19 +18040,19 @@
         <v>415</v>
       </c>
       <c r="B416" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -18065,7 +18064,7 @@
         <v>618</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -18073,13 +18072,13 @@
         <v>416</v>
       </c>
       <c r="B417" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>19</v>
@@ -18094,10 +18093,10 @@
         <v>45960</v>
       </c>
       <c r="I417" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -18105,19 +18104,19 @@
         <v>417</v>
       </c>
       <c r="B418" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -18129,7 +18128,7 @@
         <v>618</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -18137,19 +18136,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18161,7 +18160,7 @@
         <v>618</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -18169,19 +18168,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18193,7 +18192,7 @@
         <v>618</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -18201,19 +18200,19 @@
         <v>420</v>
       </c>
       <c r="B421" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18225,7 +18224,7 @@
         <v>618</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -18233,19 +18232,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18257,7 +18256,7 @@
         <v>618</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -18265,19 +18264,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -18289,7 +18288,7 @@
         <v>618</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -18297,19 +18296,19 @@
         <v>423</v>
       </c>
       <c r="B424" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -18321,7 +18320,7 @@
         <v>618</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -18329,19 +18328,19 @@
         <v>424</v>
       </c>
       <c r="B425" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18350,10 +18349,10 @@
         <v>46037</v>
       </c>
       <c r="I425" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -18361,19 +18360,19 @@
         <v>425</v>
       </c>
       <c r="B426" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -18391,19 +18390,19 @@
         <v>426</v>
       </c>
       <c r="B427" s="29" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>14</v>
@@ -18415,7 +18414,7 @@
         <v>618</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -18423,19 +18422,19 @@
         <v>427</v>
       </c>
       <c r="B428" s="40" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
@@ -18447,7 +18446,7 @@
         <v>618</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18455,19 +18454,19 @@
         <v>428</v>
       </c>
       <c r="B429" s="40" t="s">
+        <v>940</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D429" s="5" t="s">
         <v>942</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D429" s="5" t="s">
-        <v>944</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18479,7 +18478,7 @@
         <v>618</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18487,19 +18486,19 @@
         <v>429</v>
       </c>
       <c r="B430" s="40" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18511,7 +18510,7 @@
         <v>618</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18519,19 +18518,19 @@
         <v>430</v>
       </c>
       <c r="B431" s="40" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>14</v>
@@ -18543,7 +18542,7 @@
         <v>618</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18551,19 +18550,19 @@
         <v>431</v>
       </c>
       <c r="B432" s="40" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>14</v>
@@ -18575,7 +18574,7 @@
         <v>618</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -18583,19 +18582,19 @@
         <v>432</v>
       </c>
       <c r="B433" s="31" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>32</v>
@@ -18607,7 +18606,7 @@
         <v>618</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -18615,19 +18614,19 @@
         <v>433</v>
       </c>
       <c r="B434" s="31" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
@@ -18639,7 +18638,7 @@
         <v>618</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -18647,19 +18646,19 @@
         <v>434</v>
       </c>
       <c r="B435" s="31" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18671,7 +18670,7 @@
         <v>618</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -18679,19 +18678,19 @@
         <v>435</v>
       </c>
       <c r="B436" s="31" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18703,7 +18702,7 @@
         <v>618</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -18711,19 +18710,19 @@
         <v>436</v>
       </c>
       <c r="B437" s="31" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
@@ -18735,7 +18734,7 @@
         <v>618</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -18743,16 +18742,16 @@
         <v>437</v>
       </c>
       <c r="B438" s="52" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>387</v>
@@ -18767,27 +18766,27 @@
         <v>618</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="439" spans="1:10">
       <c r="A439" s="4">
         <v>438</v>
       </c>
-      <c r="B439" s="55" t="s">
-        <v>1187</v>
+      <c r="B439" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>32</v>
@@ -18799,21 +18798,21 @@
         <v>618</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="440" spans="1:10">
       <c r="A440" s="4">
         <v>439</v>
       </c>
-      <c r="B440" s="55" t="s">
-        <v>1187</v>
+      <c r="B440" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18836,14 +18835,14 @@
       <c r="A441" s="4">
         <v>440</v>
       </c>
-      <c r="B441" s="55" t="s">
-        <v>1187</v>
+      <c r="B441" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18866,14 +18865,14 @@
       <c r="A442" s="4">
         <v>441</v>
       </c>
-      <c r="B442" s="55" t="s">
-        <v>1187</v>
+      <c r="B442" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -18896,14 +18895,14 @@
       <c r="A443" s="4">
         <v>442</v>
       </c>
-      <c r="B443" s="55" t="s">
-        <v>1187</v>
+      <c r="B443" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>23</v>
@@ -18926,8 +18925,8 @@
       <c r="A444" s="4">
         <v>443</v>
       </c>
-      <c r="B444" s="55" t="s">
-        <v>1187</v>
+      <c r="B444" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
@@ -18956,8 +18955,8 @@
       <c r="A445" s="4">
         <v>444</v>
       </c>
-      <c r="B445" s="55" t="s">
-        <v>1187</v>
+      <c r="B445" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -18986,8 +18985,8 @@
       <c r="A446" s="4">
         <v>445</v>
       </c>
-      <c r="B446" s="55" t="s">
-        <v>1187</v>
+      <c r="B446" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19004,20 +19003,20 @@
       <c r="G446" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H446" s="53">
+      <c r="H446" s="23">
         <v>46081</v>
       </c>
       <c r="I446" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J446" s="54"/>
+      <c r="J446" s="24"/>
     </row>
     <row r="447" spans="1:10">
       <c r="A447" s="4">
         <v>446</v>
       </c>
-      <c r="B447" s="55" t="s">
-        <v>1187</v>
+      <c r="B447" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19034,20 +19033,20 @@
       <c r="G447" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H447" s="53">
+      <c r="H447" s="23">
         <v>46081</v>
       </c>
       <c r="I447" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J447" s="54"/>
+      <c r="J447" s="24"/>
     </row>
     <row r="448" spans="1:10">
       <c r="A448" s="4">
         <v>447</v>
       </c>
-      <c r="B448" s="55" t="s">
-        <v>1187</v>
+      <c r="B448" s="53" t="s">
+        <v>1185</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>88</v>
@@ -19064,20 +19063,20 @@
       <c r="G448" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H448" s="53">
+      <c r="H448" s="23">
         <v>46081</v>
       </c>
       <c r="I448" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J448" s="54"/>
+      <c r="J448" s="24"/>
     </row>
     <row r="449" spans="1:10">
       <c r="A449" s="4">
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
@@ -19094,20 +19093,20 @@
       <c r="G449" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H449" s="53">
+      <c r="H449" s="23">
         <v>46081</v>
       </c>
       <c r="I449" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J449" s="54"/>
+      <c r="J449" s="24"/>
     </row>
     <row r="450" spans="1:10">
       <c r="A450" s="4">
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
@@ -19124,20 +19123,20 @@
       <c r="G450" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H450" s="53">
+      <c r="H450" s="23">
         <v>46081</v>
       </c>
       <c r="I450" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J450" s="54"/>
+      <c r="J450" s="24"/>
     </row>
     <row r="451" spans="1:10">
       <c r="A451" s="4">
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
@@ -19154,20 +19153,20 @@
       <c r="G451" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H451" s="53">
+      <c r="H451" s="23">
         <v>46081</v>
       </c>
       <c r="I451" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J451" s="54"/>
+      <c r="J451" s="24"/>
     </row>
     <row r="452" spans="1:10">
       <c r="A452" s="4">
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
@@ -19184,20 +19183,20 @@
       <c r="G452" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H452" s="53">
+      <c r="H452" s="23">
         <v>46081</v>
       </c>
       <c r="I452" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J452" s="54"/>
+      <c r="J452" s="24"/>
     </row>
     <row r="453" spans="1:10">
       <c r="A453" s="4">
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
@@ -19214,20 +19213,20 @@
       <c r="G453" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H453" s="53">
+      <c r="H453" s="23">
         <v>46081</v>
       </c>
       <c r="I453" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J453" s="54"/>
+      <c r="J453" s="24"/>
     </row>
     <row r="454" spans="1:10">
       <c r="A454" s="4">
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
@@ -19244,20 +19243,20 @@
       <c r="G454" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H454" s="53">
+      <c r="H454" s="23">
         <v>46081</v>
       </c>
       <c r="I454" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J454" s="54"/>
+      <c r="J454" s="24"/>
     </row>
     <row r="455" spans="1:10">
       <c r="A455" s="4">
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
@@ -19274,20 +19273,20 @@
       <c r="G455" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H455" s="53">
+      <c r="H455" s="23">
         <v>46081</v>
       </c>
       <c r="I455" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J455" s="54"/>
+      <c r="J455" s="24"/>
     </row>
     <row r="456" spans="1:10">
       <c r="A456" s="4">
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
@@ -19304,20 +19303,20 @@
       <c r="G456" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H456" s="53">
+      <c r="H456" s="23">
         <v>46081</v>
       </c>
       <c r="I456" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J456" s="54"/>
+      <c r="J456" s="24"/>
     </row>
     <row r="457" spans="1:10">
       <c r="A457" s="4">
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
@@ -19334,20 +19333,20 @@
       <c r="G457" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H457" s="53">
+      <c r="H457" s="23">
         <v>46081</v>
       </c>
       <c r="I457" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J457" s="54"/>
+      <c r="J457" s="24"/>
     </row>
     <row r="458" spans="1:10">
       <c r="A458" s="4">
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
@@ -19364,20 +19363,20 @@
       <c r="G458" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H458" s="53">
+      <c r="H458" s="23">
         <v>46081</v>
       </c>
       <c r="I458" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J458" s="54"/>
+      <c r="J458" s="24"/>
     </row>
     <row r="459" spans="1:10">
       <c r="A459" s="4">
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19394,20 +19393,20 @@
       <c r="G459" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H459" s="53">
+      <c r="H459" s="23">
         <v>46081</v>
       </c>
       <c r="I459" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J459" s="54"/>
+      <c r="J459" s="24"/>
     </row>
     <row r="460" spans="1:10">
       <c r="A460" s="4">
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19424,20 +19423,20 @@
       <c r="G460" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H460" s="53">
+      <c r="H460" s="23">
         <v>46081</v>
       </c>
       <c r="I460" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J460" s="54"/>
+      <c r="J460" s="24"/>
     </row>
     <row r="461" spans="1:10">
       <c r="A461" s="4">
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19454,20 +19453,20 @@
       <c r="G461" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H461" s="53">
+      <c r="H461" s="23">
         <v>46081</v>
       </c>
       <c r="I461" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J461" s="54"/>
+      <c r="J461" s="24"/>
     </row>
     <row r="462" spans="1:10">
       <c r="A462" s="4">
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19484,20 +19483,20 @@
       <c r="G462" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H462" s="53">
+      <c r="H462" s="23">
         <v>46081</v>
       </c>
       <c r="I462" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J462" s="54"/>
+      <c r="J462" s="24"/>
     </row>
     <row r="463" spans="1:10">
       <c r="A463" s="4">
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19514,20 +19513,20 @@
       <c r="G463" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H463" s="53">
+      <c r="H463" s="23">
         <v>46081</v>
       </c>
       <c r="I463" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J463" s="54"/>
+      <c r="J463" s="24"/>
     </row>
     <row r="464" spans="1:10">
       <c r="A464" s="4">
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19544,20 +19543,20 @@
       <c r="G464" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H464" s="53">
+      <c r="H464" s="23">
         <v>46081</v>
       </c>
       <c r="I464" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J464" s="54"/>
+      <c r="J464" s="24"/>
     </row>
     <row r="465" spans="1:10">
       <c r="A465" s="4">
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19574,20 +19573,20 @@
       <c r="G465" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H465" s="53">
+      <c r="H465" s="23">
         <v>46081</v>
       </c>
       <c r="I465" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J465" s="54"/>
+      <c r="J465" s="24"/>
     </row>
     <row r="466" spans="1:10">
       <c r="A466" s="4">
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19604,20 +19603,20 @@
       <c r="G466" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H466" s="53">
+      <c r="H466" s="23">
         <v>46081</v>
       </c>
       <c r="I466" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J466" s="54"/>
+      <c r="J466" s="24"/>
     </row>
     <row r="467" spans="1:10">
       <c r="A467" s="4">
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19634,20 +19633,20 @@
       <c r="G467" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H467" s="53">
+      <c r="H467" s="23">
         <v>46081</v>
       </c>
       <c r="I467" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J467" s="54"/>
+      <c r="J467" s="24"/>
     </row>
     <row r="468" spans="1:10">
       <c r="A468" s="4">
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19664,20 +19663,20 @@
       <c r="G468" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H468" s="53">
+      <c r="H468" s="23">
         <v>46081</v>
       </c>
       <c r="I468" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J468" s="54"/>
+      <c r="J468" s="24"/>
     </row>
     <row r="469" spans="1:10">
       <c r="A469" s="4">
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19694,20 +19693,20 @@
       <c r="G469" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H469" s="53">
+      <c r="H469" s="23">
         <v>46081</v>
       </c>
       <c r="I469" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J469" s="54"/>
+      <c r="J469" s="24"/>
     </row>
     <row r="470" spans="1:10">
       <c r="A470" s="4">
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19724,20 +19723,20 @@
       <c r="G470" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H470" s="53">
+      <c r="H470" s="23">
         <v>46081</v>
       </c>
       <c r="I470" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J470" s="54"/>
+      <c r="J470" s="24"/>
     </row>
     <row r="471" spans="1:10">
       <c r="A471" s="4">
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19754,20 +19753,20 @@
       <c r="G471" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H471" s="53">
+      <c r="H471" s="23">
         <v>46081</v>
       </c>
       <c r="I471" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J471" s="54"/>
+      <c r="J471" s="24"/>
     </row>
     <row r="472" spans="1:10">
       <c r="A472" s="4">
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19784,20 +19783,20 @@
       <c r="G472" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H472" s="53">
+      <c r="H472" s="23">
         <v>46081</v>
       </c>
       <c r="I472" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J472" s="54"/>
+      <c r="J472" s="24"/>
     </row>
     <row r="473" spans="1:10">
       <c r="A473" s="4">
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19814,20 +19813,20 @@
       <c r="G473" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H473" s="53">
+      <c r="H473" s="23">
         <v>46081</v>
       </c>
       <c r="I473" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J473" s="54"/>
+      <c r="J473" s="24"/>
     </row>
     <row r="474" spans="1:10">
       <c r="A474" s="4">
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19844,20 +19843,20 @@
       <c r="G474" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H474" s="53">
+      <c r="H474" s="23">
         <v>46081</v>
       </c>
       <c r="I474" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J474" s="54"/>
+      <c r="J474" s="24"/>
     </row>
     <row r="475" spans="1:10">
       <c r="A475" s="4">
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19874,20 +19873,20 @@
       <c r="G475" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H475" s="53">
+      <c r="H475" s="23">
         <v>46081</v>
       </c>
       <c r="I475" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J475" s="54"/>
+      <c r="J475" s="24"/>
     </row>
     <row r="476" spans="1:10">
       <c r="A476" s="4">
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -19904,20 +19903,20 @@
       <c r="G476" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H476" s="53">
+      <c r="H476" s="23">
         <v>46081</v>
       </c>
       <c r="I476" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J476" s="54"/>
+      <c r="J476" s="24"/>
     </row>
     <row r="477" spans="1:10">
       <c r="A477" s="4">
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -19934,20 +19933,20 @@
       <c r="G477" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H477" s="53">
+      <c r="H477" s="23">
         <v>46081</v>
       </c>
       <c r="I477" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J477" s="54"/>
+      <c r="J477" s="24"/>
     </row>
     <row r="478" spans="1:10">
       <c r="A478" s="4">
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -19964,20 +19963,20 @@
       <c r="G478" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H478" s="53">
+      <c r="H478" s="23">
         <v>46081</v>
       </c>
       <c r="I478" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J478" s="54"/>
+      <c r="J478" s="24"/>
     </row>
     <row r="479" spans="1:10">
       <c r="A479" s="4">
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -19994,20 +19993,20 @@
       <c r="G479" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H479" s="53">
+      <c r="H479" s="23">
         <v>46081</v>
       </c>
       <c r="I479" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J479" s="54"/>
+      <c r="J479" s="24"/>
     </row>
     <row r="480" spans="1:10">
       <c r="A480" s="4">
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20024,20 +20023,20 @@
       <c r="G480" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H480" s="53">
+      <c r="H480" s="23">
         <v>46081</v>
       </c>
       <c r="I480" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J480" s="54"/>
+      <c r="J480" s="24"/>
     </row>
     <row r="481" spans="1:10">
       <c r="A481" s="4">
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20054,20 +20053,20 @@
       <c r="G481" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H481" s="53">
+      <c r="H481" s="23">
         <v>46081</v>
       </c>
       <c r="I481" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J481" s="54"/>
+      <c r="J481" s="24"/>
     </row>
     <row r="482" spans="1:10">
       <c r="A482" s="4">
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20084,20 +20083,20 @@
       <c r="G482" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H482" s="53">
+      <c r="H482" s="23">
         <v>46081</v>
       </c>
       <c r="I482" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J482" s="54"/>
+      <c r="J482" s="24"/>
     </row>
     <row r="483" spans="1:10">
       <c r="A483" s="4">
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20114,20 +20113,20 @@
       <c r="G483" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H483" s="53">
+      <c r="H483" s="23">
         <v>46081</v>
       </c>
       <c r="I483" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J483" s="54"/>
+      <c r="J483" s="24"/>
     </row>
     <row r="484" spans="1:10">
       <c r="A484" s="4">
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20144,20 +20143,20 @@
       <c r="G484" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H484" s="53">
+      <c r="H484" s="23">
         <v>46081</v>
       </c>
       <c r="I484" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J484" s="54"/>
+      <c r="J484" s="24"/>
     </row>
     <row r="485" spans="1:10">
       <c r="A485" s="4">
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20174,20 +20173,20 @@
       <c r="G485" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H485" s="53">
+      <c r="H485" s="23">
         <v>46081</v>
       </c>
       <c r="I485" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J485" s="54"/>
+      <c r="J485" s="24"/>
     </row>
     <row r="486" spans="1:10">
       <c r="A486" s="4">
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
@@ -20204,26 +20203,26 @@
       <c r="G486" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H486" s="53">
+      <c r="H486" s="23">
         <v>46081</v>
       </c>
       <c r="I486" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="J486" s="54"/>
+      <c r="J486" s="24"/>
     </row>
     <row r="487" spans="1:10">
       <c r="A487" s="4">
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
@@ -20247,13 +20246,13 @@
         <v>487</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>23</v>
@@ -20365,19 +20364,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C2" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>988</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>990</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
@@ -20385,19 +20384,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C3" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>989</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>991</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
@@ -20405,19 +20404,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>990</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>992</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
@@ -20425,19 +20424,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>991</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>993</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
@@ -20445,19 +20444,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>992</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>994</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
@@ -20465,19 +20464,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>959</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>993</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>960</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>961</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>995</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>962</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
@@ -20984,10 +20983,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>766</v>
+      </c>
+      <c r="E1" t="s">
         <v>767</v>
-      </c>
-      <c r="E1" t="s">
-        <v>768</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -20996,13 +20995,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>768</v>
+      </c>
+      <c r="I1" t="s">
         <v>769</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>770</v>
-      </c>
-      <c r="J1" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -21010,16 +21009,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>387</v>
@@ -21034,7 +21033,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -21042,16 +21041,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>387</v>
@@ -21066,7 +21065,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21074,16 +21073,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>387</v>
@@ -21098,7 +21097,7 @@
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -21106,16 +21105,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>387</v>
@@ -21130,7 +21129,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21138,16 +21137,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>387</v>
@@ -21162,7 +21161,7 @@
         <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21170,16 +21169,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>387</v>
@@ -21194,7 +21193,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -21202,16 +21201,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>387</v>
@@ -21226,7 +21225,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -21234,16 +21233,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>387</v>
@@ -21258,7 +21257,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21266,16 +21265,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>387</v>
@@ -21290,7 +21289,7 @@
         <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -21298,16 +21297,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>387</v>
@@ -21322,7 +21321,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -21330,16 +21329,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="D12" s="1">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>387</v>
@@ -21354,7 +21353,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21362,16 +21361,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>387</v>
@@ -21386,7 +21385,7 @@
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21394,16 +21393,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>387</v>
@@ -21418,7 +21417,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21426,16 +21425,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D15" s="1">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>713</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="D15" s="1">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>714</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>387</v>
@@ -21450,7 +21449,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21458,16 +21457,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D16" s="1">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>387</v>
@@ -21482,7 +21481,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -21490,16 +21489,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>387</v>
@@ -21514,7 +21513,7 @@
         <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -21522,16 +21521,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>387</v>
@@ -21546,7 +21545,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21554,16 +21553,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>387</v>
@@ -21578,7 +21577,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -21586,16 +21585,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D20" s="1">
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>387</v>
@@ -21610,7 +21609,7 @@
         <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21618,16 +21617,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>387</v>
@@ -21642,7 +21641,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -21650,16 +21649,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D22" s="1">
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>387</v>
@@ -21674,7 +21673,7 @@
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -21682,16 +21681,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D23" s="1">
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>387</v>
@@ -21706,7 +21705,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -21714,16 +21713,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D24" s="1">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>387</v>
@@ -21738,7 +21737,7 @@
         <v>15</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -21746,10 +21745,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D25" s="1">
         <v>24</v>
@@ -21776,10 +21775,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D26" s="1">
         <v>25</v>
@@ -21806,10 +21805,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D27" s="1">
         <v>26</v>
@@ -21836,10 +21835,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D28" s="1">
         <v>27</v>
@@ -21866,10 +21865,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D29" s="1">
         <v>28</v>
@@ -21896,10 +21895,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D30" s="1">
         <v>29</v>
@@ -21926,10 +21925,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D31" s="1">
         <v>30</v>
@@ -21956,10 +21955,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D32" s="1">
         <v>31</v>
@@ -21986,10 +21985,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D33" s="1">
         <v>32</v>
@@ -22016,10 +22015,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D34" s="1">
         <v>33</v>
@@ -22046,10 +22045,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D35" s="1">
         <v>34</v>
@@ -22076,10 +22075,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D36" s="1">
         <v>35</v>
@@ -22106,10 +22105,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D37" s="1">
         <v>36</v>
@@ -22136,10 +22135,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D38" s="1">
         <v>37</v>
@@ -22166,19 +22165,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>725</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -22196,19 +22195,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -22226,16 +22225,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>387</v>
@@ -22256,19 +22255,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
@@ -22285,19 +22284,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
@@ -22309,7 +22308,7 @@
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -22317,16 +22316,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
       </c>
       <c r="E44" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F44" t="s">
         <v>667</v>
@@ -22341,7 +22340,7 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -22349,10 +22348,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -22378,10 +22377,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -22407,10 +22406,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -22436,10 +22435,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -22465,10 +22464,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -22494,10 +22493,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -22506,7 +22505,7 @@
         <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G50" t="s">
         <v>32</v>
@@ -22518,7 +22517,7 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -22526,10 +22525,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -22538,7 +22537,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -22550,7 +22549,7 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1">
@@ -22558,13 +22557,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>936</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>71</v>
@@ -22582,7 +22581,7 @@
         <v>618</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="53" spans="1:10">

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F904D76B-3620-478A-89FD-90C07D4B3CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E9D19F-3295-4C43-9276-64E65628E1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4272" uniqueCount="1212">
   <si>
     <t>INDICE</t>
   </si>
@@ -1909,9 +1909,6 @@
     <t>DERHU - SALA 01</t>
   </si>
   <si>
-    <t>REPARADA A ENTRADA USB 10/03/2025; REPARADA MUITO BARULHO E BANDEJA DE ALIMENTAÇÃO DE FOLHAS 05/06/2025;</t>
-  </si>
-  <si>
     <t>U67030J3N175302</t>
   </si>
   <si>
@@ -3668,6 +3665,15 @@
   </si>
   <si>
     <t>ESTAVA NA ARENA LAGOS ELITE RERIRADA PARA MANUTENÇÃO 18/02/2025; INSTALADA NOVAMENTE NA ARENA LAGOS ELITE 20/02/2025; RETIRADA ARENA ELITE BICUIBA 10/03/2026;</t>
+  </si>
+  <si>
+    <t>DIVIDA ATIVA - RECEPCAO</t>
+  </si>
+  <si>
+    <t>CEMITERIO - SÃO SEBASTIAO</t>
+  </si>
+  <si>
+    <t>REPARADA A ENTRADA USB 10/03/2025; REPARADA MUITO BARULHO E BANDEJA DE ALIMENTAÇÃO DE FOLHAS 05/06/2025; INSTALADA NO CEMITERIO SÃO SEBASTIAO ARARUAMA 13/03/2026;</t>
   </si>
 </sst>
 </file>
@@ -5043,7 +5049,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -5055,7 +5061,7 @@
         <v>617</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5075,7 +5081,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -5139,7 +5145,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -5151,7 +5157,7 @@
         <v>617</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5215,7 +5221,7 @@
         <v>617</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5315,7 +5321,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5339,7 +5345,7 @@
         <v>617</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5347,7 +5353,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5359,7 +5365,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -5371,7 +5377,7 @@
         <v>617</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5385,7 +5391,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>19</v>
@@ -5423,7 +5429,7 @@
         <v>363</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5435,7 +5441,7 @@
         <v>617</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5449,7 +5455,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>19</v>
@@ -5484,10 +5490,10 @@
         <v>46</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>1209</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5548,7 +5554,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -5612,7 +5618,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5624,7 +5630,7 @@
         <v>617</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5676,7 +5682,7 @@
         <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5688,7 +5694,7 @@
         <v>617</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5708,7 +5714,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -5906,7 +5912,7 @@
         <v>617</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6022,7 +6028,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -6034,7 +6040,7 @@
         <v>617</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -6115,10 +6121,10 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>14</v>
@@ -6130,7 +6136,7 @@
         <v>617</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -6287,7 +6293,7 @@
         <v>617</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -6606,7 +6612,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6630,7 +6636,7 @@
         <v>617</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -6638,7 +6644,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6662,7 +6668,7 @@
         <v>617</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -6670,7 +6676,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6682,7 +6688,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6694,7 +6700,7 @@
         <v>617</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -6708,7 +6714,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>23</v>
@@ -7187,7 +7193,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>23</v>
@@ -7222,7 +7228,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7234,7 +7240,7 @@
         <v>617</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7469,10 +7475,10 @@
         <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7504,7 +7510,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7533,10 +7539,10 @@
         <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7559,10 +7565,10 @@
         <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7585,10 +7591,10 @@
         <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7611,10 +7617,10 @@
         <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7646,7 +7652,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7675,10 +7681,10 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7707,10 +7713,10 @@
         <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7739,10 +7745,10 @@
         <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7768,7 +7774,7 @@
         <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>23</v>
@@ -7786,7 +7792,7 @@
         <v>617</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -7800,10 +7806,10 @@
         <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7818,7 +7824,7 @@
         <v>617</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -7832,10 +7838,10 @@
         <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7858,10 +7864,10 @@
         <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -7887,7 +7893,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -7902,7 +7908,7 @@
         <v>617</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -7916,10 +7922,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>1059</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>1060</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -8134,7 +8140,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8146,7 +8152,7 @@
         <v>617</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -8320,7 +8326,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8782,7 +8788,7 @@
         <v>617</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -8825,7 +8831,7 @@
         <v>11</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>30</v>
@@ -8843,7 +8849,7 @@
         <v>617</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -8889,13 +8895,13 @@
         <v>11</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8921,13 +8927,13 @@
         <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>32</v>
@@ -9003,7 +9009,7 @@
         <v>617</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -9020,10 +9026,10 @@
         <v>234</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>1052</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9055,7 +9061,7 @@
         <v>23</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>14</v>
@@ -9067,7 +9073,7 @@
         <v>617</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -9087,7 +9093,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9099,7 +9105,7 @@
         <v>617</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -9119,7 +9125,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9131,7 +9137,7 @@
         <v>617</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9151,7 +9157,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9160,10 +9166,10 @@
         <v>45936</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -9183,7 +9189,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9195,7 +9201,7 @@
         <v>617</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9215,7 +9221,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9227,7 +9233,7 @@
         <v>617</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -9279,7 +9285,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9291,7 +9297,7 @@
         <v>617</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -9311,7 +9317,7 @@
         <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9320,10 +9326,10 @@
         <v>45952</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9387,7 +9393,7 @@
         <v>617</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -9407,7 +9413,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9419,7 +9425,7 @@
         <v>617</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -9439,7 +9445,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9451,7 +9457,7 @@
         <v>617</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -9465,13 +9471,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9483,7 +9489,7 @@
         <v>617</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -9503,7 +9509,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9561,13 +9567,13 @@
         <v>88</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9579,7 +9585,7 @@
         <v>617</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -9593,13 +9599,13 @@
         <v>88</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9611,7 +9617,7 @@
         <v>617</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -9619,13 +9625,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>363</v>
@@ -9643,7 +9649,7 @@
         <v>617</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -9739,7 +9745,7 @@
         <v>617</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -9791,7 +9797,7 @@
         <v>13</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>14</v>
@@ -9803,7 +9809,7 @@
         <v>617</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -9823,7 +9829,7 @@
         <v>363</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -9832,10 +9838,10 @@
         <v>45959</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -9937,10 +9943,10 @@
         <v>273</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>23</v>
+        <v>363</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>666</v>
+        <v>1210</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -9952,7 +9958,7 @@
         <v>617</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>623</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -10013,7 +10019,7 @@
         <v>617</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -10077,7 +10083,7 @@
         <v>617</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -10187,7 +10193,7 @@
         <v>13</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -10199,7 +10205,7 @@
         <v>617</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -10216,7 +10222,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10225,7 +10231,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -10239,13 +10245,13 @@
         <v>88</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10304,10 +10310,10 @@
         <v>296</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10333,10 +10339,10 @@
         <v>297</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -10365,7 +10371,7 @@
         <v>23</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>14</v>
@@ -10394,7 +10400,7 @@
         <v>23</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>14</v>
@@ -10423,7 +10429,7 @@
         <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>14</v>
@@ -10452,7 +10458,7 @@
         <v>23</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>14</v>
@@ -10481,7 +10487,7 @@
         <v>23</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>14</v>
@@ -10510,7 +10516,7 @@
         <v>23</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>14</v>
@@ -10539,7 +10545,7 @@
         <v>23</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>14</v>
@@ -10568,7 +10574,7 @@
         <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G180" s="5" t="s">
         <v>14</v>
@@ -10597,7 +10603,7 @@
         <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G181" s="5" t="s">
         <v>14</v>
@@ -10626,7 +10632,7 @@
         <v>23</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G182" s="5" t="s">
         <v>14</v>
@@ -10655,7 +10661,7 @@
         <v>23</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>14</v>
@@ -10684,7 +10690,7 @@
         <v>23</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G184" s="5" t="s">
         <v>14</v>
@@ -10713,7 +10719,7 @@
         <v>23</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G185" s="5" t="s">
         <v>14</v>
@@ -10742,7 +10748,7 @@
         <v>23</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G186" s="5" t="s">
         <v>14</v>
@@ -10771,7 +10777,7 @@
         <v>23</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G187" s="5" t="s">
         <v>14</v>
@@ -10800,7 +10806,7 @@
         <v>23</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G188" s="5" t="s">
         <v>14</v>
@@ -10829,7 +10835,7 @@
         <v>23</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G189" s="5" t="s">
         <v>14</v>
@@ -10858,7 +10864,7 @@
         <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>14</v>
@@ -10887,7 +10893,7 @@
         <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G191" s="5" t="s">
         <v>14</v>
@@ -10916,7 +10922,7 @@
         <v>23</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>14</v>
@@ -10945,7 +10951,7 @@
         <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>14</v>
@@ -11032,10 +11038,10 @@
         <v>325</v>
       </c>
       <c r="E196" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F196" s="4" t="s">
         <v>1051</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>1052</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11047,7 +11053,7 @@
         <v>617</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -11079,7 +11085,7 @@
         <v>617</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -11093,7 +11099,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11111,7 +11117,7 @@
         <v>617</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -11128,10 +11134,10 @@
         <v>327</v>
       </c>
       <c r="E199" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F199" s="4" t="s">
         <v>1051</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>1052</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11143,7 +11149,7 @@
         <v>617</v>
       </c>
       <c r="J199" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -11163,7 +11169,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11195,7 +11201,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11207,7 +11213,7 @@
         <v>617</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -11285,13 +11291,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11303,7 +11309,7 @@
         <v>617</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -11323,7 +11329,7 @@
         <v>23</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>32</v>
@@ -11335,7 +11341,7 @@
         <v>617</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -11355,7 +11361,7 @@
         <v>23</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>14</v>
@@ -11387,7 +11393,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11399,7 +11405,7 @@
         <v>617</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -11419,7 +11425,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11431,7 +11437,7 @@
         <v>617</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -11451,7 +11457,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11463,7 +11469,7 @@
         <v>617</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -11483,7 +11489,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
@@ -11495,7 +11501,7 @@
         <v>617</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -11591,7 +11597,7 @@
         <v>617</v>
       </c>
       <c r="J213" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -11655,7 +11661,7 @@
         <v>617</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -11675,7 +11681,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11687,7 +11693,7 @@
         <v>617</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -11739,7 +11745,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11748,10 +11754,10 @@
         <v>45933</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -11771,7 +11777,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11783,7 +11789,7 @@
         <v>617</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -11803,7 +11809,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11815,7 +11821,7 @@
         <v>617</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -11867,7 +11873,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -11899,7 +11905,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -11911,7 +11917,7 @@
         <v>617</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -11957,13 +11963,13 @@
         <v>11</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>14</v>
@@ -11975,7 +11981,7 @@
         <v>617</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -12007,7 +12013,7 @@
         <v>617</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -12027,7 +12033,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12039,7 +12045,7 @@
         <v>617</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -12091,7 +12097,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12103,7 +12109,7 @@
         <v>617</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -12123,7 +12129,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12155,7 +12161,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12167,7 +12173,7 @@
         <v>617</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -12187,7 +12193,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12196,10 +12202,10 @@
         <v>44127</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -12219,7 +12225,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12231,7 +12237,7 @@
         <v>617</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -12251,7 +12257,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12263,7 +12269,7 @@
         <v>617</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12283,7 +12289,7 @@
         <v>363</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G235" s="14" t="s">
         <v>14</v>
@@ -12295,7 +12301,7 @@
         <v>617</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12312,10 +12318,10 @@
         <v>616</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12342,10 +12348,10 @@
         <v>595</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G237" s="14" t="s">
         <v>14</v>
@@ -12357,7 +12363,7 @@
         <v>617</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -12377,7 +12383,7 @@
         <v>19</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G238" s="5" t="s">
         <v>14</v>
@@ -12389,7 +12395,7 @@
         <v>617</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -12421,7 +12427,7 @@
         <v>617</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -12441,7 +12447,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12453,7 +12459,7 @@
         <v>617</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -12461,7 +12467,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12473,7 +12479,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12531,10 +12537,10 @@
         <v>385</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -12546,7 +12552,7 @@
         <v>617</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -12560,7 +12566,7 @@
         <v>88</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>32</v>
@@ -12578,7 +12584,7 @@
         <v>617</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -12627,7 +12633,7 @@
         <v>390</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>391</v>
@@ -12653,10 +12659,10 @@
         <v>11</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>393</v>
@@ -12688,7 +12694,7 @@
         <v>394</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>395</v>
@@ -12717,7 +12723,7 @@
         <v>396</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>397</v>
@@ -12743,7 +12749,7 @@
         <v>88</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -12761,7 +12767,7 @@
         <v>617</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -12781,7 +12787,7 @@
         <v>23</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>32</v>
@@ -12793,7 +12799,7 @@
         <v>617</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -12845,7 +12851,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -12941,7 +12947,7 @@
         <v>23</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>14</v>
@@ -12953,7 +12959,7 @@
         <v>617</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -12985,7 +12991,7 @@
         <v>617</v>
       </c>
       <c r="J257" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -13017,7 +13023,7 @@
         <v>617</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -13081,7 +13087,7 @@
         <v>617</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -13101,7 +13107,7 @@
         <v>19</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>14</v>
@@ -13194,10 +13200,10 @@
         <v>421</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13357,7 +13363,7 @@
         <v>363</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13369,7 +13375,7 @@
         <v>617</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -13485,7 +13491,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13581,7 +13587,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13613,7 +13619,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13805,7 +13811,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13814,10 +13820,10 @@
         <v>45597</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -14381,7 +14387,7 @@
         <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -14425,7 +14431,7 @@
         <v>617</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -14445,7 +14451,7 @@
         <v>80</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -14457,7 +14463,7 @@
         <v>617</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -14477,7 +14483,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14489,7 +14495,7 @@
         <v>617</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -14509,7 +14515,7 @@
         <v>80</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>14</v>
@@ -14521,7 +14527,7 @@
         <v>617</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -14701,7 +14707,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14713,7 +14719,7 @@
         <v>617</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -14861,7 +14867,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14873,7 +14879,7 @@
         <v>617</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -15143,13 +15149,13 @@
         <v>11</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15161,7 +15167,7 @@
         <v>617</v>
       </c>
       <c r="J325" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -15175,13 +15181,13 @@
         <v>11</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E326" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15193,7 +15199,7 @@
         <v>617</v>
       </c>
       <c r="J326" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -15207,13 +15213,13 @@
         <v>11</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E327" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15225,7 +15231,7 @@
         <v>617</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -15239,13 +15245,13 @@
         <v>11</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15257,7 +15263,7 @@
         <v>617</v>
       </c>
       <c r="J328" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -15271,13 +15277,13 @@
         <v>11</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15289,7 +15295,7 @@
         <v>617</v>
       </c>
       <c r="J329" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -15303,13 +15309,13 @@
         <v>11</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15321,7 +15327,7 @@
         <v>617</v>
       </c>
       <c r="J330" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -15335,13 +15341,13 @@
         <v>11</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -15353,7 +15359,7 @@
         <v>617</v>
       </c>
       <c r="J331" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -15367,7 +15373,7 @@
         <v>11</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>71</v>
@@ -15385,7 +15391,7 @@
         <v>617</v>
       </c>
       <c r="J332" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -15399,13 +15405,13 @@
         <v>11</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15417,7 +15423,7 @@
         <v>617</v>
       </c>
       <c r="J333" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -15431,13 +15437,13 @@
         <v>11</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15449,7 +15455,7 @@
         <v>617</v>
       </c>
       <c r="J334" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -15463,13 +15469,13 @@
         <v>11</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15481,7 +15487,7 @@
         <v>617</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -15495,13 +15501,13 @@
         <v>11</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15513,7 +15519,7 @@
         <v>617</v>
       </c>
       <c r="J336" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -15527,13 +15533,13 @@
         <v>11</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -15545,7 +15551,7 @@
         <v>617</v>
       </c>
       <c r="J337" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -15559,13 +15565,13 @@
         <v>11</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -15577,7 +15583,7 @@
         <v>617</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -15591,13 +15597,13 @@
         <v>11</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -15609,7 +15615,7 @@
         <v>617</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -15623,13 +15629,13 @@
         <v>11</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -15641,7 +15647,7 @@
         <v>617</v>
       </c>
       <c r="J340" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -15655,13 +15661,13 @@
         <v>11</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -15673,7 +15679,7 @@
         <v>617</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -15687,13 +15693,13 @@
         <v>11</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -15705,7 +15711,7 @@
         <v>617</v>
       </c>
       <c r="J342" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -15719,13 +15725,13 @@
         <v>11</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -15737,7 +15743,7 @@
         <v>617</v>
       </c>
       <c r="J343" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -15789,7 +15795,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15801,7 +15807,7 @@
         <v>617</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -15809,10 +15815,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C346" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="D346" s="14">
         <v>22011316</v>
@@ -15833,7 +15839,7 @@
         <v>617</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -15847,7 +15853,7 @@
         <v>11</v>
       </c>
       <c r="D347" s="38" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>80</v>
@@ -15865,7 +15871,7 @@
         <v>617</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -15879,7 +15885,7 @@
         <v>11</v>
       </c>
       <c r="D348" s="38" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>80</v>
@@ -15897,7 +15903,7 @@
         <v>617</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -15911,13 +15917,13 @@
         <v>11</v>
       </c>
       <c r="D349" s="38" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -15929,7 +15935,7 @@
         <v>617</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -15943,13 +15949,13 @@
         <v>11</v>
       </c>
       <c r="D350" s="38" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -15961,7 +15967,7 @@
         <v>617</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -15975,13 +15981,13 @@
         <v>11</v>
       </c>
       <c r="D351" s="38" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -15993,7 +15999,7 @@
         <v>617</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -16007,13 +16013,13 @@
         <v>11</v>
       </c>
       <c r="D352" s="38" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
@@ -16025,7 +16031,7 @@
         <v>617</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -16039,7 +16045,7 @@
         <v>11</v>
       </c>
       <c r="D353" s="38" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>32</v>
@@ -16057,7 +16063,7 @@
         <v>617</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -16071,13 +16077,13 @@
         <v>11</v>
       </c>
       <c r="D354" s="38" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
@@ -16089,7 +16095,7 @@
         <v>617</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -16103,13 +16109,13 @@
         <v>11</v>
       </c>
       <c r="D355" s="38" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
@@ -16121,7 +16127,7 @@
         <v>617</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -16135,13 +16141,13 @@
         <v>11</v>
       </c>
       <c r="D356" s="38" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
@@ -16153,7 +16159,7 @@
         <v>617</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -16167,13 +16173,13 @@
         <v>11</v>
       </c>
       <c r="D357" s="38" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>14</v>
@@ -16185,7 +16191,7 @@
         <v>617</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -16199,13 +16205,13 @@
         <v>11</v>
       </c>
       <c r="D358" s="38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>14</v>
@@ -16217,7 +16223,7 @@
         <v>617</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -16231,13 +16237,13 @@
         <v>11</v>
       </c>
       <c r="D359" s="38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>14</v>
@@ -16249,7 +16255,7 @@
         <v>617</v>
       </c>
       <c r="J359" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -16263,13 +16269,13 @@
         <v>11</v>
       </c>
       <c r="D360" s="38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
@@ -16281,7 +16287,7 @@
         <v>617</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -16295,13 +16301,13 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
@@ -16313,7 +16319,7 @@
         <v>617</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -16327,7 +16333,7 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
@@ -16345,7 +16351,7 @@
         <v>617</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -16359,13 +16365,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -16377,7 +16383,7 @@
         <v>617</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -16391,13 +16397,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16409,7 +16415,7 @@
         <v>617</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -16423,13 +16429,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16441,7 +16447,7 @@
         <v>617</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -16455,13 +16461,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16470,10 +16476,10 @@
         <v>45968</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -16487,13 +16493,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16502,10 +16508,10 @@
         <v>45968</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -16519,13 +16525,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16537,7 +16543,7 @@
         <v>617</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -16551,13 +16557,13 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16566,10 +16572,10 @@
         <v>45968</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -16583,13 +16589,13 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
@@ -16598,10 +16604,10 @@
         <v>45968</v>
       </c>
       <c r="I370" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -16615,13 +16621,13 @@
         <v>11</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16630,10 +16636,10 @@
         <v>45971</v>
       </c>
       <c r="I371" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -16641,19 +16647,19 @@
         <v>371</v>
       </c>
       <c r="B372" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -16665,7 +16671,7 @@
         <v>617</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -16673,13 +16679,13 @@
         <v>372</v>
       </c>
       <c r="B373" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>363</v>
@@ -16697,7 +16703,7 @@
         <v>617</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -16705,19 +16711,19 @@
         <v>373</v>
       </c>
       <c r="B374" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
@@ -16729,7 +16735,7 @@
         <v>617</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -16737,19 +16743,19 @@
         <v>374</v>
       </c>
       <c r="B375" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D375" s="38" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
@@ -16761,7 +16767,7 @@
         <v>617</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -16769,19 +16775,19 @@
         <v>375</v>
       </c>
       <c r="B376" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D376" s="38" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>14</v>
@@ -16799,19 +16805,19 @@
         <v>376</v>
       </c>
       <c r="B377" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D377" s="39" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
@@ -16823,7 +16829,7 @@
         <v>617</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -16831,19 +16837,19 @@
         <v>377</v>
       </c>
       <c r="B378" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D378" s="38" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16861,19 +16867,19 @@
         <v>378</v>
       </c>
       <c r="B379" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D379" s="38" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>14</v>
@@ -16891,19 +16897,19 @@
         <v>379</v>
       </c>
       <c r="B380" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D380" s="39" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>14</v>
@@ -16915,7 +16921,7 @@
         <v>617</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -16923,19 +16929,19 @@
         <v>380</v>
       </c>
       <c r="B381" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D381" s="39" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -16947,7 +16953,7 @@
         <v>617</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -16955,19 +16961,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D382" s="38" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -16979,7 +16985,7 @@
         <v>617</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -16987,19 +16993,19 @@
         <v>382</v>
       </c>
       <c r="B383" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D383" s="38" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17011,7 +17017,7 @@
         <v>617</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -17019,13 +17025,13 @@
         <v>383</v>
       </c>
       <c r="B384" s="25" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D384" s="38" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>71</v>
@@ -17043,7 +17049,7 @@
         <v>617</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -17051,19 +17057,19 @@
         <v>384</v>
       </c>
       <c r="B385" s="26" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D385" s="39" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>14</v>
@@ -17075,7 +17081,7 @@
         <v>617</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -17089,7 +17095,7 @@
         <v>11</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>13</v>
@@ -17107,7 +17113,7 @@
         <v>617</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -17121,13 +17127,13 @@
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
@@ -17139,7 +17145,7 @@
         <v>617</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -17153,13 +17159,13 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
@@ -17171,7 +17177,7 @@
         <v>617</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17185,13 +17191,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17200,10 +17206,10 @@
         <v>45960</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17217,13 +17223,13 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>14</v>
@@ -17235,7 +17241,7 @@
         <v>617</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -17249,7 +17255,7 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
@@ -17267,7 +17273,7 @@
         <v>617</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -17281,13 +17287,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17299,7 +17305,7 @@
         <v>617</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17313,13 +17319,13 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17331,7 +17337,7 @@
         <v>617</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17345,13 +17351,13 @@
         <v>11</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17363,7 +17369,7 @@
         <v>617</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -17371,19 +17377,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>14</v>
@@ -17395,7 +17401,7 @@
         <v>617</v>
       </c>
       <c r="J395" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -17403,19 +17409,19 @@
         <v>395</v>
       </c>
       <c r="B396" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F396" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>14</v>
@@ -17427,7 +17433,7 @@
         <v>617</v>
       </c>
       <c r="J396" s="24" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -17435,19 +17441,19 @@
         <v>396</v>
       </c>
       <c r="B397" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>14</v>
@@ -17459,7 +17465,7 @@
         <v>617</v>
       </c>
       <c r="J397" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -17467,19 +17473,19 @@
         <v>397</v>
       </c>
       <c r="B398" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>14</v>
@@ -17491,7 +17497,7 @@
         <v>617</v>
       </c>
       <c r="J398" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -17499,19 +17505,19 @@
         <v>398</v>
       </c>
       <c r="B399" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>14</v>
@@ -17523,7 +17529,7 @@
         <v>617</v>
       </c>
       <c r="J399" s="24" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -17531,19 +17537,19 @@
         <v>399</v>
       </c>
       <c r="B400" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>14</v>
@@ -17555,7 +17561,7 @@
         <v>617</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -17563,19 +17569,19 @@
         <v>400</v>
       </c>
       <c r="B401" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F401" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G401" s="2" t="s">
         <v>14</v>
@@ -17587,7 +17593,7 @@
         <v>617</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -17595,19 +17601,19 @@
         <v>401</v>
       </c>
       <c r="B402" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>14</v>
@@ -17619,7 +17625,7 @@
         <v>617</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -17627,19 +17633,19 @@
         <v>402</v>
       </c>
       <c r="B403" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
@@ -17651,7 +17657,7 @@
         <v>617</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -17659,19 +17665,19 @@
         <v>403</v>
       </c>
       <c r="B404" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -17683,7 +17689,7 @@
         <v>617</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -17691,19 +17697,19 @@
         <v>404</v>
       </c>
       <c r="B405" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17715,7 +17721,7 @@
         <v>617</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -17723,19 +17729,19 @@
         <v>405</v>
       </c>
       <c r="B406" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -17747,7 +17753,7 @@
         <v>617</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -17755,19 +17761,19 @@
         <v>406</v>
       </c>
       <c r="B407" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17779,7 +17785,7 @@
         <v>617</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -17787,19 +17793,19 @@
         <v>407</v>
       </c>
       <c r="B408" s="28" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>14</v>
@@ -17811,7 +17817,7 @@
         <v>617</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -17819,19 +17825,19 @@
         <v>408</v>
       </c>
       <c r="B409" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>14</v>
@@ -17843,7 +17849,7 @@
         <v>617</v>
       </c>
       <c r="J409" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -17851,19 +17857,19 @@
         <v>409</v>
       </c>
       <c r="B410" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>14</v>
@@ -17875,7 +17881,7 @@
         <v>617</v>
       </c>
       <c r="J410" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -17883,19 +17889,19 @@
         <v>410</v>
       </c>
       <c r="B411" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>14</v>
@@ -17907,7 +17913,7 @@
         <v>617</v>
       </c>
       <c r="J411" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -17915,19 +17921,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>14</v>
@@ -17939,7 +17945,7 @@
         <v>617</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -17947,19 +17953,19 @@
         <v>412</v>
       </c>
       <c r="B413" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>14</v>
@@ -17971,7 +17977,7 @@
         <v>617</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -17979,19 +17985,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>14</v>
@@ -18003,7 +18009,7 @@
         <v>617</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -18011,19 +18017,19 @@
         <v>414</v>
       </c>
       <c r="B415" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
@@ -18035,7 +18041,7 @@
         <v>617</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -18043,19 +18049,19 @@
         <v>415</v>
       </c>
       <c r="B416" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -18067,7 +18073,7 @@
         <v>617</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -18075,13 +18081,13 @@
         <v>416</v>
       </c>
       <c r="B417" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>19</v>
@@ -18096,10 +18102,10 @@
         <v>45960</v>
       </c>
       <c r="I417" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -18107,19 +18113,19 @@
         <v>417</v>
       </c>
       <c r="B418" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -18131,7 +18137,7 @@
         <v>617</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -18139,19 +18145,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18163,7 +18169,7 @@
         <v>617</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -18171,19 +18177,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18195,7 +18201,7 @@
         <v>617</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -18203,19 +18209,19 @@
         <v>420</v>
       </c>
       <c r="B421" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18227,7 +18233,7 @@
         <v>617</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -18235,19 +18241,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18259,7 +18265,7 @@
         <v>617</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -18267,19 +18273,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -18291,7 +18297,7 @@
         <v>617</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -18299,19 +18305,19 @@
         <v>423</v>
       </c>
       <c r="B424" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -18323,7 +18329,7 @@
         <v>617</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -18331,19 +18337,19 @@
         <v>424</v>
       </c>
       <c r="B425" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18352,10 +18358,10 @@
         <v>46037</v>
       </c>
       <c r="I425" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -18363,19 +18369,19 @@
         <v>425</v>
       </c>
       <c r="B426" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -18393,19 +18399,19 @@
         <v>426</v>
       </c>
       <c r="B427" s="29" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C427" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>14</v>
@@ -18417,7 +18423,7 @@
         <v>617</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -18425,19 +18431,19 @@
         <v>427</v>
       </c>
       <c r="B428" s="40" t="s">
+        <v>936</v>
+      </c>
+      <c r="C428" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D428" s="5" t="s">
         <v>937</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D428" s="5" t="s">
-        <v>938</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
@@ -18449,7 +18455,7 @@
         <v>617</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18457,19 +18463,19 @@
         <v>428</v>
       </c>
       <c r="B429" s="40" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18481,7 +18487,7 @@
         <v>617</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18489,19 +18495,19 @@
         <v>429</v>
       </c>
       <c r="B430" s="40" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18513,7 +18519,7 @@
         <v>617</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18521,19 +18527,19 @@
         <v>430</v>
       </c>
       <c r="B431" s="40" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G431" s="2" t="s">
         <v>14</v>
@@ -18545,7 +18551,7 @@
         <v>617</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18553,19 +18559,19 @@
         <v>431</v>
       </c>
       <c r="B432" s="40" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>14</v>
@@ -18577,7 +18583,7 @@
         <v>617</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -18585,19 +18591,19 @@
         <v>432</v>
       </c>
       <c r="B433" s="31" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>32</v>
@@ -18609,7 +18615,7 @@
         <v>617</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -18617,19 +18623,19 @@
         <v>433</v>
       </c>
       <c r="B434" s="31" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
@@ -18641,7 +18647,7 @@
         <v>617</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -18649,19 +18655,19 @@
         <v>434</v>
       </c>
       <c r="B435" s="31" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18673,7 +18679,7 @@
         <v>617</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -18681,19 +18687,19 @@
         <v>435</v>
       </c>
       <c r="B436" s="31" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18705,7 +18711,7 @@
         <v>617</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -18713,19 +18719,19 @@
         <v>436</v>
       </c>
       <c r="B437" s="31" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>363</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
@@ -18737,7 +18743,7 @@
         <v>617</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -18745,16 +18751,16 @@
         <v>437</v>
       </c>
       <c r="B438" s="52" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>386</v>
@@ -18769,7 +18775,7 @@
         <v>617</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -18777,19 +18783,19 @@
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>32</v>
@@ -18801,7 +18807,7 @@
         <v>617</v>
       </c>
       <c r="J439" s="3" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -18809,19 +18815,19 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>32</v>
@@ -18839,19 +18845,19 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>32</v>
@@ -18869,19 +18875,19 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>32</v>
@@ -18899,19 +18905,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
@@ -18929,7 +18935,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
@@ -18941,7 +18947,7 @@
         <v>23</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
@@ -18959,7 +18965,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -18971,7 +18977,7 @@
         <v>23</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>32</v>
@@ -18989,7 +18995,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19001,7 +19007,7 @@
         <v>23</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>32</v>
@@ -19019,7 +19025,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19031,7 +19037,7 @@
         <v>23</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>32</v>
@@ -19049,7 +19055,7 @@
         <v>447</v>
       </c>
       <c r="B448" s="53" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>88</v>
@@ -19061,7 +19067,7 @@
         <v>23</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
@@ -19079,19 +19085,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
@@ -19100,7 +19106,7 @@
         <v>46091</v>
       </c>
       <c r="I449" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="J449" s="24"/>
     </row>
@@ -19109,7 +19115,7 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
@@ -19121,7 +19127,7 @@
         <v>23</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>32</v>
@@ -19139,7 +19145,7 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
@@ -19151,7 +19157,7 @@
         <v>23</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19169,7 +19175,7 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
@@ -19181,7 +19187,7 @@
         <v>23</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>32</v>
@@ -19199,7 +19205,7 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
@@ -19211,7 +19217,7 @@
         <v>23</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
@@ -19229,7 +19235,7 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
@@ -19241,7 +19247,7 @@
         <v>23</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
@@ -19259,7 +19265,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
@@ -19271,7 +19277,7 @@
         <v>23</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>32</v>
@@ -19289,7 +19295,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
@@ -19301,7 +19307,7 @@
         <v>23</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>32</v>
@@ -19319,7 +19325,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
@@ -19331,7 +19337,7 @@
         <v>23</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>32</v>
@@ -19349,7 +19355,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
@@ -19361,7 +19367,7 @@
         <v>23</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>32</v>
@@ -19379,7 +19385,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19391,7 +19397,7 @@
         <v>23</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>32</v>
@@ -19409,7 +19415,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19421,7 +19427,7 @@
         <v>23</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>32</v>
@@ -19439,7 +19445,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19451,7 +19457,7 @@
         <v>23</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>32</v>
@@ -19469,7 +19475,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19481,7 +19487,7 @@
         <v>23</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>32</v>
@@ -19499,7 +19505,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19511,7 +19517,7 @@
         <v>23</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>32</v>
@@ -19529,7 +19535,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19541,7 +19547,7 @@
         <v>23</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>32</v>
@@ -19559,7 +19565,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19571,7 +19577,7 @@
         <v>23</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>32</v>
@@ -19589,7 +19595,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19601,7 +19607,7 @@
         <v>23</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>32</v>
@@ -19619,7 +19625,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19631,7 +19637,7 @@
         <v>23</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>32</v>
@@ -19649,7 +19655,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19661,7 +19667,7 @@
         <v>23</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>32</v>
@@ -19679,7 +19685,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19691,7 +19697,7 @@
         <v>23</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>32</v>
@@ -19709,7 +19715,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19721,7 +19727,7 @@
         <v>23</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>32</v>
@@ -19739,7 +19745,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19751,7 +19757,7 @@
         <v>23</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>32</v>
@@ -19769,7 +19775,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19781,7 +19787,7 @@
         <v>23</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G472" s="2" t="s">
         <v>32</v>
@@ -19799,7 +19805,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19811,7 +19817,7 @@
         <v>23</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>32</v>
@@ -19829,7 +19835,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19841,7 +19847,7 @@
         <v>23</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>32</v>
@@ -19859,7 +19865,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19871,7 +19877,7 @@
         <v>23</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G475" s="2" t="s">
         <v>32</v>
@@ -19889,7 +19895,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -19901,7 +19907,7 @@
         <v>23</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G476" s="2" t="s">
         <v>32</v>
@@ -19919,7 +19925,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -19931,7 +19937,7 @@
         <v>23</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G477" s="2" t="s">
         <v>32</v>
@@ -19949,7 +19955,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -19961,7 +19967,7 @@
         <v>23</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G478" s="2" t="s">
         <v>32</v>
@@ -19979,7 +19985,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -19991,7 +19997,7 @@
         <v>23</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>32</v>
@@ -20009,7 +20015,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20021,7 +20027,7 @@
         <v>23</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G480" s="2" t="s">
         <v>32</v>
@@ -20039,7 +20045,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20051,7 +20057,7 @@
         <v>23</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G481" s="2" t="s">
         <v>32</v>
@@ -20069,7 +20075,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20081,7 +20087,7 @@
         <v>23</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G482" s="2" t="s">
         <v>32</v>
@@ -20099,7 +20105,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20111,7 +20117,7 @@
         <v>23</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>32</v>
@@ -20129,7 +20135,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20141,7 +20147,7 @@
         <v>23</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G484" s="2" t="s">
         <v>32</v>
@@ -20159,7 +20165,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20171,7 +20177,7 @@
         <v>23</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G485" s="2" t="s">
         <v>32</v>
@@ -20189,7 +20195,7 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
@@ -20201,7 +20207,7 @@
         <v>23</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G486" s="2" t="s">
         <v>32</v>
@@ -20219,19 +20225,19 @@
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G487" s="2" t="s">
         <v>32</v>
@@ -20249,19 +20255,19 @@
         <v>487</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D488" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G488" s="2" t="s">
         <v>32</v>
@@ -20367,19 +20373,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B2" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C2" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>984</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>985</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
@@ -20387,19 +20393,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="C3" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>985</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>986</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
@@ -20407,19 +20413,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="C4" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>986</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>987</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
@@ -20427,19 +20433,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B5" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C5" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>987</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>988</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
@@ -20447,19 +20453,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B6" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="C6" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>988</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>989</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
@@ -20467,19 +20473,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
+        <v>953</v>
+      </c>
+      <c r="B7" s="42" t="s">
         <v>954</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="C7" s="42" t="s">
         <v>955</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>989</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>956</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>990</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>957</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
@@ -20986,10 +20992,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>764</v>
+      </c>
+      <c r="E1" t="s">
         <v>765</v>
-      </c>
-      <c r="E1" t="s">
-        <v>766</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -20998,13 +21004,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>766</v>
+      </c>
+      <c r="I1" t="s">
         <v>767</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>768</v>
-      </c>
-      <c r="J1" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -21012,16 +21018,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>386</v>
@@ -21036,7 +21042,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -21044,16 +21050,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>386</v>
@@ -21068,7 +21074,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21076,16 +21082,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>386</v>
@@ -21100,7 +21106,7 @@
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -21108,16 +21114,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>386</v>
@@ -21132,7 +21138,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21140,16 +21146,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>386</v>
@@ -21164,7 +21170,7 @@
         <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21172,16 +21178,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>386</v>
@@ -21196,7 +21202,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -21204,16 +21210,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>386</v>
@@ -21228,7 +21234,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -21236,16 +21242,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>386</v>
@@ -21260,7 +21266,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21268,16 +21274,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>386</v>
@@ -21292,7 +21298,7 @@
         <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -21300,16 +21306,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>386</v>
@@ -21324,7 +21330,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -21332,16 +21338,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D12" s="1">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>386</v>
@@ -21356,7 +21362,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21364,16 +21370,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>386</v>
@@ -21388,7 +21394,7 @@
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21396,16 +21402,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>386</v>
@@ -21420,7 +21426,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21428,16 +21434,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D15" s="1">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>711</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="D15" s="1">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>712</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>386</v>
@@ -21452,7 +21458,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21460,16 +21466,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D16" s="1">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>386</v>
@@ -21484,7 +21490,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -21492,16 +21498,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>386</v>
@@ -21516,7 +21522,7 @@
         <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -21524,16 +21530,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>386</v>
@@ -21548,7 +21554,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21556,16 +21562,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>386</v>
@@ -21580,7 +21586,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -21588,16 +21594,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D20" s="1">
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>386</v>
@@ -21612,7 +21618,7 @@
         <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21620,16 +21626,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>386</v>
@@ -21644,7 +21650,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -21652,16 +21658,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D22" s="1">
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>386</v>
@@ -21676,7 +21682,7 @@
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -21684,16 +21690,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D23" s="1">
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>386</v>
@@ -21708,7 +21714,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -21716,16 +21722,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D24" s="1">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>386</v>
@@ -21740,7 +21746,7 @@
         <v>15</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -21748,10 +21754,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D25" s="1">
         <v>24</v>
@@ -21760,7 +21766,7 @@
         <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -21778,10 +21784,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D26" s="1">
         <v>25</v>
@@ -21790,7 +21796,7 @@
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>32</v>
@@ -21808,10 +21814,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D27" s="1">
         <v>26</v>
@@ -21820,7 +21826,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
@@ -21838,10 +21844,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D28" s="1">
         <v>27</v>
@@ -21850,7 +21856,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -21868,10 +21874,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D29" s="1">
         <v>28</v>
@@ -21880,7 +21886,7 @@
         <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -21898,10 +21904,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D30" s="1">
         <v>29</v>
@@ -21910,7 +21916,7 @@
         <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -21928,10 +21934,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D31" s="1">
         <v>30</v>
@@ -21940,7 +21946,7 @@
         <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -21958,10 +21964,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D32" s="1">
         <v>31</v>
@@ -21970,7 +21976,7 @@
         <v>23</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -21988,10 +21994,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D33" s="1">
         <v>32</v>
@@ -22000,7 +22006,7 @@
         <v>23</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -22018,10 +22024,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D34" s="1">
         <v>33</v>
@@ -22030,7 +22036,7 @@
         <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>32</v>
@@ -22048,10 +22054,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D35" s="1">
         <v>34</v>
@@ -22060,7 +22066,7 @@
         <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>32</v>
@@ -22078,10 +22084,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D36" s="1">
         <v>35</v>
@@ -22090,7 +22096,7 @@
         <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
@@ -22108,10 +22114,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D37" s="1">
         <v>36</v>
@@ -22120,7 +22126,7 @@
         <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>32</v>
@@ -22138,10 +22144,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D38" s="1">
         <v>37</v>
@@ -22150,7 +22156,7 @@
         <v>23</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>32</v>
@@ -22168,19 +22174,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>723</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -22198,19 +22204,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -22228,16 +22234,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>386</v>
@@ -22258,19 +22264,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
@@ -22287,19 +22293,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
@@ -22311,7 +22317,7 @@
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -22319,19 +22325,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>958</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>959</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>960</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
       </c>
       <c r="E44" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F44" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G44" t="s">
         <v>32</v>
@@ -22343,7 +22349,7 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -22351,10 +22357,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>958</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>959</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>960</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -22363,7 +22369,7 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G45" t="s">
         <v>32</v>
@@ -22380,10 +22386,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -22392,7 +22398,7 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G46" t="s">
         <v>32</v>
@@ -22409,10 +22415,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -22421,7 +22427,7 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G47" t="s">
         <v>32</v>
@@ -22438,10 +22444,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -22450,7 +22456,7 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G48" t="s">
         <v>32</v>
@@ -22467,10 +22473,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -22479,7 +22485,7 @@
         <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G49" t="s">
         <v>32</v>
@@ -22496,10 +22502,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -22508,7 +22514,7 @@
         <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G50" t="s">
         <v>32</v>
@@ -22520,7 +22526,7 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -22528,10 +22534,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -22540,7 +22546,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -22552,7 +22558,7 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1">
@@ -22560,13 +22566,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>931</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>71</v>
@@ -22584,7 +22590,7 @@
         <v>617</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="53" spans="1:10">

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\files\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824DA29A-03E8-4CA1-9C65-1A2694A156CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C2D1A8-BEF6-4EDE-AA2D-6774CE13CC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1225">
   <si>
     <t>INDICE</t>
   </si>
@@ -3067,9 +3067,6 @@
     <t>UPA - SALA VERMELHA</t>
   </si>
   <si>
-    <t>RESERVA 7</t>
-  </si>
-  <si>
     <t>INSTALADA SAUDE COLETIVA ARARUAMA 30/10/2025; RETIRADA 14/11/2025 DA SAUDE; INSTALAÇÃO NO PAÇO DIVIDA ATIVA 05/01/2026;</t>
   </si>
   <si>
@@ -3707,6 +3704,15 @@
   </si>
   <si>
     <t>E.M. PROFª. NAIR VALADARES</t>
+  </si>
+  <si>
+    <t>SEMFAT-RESERVA-2</t>
+  </si>
+  <si>
+    <t>XC75051352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.B.M. PROF. JOAO RAPOSO </t>
   </si>
 </sst>
 </file>
@@ -5301,7 +5307,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>31</v>
@@ -5408,7 +5414,7 @@
         <v>593</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5556,7 +5562,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5614,10 +5620,10 @@
         <v>49</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1026</v>
+        <v>25</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>14</v>
@@ -5681,7 +5687,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5693,7 +5699,7 @@
         <v>593</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5742,10 +5748,10 @@
         <v>56</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>25</v>
+        <v>1025</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5757,7 +5763,7 @@
         <v>593</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5777,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -6751,7 +6757,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -7291,7 +7297,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7840,10 +7846,10 @@
         <v>688</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>23</v>
+        <v>1004</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>25</v>
+        <v>1222</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -8203,7 +8209,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8215,7 +8221,7 @@
         <v>593</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -8389,7 +8395,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8871,7 +8877,7 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -8897,10 +8903,10 @@
         <v>661</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>31</v>
+        <v>1145</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>32</v>
@@ -8964,7 +8970,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8993,10 +8999,10 @@
         <v>693</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>1004</v>
+        <v>30</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>1009</v>
+        <v>31</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>32</v>
@@ -9156,7 +9162,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9188,7 +9194,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9200,7 +9206,7 @@
         <v>593</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9220,7 +9226,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9252,7 +9258,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9264,7 +9270,7 @@
         <v>593</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9284,7 +9290,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9348,7 +9354,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9360,7 +9366,7 @@
         <v>593</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -9392,7 +9398,7 @@
         <v>671</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9444,7 +9450,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>14</v>
@@ -9476,7 +9482,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9508,7 +9514,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9520,7 +9526,7 @@
         <v>593</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -9534,13 +9540,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9552,7 +9558,7 @@
         <v>593</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -9572,7 +9578,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9604,7 +9610,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>14</v>
@@ -9636,7 +9642,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9668,7 +9674,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9796,7 +9802,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>14</v>
@@ -9808,7 +9814,7 @@
         <v>593</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -10009,7 +10015,7 @@
         <v>359</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -10021,7 +10027,7 @@
         <v>593</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -10146,7 +10152,7 @@
         <v>593</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -10356,7 +10362,7 @@
         <v>593</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -11180,7 +11186,7 @@
         <v>593</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -11232,7 +11238,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11264,7 +11270,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11276,7 +11282,7 @@
         <v>593</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -11360,7 +11366,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11389,10 +11395,10 @@
         <v>332</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>627</v>
+        <v>31</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>32</v>
@@ -11404,7 +11410,7 @@
         <v>593</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -11456,7 +11462,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11468,7 +11474,7 @@
         <v>593</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -11488,7 +11494,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11520,7 +11526,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11532,7 +11538,7 @@
         <v>593</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -11724,7 +11730,7 @@
         <v>593</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -11744,7 +11750,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11756,7 +11762,7 @@
         <v>593</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -11808,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11840,7 +11846,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11872,7 +11878,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11884,7 +11890,7 @@
         <v>593</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -11936,7 +11942,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -11968,7 +11974,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -12096,7 +12102,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12108,7 +12114,7 @@
         <v>593</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -12160,7 +12166,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12172,7 +12178,7 @@
         <v>593</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -12192,7 +12198,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12224,7 +12230,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12236,7 +12242,7 @@
         <v>593</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -12256,7 +12262,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12268,7 +12274,7 @@
         <v>671</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -12288,7 +12294,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12320,7 +12326,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12332,7 +12338,7 @@
         <v>593</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -12364,7 +12370,7 @@
         <v>593</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -12510,7 +12516,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12542,7 +12548,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12862,7 +12868,7 @@
         <v>593</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -12914,7 +12920,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -13022,7 +13028,7 @@
         <v>593</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -13182,7 +13188,7 @@
         <v>593</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -13266,7 +13272,7 @@
         <v>995</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13426,7 +13432,7 @@
         <v>359</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13438,7 +13444,7 @@
         <v>593</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -13458,7 +13464,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
@@ -13490,7 +13496,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -13522,7 +13528,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -13554,7 +13560,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13586,7 +13592,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -13618,7 +13624,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13650,7 +13656,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13682,7 +13688,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13714,7 +13720,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -13746,7 +13752,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13778,7 +13784,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13810,7 +13816,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -13842,7 +13848,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13874,7 +13880,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13886,7 +13892,7 @@
         <v>671</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -13906,7 +13912,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13938,7 +13944,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -13970,7 +13976,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -14002,7 +14008,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -14494,7 +14500,7 @@
         <v>593</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -14546,7 +14552,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14590,7 +14596,7 @@
         <v>593</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -14770,7 +14776,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14898,7 +14904,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -14930,7 +14936,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14962,7 +14968,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -14994,7 +15000,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -15026,7 +15032,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -15058,7 +15064,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -15090,7 +15096,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -15122,7 +15128,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15154,7 +15160,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15186,7 +15192,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -15218,7 +15224,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15250,7 +15256,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15282,7 +15288,7 @@
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15314,7 +15320,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15346,7 +15352,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15378,7 +15384,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15442,7 +15448,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -15474,7 +15480,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15506,7 +15512,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15538,7 +15544,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15570,7 +15576,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15602,7 +15608,7 @@
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -15858,7 +15864,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15870,7 +15876,7 @@
         <v>593</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -16382,7 +16388,7 @@
         <v>593</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -16414,7 +16420,7 @@
         <v>593</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -16498,7 +16504,7 @@
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16562,7 +16568,7 @@
         <v>71</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16626,7 +16632,7 @@
         <v>71</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16690,7 +16696,7 @@
         <v>71</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16702,7 +16708,7 @@
         <v>593</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -16754,7 +16760,7 @@
         <v>19</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -16766,7 +16772,7 @@
         <v>593</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -16910,7 +16916,7 @@
         <v>19</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16922,7 +16928,7 @@
         <v>593</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -17006,7 +17012,7 @@
         <v>19</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -17018,7 +17024,7 @@
         <v>593</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -17038,7 +17044,7 @@
         <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -17050,7 +17056,7 @@
         <v>593</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -17070,7 +17076,7 @@
         <v>71</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17166,7 +17172,7 @@
         <v>19</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
@@ -17230,7 +17236,7 @@
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
@@ -17242,7 +17248,7 @@
         <v>671</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -17256,13 +17262,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17274,7 +17280,7 @@
         <v>593</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -17288,7 +17294,7 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
@@ -17306,7 +17312,7 @@
         <v>593</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -17320,13 +17326,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17338,7 +17344,7 @@
         <v>593</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -17352,13 +17358,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17370,7 +17376,7 @@
         <v>593</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -17384,13 +17390,13 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17402,7 +17408,7 @@
         <v>593</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -17850,7 +17856,7 @@
         <v>593</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -18312,13 +18318,13 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18330,7 +18336,7 @@
         <v>593</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -18344,7 +18350,7 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
@@ -18362,7 +18368,7 @@
         <v>593</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -18376,7 +18382,7 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
@@ -18394,7 +18400,7 @@
         <v>671</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -18408,13 +18414,13 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18438,7 +18444,7 @@
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
@@ -18456,7 +18462,7 @@
         <v>593</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -18488,7 +18494,7 @@
         <v>593</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -18520,7 +18526,7 @@
         <v>593</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -18540,7 +18546,7 @@
         <v>80</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18552,7 +18558,7 @@
         <v>593</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -18566,13 +18572,13 @@
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18584,7 +18590,7 @@
         <v>593</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -18616,7 +18622,7 @@
         <v>593</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -18630,7 +18636,7 @@
         <v>11</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>359</v>
@@ -18648,7 +18654,7 @@
         <v>593</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -18662,7 +18668,7 @@
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>359</v>
@@ -18680,7 +18686,7 @@
         <v>593</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -18694,13 +18700,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
@@ -18712,7 +18718,7 @@
         <v>593</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -18726,13 +18732,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18744,7 +18750,7 @@
         <v>593</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -18758,13 +18764,13 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18776,7 +18782,7 @@
         <v>593</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -18816,13 +18822,13 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>19</v>
@@ -18840,7 +18846,7 @@
         <v>593</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -18848,13 +18854,13 @@
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -18878,13 +18884,13 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18908,13 +18914,13 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18938,13 +18944,13 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -18968,7 +18974,7 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
@@ -18998,7 +19004,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
@@ -19028,7 +19034,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19058,7 +19064,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19088,7 +19094,7 @@
         <v>446</v>
       </c>
       <c r="B447" s="53" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19118,19 +19124,19 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
@@ -19148,19 +19154,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
@@ -19178,19 +19184,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>32</v>
@@ -19208,19 +19214,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19238,19 +19244,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>32</v>
@@ -19268,19 +19274,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
@@ -19298,19 +19304,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>552</v>
+        <v>1223</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>627</v>
+        <v>1224</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
@@ -19328,7 +19334,7 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
@@ -19358,7 +19364,7 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
@@ -19388,7 +19394,7 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
@@ -19418,7 +19424,7 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
@@ -19448,7 +19454,7 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19478,7 +19484,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19508,7 +19514,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19538,7 +19544,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19568,7 +19574,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19598,7 +19604,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19628,7 +19634,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19658,7 +19664,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19688,7 +19694,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19718,7 +19724,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19748,7 +19754,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19778,7 +19784,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19808,7 +19814,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19838,7 +19844,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19868,7 +19874,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19898,7 +19904,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19928,7 +19934,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19958,7 +19964,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -19988,7 +19994,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20018,7 +20024,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20048,7 +20054,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20078,7 +20084,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20108,7 +20114,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20138,7 +20144,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20168,7 +20174,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20198,7 +20204,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20228,7 +20234,7 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20258,13 +20264,13 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20288,13 +20294,13 @@
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
@@ -22643,7 +22649,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C2D1A8-BEF6-4EDE-AA2D-6774CE13CC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8682B7-866A-4E31-8664-8E2554B597C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1227">
   <si>
     <t>INDICE</t>
   </si>
@@ -3289,9 +3289,6 @@
     <t>TROCA EM 08/11/2023 / ESTAVA NA GUARDA CIVIL, EMPRESTADA SEC. MEIO AMBIENTE; INSTALADA NA Escola Municipal Anderson Domingues de Oliveira. 02/02/2026;</t>
   </si>
   <si>
-    <t xml:space="preserve">SEDUC - SUPERVISÃO GESTAO </t>
-  </si>
-  <si>
     <t>INSTALAÇÃO CIMI 30/09/2025; E. M. CELINA MESQUITA PEDROSA 02/02/2026;</t>
   </si>
   <si>
@@ -3496,9 +3493,6 @@
     <t>XC75051317</t>
   </si>
   <si>
-    <t xml:space="preserve">SEDUC - JURIDICO </t>
-  </si>
-  <si>
     <t>INSTALACAO SEDUC JURICO 17/03/2026;</t>
   </si>
   <si>
@@ -3713,13 +3707,25 @@
   </si>
   <si>
     <t xml:space="preserve">E.B.M. PROF. JOAO RAPOSO </t>
+  </si>
+  <si>
+    <t>XBJZ043843</t>
+  </si>
+  <si>
+    <t>XBJZ044248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEDUC GESTÃO </t>
+  </si>
+  <si>
+    <t>SEDUC JURIDICA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4702,7 +4708,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J487" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="SEDUC"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -5054,7 +5066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J487"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5069,7 +5081,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5101,7 +5113,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5133,7 +5145,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5165,7 +5177,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5197,7 +5209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5229,7 +5241,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5261,7 +5273,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5293,7 +5305,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5325,7 +5337,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5355,7 +5367,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5417,7 +5429,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5449,7 +5461,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5481,7 +5493,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5513,7 +5525,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5545,7 +5557,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5562,7 +5574,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5574,7 +5586,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5606,7 +5618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5638,7 +5650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5670,7 +5682,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5687,7 +5699,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5699,10 +5711,10 @@
         <v>593</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -5734,7 +5746,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5763,10 +5775,10 @@
         <v>593</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -5780,10 +5792,10 @@
         <v>57</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1114</v>
+        <v>25</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>14</v>
@@ -5798,7 +5810,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5830,7 +5842,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5862,7 +5874,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5891,7 +5903,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5920,7 +5932,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5952,7 +5964,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -5984,7 +5996,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6016,7 +6028,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6048,7 +6060,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6080,7 +6092,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6112,7 +6124,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6144,7 +6156,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6176,7 +6188,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6208,7 +6220,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6237,7 +6249,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6269,7 +6281,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6301,7 +6313,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6333,7 +6345,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6365,7 +6377,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6397,7 +6409,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6429,7 +6441,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6461,7 +6473,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6490,7 +6502,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6522,7 +6534,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6554,7 +6566,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6586,7 +6598,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6615,7 +6627,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6644,7 +6656,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6676,7 +6688,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -6708,7 +6720,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -6740,7 +6752,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -6757,7 +6769,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6772,7 +6784,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -6801,7 +6813,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -6830,7 +6842,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -6859,7 +6871,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -6888,7 +6900,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -6917,7 +6929,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -6946,7 +6958,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -6978,7 +6990,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7010,7 +7022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7039,7 +7051,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7071,7 +7083,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7100,7 +7112,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7129,7 +7141,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7158,7 +7170,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7187,7 +7199,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7219,7 +7231,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7251,7 +7263,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7280,7 +7292,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7297,7 +7309,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7312,7 +7324,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7344,7 +7356,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7376,7 +7388,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7405,7 +7417,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7437,7 +7449,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7469,7 +7481,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7501,7 +7513,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7533,7 +7545,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7565,7 +7577,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7597,7 +7609,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7623,7 +7635,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7649,7 +7661,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7675,7 +7687,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7707,7 +7719,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -7739,7 +7751,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -7771,7 +7783,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -7803,7 +7815,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -7832,7 +7844,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -7849,7 +7861,7 @@
         <v>1004</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -7864,7 +7876,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -7896,7 +7908,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -7922,7 +7934,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -7948,7 +7960,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -7980,7 +7992,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8009,7 +8021,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8038,7 +8050,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8067,7 +8079,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8096,7 +8108,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8128,7 +8140,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8160,7 +8172,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8192,7 +8204,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8209,7 +8221,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8224,7 +8236,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8256,7 +8268,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8288,7 +8300,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8320,7 +8332,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8352,7 +8364,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8384,7 +8396,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8412,7 +8424,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8444,7 +8456,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8476,7 +8488,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8508,7 +8520,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8540,7 +8552,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8572,7 +8584,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8604,7 +8616,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8636,7 +8648,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8668,7 +8680,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -8700,7 +8712,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -8732,7 +8744,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -8764,7 +8776,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -8796,7 +8808,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -8828,7 +8840,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -8860,7 +8872,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8877,7 +8889,7 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -8889,7 +8901,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8906,7 +8918,7 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>32</v>
@@ -8921,7 +8933,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -8953,7 +8965,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -8970,7 +8982,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8985,7 +8997,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9017,7 +9029,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9049,7 +9061,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9081,7 +9093,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9113,7 +9125,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9145,7 +9157,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9162,7 +9174,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9177,7 +9189,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9194,7 +9206,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9209,7 +9221,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9226,7 +9238,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9241,7 +9253,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9258,7 +9270,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9270,10 +9282,10 @@
         <v>593</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9290,7 +9302,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9305,7 +9317,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9337,7 +9349,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9354,7 +9366,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9366,10 +9378,10 @@
         <v>593</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9398,10 +9410,10 @@
         <v>671</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9433,7 +9445,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9450,7 +9462,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>14</v>
@@ -9465,7 +9477,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9482,7 +9494,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9497,7 +9509,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9529,7 +9541,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9561,7 +9573,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9578,7 +9590,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9593,7 +9605,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9610,7 +9622,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>14</v>
@@ -9625,7 +9637,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9642,7 +9654,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9657,7 +9669,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9674,7 +9686,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9689,7 +9701,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -9721,7 +9733,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9753,7 +9765,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -9785,7 +9797,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9802,7 +9814,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>14</v>
@@ -9814,10 +9826,10 @@
         <v>593</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -9849,7 +9861,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -9881,7 +9893,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -9913,7 +9925,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -9942,7 +9954,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -9971,7 +9983,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -9998,7 +10010,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -10015,7 +10027,7 @@
         <v>359</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -10027,10 +10039,10 @@
         <v>593</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -10059,7 +10071,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10091,7 +10103,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10123,7 +10135,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10152,10 +10164,10 @@
         <v>593</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10187,7 +10199,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10216,7 +10228,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10245,7 +10257,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10277,7 +10289,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10303,7 +10315,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10333,7 +10345,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10362,10 +10374,10 @@
         <v>593</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10394,7 +10406,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10423,7 +10435,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10452,7 +10464,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10481,7 +10493,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10510,7 +10522,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10539,7 +10551,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10568,7 +10580,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10597,7 +10609,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10626,7 +10638,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -10655,7 +10667,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -10684,7 +10696,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10713,7 +10725,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -10742,7 +10754,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -10771,7 +10783,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -10800,7 +10812,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -10829,7 +10841,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -10858,7 +10870,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -10887,7 +10899,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -10916,7 +10928,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -10945,7 +10957,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -10974,7 +10986,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11003,7 +11015,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -11032,7 +11044,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -11061,7 +11073,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -11093,7 +11105,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11125,7 +11137,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11157,7 +11169,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11189,7 +11201,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11221,7 +11233,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -11238,7 +11250,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11253,7 +11265,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -11270,7 +11282,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11285,7 +11297,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11317,7 +11329,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -11349,7 +11361,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -11366,7 +11378,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11381,7 +11393,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11413,7 +11425,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11445,7 +11457,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -11462,7 +11474,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11474,10 +11486,10 @@
         <v>593</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -11494,7 +11506,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11509,7 +11521,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11526,7 +11538,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11541,7 +11553,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11573,7 +11585,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11605,7 +11617,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -11637,7 +11649,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -11669,7 +11681,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -11701,7 +11713,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -11730,10 +11742,10 @@
         <v>593</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -11750,7 +11762,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11762,10 +11774,10 @@
         <v>593</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -11797,7 +11809,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -11814,7 +11826,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11829,7 +11841,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -11846,7 +11858,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11861,7 +11873,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -11878,7 +11890,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11890,10 +11902,10 @@
         <v>593</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -11907,10 +11919,10 @@
         <v>353</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>25</v>
+        <v>1113</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>14</v>
@@ -11925,7 +11937,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -11942,7 +11954,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -11957,7 +11969,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -11974,7 +11986,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -11989,7 +12001,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -12021,7 +12033,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -12053,7 +12065,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -12085,7 +12097,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -12102,7 +12114,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12114,10 +12126,10 @@
         <v>593</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -12149,7 +12161,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -12166,7 +12178,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12178,10 +12190,10 @@
         <v>593</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -12198,7 +12210,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12213,7 +12225,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15.6">
+    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12245,7 +12257,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -12262,7 +12274,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12277,7 +12289,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -12294,7 +12306,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12309,7 +12321,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -12326,7 +12338,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12338,10 +12350,10 @@
         <v>593</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -12373,7 +12385,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12403,7 +12415,7 @@
       </c>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12435,7 +12447,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -12467,7 +12479,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -12499,7 +12511,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12516,7 +12528,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12531,7 +12543,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -12548,7 +12560,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12563,7 +12575,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -12592,7 +12604,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -12624,7 +12636,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12656,7 +12668,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -12688,7 +12700,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -12717,7 +12729,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -12749,7 +12761,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -12778,7 +12790,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -12807,7 +12819,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12839,7 +12851,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -12868,10 +12880,10 @@
         <v>593</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -12903,7 +12915,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12920,7 +12932,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -12935,7 +12947,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -12967,7 +12979,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -12999,7 +13011,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -13028,10 +13040,10 @@
         <v>593</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -13063,7 +13075,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -13095,7 +13107,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13127,7 +13139,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13159,7 +13171,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13188,10 +13200,10 @@
         <v>593</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13223,7 +13235,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13255,7 +13267,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -13287,7 +13299,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -13319,7 +13331,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13351,7 +13363,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13383,7 +13395,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13415,7 +13427,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13432,7 +13444,7 @@
         <v>359</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13444,10 +13456,10 @@
         <v>593</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13464,7 +13476,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
@@ -13479,7 +13491,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13496,7 +13508,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -13511,7 +13523,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13528,7 +13540,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -13543,7 +13555,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13560,7 +13572,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13575,7 +13587,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13592,7 +13604,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -13607,7 +13619,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13624,7 +13636,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13639,7 +13651,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13671,7 +13683,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13703,7 +13715,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13720,7 +13732,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -13735,7 +13747,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13752,7 +13764,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13767,7 +13779,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13784,7 +13796,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13799,7 +13811,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13816,7 +13828,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -13831,7 +13843,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13848,7 +13860,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13863,7 +13875,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13895,7 +13907,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13912,7 +13924,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13927,7 +13939,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13944,7 +13956,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -13959,7 +13971,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -13976,7 +13988,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -13991,7 +14003,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14008,7 +14020,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -14023,7 +14035,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -14055,7 +14067,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -14087,7 +14099,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14119,7 +14131,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14151,7 +14163,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14183,7 +14195,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14215,7 +14227,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14247,7 +14259,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14279,7 +14291,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14311,7 +14323,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14343,7 +14355,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14375,7 +14387,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14407,7 +14419,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14439,7 +14451,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14471,7 +14483,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14503,7 +14515,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14535,7 +14547,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14552,7 +14564,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14567,7 +14579,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14599,7 +14611,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14631,7 +14643,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14663,7 +14675,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -14695,7 +14707,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -14727,7 +14739,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -14759,7 +14771,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14776,7 +14788,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14791,7 +14803,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -14823,7 +14835,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -14855,7 +14867,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -14887,7 +14899,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14904,7 +14916,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -14919,7 +14931,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14936,7 +14948,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14951,7 +14963,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -14968,7 +14980,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -14983,7 +14995,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15000,7 +15012,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -15015,7 +15027,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15032,7 +15044,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -15047,7 +15059,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15064,7 +15076,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -15079,7 +15091,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15096,7 +15108,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -15111,7 +15123,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15128,7 +15140,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15143,7 +15155,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15160,7 +15172,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15175,7 +15187,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15192,7 +15204,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -15207,7 +15219,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15224,7 +15236,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15239,7 +15251,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15256,7 +15268,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15271,7 +15283,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15288,7 +15300,7 @@
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15303,7 +15315,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15320,7 +15332,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15335,7 +15347,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15352,7 +15364,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15367,7 +15379,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15384,7 +15396,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15399,7 +15411,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15431,7 +15443,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15448,7 +15460,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -15463,7 +15475,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15480,7 +15492,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15495,7 +15507,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15512,7 +15524,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15527,7 +15539,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15544,7 +15556,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15559,7 +15571,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15576,7 +15588,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15591,7 +15603,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15623,7 +15635,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15655,7 +15667,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15687,7 +15699,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15719,7 +15731,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15751,7 +15763,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15783,7 +15795,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15815,7 +15827,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -15847,7 +15859,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15879,7 +15891,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -15911,7 +15923,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -15943,7 +15955,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -15975,7 +15987,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16007,7 +16019,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16039,7 +16051,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16071,7 +16083,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16103,7 +16115,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16135,7 +16147,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16167,7 +16179,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16199,7 +16211,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16231,7 +16243,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16263,7 +16275,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16295,7 +16307,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16327,7 +16339,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16359,7 +16371,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16391,7 +16403,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16423,7 +16435,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16455,7 +16467,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16487,7 +16499,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16504,7 +16516,7 @@
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16519,7 +16531,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16551,7 +16563,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16568,7 +16580,7 @@
         <v>71</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16583,7 +16595,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16615,7 +16627,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16632,7 +16644,7 @@
         <v>71</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16647,7 +16659,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16679,7 +16691,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -16696,7 +16708,7 @@
         <v>71</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16711,7 +16723,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16743,7 +16755,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16757,10 +16769,10 @@
         <v>745</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1083</v>
+        <v>627</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -16772,10 +16784,10 @@
         <v>593</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -16807,7 +16819,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -16837,7 +16849,7 @@
       </c>
       <c r="J375" s="24"/>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16869,7 +16881,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16899,7 +16911,7 @@
       </c>
       <c r="J377" s="24"/>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -16913,10 +16925,10 @@
         <v>750</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1152</v>
+        <v>627</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16928,10 +16940,10 @@
         <v>593</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -16963,7 +16975,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -16995,7 +17007,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -17012,7 +17024,7 @@
         <v>19</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -17024,10 +17036,10 @@
         <v>593</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -17044,7 +17056,7 @@
         <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -17056,10 +17068,10 @@
         <v>593</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -17076,7 +17088,7 @@
         <v>71</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17091,7 +17103,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17123,7 +17135,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17155,7 +17167,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -17172,7 +17184,7 @@
         <v>19</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
@@ -17187,7 +17199,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17219,7 +17231,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17251,7 +17263,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17268,7 +17280,7 @@
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17283,7 +17295,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17315,7 +17327,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17332,7 +17344,7 @@
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17347,7 +17359,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17364,7 +17376,7 @@
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17379,7 +17391,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17396,7 +17408,7 @@
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17411,7 +17423,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17443,7 +17455,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17475,7 +17487,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17507,7 +17519,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17539,7 +17551,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17571,7 +17583,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17603,7 +17615,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17635,7 +17647,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -17667,7 +17679,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17699,7 +17711,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17731,7 +17743,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17763,7 +17775,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17795,7 +17807,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17827,7 +17839,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -17859,7 +17871,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -17891,7 +17903,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -17923,7 +17935,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -17955,7 +17967,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -17987,7 +17999,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -18019,7 +18031,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -18051,7 +18063,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="414" spans="1:10">
+    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -18083,7 +18095,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18115,7 +18127,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18147,7 +18159,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18179,7 +18191,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18211,7 +18223,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18243,7 +18255,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18275,7 +18287,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18307,7 +18319,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18339,7 +18351,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18371,7 +18383,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18403,7 +18415,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18433,7 +18445,7 @@
       </c>
       <c r="J425" s="24"/>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18465,7 +18477,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18497,7 +18509,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="428" spans="1:10">
+    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18529,7 +18541,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="429" spans="1:10">
+    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -18561,7 +18573,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="430" spans="1:10">
+    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18578,7 +18590,7 @@
         <v>71</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18593,7 +18605,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="431" spans="1:10">
+    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -18625,7 +18637,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -18657,7 +18669,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="433" spans="1:10">
+    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -18689,7 +18701,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
+    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -18721,7 +18733,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="435" spans="1:10">
+    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -18753,7 +18765,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -18785,7 +18797,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -18817,18 +18829,18 @@
         <v>672</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>19</v>
@@ -18846,21 +18858,21 @@
         <v>593</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -18879,18 +18891,18 @@
       </c>
       <c r="J439" s="24"/>
     </row>
-    <row r="440" spans="1:10">
+    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18909,18 +18921,18 @@
       </c>
       <c r="J440" s="24"/>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18939,18 +18951,18 @@
       </c>
       <c r="J441" s="24"/>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -18969,72 +18981,72 @@
       </c>
       <c r="J442" s="24"/>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>552</v>
+        <v>1224</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>627</v>
+        <v>1225</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H443" s="23">
-        <v>46063</v>
+        <v>46104</v>
       </c>
       <c r="I443" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J443" s="24"/>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>552</v>
+        <v>1223</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>627</v>
+        <v>1226</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H444" s="23">
-        <v>46063</v>
+        <v>46104</v>
       </c>
       <c r="I444" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J444" s="24"/>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19059,12 +19071,12 @@
       </c>
       <c r="J445" s="24"/>
     </row>
-    <row r="446" spans="1:10">
+    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19089,12 +19101,12 @@
       </c>
       <c r="J446" s="24"/>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>446</v>
       </c>
       <c r="B447" s="53" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19119,24 +19131,24 @@
       </c>
       <c r="J447" s="24"/>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
@@ -19149,24 +19161,24 @@
       </c>
       <c r="J448" s="24"/>
     </row>
-    <row r="449" spans="1:10">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
@@ -19179,24 +19191,24 @@
       </c>
       <c r="J449" s="24"/>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="4">
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>32</v>
@@ -19209,24 +19221,24 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19239,24 +19251,24 @@
       </c>
       <c r="J451" s="24"/>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="4">
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>32</v>
@@ -19269,24 +19281,24 @@
       </c>
       <c r="J452" s="24"/>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
@@ -19299,24 +19311,24 @@
       </c>
       <c r="J453" s="24"/>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
@@ -19329,12 +19341,12 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
@@ -19359,12 +19371,12 @@
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
@@ -19389,12 +19401,12 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
@@ -19419,12 +19431,12 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
@@ -19449,12 +19461,12 @@
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19479,12 +19491,12 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19509,12 +19521,12 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19539,12 +19551,12 @@
       </c>
       <c r="J461" s="24"/>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19569,12 +19581,12 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19599,12 +19611,12 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19629,12 +19641,12 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19659,12 +19671,12 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19689,12 +19701,12 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19719,12 +19731,12 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="4">
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19749,12 +19761,12 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19779,12 +19791,12 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19809,12 +19821,12 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19839,12 +19851,12 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19869,12 +19881,12 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19899,12 +19911,12 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19929,12 +19941,12 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19959,12 +19971,12 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -19989,12 +20001,12 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20019,12 +20031,12 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20049,12 +20061,12 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20079,12 +20091,12 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20109,12 +20121,12 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20139,12 +20151,12 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20169,12 +20181,12 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20199,12 +20211,12 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20229,12 +20241,12 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20259,18 +20271,18 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20289,18 +20301,18 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
@@ -20381,7 +20393,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -20390,7 +20402,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>527</v>
       </c>
@@ -20410,7 +20422,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
         <v>904</v>
       </c>
@@ -20430,7 +20442,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
         <v>904</v>
       </c>
@@ -20450,7 +20462,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="42" t="s">
         <v>904</v>
       </c>
@@ -20470,7 +20482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="42" t="s">
         <v>904</v>
       </c>
@@ -20490,7 +20502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="42" t="s">
         <v>904</v>
       </c>
@@ -20510,7 +20522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="42" t="s">
         <v>904</v>
       </c>
@@ -20530,7 +20542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>532</v>
       </c>
@@ -20547,7 +20559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>532</v>
       </c>
@@ -20564,7 +20576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>532</v>
       </c>
@@ -20581,7 +20593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>532</v>
       </c>
@@ -20598,7 +20610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>532</v>
       </c>
@@ -20615,7 +20627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>532</v>
       </c>
@@ -20632,7 +20644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>532</v>
       </c>
@@ -20649,7 +20661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>532</v>
       </c>
@@ -20666,7 +20678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>532</v>
       </c>
@@ -20683,7 +20695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>532</v>
       </c>
@@ -20700,7 +20712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>532</v>
       </c>
@@ -20717,7 +20729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>532</v>
       </c>
@@ -20734,7 +20746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>532</v>
       </c>
@@ -20751,7 +20763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>537</v>
       </c>
@@ -20771,7 +20783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>537</v>
       </c>
@@ -20791,7 +20803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>537</v>
       </c>
@@ -20811,7 +20823,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>537</v>
       </c>
@@ -20831,7 +20843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>537</v>
       </c>
@@ -20851,7 +20863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>537</v>
       </c>
@@ -20871,7 +20883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>537</v>
       </c>
@@ -20891,7 +20903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>550</v>
       </c>
@@ -20911,7 +20923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>554</v>
       </c>
@@ -20931,7 +20943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>556</v>
       </c>
@@ -20951,7 +20963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>556</v>
       </c>
@@ -20971,7 +20983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>550</v>
       </c>
@@ -21003,7 +21015,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -21020,7 +21032,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21052,7 +21064,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -21084,7 +21096,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -21116,7 +21128,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -21148,7 +21160,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -21180,7 +21192,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -21212,7 +21224,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -21244,7 +21256,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -21276,7 +21288,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -21308,7 +21320,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -21340,7 +21352,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -21372,7 +21384,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -21404,7 +21416,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -21436,7 +21448,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -21468,7 +21480,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -21500,7 +21512,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -21532,7 +21544,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -21564,7 +21576,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -21596,7 +21608,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -21628,7 +21640,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -21660,7 +21672,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -21692,7 +21704,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -21724,7 +21736,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -21756,7 +21768,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -21788,7 +21800,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -21818,7 +21830,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -21848,7 +21860,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -21878,7 +21890,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -21908,7 +21920,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -21938,7 +21950,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -21968,7 +21980,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -21998,7 +22010,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -22028,7 +22040,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -22058,7 +22070,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -22088,7 +22100,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -22118,7 +22130,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -22148,7 +22160,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -22178,7 +22190,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -22208,7 +22220,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -22238,7 +22250,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -22268,7 +22280,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -22298,7 +22310,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -22327,7 +22339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -22359,7 +22371,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="33">
         <v>43</v>
       </c>
@@ -22391,7 +22403,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -22420,7 +22432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="18">
         <v>45</v>
       </c>
@@ -22449,7 +22461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -22478,7 +22490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="18">
         <v>47</v>
       </c>
@@ -22507,7 +22519,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="18">
         <v>48</v>
       </c>
@@ -22536,7 +22548,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="18">
         <v>49</v>
       </c>
@@ -22568,7 +22580,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="18">
         <v>50</v>
       </c>
@@ -22600,7 +22612,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="3" customFormat="1">
+    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -22632,7 +22644,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="3" customFormat="1">
+    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -22649,7 +22661,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -22664,102 +22676,102 @@
         <v>716</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8682B7-866A-4E31-8664-8E2554B597C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F52858-2823-452D-BCF6-66DB57BCB516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4274" uniqueCount="1235">
   <si>
     <t>INDICE</t>
   </si>
@@ -3370,9 +3370,6 @@
     <t>E.M. HONORINO COUTINHO</t>
   </si>
   <si>
-    <t>INSTALAÇÃO 10/01/2026 SEDUC GESTÃO;</t>
-  </si>
-  <si>
     <t>IMPRESSORA INSTALADA EM 25/10/2024 - SUBSTITUIU IMPRESSORA RICOH MP 501;  RETIRADA DA PROCURADORIA 30/12/2026; INSTALADA NA CASA DE CONVIVENCIA 12/02/2026;</t>
   </si>
   <si>
@@ -3433,15 +3430,9 @@
     <t xml:space="preserve">E.M. PASTOR ALCEBIADES </t>
   </si>
   <si>
-    <t>INSTALADA 20/10/2025 SEDUC GABINETE; INSTALADA ESCOLA PASTOR ALCEBIDES F. DE MENDONÇA 26/02/2026;</t>
-  </si>
-  <si>
     <t>E.M. JOAO AUGUSTO CHAVES</t>
   </si>
   <si>
-    <t>INSTALADA 20/10/2025 SOLAGOS ADM; INSTALADA JOAO AUGUSTO CHAVES 26/02/2026;</t>
-  </si>
-  <si>
     <t>PAM - ESPACO DA MULHER</t>
   </si>
   <si>
@@ -3493,9 +3484,6 @@
     <t>XC75051317</t>
   </si>
   <si>
-    <t>INSTALACAO SEDUC JURICO 17/03/2026;</t>
-  </si>
-  <si>
     <t>ESTAVA NA MULTISHOP FRIBURGO; TROCA CAIXA DE MANUTENÇÃO 11/03/2026;</t>
   </si>
   <si>
@@ -3719,6 +3707,42 @@
   </si>
   <si>
     <t>SEDUC JURIDICA</t>
+  </si>
+  <si>
+    <t>XC75051308</t>
+  </si>
+  <si>
+    <t>XC75051311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBS - ITATIQUARA </t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO 10/01/2026 SEDUC GESTÃO; INSTALAÇÃ UBS ITATIQUARA 25/03/2026;</t>
+  </si>
+  <si>
+    <t>UBS - PARATI</t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO UBS PARATI 25/03/2026;</t>
+  </si>
+  <si>
+    <t>UBS - AURORA</t>
+  </si>
+  <si>
+    <t>INSTALACAO UBS AURORA 25/09/2026;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBS - JARDIM CALIFORNIA </t>
+  </si>
+  <si>
+    <t>INSTALADA 20/10/2025 SEDUC GABINETE; INSTALADA ESCOLA PASTOR ALCEBIDES F. DE MENDONÇA 26/02/2026; INSTALADA UBS JARDIM CALIFORNIA 25/03/2026;</t>
+  </si>
+  <si>
+    <t>UBS - POSSE</t>
+  </si>
+  <si>
+    <t>INSTALADA 20/10/2025 SOLAGOS ADM; INSTALADA JOAO AUGUSTO CHAVES 26/02/2026; INSTALADA UBS POSSE 25/03/2026;</t>
   </si>
 </sst>
 </file>
@@ -4708,13 +4732,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J487" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="SEDUC"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -5113,7 +5131,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5145,7 +5163,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5209,7 +5227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5241,7 +5259,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5273,7 +5291,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5305,7 +5323,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5337,7 +5355,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5367,7 +5385,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5493,7 +5511,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5557,7 +5575,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5574,7 +5592,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5586,7 +5604,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5618,7 +5636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5650,7 +5668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5714,7 +5732,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -5746,7 +5764,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5810,7 +5828,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5842,7 +5860,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5874,7 +5892,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5903,7 +5921,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5932,7 +5950,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5964,7 +5982,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -5996,7 +6014,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6028,7 +6046,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6060,7 +6078,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6092,7 +6110,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6124,7 +6142,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6156,7 +6174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6188,7 +6206,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6220,7 +6238,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6249,7 +6267,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6281,7 +6299,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6313,7 +6331,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6345,7 +6363,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6377,7 +6395,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6409,7 +6427,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6441,7 +6459,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6473,7 +6491,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6502,7 +6520,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6534,7 +6552,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6566,7 +6584,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6598,7 +6616,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6627,7 +6645,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6656,7 +6674,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6688,7 +6706,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -6720,7 +6738,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -6752,7 +6770,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -6769,7 +6787,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6784,7 +6802,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -6813,7 +6831,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -6842,7 +6860,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -6871,7 +6889,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -6900,7 +6918,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -6929,7 +6947,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -6958,7 +6976,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -6990,7 +7008,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7022,7 +7040,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7051,7 +7069,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7083,7 +7101,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7112,7 +7130,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7141,7 +7159,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7170,7 +7188,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7199,7 +7217,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7231,7 +7249,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7263,7 +7281,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7324,7 +7342,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7356,7 +7374,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7388,7 +7406,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7417,7 +7435,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7449,7 +7467,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7481,7 +7499,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7513,7 +7531,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7545,7 +7563,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7577,7 +7595,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7609,7 +7627,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7635,7 +7653,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7661,7 +7679,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7687,7 +7705,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7719,7 +7737,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -7751,7 +7769,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -7783,7 +7801,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -7815,7 +7833,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -7844,7 +7862,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -7861,7 +7879,7 @@
         <v>1004</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -7876,7 +7894,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -7908,7 +7926,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -7934,7 +7952,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -7960,7 +7978,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -7992,7 +8010,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8021,7 +8039,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8050,7 +8068,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8079,7 +8097,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8108,7 +8126,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8140,7 +8158,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8172,7 +8190,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8204,7 +8222,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8221,7 +8239,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8236,7 +8254,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8268,7 +8286,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8300,7 +8318,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8332,7 +8350,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8364,7 +8382,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8396,7 +8414,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8424,7 +8442,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8456,7 +8474,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8488,7 +8506,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8520,7 +8538,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8552,7 +8570,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8584,7 +8602,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8616,7 +8634,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8648,7 +8666,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8680,7 +8698,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -8712,7 +8730,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -8744,7 +8762,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -8776,7 +8794,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -8808,7 +8826,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -8840,7 +8858,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -8872,7 +8890,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8889,7 +8907,7 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -8901,7 +8919,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8918,7 +8936,7 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>32</v>
@@ -8933,7 +8951,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -8982,7 +9000,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -8997,7 +9015,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9029,7 +9047,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9061,7 +9079,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9093,7 +9111,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9125,7 +9143,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9174,7 +9192,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9253,7 +9271,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9270,7 +9288,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9282,7 +9300,7 @@
         <v>593</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
@@ -9302,7 +9320,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9317,7 +9335,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9381,7 +9399,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9410,10 +9428,10 @@
         <v>671</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9445,7 +9463,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9462,7 +9480,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>14</v>
@@ -9477,7 +9495,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9494,7 +9512,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9509,7 +9527,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9541,7 +9559,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9573,7 +9591,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9590,7 +9608,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9605,7 +9623,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9622,7 +9640,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>14</v>
@@ -9637,7 +9655,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9654,7 +9672,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9669,7 +9687,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9686,7 +9704,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9701,7 +9719,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -9733,7 +9751,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9765,7 +9783,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -9797,7 +9815,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9814,7 +9832,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>14</v>
@@ -9826,10 +9844,10 @@
         <v>593</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -9861,7 +9879,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -9893,7 +9911,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -9925,7 +9943,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -9954,7 +9972,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -9983,7 +10001,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -10010,7 +10028,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -10027,7 +10045,7 @@
         <v>359</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -10039,10 +10057,10 @@
         <v>593</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -10071,7 +10089,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10103,7 +10121,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10135,7 +10153,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10164,10 +10182,10 @@
         <v>593</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10199,7 +10217,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10228,7 +10246,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10257,7 +10275,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10289,7 +10307,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10315,7 +10333,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10345,7 +10363,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10374,10 +10392,10 @@
         <v>593</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10406,7 +10424,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10435,7 +10453,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10464,7 +10482,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10493,7 +10511,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10522,7 +10540,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10551,7 +10569,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10580,7 +10598,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10609,7 +10627,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10638,7 +10656,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -10667,7 +10685,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -10696,7 +10714,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10725,7 +10743,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -10754,7 +10772,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -10783,7 +10801,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -10812,7 +10830,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -10841,7 +10859,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -10870,7 +10888,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -10899,7 +10917,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -10928,7 +10946,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -10957,7 +10975,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -10986,7 +11004,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11015,7 +11033,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -11044,7 +11062,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -11073,7 +11091,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -11105,7 +11123,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11137,7 +11155,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11169,7 +11187,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11201,7 +11219,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11250,7 +11268,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11297,7 +11315,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11393,7 +11411,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11425,7 +11443,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11521,7 +11539,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11538,7 +11556,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11553,7 +11571,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11585,7 +11603,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11617,7 +11635,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -11649,7 +11667,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -11681,7 +11699,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -11713,7 +11731,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -11777,7 +11795,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -11890,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11902,7 +11920,7 @@
         <v>593</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
@@ -11922,7 +11940,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>14</v>
@@ -11969,7 +11987,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -11986,7 +12004,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -12001,7 +12019,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -12033,7 +12051,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -12065,7 +12083,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -12129,7 +12147,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -12178,7 +12196,7 @@
         <v>19</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12190,7 +12208,7 @@
         <v>593</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
@@ -12210,7 +12228,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12353,7 +12371,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -12385,7 +12403,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12415,7 +12433,7 @@
       </c>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12511,7 +12529,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12528,7 +12546,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12575,7 +12593,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -12604,7 +12622,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -12636,7 +12654,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12668,7 +12686,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -12700,7 +12718,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -12729,7 +12747,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -12761,7 +12779,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -12790,7 +12808,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -12819,7 +12837,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12851,7 +12869,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -12880,7 +12898,7 @@
         <v>593</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
@@ -12915,7 +12933,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12932,7 +12950,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -12947,7 +12965,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -12979,7 +12997,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -13011,7 +13029,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -13040,10 +13058,10 @@
         <v>593</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -13075,7 +13093,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -13107,7 +13125,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13139,7 +13157,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13171,7 +13189,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13200,10 +13218,10 @@
         <v>593</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13235,7 +13253,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13267,7 +13285,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -13299,7 +13317,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -13331,7 +13349,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13363,7 +13381,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13395,7 +13413,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13427,7 +13445,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13444,7 +13462,7 @@
         <v>359</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13456,10 +13474,10 @@
         <v>593</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13476,7 +13494,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
@@ -13491,7 +13509,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13508,7 +13526,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -13523,7 +13541,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13540,7 +13558,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -13555,7 +13573,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13572,7 +13590,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13587,7 +13605,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13604,7 +13622,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -13619,7 +13637,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13636,7 +13654,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13651,7 +13669,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13683,7 +13701,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13715,7 +13733,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13732,7 +13750,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -13747,7 +13765,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13764,7 +13782,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13779,7 +13797,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13796,7 +13814,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13811,7 +13829,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13828,7 +13846,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -13843,7 +13861,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13860,7 +13878,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13875,7 +13893,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13907,7 +13925,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13924,7 +13942,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13939,7 +13957,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13956,7 +13974,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -13971,7 +13989,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -13988,7 +14006,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -14003,7 +14021,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14020,7 +14038,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -14035,7 +14053,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -14067,7 +14085,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -14099,7 +14117,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14131,7 +14149,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14163,7 +14181,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14195,7 +14213,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14227,7 +14245,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14259,7 +14277,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14291,7 +14309,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14323,7 +14341,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14355,7 +14373,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14387,7 +14405,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="299" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14419,7 +14437,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="300" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14451,7 +14469,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14483,7 +14501,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14515,7 +14533,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="303" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14547,7 +14565,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="304" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14564,7 +14582,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14579,7 +14597,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="305" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14611,7 +14629,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="306" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14643,7 +14661,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="307" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14675,7 +14693,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="308" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -14707,7 +14725,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="309" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -14739,7 +14757,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="310" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -14771,7 +14789,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="311" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14788,7 +14806,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14803,7 +14821,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="312" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -14835,7 +14853,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="313" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -14867,7 +14885,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="314" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -14899,7 +14917,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="315" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14916,7 +14934,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -14931,7 +14949,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="316" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14948,7 +14966,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14963,7 +14981,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="317" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -14980,7 +14998,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -14995,7 +15013,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15012,7 +15030,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -15027,7 +15045,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15044,7 +15062,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -15059,7 +15077,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="320" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15076,7 +15094,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -15091,7 +15109,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="321" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15108,7 +15126,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -15123,7 +15141,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="322" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15140,7 +15158,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15155,7 +15173,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="323" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15172,7 +15190,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15187,7 +15205,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15204,7 +15222,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -15219,7 +15237,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15236,7 +15254,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15251,7 +15269,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15268,7 +15286,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15283,7 +15301,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15300,7 +15318,7 @@
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15315,7 +15333,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15332,7 +15350,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15347,7 +15365,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15364,7 +15382,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15379,7 +15397,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15396,7 +15414,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15411,7 +15429,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15443,7 +15461,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15460,7 +15478,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -15475,7 +15493,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15492,7 +15510,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15507,7 +15525,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15524,7 +15542,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15539,7 +15557,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15556,7 +15574,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15571,7 +15589,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15588,7 +15606,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15603,7 +15621,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15635,7 +15653,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15667,7 +15685,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15699,7 +15717,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="340" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15731,7 +15749,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15763,7 +15781,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="342" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15795,7 +15813,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15827,7 +15845,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="344" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -15859,7 +15877,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15891,7 +15909,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="346" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -15923,7 +15941,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="347" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -15955,7 +15973,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="348" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -15987,7 +16005,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16019,7 +16037,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="350" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16051,7 +16069,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="351" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16083,7 +16101,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="352" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16115,7 +16133,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="353" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16147,7 +16165,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16179,7 +16197,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16211,7 +16229,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16243,7 +16261,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16275,7 +16293,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16307,7 +16325,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16339,7 +16357,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16371,7 +16389,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="361" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16403,7 +16421,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="362" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16435,7 +16453,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16467,7 +16485,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16499,7 +16517,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16516,7 +16534,7 @@
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16531,7 +16549,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="366" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16563,7 +16581,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="367" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16580,7 +16598,7 @@
         <v>71</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16595,7 +16613,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="368" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16627,7 +16645,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="369" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16644,7 +16662,7 @@
         <v>71</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16659,7 +16677,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="370" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16691,7 +16709,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="371" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -16708,7 +16726,7 @@
         <v>71</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16723,7 +16741,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="372" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16769,10 +16787,10 @@
         <v>745</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>627</v>
+        <v>1225</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -16784,10 +16802,10 @@
         <v>593</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -16819,7 +16837,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="375" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -16849,7 +16867,7 @@
       </c>
       <c r="J375" s="24"/>
     </row>
-    <row r="376" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16881,7 +16899,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="377" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16895,10 +16913,10 @@
         <v>749</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>765</v>
+        <v>1227</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
@@ -16909,7 +16927,9 @@
       <c r="I377" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J377" s="24"/>
+      <c r="J377" s="3" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
@@ -16925,10 +16945,10 @@
         <v>750</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>627</v>
+        <v>1229</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16940,10 +16960,10 @@
         <v>593</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -16975,7 +16995,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="380" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -17021,10 +17041,10 @@
         <v>753</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1130</v>
+        <v>1231</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -17036,7 +17056,7 @@
         <v>593</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1131</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.3">
@@ -17053,10 +17073,10 @@
         <v>754</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1132</v>
+        <v>1233</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -17068,10 +17088,10 @@
         <v>593</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -17088,7 +17108,7 @@
         <v>71</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17103,7 +17123,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="384" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17135,7 +17155,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="385" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17184,7 +17204,7 @@
         <v>19</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
@@ -17199,7 +17219,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="387" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17231,7 +17251,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="388" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17263,7 +17283,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="389" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17280,7 +17300,7 @@
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17295,7 +17315,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="390" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17327,7 +17347,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="391" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17344,7 +17364,7 @@
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17359,7 +17379,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="392" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17376,7 +17396,7 @@
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17391,7 +17411,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="393" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17408,7 +17428,7 @@
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17423,7 +17443,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="394" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17455,7 +17475,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="395" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17487,7 +17507,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="396" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17519,7 +17539,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="397" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17551,7 +17571,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="398" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17583,7 +17603,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="399" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17615,7 +17635,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="400" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17647,7 +17667,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="401" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -17679,7 +17699,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="402" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17711,7 +17731,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17743,7 +17763,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17775,7 +17795,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17807,7 +17827,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17839,7 +17859,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="407" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -17871,7 +17891,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="408" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -17903,7 +17923,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="409" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -17935,7 +17955,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="410" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -17967,7 +17987,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="411" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -17999,7 +18019,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="412" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -18031,7 +18051,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="413" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -18063,7 +18083,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="414" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -18095,7 +18115,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="415" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18159,7 +18179,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="417" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18191,7 +18211,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="418" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18223,7 +18243,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="419" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18255,7 +18275,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="420" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18287,7 +18307,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="421" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18319,7 +18339,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="422" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18351,7 +18371,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="423" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18383,7 +18403,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="424" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18415,7 +18435,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="425" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18445,7 +18465,7 @@
       </c>
       <c r="J425" s="24"/>
     </row>
-    <row r="426" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18477,7 +18497,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="427" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18509,7 +18529,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="428" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18541,7 +18561,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="429" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -18573,7 +18593,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="430" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18590,7 +18610,7 @@
         <v>71</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18605,7 +18625,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="431" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -18637,7 +18657,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="432" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -18669,7 +18689,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="433" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -18701,7 +18721,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="434" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -18733,7 +18753,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="435" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -18765,7 +18785,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="436" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -18797,7 +18817,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="437" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -18834,13 +18854,13 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>19</v>
@@ -18858,21 +18878,21 @@
         <v>593</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -18891,18 +18911,18 @@
       </c>
       <c r="J439" s="24"/>
     </row>
-    <row r="440" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18921,18 +18941,18 @@
       </c>
       <c r="J440" s="24"/>
     </row>
-    <row r="441" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18951,18 +18971,18 @@
       </c>
       <c r="J441" s="24"/>
     </row>
-    <row r="442" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -18986,19 +19006,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
@@ -19016,19 +19036,19 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
@@ -19041,12 +19061,12 @@
       </c>
       <c r="J444" s="24"/>
     </row>
-    <row r="445" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19071,12 +19091,12 @@
       </c>
       <c r="J445" s="24"/>
     </row>
-    <row r="446" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19101,12 +19121,12 @@
       </c>
       <c r="J446" s="24"/>
     </row>
-    <row r="447" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>446</v>
       </c>
       <c r="B447" s="53" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19136,19 +19156,19 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
@@ -19166,19 +19186,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
@@ -19196,13 +19216,13 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
@@ -19226,19 +19246,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19256,19 +19276,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>32</v>
@@ -19286,19 +19306,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
@@ -19316,19 +19336,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
@@ -19341,72 +19361,72 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>552</v>
+        <v>1223</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>627</v>
+        <v>1130</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H455" s="23">
-        <v>46081</v>
+        <v>46105</v>
       </c>
       <c r="I455" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>552</v>
+        <v>1224</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>627</v>
+        <v>1129</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H456" s="23">
-        <v>46081</v>
+        <v>46105</v>
       </c>
       <c r="I456" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
@@ -19431,12 +19451,12 @@
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
@@ -19461,12 +19481,12 @@
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19491,12 +19511,12 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19521,12 +19541,12 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19551,12 +19571,12 @@
       </c>
       <c r="J461" s="24"/>
     </row>
-    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19581,12 +19601,12 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19611,12 +19631,12 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19641,12 +19661,12 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19671,12 +19691,12 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19701,12 +19721,12 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19731,12 +19751,12 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="4">
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19761,12 +19781,12 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19791,12 +19811,12 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19821,12 +19841,12 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19851,12 +19871,12 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19881,12 +19901,12 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19911,12 +19931,12 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19941,12 +19961,12 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19971,12 +19991,12 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20001,12 +20021,12 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20031,12 +20051,12 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20061,12 +20081,12 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20091,12 +20111,12 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20121,12 +20141,12 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20151,12 +20171,12 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20181,12 +20201,12 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20211,12 +20231,12 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20241,12 +20261,12 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20271,18 +20291,18 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20301,18 +20321,18 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
@@ -22661,7 +22681,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F52858-2823-452D-BCF6-66DB57BCB516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0998ED-032F-4112-A15C-E542BE0B7BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4274" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4274" uniqueCount="1240">
   <si>
     <t>INDICE</t>
   </si>
@@ -2764,9 +2764,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>INSTALADA SEDUC TESOURARIA 31/10/2025;</t>
-  </si>
-  <si>
     <t>FRAGMENTADORA</t>
   </si>
   <si>
@@ -3743,13 +3740,31 @@
   </si>
   <si>
     <t>INSTALADA 20/10/2025 SOLAGOS ADM; INSTALADA JOAO AUGUSTO CHAVES 26/02/2026; INSTALADA UBS POSSE 25/03/2026;</t>
+  </si>
+  <si>
+    <t>XC75051312</t>
+  </si>
+  <si>
+    <t>XC75051320</t>
+  </si>
+  <si>
+    <t>E.M. DR. JOAO VASCONCELLOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEDUC - TESOURARIA </t>
+  </si>
+  <si>
+    <t>UBS - VILA CANAA</t>
+  </si>
+  <si>
+    <t>INSTALADA SEDUC TESOURARIA 31/10/2025; INSTALADA UBS VILA CANAA 27/03/2026;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4732,7 +4747,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J487" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
+  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="PAÇO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
@@ -5084,7 +5105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
   <dimension ref="A1:J487"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.109375" style="2" bestFit="1" customWidth="1"/>
@@ -5099,7 +5120,7 @@
     <col min="11" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5131,7 +5152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" hidden="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5163,7 +5184,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" hidden="1">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5195,7 +5216,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" hidden="1">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5227,7 +5248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" hidden="1">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5259,7 +5280,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5291,7 +5312,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5323,7 +5344,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5355,7 +5376,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" hidden="1">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5385,7 +5406,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5415,12 +5436,12 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5444,15 +5465,15 @@
         <v>593</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5479,7 +5500,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5511,7 +5532,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -5528,7 +5549,7 @@
         <v>359</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5540,10 +5561,10 @@
         <v>593</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -5575,7 +5596,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5592,7 +5613,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5604,7 +5625,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -5636,7 +5657,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" hidden="1">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -5668,7 +5689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -5700,7 +5721,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" hidden="1">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -5717,7 +5738,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5729,10 +5750,10 @@
         <v>593</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -5764,7 +5785,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5781,7 +5802,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5793,10 +5814,10 @@
         <v>593</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -5828,7 +5849,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -5860,7 +5881,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -5892,7 +5913,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" hidden="1">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -5921,7 +5942,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" hidden="1">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -5950,7 +5971,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" hidden="1">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -5982,7 +6003,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -6011,10 +6032,10 @@
         <v>593</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -6046,7 +6067,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -6078,7 +6099,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" hidden="1">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6110,7 +6131,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6142,7 +6163,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" hidden="1">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6174,7 +6195,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -6206,7 +6227,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -6220,7 +6241,7 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>869</v>
@@ -6238,7 +6259,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6267,7 +6288,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -6299,7 +6320,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -6331,7 +6352,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -6363,7 +6384,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -6395,7 +6416,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -6427,7 +6448,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -6459,7 +6480,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -6491,7 +6512,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -6520,7 +6541,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -6552,7 +6573,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -6584,7 +6605,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -6616,7 +6637,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -6645,7 +6666,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -6674,7 +6695,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -6706,12 +6727,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6738,12 +6759,12 @@
         <v>649</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6770,12 +6791,12 @@
         <v>650</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6787,7 +6808,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6802,7 +6823,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -6831,7 +6852,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -6860,7 +6881,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -6889,7 +6910,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -6918,7 +6939,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -6947,7 +6968,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -6976,7 +6997,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -7008,7 +7029,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -7040,7 +7061,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -7069,7 +7090,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -7101,7 +7122,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -7130,7 +7151,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" hidden="1">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -7159,7 +7180,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -7188,7 +7209,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -7217,7 +7238,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -7249,7 +7270,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -7281,7 +7302,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -7310,7 +7331,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" hidden="1">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -7327,7 +7348,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7342,7 +7363,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -7374,7 +7395,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -7406,7 +7427,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -7435,7 +7456,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -7467,7 +7488,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -7499,7 +7520,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -7531,7 +7552,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -7563,7 +7584,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -7577,7 +7598,7 @@
         <v>680</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7595,7 +7616,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -7609,7 +7630,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7627,7 +7648,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -7641,7 +7662,7 @@
         <v>681</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7653,7 +7674,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -7667,7 +7688,7 @@
         <v>682</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7679,7 +7700,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -7693,7 +7714,7 @@
         <v>683</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7705,7 +7726,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -7719,7 +7740,7 @@
         <v>684</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7737,7 +7758,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -7751,7 +7772,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7769,7 +7790,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -7783,7 +7804,7 @@
         <v>685</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7801,7 +7822,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -7815,7 +7836,7 @@
         <v>686</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7833,7 +7854,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -7847,7 +7868,7 @@
         <v>687</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7862,7 +7883,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -7876,10 +7897,10 @@
         <v>688</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -7891,10 +7912,10 @@
         <v>593</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -7908,7 +7929,7 @@
         <v>689</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7926,7 +7947,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -7940,7 +7961,7 @@
         <v>690</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7952,7 +7973,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -7966,7 +7987,7 @@
         <v>691</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -7978,7 +7999,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -7992,7 +8013,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -8010,7 +8031,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -8021,10 +8042,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>1003</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>1004</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -8039,7 +8060,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -8068,7 +8089,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -8097,7 +8118,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -8126,7 +8147,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -8158,7 +8179,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -8190,7 +8211,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -8222,7 +8243,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8239,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8251,10 +8272,10 @@
         <v>593</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -8286,7 +8307,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -8318,7 +8339,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -8350,7 +8371,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -8382,7 +8403,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -8414,7 +8435,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -8425,7 +8446,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8442,7 +8463,7 @@
       </c>
       <c r="J108" s="24"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -8474,7 +8495,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -8506,7 +8527,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -8538,7 +8559,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -8570,7 +8591,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -8602,7 +8623,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -8634,7 +8655,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -8666,7 +8687,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -8698,7 +8719,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -8730,7 +8751,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -8762,7 +8783,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -8794,7 +8815,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -8826,7 +8847,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -8858,7 +8879,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -8890,7 +8911,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8907,7 +8928,7 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -8919,7 +8940,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8936,7 +8957,7 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>32</v>
@@ -8951,7 +8972,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -8983,7 +9004,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" hidden="1">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -9000,7 +9021,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -9015,7 +9036,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -9047,7 +9068,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -9079,7 +9100,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -9111,7 +9132,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -9125,10 +9146,10 @@
         <v>233</v>
       </c>
       <c r="E130" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="F130" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9143,7 +9164,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -9175,7 +9196,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" hidden="1">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -9192,7 +9213,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9207,7 +9228,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" hidden="1">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -9224,7 +9245,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9236,10 +9257,10 @@
         <v>593</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" hidden="1">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -9256,7 +9277,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9271,7 +9292,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9288,7 +9309,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9300,10 +9321,10 @@
         <v>593</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" hidden="1">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -9320,7 +9341,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9335,7 +9356,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -9367,7 +9388,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -9384,7 +9405,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9396,10 +9417,10 @@
         <v>593</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" hidden="1">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9428,10 +9449,10 @@
         <v>671</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" hidden="1">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -9463,7 +9484,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9480,7 +9501,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>14</v>
@@ -9495,7 +9516,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9512,7 +9533,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9527,7 +9548,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9544,7 +9565,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9556,10 +9577,10 @@
         <v>593</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9570,13 +9591,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9588,10 +9609,10 @@
         <v>593</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9608,7 +9629,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9623,7 +9644,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9640,7 +9661,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>14</v>
@@ -9655,7 +9676,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9672,7 +9693,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9687,7 +9708,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9704,7 +9725,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9719,7 +9740,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -9748,10 +9769,10 @@
         <v>593</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" hidden="1">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -9783,7 +9804,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" hidden="1">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -9815,7 +9836,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9832,7 +9853,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>14</v>
@@ -9844,10 +9865,10 @@
         <v>593</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" hidden="1">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -9879,7 +9900,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" hidden="1">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -9908,10 +9929,10 @@
         <v>593</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" hidden="1">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -9943,7 +9964,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -9972,7 +9993,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" hidden="1">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -10001,7 +10022,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -10028,7 +10049,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -10045,7 +10066,7 @@
         <v>359</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -10057,10 +10078,10 @@
         <v>593</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" hidden="1">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -10089,7 +10110,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10121,7 +10142,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -10153,7 +10174,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -10182,10 +10203,10 @@
         <v>593</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" hidden="1">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10217,7 +10238,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -10246,7 +10267,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10275,7 +10296,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10307,7 +10328,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -10321,7 +10342,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10333,7 +10354,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -10347,10 +10368,10 @@
         <v>846</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10363,7 +10384,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10392,10 +10413,10 @@
         <v>593</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" hidden="1">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -10409,10 +10430,10 @@
         <v>293</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10424,7 +10445,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -10438,10 +10459,10 @@
         <v>294</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -10453,7 +10474,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -10482,7 +10503,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -10511,7 +10532,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -10540,7 +10561,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -10569,7 +10590,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" hidden="1">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -10598,7 +10619,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -10627,7 +10648,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -10656,7 +10677,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -10685,7 +10706,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -10714,7 +10735,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -10743,7 +10764,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1">
       <c r="A183" s="4">
         <v>182</v>
       </c>
@@ -10772,7 +10793,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1">
       <c r="A184" s="4">
         <v>183</v>
       </c>
@@ -10801,7 +10822,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1">
       <c r="A185" s="4">
         <v>184</v>
       </c>
@@ -10830,7 +10851,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1">
       <c r="A186" s="4">
         <v>185</v>
       </c>
@@ -10859,7 +10880,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" hidden="1">
       <c r="A187" s="4">
         <v>186</v>
       </c>
@@ -10888,7 +10909,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" hidden="1">
       <c r="A188" s="4">
         <v>187</v>
       </c>
@@ -10917,7 +10938,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1">
       <c r="A189" s="4">
         <v>188</v>
       </c>
@@ -10946,7 +10967,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" hidden="1">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -10975,7 +10996,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" hidden="1">
       <c r="A191" s="4">
         <v>190</v>
       </c>
@@ -11004,7 +11025,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" hidden="1">
       <c r="A192" s="4">
         <v>191</v>
       </c>
@@ -11033,7 +11054,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" s="4">
         <v>192</v>
       </c>
@@ -11062,7 +11083,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" s="4">
         <v>193</v>
       </c>
@@ -11091,7 +11112,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" s="4">
         <v>194</v>
       </c>
@@ -11123,7 +11144,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" s="4">
         <v>195</v>
       </c>
@@ -11137,10 +11158,10 @@
         <v>322</v>
       </c>
       <c r="E196" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="F196" s="4" t="s">
         <v>995</v>
-      </c>
-      <c r="F196" s="4" t="s">
-        <v>996</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11155,7 +11176,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197" s="4">
         <v>196</v>
       </c>
@@ -11187,7 +11208,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1">
       <c r="A198" s="4">
         <v>197</v>
       </c>
@@ -11198,7 +11219,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11216,10 +11237,10 @@
         <v>593</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" hidden="1">
       <c r="A199" s="4">
         <v>198</v>
       </c>
@@ -11233,10 +11254,10 @@
         <v>324</v>
       </c>
       <c r="E199" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="F199" s="4" t="s">
         <v>995</v>
-      </c>
-      <c r="F199" s="4" t="s">
-        <v>996</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11251,7 +11272,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1">
       <c r="A200" s="4">
         <v>199</v>
       </c>
@@ -11268,7 +11289,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11283,7 +11304,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1">
       <c r="A201" s="4">
         <v>200</v>
       </c>
@@ -11300,7 +11321,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11312,10 +11333,10 @@
         <v>593</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" hidden="1">
       <c r="A202" s="4">
         <v>201</v>
       </c>
@@ -11347,7 +11368,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1">
       <c r="A203" s="4">
         <v>202</v>
       </c>
@@ -11379,7 +11400,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1">
       <c r="A204" s="4">
         <v>203</v>
       </c>
@@ -11390,13 +11411,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11408,10 +11429,10 @@
         <v>593</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" hidden="1">
       <c r="A205" s="4">
         <v>204</v>
       </c>
@@ -11440,10 +11461,10 @@
         <v>593</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" hidden="1">
       <c r="A206" s="4">
         <v>205</v>
       </c>
@@ -11475,7 +11496,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1">
       <c r="A207" s="4">
         <v>206</v>
       </c>
@@ -11492,7 +11513,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11504,10 +11525,10 @@
         <v>593</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" hidden="1">
       <c r="A208" s="4">
         <v>207</v>
       </c>
@@ -11524,7 +11545,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11539,7 +11560,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11556,7 +11577,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11568,10 +11589,10 @@
         <v>593</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" hidden="1">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11600,10 +11621,10 @@
         <v>593</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" hidden="1">
       <c r="A211" s="4">
         <v>210</v>
       </c>
@@ -11635,7 +11656,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" hidden="1">
       <c r="A212" s="4">
         <v>211</v>
       </c>
@@ -11667,7 +11688,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1">
       <c r="A213" s="4">
         <v>212</v>
       </c>
@@ -11699,7 +11720,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" hidden="1">
       <c r="A214" s="4">
         <v>213</v>
       </c>
@@ -11731,7 +11752,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" hidden="1">
       <c r="A215" s="4">
         <v>214</v>
       </c>
@@ -11760,10 +11781,10 @@
         <v>593</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" hidden="1">
       <c r="A216" s="4">
         <v>215</v>
       </c>
@@ -11780,7 +11801,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11792,10 +11813,10 @@
         <v>593</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" hidden="1">
       <c r="A217" s="4">
         <v>216</v>
       </c>
@@ -11827,7 +11848,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" hidden="1">
       <c r="A218" s="4">
         <v>217</v>
       </c>
@@ -11844,7 +11865,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11859,7 +11880,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" hidden="1">
       <c r="A219" s="4">
         <v>218</v>
       </c>
@@ -11876,7 +11897,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11888,10 +11909,10 @@
         <v>593</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" hidden="1">
       <c r="A220" s="4">
         <v>219</v>
       </c>
@@ -11908,7 +11929,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11920,10 +11941,10 @@
         <v>593</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" hidden="1">
       <c r="A221" s="4">
         <v>220</v>
       </c>
@@ -11940,7 +11961,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>14</v>
@@ -11955,7 +11976,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1">
       <c r="A222" s="4">
         <v>221</v>
       </c>
@@ -11972,7 +11993,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -11987,7 +12008,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -12004,7 +12025,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -12019,7 +12040,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1">
       <c r="A224" s="4">
         <v>223</v>
       </c>
@@ -12051,7 +12072,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" hidden="1">
       <c r="A225" s="4">
         <v>224</v>
       </c>
@@ -12083,7 +12104,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" hidden="1">
       <c r="A226" s="4">
         <v>225</v>
       </c>
@@ -12115,7 +12136,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" hidden="1">
       <c r="A227" s="4">
         <v>226</v>
       </c>
@@ -12132,7 +12153,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12144,10 +12165,10 @@
         <v>593</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" hidden="1">
       <c r="A228" s="4">
         <v>227</v>
       </c>
@@ -12179,7 +12200,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" hidden="1">
       <c r="A229" s="4">
         <v>228</v>
       </c>
@@ -12193,10 +12214,10 @@
         <v>364</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1137</v>
+        <v>25</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>14</v>
@@ -12208,10 +12229,10 @@
         <v>593</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" hidden="1">
       <c r="A230" s="4">
         <v>229</v>
       </c>
@@ -12228,7 +12249,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12243,7 +12264,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" ht="15.6" hidden="1">
       <c r="A231" s="4">
         <v>230</v>
       </c>
@@ -12260,7 +12281,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12272,10 +12293,10 @@
         <v>593</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" hidden="1">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -12292,7 +12313,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12304,10 +12325,10 @@
         <v>671</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" hidden="1">
       <c r="A233" s="4">
         <v>232</v>
       </c>
@@ -12324,7 +12345,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12339,7 +12360,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" hidden="1">
       <c r="A234" s="4">
         <v>233</v>
       </c>
@@ -12356,7 +12377,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12368,10 +12389,10 @@
         <v>593</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" hidden="1">
       <c r="A235" s="4">
         <v>234</v>
       </c>
@@ -12400,10 +12421,10 @@
         <v>593</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" hidden="1">
       <c r="A236" s="4">
         <v>235</v>
       </c>
@@ -12417,10 +12438,10 @@
         <v>592</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12433,7 +12454,7 @@
       </c>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1">
       <c r="A237" s="4">
         <v>236</v>
       </c>
@@ -12465,7 +12486,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" hidden="1">
       <c r="A238" s="4">
         <v>237</v>
       </c>
@@ -12497,7 +12518,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1">
       <c r="A239" s="4">
         <v>238</v>
       </c>
@@ -12529,7 +12550,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12546,7 +12567,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12558,15 +12579,15 @@
         <v>593</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" hidden="1">
       <c r="A241" s="4">
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12578,7 +12599,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12593,7 +12614,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" hidden="1">
       <c r="A242" s="4">
         <v>241</v>
       </c>
@@ -12622,7 +12643,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" hidden="1">
       <c r="A243" s="4">
         <v>242</v>
       </c>
@@ -12654,7 +12675,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" hidden="1">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12683,10 +12704,10 @@
         <v>593</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" hidden="1">
       <c r="A245" s="4">
         <v>244</v>
       </c>
@@ -12718,7 +12739,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" hidden="1">
       <c r="A246" s="4">
         <v>245</v>
       </c>
@@ -12732,7 +12753,7 @@
         <v>386</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>387</v>
@@ -12747,7 +12768,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" hidden="1">
       <c r="A247" s="4">
         <v>246</v>
       </c>
@@ -12761,7 +12782,7 @@
         <v>694</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>389</v>
@@ -12779,7 +12800,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" hidden="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -12793,7 +12814,7 @@
         <v>390</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>391</v>
@@ -12808,7 +12829,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" hidden="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -12822,7 +12843,7 @@
         <v>392</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>393</v>
@@ -12837,7 +12858,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" hidden="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12869,7 +12890,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" hidden="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -12898,10 +12919,10 @@
         <v>593</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" hidden="1">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -12933,7 +12954,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12950,7 +12971,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -12965,7 +12986,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" hidden="1">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -12997,7 +13018,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" hidden="1">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -13029,7 +13050,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" hidden="1">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -13058,10 +13079,10 @@
         <v>593</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" hidden="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -13093,7 +13114,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" hidden="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -13125,7 +13146,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" hidden="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13157,7 +13178,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" hidden="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -13189,7 +13210,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" hidden="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -13218,10 +13239,10 @@
         <v>593</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" hidden="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13253,7 +13274,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" hidden="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -13285,7 +13306,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" hidden="1">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -13299,10 +13320,10 @@
         <v>416</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13317,7 +13338,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" hidden="1">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -13349,7 +13370,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" hidden="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -13381,7 +13402,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" hidden="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -13413,7 +13434,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" hidden="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -13445,7 +13466,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" hidden="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -13462,7 +13483,7 @@
         <v>359</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13474,10 +13495,10 @@
         <v>593</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13494,7 +13515,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
@@ -13509,7 +13530,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13526,7 +13547,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -13541,7 +13562,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13558,7 +13579,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -13573,7 +13594,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13590,7 +13611,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13605,7 +13626,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13622,7 +13643,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -13637,7 +13658,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13654,7 +13675,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13669,7 +13690,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13686,7 +13707,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13701,7 +13722,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13718,7 +13739,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13733,7 +13754,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13750,7 +13771,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -13765,7 +13786,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13782,7 +13803,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13797,7 +13818,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13814,7 +13835,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13829,7 +13850,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13846,7 +13867,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -13861,7 +13882,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13878,7 +13899,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13893,7 +13914,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13910,7 +13931,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13922,10 +13943,10 @@
         <v>671</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13942,7 +13963,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13957,7 +13978,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13974,7 +13995,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -13989,7 +14010,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -14006,7 +14027,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -14021,7 +14042,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14038,7 +14059,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -14053,7 +14074,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" hidden="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -14085,7 +14106,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" hidden="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -14117,7 +14138,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" hidden="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -14149,7 +14170,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" hidden="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -14181,7 +14202,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" hidden="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -14213,7 +14234,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" hidden="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -14245,7 +14266,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" hidden="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -14277,7 +14298,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" hidden="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -14309,7 +14330,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" hidden="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -14341,7 +14362,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" hidden="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -14373,7 +14394,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:10" hidden="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -14405,7 +14426,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:10" hidden="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -14437,7 +14458,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:10" hidden="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -14469,7 +14490,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:10" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14501,7 +14522,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:10" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14530,10 +14551,10 @@
         <v>593</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14565,7 +14586,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:10">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14582,7 +14603,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14597,7 +14618,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:10" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14626,10 +14647,10 @@
         <v>593</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" hidden="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -14661,7 +14682,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:10" hidden="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -14693,7 +14714,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:10" hidden="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -14725,7 +14746,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:10" hidden="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -14757,7 +14778,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:10" hidden="1">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -14789,7 +14810,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:10">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14806,7 +14827,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14821,7 +14842,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:10" hidden="1">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -14853,7 +14874,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:10" hidden="1">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -14885,7 +14906,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:10" hidden="1">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -14917,7 +14938,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:10">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14934,7 +14955,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -14949,7 +14970,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:10">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14966,7 +14987,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14981,7 +15002,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:10">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -14998,7 +15019,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -15013,7 +15034,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:10">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15030,7 +15051,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -15045,7 +15066,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:10">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15062,7 +15083,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -15077,7 +15098,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:10">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15094,7 +15115,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -15109,7 +15130,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:10">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15126,7 +15147,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -15141,7 +15162,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:10">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15158,7 +15179,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15173,7 +15194,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:10">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15190,7 +15211,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15205,7 +15226,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15222,7 +15243,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -15237,7 +15258,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15254,7 +15275,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15269,7 +15290,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15286,7 +15307,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15301,7 +15322,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15318,7 +15339,7 @@
         <v>71</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15333,7 +15354,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15350,7 +15371,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15365,7 +15386,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15382,7 +15403,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15397,7 +15418,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15414,7 +15435,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15429,7 +15450,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15461,7 +15482,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15478,7 +15499,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -15493,7 +15514,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15510,7 +15531,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15525,7 +15546,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15542,7 +15563,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15557,7 +15578,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15574,7 +15595,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15589,7 +15610,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15606,7 +15627,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15621,7 +15642,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15638,7 +15659,7 @@
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -15653,7 +15674,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:10" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15685,7 +15706,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:10" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15717,7 +15738,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:10" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15749,7 +15770,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:10" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15781,7 +15802,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:10" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15813,7 +15834,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:10" hidden="1">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15845,7 +15866,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:10" hidden="1">
       <c r="A344" s="4">
         <v>343</v>
       </c>
@@ -15877,7 +15898,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15894,7 +15915,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15906,10 +15927,10 @@
         <v>593</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -15941,7 +15962,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -15973,7 +15994,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -16005,7 +16026,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:10" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16037,7 +16058,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:10" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16069,7 +16090,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:10" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16101,7 +16122,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:10" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16130,10 +16151,10 @@
         <v>593</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="353" spans="1:10" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16162,10 +16183,10 @@
         <v>593</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="354" spans="1:10" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16197,7 +16218,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:10" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16229,7 +16250,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:10" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16261,7 +16282,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:10" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16293,7 +16314,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:10" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16325,7 +16346,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:10" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16357,7 +16378,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:10" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16374,7 +16395,7 @@
         <v>80</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
@@ -16389,7 +16410,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:10" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16400,7 +16421,7 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>80</v>
@@ -16418,10 +16439,10 @@
         <v>593</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16432,13 +16453,13 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>14</v>
@@ -16450,10 +16471,10 @@
         <v>593</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="363" spans="1:10" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16464,13 +16485,13 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
@@ -16482,10 +16503,10 @@
         <v>593</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16496,13 +16517,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16514,10 +16535,10 @@
         <v>593</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16528,13 +16549,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16546,10 +16567,10 @@
         <v>671</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16560,13 +16581,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16578,10 +16599,10 @@
         <v>671</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16592,13 +16613,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16610,10 +16631,10 @@
         <v>593</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="368" spans="1:10" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16624,7 +16645,7 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>80</v>
@@ -16642,10 +16663,10 @@
         <v>671</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16656,13 +16677,13 @@
         <v>11</v>
       </c>
       <c r="D369" s="38" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
@@ -16674,10 +16695,10 @@
         <v>671</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16688,7 +16709,7 @@
         <v>11</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>80</v>
@@ -16706,10 +16727,10 @@
         <v>671</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10">
       <c r="A371" s="4">
         <v>370</v>
       </c>
@@ -16726,7 +16747,7 @@
         <v>71</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16738,10 +16759,10 @@
         <v>593</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16773,7 +16794,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:10" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16790,7 +16811,7 @@
         <v>80</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
@@ -16802,10 +16823,10 @@
         <v>593</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="374" spans="1:10" hidden="1">
       <c r="A374" s="4">
         <v>373</v>
       </c>
@@ -16834,10 +16855,10 @@
         <v>593</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="375" spans="1:10" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
@@ -16867,7 +16888,7 @@
       </c>
       <c r="J375" s="24"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:10" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16899,7 +16920,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:10" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16916,7 +16937,7 @@
         <v>80</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G377" s="2" t="s">
         <v>14</v>
@@ -16928,10 +16949,10 @@
         <v>593</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="378" spans="1:10" hidden="1">
       <c r="A378" s="4">
         <v>377</v>
       </c>
@@ -16948,7 +16969,7 @@
         <v>80</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
@@ -16960,10 +16981,10 @@
         <v>593</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="379" spans="1:10" hidden="1">
       <c r="A379" s="4">
         <v>378</v>
       </c>
@@ -16995,7 +17016,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:10" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -17027,7 +17048,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:10" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -17044,7 +17065,7 @@
         <v>80</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="G381" s="2" t="s">
         <v>14</v>
@@ -17056,10 +17077,10 @@
         <v>593</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -17076,7 +17097,7 @@
         <v>80</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
@@ -17088,10 +17109,10 @@
         <v>593</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10">
       <c r="A383" s="4">
         <v>382</v>
       </c>
@@ -17108,7 +17129,7 @@
         <v>71</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
@@ -17120,10 +17141,10 @@
         <v>593</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="384" spans="1:10" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17155,7 +17176,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:10" hidden="1">
       <c r="A385" s="4">
         <v>384</v>
       </c>
@@ -17187,7 +17208,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:10" hidden="1">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -17204,7 +17225,7 @@
         <v>19</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
@@ -17219,7 +17240,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:10" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17248,10 +17269,10 @@
         <v>593</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17262,13 +17283,13 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
@@ -17280,10 +17301,10 @@
         <v>671</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17294,13 +17315,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17312,10 +17333,10 @@
         <v>593</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17326,7 +17347,7 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
@@ -17344,10 +17365,10 @@
         <v>593</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17358,13 +17379,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17376,10 +17397,10 @@
         <v>593</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17390,13 +17411,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17408,10 +17429,10 @@
         <v>593</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
       <c r="A393" s="4">
         <v>392</v>
       </c>
@@ -17422,13 +17443,13 @@
         <v>11</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
@@ -17440,10 +17461,10 @@
         <v>593</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="394" spans="1:10" hidden="1">
       <c r="A394" s="4">
         <v>393</v>
       </c>
@@ -17475,7 +17496,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:10" hidden="1">
       <c r="A395" s="4">
         <v>394</v>
       </c>
@@ -17507,7 +17528,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:10" hidden="1">
       <c r="A396" s="4">
         <v>395</v>
       </c>
@@ -17539,7 +17560,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:10" hidden="1">
       <c r="A397" s="4">
         <v>396</v>
       </c>
@@ -17571,7 +17592,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:10" hidden="1">
       <c r="A398" s="4">
         <v>397</v>
       </c>
@@ -17603,7 +17624,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:10" hidden="1">
       <c r="A399" s="4">
         <v>398</v>
       </c>
@@ -17635,7 +17656,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:10" hidden="1">
       <c r="A400" s="4">
         <v>399</v>
       </c>
@@ -17667,7 +17688,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:10" hidden="1">
       <c r="A401" s="4">
         <v>400</v>
       </c>
@@ -17699,7 +17720,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:10" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17731,7 +17752,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:10" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17742,13 +17763,13 @@
         <v>11</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
@@ -17760,10 +17781,10 @@
         <v>593</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17774,13 +17795,13 @@
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
@@ -17792,10 +17813,10 @@
         <v>593</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17806,13 +17827,13 @@
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17824,10 +17845,10 @@
         <v>593</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17838,13 +17859,13 @@
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
@@ -17856,10 +17877,10 @@
         <v>593</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
@@ -17870,13 +17891,13 @@
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
@@ -17888,10 +17909,10 @@
         <v>593</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="408" spans="1:10" hidden="1">
       <c r="A408" s="4">
         <v>407</v>
       </c>
@@ -17923,7 +17944,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:10" hidden="1">
       <c r="A409" s="4">
         <v>408</v>
       </c>
@@ -17955,7 +17976,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:10" hidden="1">
       <c r="A410" s="4">
         <v>409</v>
       </c>
@@ -17987,7 +18008,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:10" hidden="1">
       <c r="A411" s="4">
         <v>410</v>
       </c>
@@ -18019,7 +18040,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:10" hidden="1">
       <c r="A412" s="4">
         <v>411</v>
       </c>
@@ -18051,7 +18072,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:10" hidden="1">
       <c r="A413" s="4">
         <v>412</v>
       </c>
@@ -18083,7 +18104,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:10" hidden="1">
       <c r="A414" s="4">
         <v>413</v>
       </c>
@@ -18115,7 +18136,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:10" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18147,7 +18168,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:10" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18161,10 +18182,10 @@
         <v>886</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>585</v>
+        <v>1238</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
@@ -18176,10 +18197,10 @@
         <v>671</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18190,13 +18211,13 @@
         <v>11</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>14</v>
@@ -18208,10 +18229,10 @@
         <v>593</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="418" spans="1:10" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18222,13 +18243,13 @@
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
@@ -18240,10 +18261,10 @@
         <v>593</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="419" spans="1:10" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18254,13 +18275,13 @@
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18272,10 +18293,10 @@
         <v>593</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18286,13 +18307,13 @@
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18304,10 +18325,10 @@
         <v>593</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18318,13 +18339,13 @@
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
@@ -18336,10 +18357,10 @@
         <v>593</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18350,13 +18371,13 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
@@ -18368,10 +18389,10 @@
         <v>593</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18382,13 +18403,13 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
@@ -18400,10 +18421,10 @@
         <v>593</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18414,13 +18435,13 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
@@ -18432,10 +18453,10 @@
         <v>671</v>
       </c>
       <c r="J424" s="3" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18446,13 +18467,13 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
@@ -18465,7 +18486,7 @@
       </c>
       <c r="J425" s="24"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:10" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18476,7 +18497,7 @@
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
@@ -18494,10 +18515,10 @@
         <v>593</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" hidden="1">
       <c r="A427" s="4">
         <v>426</v>
       </c>
@@ -18526,10 +18547,10 @@
         <v>593</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18546,7 +18567,7 @@
         <v>359</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
@@ -18558,10 +18579,10 @@
         <v>593</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -18578,7 +18599,7 @@
         <v>80</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
@@ -18590,10 +18611,10 @@
         <v>593</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18604,13 +18625,13 @@
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
@@ -18622,10 +18643,10 @@
         <v>593</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
@@ -18654,10 +18675,10 @@
         <v>593</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" hidden="1">
       <c r="A432" s="4">
         <v>431</v>
       </c>
@@ -18668,7 +18689,7 @@
         <v>11</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>359</v>
@@ -18686,10 +18707,10 @@
         <v>593</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" hidden="1">
       <c r="A433" s="4">
         <v>432</v>
       </c>
@@ -18700,7 +18721,7 @@
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>359</v>
@@ -18718,10 +18739,10 @@
         <v>593</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="434" spans="1:10" hidden="1">
       <c r="A434" s="4">
         <v>433</v>
       </c>
@@ -18732,13 +18753,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
@@ -18750,10 +18771,10 @@
         <v>593</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="435" spans="1:10" hidden="1">
       <c r="A435" s="4">
         <v>434</v>
       </c>
@@ -18764,13 +18785,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
@@ -18782,10 +18803,10 @@
         <v>593</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
@@ -18796,13 +18817,13 @@
         <v>11</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
@@ -18814,10 +18835,10 @@
         <v>593</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
@@ -18849,18 +18870,18 @@
         <v>672</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:10" hidden="1">
       <c r="A438" s="4">
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>19</v>
@@ -18878,21 +18899,21 @@
         <v>593</v>
       </c>
       <c r="J438" s="3" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="439" spans="1:10" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -18911,18 +18932,18 @@
       </c>
       <c r="J439" s="24"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:10" hidden="1">
       <c r="A440" s="4">
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -18941,18 +18962,18 @@
       </c>
       <c r="J440" s="24"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:10" hidden="1">
       <c r="A441" s="4">
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -18971,18 +18992,18 @@
       </c>
       <c r="J441" s="24"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:10" hidden="1">
       <c r="A442" s="4">
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>23</v>
@@ -19001,24 +19022,24 @@
       </c>
       <c r="J442" s="24"/>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:10" hidden="1">
       <c r="A443" s="4">
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
@@ -19031,24 +19052,24 @@
       </c>
       <c r="J443" s="24"/>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:10" hidden="1">
       <c r="A444" s="4">
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
@@ -19061,12 +19082,12 @@
       </c>
       <c r="J444" s="24"/>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:10" hidden="1">
       <c r="A445" s="4">
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19091,12 +19112,12 @@
       </c>
       <c r="J445" s="24"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:10" hidden="1">
       <c r="A446" s="4">
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19121,12 +19142,12 @@
       </c>
       <c r="J446" s="24"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:10" hidden="1">
       <c r="A447" s="4">
         <v>446</v>
       </c>
       <c r="B447" s="53" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>88</v>
@@ -19151,24 +19172,24 @@
       </c>
       <c r="J447" s="24"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:10" hidden="1">
       <c r="A448" s="4">
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
@@ -19181,24 +19202,24 @@
       </c>
       <c r="J448" s="24"/>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:10" hidden="1">
       <c r="A449" s="4">
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
@@ -19211,24 +19232,24 @@
       </c>
       <c r="J449" s="24"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:10" hidden="1">
       <c r="A450" s="4">
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>32</v>
@@ -19241,24 +19262,24 @@
       </c>
       <c r="J450" s="24"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:10" hidden="1">
       <c r="A451" s="4">
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19271,24 +19292,24 @@
       </c>
       <c r="J451" s="24"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:10" hidden="1">
       <c r="A452" s="4">
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G452" s="2" t="s">
         <v>32</v>
@@ -19301,24 +19322,24 @@
       </c>
       <c r="J452" s="24"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:10" hidden="1">
       <c r="A453" s="4">
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
@@ -19331,24 +19352,24 @@
       </c>
       <c r="J453" s="24"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:10" hidden="1">
       <c r="A454" s="4">
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
@@ -19361,24 +19382,24 @@
       </c>
       <c r="J454" s="24"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:10" hidden="1">
       <c r="A455" s="4">
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>32</v>
@@ -19391,24 +19412,24 @@
       </c>
       <c r="J455" s="24"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:10" hidden="1">
       <c r="A456" s="4">
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>32</v>
@@ -19421,72 +19442,72 @@
       </c>
       <c r="J456" s="24"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:10" hidden="1">
       <c r="A457" s="4">
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>552</v>
+        <v>1235</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>627</v>
+        <v>1236</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H457" s="23">
-        <v>46081</v>
+        <v>46108</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J457" s="24"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:10" hidden="1">
       <c r="A458" s="4">
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>552</v>
+        <v>1234</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>627</v>
+        <v>1237</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H458" s="23">
-        <v>46081</v>
+        <v>46108</v>
       </c>
       <c r="I458" s="4" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
       <c r="J458" s="24"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:10" hidden="1">
       <c r="A459" s="4">
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
@@ -19511,12 +19532,12 @@
       </c>
       <c r="J459" s="24"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:10" hidden="1">
       <c r="A460" s="4">
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19541,12 +19562,12 @@
       </c>
       <c r="J460" s="24"/>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:10" hidden="1">
       <c r="A461" s="4">
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19571,12 +19592,12 @@
       </c>
       <c r="J461" s="24"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:10" hidden="1">
       <c r="A462" s="4">
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19601,12 +19622,12 @@
       </c>
       <c r="J462" s="24"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:10" hidden="1">
       <c r="A463" s="4">
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19631,12 +19652,12 @@
       </c>
       <c r="J463" s="24"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:10" hidden="1">
       <c r="A464" s="4">
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19661,12 +19682,12 @@
       </c>
       <c r="J464" s="24"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:10" hidden="1">
       <c r="A465" s="4">
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19691,12 +19712,12 @@
       </c>
       <c r="J465" s="24"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:10" hidden="1">
       <c r="A466" s="4">
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19721,12 +19742,12 @@
       </c>
       <c r="J466" s="24"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:10" hidden="1">
       <c r="A467" s="4">
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19751,12 +19772,12 @@
       </c>
       <c r="J467" s="24"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:10" hidden="1">
       <c r="A468" s="4">
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19781,12 +19802,12 @@
       </c>
       <c r="J468" s="24"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:10" hidden="1">
       <c r="A469" s="4">
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19811,12 +19832,12 @@
       </c>
       <c r="J469" s="24"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:10" hidden="1">
       <c r="A470" s="4">
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19841,12 +19862,12 @@
       </c>
       <c r="J470" s="24"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:10" hidden="1">
       <c r="A471" s="4">
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19871,12 +19892,12 @@
       </c>
       <c r="J471" s="24"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:10" hidden="1">
       <c r="A472" s="4">
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19901,12 +19922,12 @@
       </c>
       <c r="J472" s="24"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:10" hidden="1">
       <c r="A473" s="4">
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19931,12 +19952,12 @@
       </c>
       <c r="J473" s="24"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:10" hidden="1">
       <c r="A474" s="4">
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19961,12 +19982,12 @@
       </c>
       <c r="J474" s="24"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:10" hidden="1">
       <c r="A475" s="4">
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19991,12 +20012,12 @@
       </c>
       <c r="J475" s="24"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:10" hidden="1">
       <c r="A476" s="4">
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20021,12 +20042,12 @@
       </c>
       <c r="J476" s="24"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:10" hidden="1">
       <c r="A477" s="4">
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20051,12 +20072,12 @@
       </c>
       <c r="J477" s="24"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:10" hidden="1">
       <c r="A478" s="4">
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20081,12 +20102,12 @@
       </c>
       <c r="J478" s="24"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:10" hidden="1">
       <c r="A479" s="4">
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20111,12 +20132,12 @@
       </c>
       <c r="J479" s="24"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:10" hidden="1">
       <c r="A480" s="4">
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20141,12 +20162,12 @@
       </c>
       <c r="J480" s="24"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:10" hidden="1">
       <c r="A481" s="4">
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20171,12 +20192,12 @@
       </c>
       <c r="J481" s="24"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:10" hidden="1">
       <c r="A482" s="4">
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20201,12 +20222,12 @@
       </c>
       <c r="J482" s="24"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:10" hidden="1">
       <c r="A483" s="4">
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20231,12 +20252,12 @@
       </c>
       <c r="J483" s="24"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:10" hidden="1">
       <c r="A484" s="4">
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20261,12 +20282,12 @@
       </c>
       <c r="J484" s="24"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:10" hidden="1">
       <c r="A485" s="4">
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
@@ -20291,18 +20312,18 @@
       </c>
       <c r="J485" s="24"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:10" hidden="1">
       <c r="A486" s="4">
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20321,18 +20342,18 @@
       </c>
       <c r="J486" s="24"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:10" hidden="1">
       <c r="A487" s="4">
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>23</v>
@@ -20413,7 +20434,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6771508-02DF-4FAC-B7A7-A6278CE7AE5B}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -20422,7 +20443,7 @@
     <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>527</v>
       </c>
@@ -20442,7 +20463,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
         <v>904</v>
       </c>
@@ -20453,7 +20474,7 @@
         <v>906</v>
       </c>
       <c r="D2" s="43" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E2" s="44" t="s">
         <v>907</v>
@@ -20462,7 +20483,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
         <v>904</v>
       </c>
@@ -20473,7 +20494,7 @@
         <v>906</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>907</v>
@@ -20482,7 +20503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
         <v>904</v>
       </c>
@@ -20493,7 +20514,7 @@
         <v>906</v>
       </c>
       <c r="D4" s="43" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E4" s="44" t="s">
         <v>907</v>
@@ -20502,7 +20523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
         <v>904</v>
       </c>
@@ -20513,7 +20534,7 @@
         <v>906</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E5" s="44" t="s">
         <v>907</v>
@@ -20522,7 +20543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
         <v>904</v>
       </c>
@@ -20533,7 +20554,7 @@
         <v>906</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E6" s="44" t="s">
         <v>907</v>
@@ -20542,7 +20563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
         <v>904</v>
       </c>
@@ -20553,7 +20574,7 @@
         <v>906</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E7" s="44" t="s">
         <v>907</v>
@@ -20562,7 +20583,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>532</v>
       </c>
@@ -20579,7 +20600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>532</v>
       </c>
@@ -20596,7 +20617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>532</v>
       </c>
@@ -20613,7 +20634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>532</v>
       </c>
@@ -20630,7 +20651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>532</v>
       </c>
@@ -20647,7 +20668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>532</v>
       </c>
@@ -20664,7 +20685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>532</v>
       </c>
@@ -20681,7 +20702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>532</v>
       </c>
@@ -20698,7 +20719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>532</v>
       </c>
@@ -20715,7 +20736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>532</v>
       </c>
@@ -20732,7 +20753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>532</v>
       </c>
@@ -20749,7 +20770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>532</v>
       </c>
@@ -20766,7 +20787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>532</v>
       </c>
@@ -20783,7 +20804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>537</v>
       </c>
@@ -20803,7 +20824,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>537</v>
       </c>
@@ -20823,7 +20844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>537</v>
       </c>
@@ -20843,7 +20864,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>537</v>
       </c>
@@ -20863,7 +20884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>537</v>
       </c>
@@ -20883,7 +20904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>537</v>
       </c>
@@ -20903,7 +20924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>537</v>
       </c>
@@ -20923,7 +20944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>550</v>
       </c>
@@ -20943,7 +20964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>554</v>
       </c>
@@ -20963,7 +20984,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>556</v>
       </c>
@@ -20983,7 +21004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>556</v>
       </c>
@@ -21003,7 +21024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>550</v>
       </c>
@@ -21035,7 +21056,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD4931DD-77FA-4EF6-BAB3-744C5E5D53EC}">
   <dimension ref="A1:XFC75"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -21052,7 +21073,7 @@
     <col min="16384" max="16384" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21084,7 +21105,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -21116,7 +21137,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -21148,7 +21169,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -21180,7 +21201,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -21212,7 +21233,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -21244,7 +21265,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -21276,7 +21297,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -21308,7 +21329,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -21340,7 +21361,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -21372,7 +21393,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -21404,7 +21425,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -21436,7 +21457,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -21468,7 +21489,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -21500,7 +21521,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -21532,7 +21553,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -21564,7 +21585,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -21596,7 +21617,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -21628,7 +21649,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -21660,7 +21681,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -21692,7 +21713,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -21724,7 +21745,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -21756,7 +21777,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -21788,7 +21809,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -21820,7 +21841,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -21850,7 +21871,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="4">
         <v>25</v>
       </c>
@@ -21880,7 +21901,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -21910,7 +21931,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -21940,7 +21961,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -21970,7 +21991,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -22000,7 +22021,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10">
       <c r="A31" s="4">
         <v>30</v>
       </c>
@@ -22030,7 +22051,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -22060,7 +22081,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -22090,7 +22111,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -22120,7 +22141,7 @@
       </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -22150,7 +22171,7 @@
       </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -22180,7 +22201,7 @@
       </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -22210,7 +22231,7 @@
       </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -22240,7 +22261,7 @@
       </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -22270,7 +22291,7 @@
       </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -22300,7 +22321,7 @@
       </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -22330,7 +22351,7 @@
       </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -22359,7 +22380,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -22391,15 +22412,15 @@
         <v>833</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="33">
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>908</v>
+      </c>
+      <c r="C44" s="33" t="s">
         <v>909</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>910</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
@@ -22420,18 +22441,18 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="18">
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>908</v>
+      </c>
+      <c r="C45" s="48" t="s">
         <v>909</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>910</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -22452,15 +22473,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="18">
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -22481,15 +22502,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="18">
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -22510,15 +22531,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="18">
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -22539,15 +22560,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="18">
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -22568,15 +22589,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="18">
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -22597,18 +22618,18 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="18">
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -22617,7 +22638,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -22629,10 +22650,10 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="3" customFormat="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -22661,10 +22682,10 @@
         <v>593</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" s="3" customFormat="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -22681,7 +22702,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -22696,102 +22717,102 @@
         <v>716</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" s="18"/>
       <c r="B54" s="21"/>
       <c r="C54" s="49"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="18"/>
       <c r="B55" s="21"/>
       <c r="C55" s="49"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="B56" s="21"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="B57" s="21"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="18"/>
       <c r="B58" s="22"/>
       <c r="C58" s="49"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" s="18"/>
       <c r="B59" s="22"/>
       <c r="C59" s="49"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="18"/>
       <c r="B60" s="22"/>
       <c r="C60" s="49"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10">
       <c r="A61" s="18"/>
       <c r="B61" s="22"/>
       <c r="C61" s="49"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="18"/>
       <c r="B62" s="22"/>
       <c r="C62" s="49"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10">
       <c r="A63" s="18"/>
       <c r="B63" s="22"/>
       <c r="C63" s="49"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" s="18"/>
       <c r="B64" s="22"/>
       <c r="C64" s="49"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3">
       <c r="A65" s="18"/>
       <c r="B65" s="22"/>
       <c r="C65" s="49"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3">
       <c r="A66" s="18"/>
       <c r="B66" s="22"/>
       <c r="C66" s="49"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3">
       <c r="A67" s="18"/>
       <c r="B67" s="22"/>
       <c r="C67" s="49"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3">
       <c r="A68" s="18"/>
       <c r="B68" s="22"/>
       <c r="C68" s="49"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3">
       <c r="A69" s="18"/>
       <c r="B69" s="22"/>
       <c r="C69" s="49"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3">
       <c r="A70" s="18"/>
       <c r="B70" s="22"/>
       <c r="C70" s="49"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3">
       <c r="A71" s="18"/>
       <c r="B71" s="22"/>
       <c r="C71" s="49"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3">
       <c r="B72" s="21"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3">
       <c r="B73" s="21"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3">
       <c r="B74" s="21"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3">
       <c r="B75" s="21"/>
     </row>
   </sheetData>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0998ED-032F-4112-A15C-E542BE0B7BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B094A80-6AF0-4D5E-84FE-D23D217D72A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="COMPUTER" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$487</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$486</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4274" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="1242">
   <si>
     <t>INDICE</t>
   </si>
@@ -1861,9 +1861,6 @@
     <t>U67030J3N175301</t>
   </si>
   <si>
-    <t>INSTALAÇÃO FEITA 30/06/2025 DECAD;</t>
-  </si>
-  <si>
     <t>U67030J3N174340</t>
   </si>
   <si>
@@ -2227,9 +2224,6 @@
     <t>U68089M4N395130</t>
   </si>
   <si>
-    <t>U68089M4N395118</t>
-  </si>
-  <si>
     <t>U68089M4N395116</t>
   </si>
   <si>
@@ -3019,9 +3013,6 @@
     <t>INSTALADA DIA 12/09/2024 - NO ANTIGO COLÉGIO MUNICIPAL GUSTAVO CAMPOS DA SILVEIRA - HYDRA; QUEIMOU A PLACA DA  FONTE HYDRA; RICOH 3004EX SUBISTITUIDA  3003; INSTALADA SEPOL 08/10/2025; RETIRADA DA SEPOL COM PROBLEMAS DE BANDEJA UNIDADE DE IMAGEM SISTEMA 12/12/2025;</t>
   </si>
   <si>
-    <t>INSTALAÇÃO FEITA 16/10/2025 UBS MATARUNA; RETIRADA UBS MATARUNA POIS QUEIMOU A IMPRESSORA 05/12/2025;</t>
-  </si>
-  <si>
     <t xml:space="preserve">OPERACIONAL </t>
   </si>
   <si>
@@ -3758,6 +3749,21 @@
   </si>
   <si>
     <t>INSTALADA SEDUC TESOURARIA 31/10/2025; INSTALADA UBS VILA CANAA 27/03/2026;</t>
+  </si>
+  <si>
+    <t>XC75051313</t>
+  </si>
+  <si>
+    <t>P.E.M. COM. SERGIO R. VASCONCELLOS</t>
+  </si>
+  <si>
+    <t>XC75051800</t>
+  </si>
+  <si>
+    <t>E.E.Mz. FAZENDA JAPÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACA FONTE DEFEITO </t>
   </si>
 </sst>
 </file>
@@ -4746,11 +4752,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J487" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J486" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+  <autoFilter ref="A1:J486" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
     <filterColumn colId="4">
       <filters>
-        <filter val="PAÇO"/>
+        <filter val="WP"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5104,7 +5110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
-  <dimension ref="A1:J487"/>
+  <dimension ref="A1:J486"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -5169,7 +5175,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>14</v>
@@ -5181,7 +5187,7 @@
         <v>593</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3" spans="1:10" hidden="1">
@@ -5201,7 +5207,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
@@ -5265,7 +5271,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
@@ -5277,7 +5283,7 @@
         <v>593</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6" spans="1:10" hidden="1">
@@ -5341,7 +5347,7 @@
         <v>593</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8" spans="1:10" hidden="1">
@@ -5441,7 +5447,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>11</v>
@@ -5465,7 +5471,7 @@
         <v>593</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" spans="1:10" hidden="1">
@@ -5473,7 +5479,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -5485,7 +5491,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -5497,7 +5503,7 @@
         <v>593</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="1:10" hidden="1">
@@ -5511,7 +5517,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>19</v>
@@ -5549,7 +5555,7 @@
         <v>359</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>14</v>
@@ -5561,7 +5567,7 @@
         <v>593</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:10" hidden="1">
@@ -5575,7 +5581,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>19</v>
@@ -5596,7 +5602,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5613,7 +5619,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>14</v>
@@ -5738,7 +5744,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>14</v>
@@ -5750,7 +5756,7 @@
         <v>593</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="21" spans="1:10" hidden="1">
@@ -5802,7 +5808,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>14</v>
@@ -5814,7 +5820,7 @@
         <v>593</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="23" spans="1:10" hidden="1">
@@ -6032,7 +6038,7 @@
         <v>593</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="30" spans="1:10" hidden="1">
@@ -6148,7 +6154,7 @@
         <v>13</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>14</v>
@@ -6160,7 +6166,7 @@
         <v>593</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="34" spans="1:10" hidden="1">
@@ -6241,10 +6247,10 @@
         <v>89</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>14</v>
@@ -6256,7 +6262,7 @@
         <v>593</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="37" spans="1:10" hidden="1">
@@ -6413,7 +6419,7 @@
         <v>593</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="42" spans="1:10" hidden="1">
@@ -6727,12 +6733,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>11</v>
@@ -6756,15 +6762,15 @@
         <v>593</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>11</v>
@@ -6788,15 +6794,15 @@
         <v>593</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>11</v>
@@ -6808,7 +6814,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>71</v>
@@ -6820,7 +6826,7 @@
         <v>593</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="55" spans="1:10" hidden="1">
@@ -6834,7 +6840,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>23</v>
@@ -7313,7 +7319,7 @@
         <v>11</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>23</v>
@@ -7348,7 +7354,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>14</v>
@@ -7360,7 +7366,7 @@
         <v>593</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="73" spans="1:10" hidden="1">
@@ -7595,10 +7601,10 @@
         <v>11</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>167</v>
@@ -7630,7 +7636,7 @@
         <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>170</v>
@@ -7659,10 +7665,10 @@
         <v>11</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>172</v>
@@ -7685,10 +7691,10 @@
         <v>11</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>173</v>
@@ -7711,10 +7717,10 @@
         <v>11</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>174</v>
@@ -7737,10 +7743,10 @@
         <v>11</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>175</v>
@@ -7772,7 +7778,7 @@
         <v>177</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -7801,10 +7807,10 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>180</v>
@@ -7833,10 +7839,10 @@
         <v>11</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>182</v>
@@ -7865,10 +7871,10 @@
         <v>11</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>184</v>
@@ -7894,13 +7900,13 @@
         <v>11</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>32</v>
@@ -7912,7 +7918,7 @@
         <v>593</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="91" spans="1:10" hidden="1">
@@ -7926,10 +7932,10 @@
         <v>11</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>186</v>
@@ -7958,10 +7964,10 @@
         <v>11</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>187</v>
@@ -7984,10 +7990,10 @@
         <v>11</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>188</v>
@@ -8013,7 +8019,7 @@
         <v>190</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>191</v>
@@ -8028,7 +8034,7 @@
         <v>593</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="95" spans="1:10" hidden="1">
@@ -8042,10 +8048,10 @@
         <v>11</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>196</v>
@@ -8260,7 +8266,7 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="G102" s="5" t="s">
         <v>14</v>
@@ -8272,7 +8278,7 @@
         <v>593</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="103" spans="1:10" hidden="1">
@@ -8446,7 +8452,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8908,10 +8914,10 @@
         <v>593</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8928,7 +8934,7 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>14</v>
@@ -8940,7 +8946,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8951,13 +8957,13 @@
         <v>11</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>32</v>
@@ -8969,7 +8975,7 @@
         <v>593</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="125" spans="1:10" hidden="1">
@@ -9015,13 +9021,13 @@
         <v>11</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>32</v>
@@ -9047,7 +9053,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>30</v>
@@ -9129,7 +9135,7 @@
         <v>593</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="130" spans="1:10" hidden="1">
@@ -9146,10 +9152,10 @@
         <v>233</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>14</v>
@@ -9181,7 +9187,7 @@
         <v>23</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>14</v>
@@ -9193,7 +9199,7 @@
         <v>593</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="132" spans="1:10" hidden="1">
@@ -9213,7 +9219,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>14</v>
@@ -9225,7 +9231,7 @@
         <v>593</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133" spans="1:10" hidden="1">
@@ -9245,7 +9251,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>14</v>
@@ -9257,7 +9263,7 @@
         <v>593</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="134" spans="1:10" hidden="1">
@@ -9277,7 +9283,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>14</v>
@@ -9286,10 +9292,10 @@
         <v>45936</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="135" spans="1:10" hidden="1">
@@ -9309,7 +9315,7 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>14</v>
@@ -9321,7 +9327,7 @@
         <v>593</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="136" spans="1:10" hidden="1">
@@ -9341,7 +9347,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>14</v>
@@ -9353,7 +9359,7 @@
         <v>593</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="137" spans="1:10" hidden="1">
@@ -9405,7 +9411,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>14</v>
@@ -9417,7 +9423,7 @@
         <v>593</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="139" spans="1:10" hidden="1">
@@ -9437,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>14</v>
@@ -9446,10 +9452,10 @@
         <v>45952</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="140" spans="1:10" hidden="1">
@@ -9501,7 +9507,7 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>14</v>
@@ -9513,10 +9519,10 @@
         <v>593</v>
       </c>
       <c r="J141" s="12" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9533,7 +9539,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>14</v>
@@ -9548,7 +9554,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9565,7 +9571,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>14</v>
@@ -9577,7 +9583,7 @@
         <v>593</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="144" spans="1:10" hidden="1">
@@ -9591,13 +9597,13 @@
         <v>88</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="G144" s="5" t="s">
         <v>14</v>
@@ -9609,10 +9615,10 @@
         <v>593</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9629,7 +9635,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>14</v>
@@ -9644,7 +9650,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9661,7 +9667,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>14</v>
@@ -9676,7 +9682,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" hidden="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9687,13 +9693,13 @@
         <v>88</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="G147" s="14" t="s">
         <v>14</v>
@@ -9705,10 +9711,10 @@
         <v>593</v>
       </c>
       <c r="J147" s="3" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9719,13 +9725,13 @@
         <v>88</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G148" s="14" t="s">
         <v>14</v>
@@ -9737,7 +9743,7 @@
         <v>593</v>
       </c>
       <c r="J148" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="149" spans="1:10" hidden="1">
@@ -9745,13 +9751,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>359</v>
@@ -9769,7 +9775,7 @@
         <v>593</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="150" spans="1:10" hidden="1">
@@ -9836,7 +9842,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" hidden="1">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9853,7 +9859,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>14</v>
@@ -9865,7 +9871,7 @@
         <v>593</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="153" spans="1:10" hidden="1">
@@ -9917,7 +9923,7 @@
         <v>13</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>14</v>
@@ -9929,7 +9935,7 @@
         <v>593</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="155" spans="1:10" hidden="1">
@@ -9949,7 +9955,7 @@
         <v>359</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>14</v>
@@ -9958,10 +9964,10 @@
         <v>45959</v>
       </c>
       <c r="I155" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="156" spans="1:10" hidden="1">
@@ -10066,7 +10072,7 @@
         <v>359</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>14</v>
@@ -10078,7 +10084,7 @@
         <v>593</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="160" spans="1:10" hidden="1">
@@ -10110,7 +10116,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1">
+    <row r="161" spans="1:10">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -10139,7 +10145,7 @@
         <v>593</v>
       </c>
       <c r="J161" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="162" spans="1:10" hidden="1">
@@ -10203,7 +10209,7 @@
         <v>593</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="164" spans="1:10" hidden="1">
@@ -10313,7 +10319,7 @@
         <v>13</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>14</v>
@@ -10325,7 +10331,7 @@
         <v>593</v>
       </c>
       <c r="J167" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="168" spans="1:10" hidden="1">
@@ -10342,7 +10348,7 @@
         <v>194</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>195</v>
@@ -10351,7 +10357,7 @@
         <v>14</v>
       </c>
       <c r="I168" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="169" spans="1:10" hidden="1">
@@ -10365,13 +10371,13 @@
         <v>88</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>14</v>
@@ -10413,7 +10419,7 @@
         <v>593</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="171" spans="1:10" hidden="1">
@@ -10430,10 +10436,10 @@
         <v>293</v>
       </c>
       <c r="E171" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>997</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>14</v>
@@ -10459,10 +10465,10 @@
         <v>294</v>
       </c>
       <c r="E172" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>997</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>14</v>
@@ -10491,7 +10497,7 @@
         <v>23</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>14</v>
@@ -10520,7 +10526,7 @@
         <v>23</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>14</v>
@@ -10549,7 +10555,7 @@
         <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>14</v>
@@ -10578,7 +10584,7 @@
         <v>23</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>14</v>
@@ -10607,7 +10613,7 @@
         <v>23</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>14</v>
@@ -10636,7 +10642,7 @@
         <v>23</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>14</v>
@@ -10665,7 +10671,7 @@
         <v>23</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>14</v>
@@ -10694,7 +10700,7 @@
         <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G180" s="5" t="s">
         <v>14</v>
@@ -10723,7 +10729,7 @@
         <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G181" s="5" t="s">
         <v>14</v>
@@ -10752,7 +10758,7 @@
         <v>23</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G182" s="5" t="s">
         <v>14</v>
@@ -10781,7 +10787,7 @@
         <v>23</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>14</v>
@@ -10810,7 +10816,7 @@
         <v>23</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G184" s="5" t="s">
         <v>14</v>
@@ -10839,7 +10845,7 @@
         <v>23</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G185" s="5" t="s">
         <v>14</v>
@@ -10868,7 +10874,7 @@
         <v>23</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G186" s="5" t="s">
         <v>14</v>
@@ -10897,7 +10903,7 @@
         <v>23</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G187" s="5" t="s">
         <v>14</v>
@@ -10926,7 +10932,7 @@
         <v>23</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G188" s="5" t="s">
         <v>14</v>
@@ -10955,7 +10961,7 @@
         <v>23</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G189" s="5" t="s">
         <v>14</v>
@@ -10984,7 +10990,7 @@
         <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>14</v>
@@ -11013,7 +11019,7 @@
         <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G191" s="5" t="s">
         <v>14</v>
@@ -11042,7 +11048,7 @@
         <v>23</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>14</v>
@@ -11071,7 +11077,7 @@
         <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>14</v>
@@ -11158,10 +11164,10 @@
         <v>322</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>14</v>
@@ -11173,7 +11179,7 @@
         <v>593</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="197" spans="1:10" hidden="1">
@@ -11205,7 +11211,7 @@
         <v>593</v>
       </c>
       <c r="J197" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="198" spans="1:10" hidden="1">
@@ -11219,7 +11225,7 @@
         <v>11</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E198" s="4" t="s">
         <v>23</v>
@@ -11237,7 +11243,7 @@
         <v>593</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="199" spans="1:10" hidden="1">
@@ -11254,10 +11260,10 @@
         <v>324</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>14</v>
@@ -11289,7 +11295,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>14</v>
@@ -11321,7 +11327,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="G201" s="5" t="s">
         <v>14</v>
@@ -11333,7 +11339,7 @@
         <v>593</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="202" spans="1:10" hidden="1">
@@ -11411,13 +11417,13 @@
         <v>11</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>32</v>
@@ -11429,7 +11435,7 @@
         <v>593</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="205" spans="1:10" hidden="1">
@@ -11461,7 +11467,7 @@
         <v>593</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="206" spans="1:10" hidden="1">
@@ -11481,7 +11487,7 @@
         <v>23</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G206" s="5" t="s">
         <v>14</v>
@@ -11513,7 +11519,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>14</v>
@@ -11525,7 +11531,7 @@
         <v>593</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="208" spans="1:10" hidden="1">
@@ -11545,7 +11551,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>14</v>
@@ -11557,7 +11563,7 @@
         <v>593</v>
       </c>
       <c r="J208" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="209" spans="1:10" hidden="1">
@@ -11577,7 +11583,7 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>14</v>
@@ -11589,7 +11595,7 @@
         <v>593</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="210" spans="1:10" hidden="1">
@@ -11609,7 +11615,7 @@
         <v>13</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>14</v>
@@ -11621,7 +11627,7 @@
         <v>593</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="211" spans="1:10" hidden="1">
@@ -11781,7 +11787,7 @@
         <v>593</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="216" spans="1:10" hidden="1">
@@ -11801,7 +11807,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>14</v>
@@ -11813,7 +11819,7 @@
         <v>593</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="217" spans="1:10" hidden="1">
@@ -11865,7 +11871,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="G218" s="5" t="s">
         <v>14</v>
@@ -11874,10 +11880,10 @@
         <v>45933</v>
       </c>
       <c r="I218" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J218" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="219" spans="1:10" hidden="1">
@@ -11897,7 +11903,7 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>14</v>
@@ -11909,7 +11915,7 @@
         <v>593</v>
       </c>
       <c r="J219" s="3" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="220" spans="1:10" hidden="1">
@@ -11929,7 +11935,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G220" s="5" t="s">
         <v>14</v>
@@ -11941,7 +11947,7 @@
         <v>593</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="221" spans="1:10" hidden="1">
@@ -11961,7 +11967,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="G221" s="5" t="s">
         <v>14</v>
@@ -11993,7 +11999,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>14</v>
@@ -12008,7 +12014,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -12025,7 +12031,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>14</v>
@@ -12037,7 +12043,7 @@
         <v>593</v>
       </c>
       <c r="J223" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="224" spans="1:10" hidden="1">
@@ -12083,13 +12089,13 @@
         <v>11</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>14</v>
@@ -12101,7 +12107,7 @@
         <v>593</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="226" spans="1:10" hidden="1">
@@ -12153,7 +12159,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="G227" s="5" t="s">
         <v>14</v>
@@ -12165,7 +12171,7 @@
         <v>593</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="228" spans="1:10" hidden="1">
@@ -12229,7 +12235,7 @@
         <v>593</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="230" spans="1:10" hidden="1">
@@ -12249,7 +12255,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>14</v>
@@ -12281,7 +12287,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>14</v>
@@ -12293,7 +12299,7 @@
         <v>593</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="232" spans="1:10" hidden="1">
@@ -12313,7 +12319,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>14</v>
@@ -12322,10 +12328,10 @@
         <v>44127</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="233" spans="1:10" hidden="1">
@@ -12345,7 +12351,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>14</v>
@@ -12357,7 +12363,7 @@
         <v>593</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="234" spans="1:10" hidden="1">
@@ -12377,7 +12383,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>14</v>
@@ -12389,7 +12395,7 @@
         <v>593</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="235" spans="1:10" hidden="1">
@@ -12409,7 +12415,7 @@
         <v>359</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G235" s="14" t="s">
         <v>14</v>
@@ -12421,7 +12427,7 @@
         <v>593</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="236" spans="1:10" hidden="1">
@@ -12438,10 +12444,10 @@
         <v>592</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="G236" s="2" t="s">
         <v>14</v>
@@ -12468,10 +12474,10 @@
         <v>571</v>
       </c>
       <c r="E237" s="33" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G237" s="14" t="s">
         <v>14</v>
@@ -12483,7 +12489,7 @@
         <v>593</v>
       </c>
       <c r="J237" s="8" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="238" spans="1:10" hidden="1">
@@ -12503,7 +12509,7 @@
         <v>19</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="G238" s="5" t="s">
         <v>14</v>
@@ -12515,7 +12521,7 @@
         <v>593</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="239" spans="1:10" hidden="1">
@@ -12547,10 +12553,10 @@
         <v>593</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="240" spans="1:10">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12567,7 +12573,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>14</v>
@@ -12579,7 +12585,7 @@
         <v>593</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="241" spans="1:10" hidden="1">
@@ -12587,7 +12593,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>11</v>
@@ -12599,7 +12605,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G241" s="2" t="s">
         <v>19</v>
@@ -12657,10 +12663,10 @@
         <v>381</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>14</v>
@@ -12672,10 +12678,10 @@
         <v>593</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="244" spans="1:10" hidden="1">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
       <c r="A244" s="4">
         <v>243</v>
       </c>
@@ -12686,7 +12692,7 @@
         <v>88</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>32</v>
@@ -12704,7 +12710,7 @@
         <v>593</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="245" spans="1:10" hidden="1">
@@ -12753,7 +12759,7 @@
         <v>386</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>387</v>
@@ -12779,10 +12785,10 @@
         <v>11</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>389</v>
@@ -12814,7 +12820,7 @@
         <v>390</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>391</v>
@@ -12843,7 +12849,7 @@
         <v>392</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>393</v>
@@ -12858,7 +12864,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1">
+    <row r="250" spans="1:10">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -12869,7 +12875,7 @@
         <v>88</v>
       </c>
       <c r="D250" s="35" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E250" s="1" t="s">
         <v>32</v>
@@ -12887,7 +12893,7 @@
         <v>593</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="251" spans="1:10" hidden="1">
@@ -12907,7 +12913,7 @@
         <v>23</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>32</v>
@@ -12919,7 +12925,7 @@
         <v>593</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="252" spans="1:10" hidden="1">
@@ -12954,7 +12960,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -12971,7 +12977,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>14</v>
@@ -13067,7 +13073,7 @@
         <v>23</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G256" s="5" t="s">
         <v>14</v>
@@ -13079,10 +13085,10 @@
         <v>593</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" hidden="1">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -13111,7 +13117,7 @@
         <v>593</v>
       </c>
       <c r="J257" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="258" spans="1:10" hidden="1">
@@ -13143,10 +13149,10 @@
         <v>593</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="259" spans="1:10" hidden="1">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -13207,7 +13213,7 @@
         <v>593</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="261" spans="1:10" hidden="1">
@@ -13239,10 +13245,10 @@
         <v>593</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="262" spans="1:10" hidden="1">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -13320,10 +13326,10 @@
         <v>416</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>14</v>
@@ -13483,7 +13489,7 @@
         <v>359</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="G269" s="2" t="s">
         <v>14</v>
@@ -13495,10 +13501,10 @@
         <v>593</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13515,7 +13521,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G270" s="2" t="s">
         <v>14</v>
@@ -13530,7 +13536,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13547,7 +13553,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>14</v>
@@ -13562,7 +13568,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13579,7 +13585,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="G272" s="2" t="s">
         <v>14</v>
@@ -13594,7 +13600,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13611,7 +13617,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>14</v>
@@ -13626,7 +13632,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" hidden="1">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13643,7 +13649,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>14</v>
@@ -13658,7 +13664,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" hidden="1">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13675,7 +13681,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="G275" s="2" t="s">
         <v>14</v>
@@ -13690,7 +13696,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>14</v>
@@ -13722,7 +13728,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13739,7 +13745,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>14</v>
@@ -13754,7 +13760,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13771,7 +13777,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>14</v>
@@ -13786,7 +13792,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13803,7 +13809,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="G279" s="2" t="s">
         <v>14</v>
@@ -13818,7 +13824,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13835,7 +13841,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="G280" s="2" t="s">
         <v>14</v>
@@ -13850,7 +13856,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13867,7 +13873,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>14</v>
@@ -13882,7 +13888,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13899,7 +13905,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>14</v>
@@ -13931,7 +13937,7 @@
         <v>80</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>14</v>
@@ -13940,13 +13946,13 @@
         <v>45597</v>
       </c>
       <c r="I283" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -13963,7 +13969,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>14</v>
@@ -13978,7 +13984,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -13995,7 +14001,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>14</v>
@@ -14010,7 +14016,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -14027,7 +14033,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>14</v>
@@ -14042,7 +14048,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14059,7 +14065,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>14</v>
@@ -14507,7 +14513,7 @@
         <v>80</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G301" s="2" t="s">
         <v>14</v>
@@ -14551,7 +14557,7 @@
         <v>593</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="303" spans="1:10" hidden="1">
@@ -14571,7 +14577,7 @@
         <v>80</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>14</v>
@@ -14583,10 +14589,10 @@
         <v>593</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14603,7 +14609,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="G304" s="2" t="s">
         <v>14</v>
@@ -14635,7 +14641,7 @@
         <v>80</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G305" s="2" t="s">
         <v>14</v>
@@ -14647,7 +14653,7 @@
         <v>593</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="306" spans="1:10" hidden="1">
@@ -14810,7 +14816,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14827,7 +14833,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="G311" s="2" t="s">
         <v>14</v>
@@ -14839,7 +14845,7 @@
         <v>593</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="312" spans="1:10" hidden="1">
@@ -14938,7 +14944,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14955,7 +14961,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="G315" s="2" t="s">
         <v>14</v>
@@ -14970,7 +14976,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -14987,7 +14993,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="G316" s="2" t="s">
         <v>14</v>
@@ -14999,10 +15005,10 @@
         <v>593</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -15019,7 +15025,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>14</v>
@@ -15034,7 +15040,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15051,7 +15057,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="G318" s="2" t="s">
         <v>14</v>
@@ -15066,7 +15072,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15083,7 +15089,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>14</v>
@@ -15098,7 +15104,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15115,7 +15121,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="G320" s="2" t="s">
         <v>14</v>
@@ -15130,7 +15136,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15147,7 +15153,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>14</v>
@@ -15162,7 +15168,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15179,7 +15185,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="G322" s="2" t="s">
         <v>14</v>
@@ -15194,7 +15200,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15211,7 +15217,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>14</v>
@@ -15226,7 +15232,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15243,7 +15249,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="G324" s="2" t="s">
         <v>14</v>
@@ -15258,7 +15264,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15275,7 +15281,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>14</v>
@@ -15290,7 +15296,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15307,7 +15313,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="G326" s="2" t="s">
         <v>14</v>
@@ -15322,7 +15328,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" hidden="1">
       <c r="A327" s="4">
         <v>326</v>
       </c>
@@ -15336,10 +15342,10 @@
         <v>606</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1158</v>
+        <v>25</v>
       </c>
       <c r="G327" s="2" t="s">
         <v>14</v>
@@ -15351,10 +15357,10 @@
         <v>593</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15365,13 +15371,13 @@
         <v>11</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="G328" s="2" t="s">
         <v>14</v>
@@ -15383,10 +15389,10 @@
         <v>593</v>
       </c>
       <c r="J328" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15397,13 +15403,13 @@
         <v>11</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="G329" s="2" t="s">
         <v>14</v>
@@ -15415,10 +15421,10 @@
         <v>593</v>
       </c>
       <c r="J329" s="3" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="330" spans="1:10">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="330" spans="1:10" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15429,13 +15435,13 @@
         <v>11</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="G330" s="2" t="s">
         <v>14</v>
@@ -15447,7 +15453,7 @@
         <v>593</v>
       </c>
       <c r="J330" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="331" spans="1:10" hidden="1">
@@ -15461,13 +15467,13 @@
         <v>11</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G331" s="2" t="s">
         <v>14</v>
@@ -15479,10 +15485,10 @@
         <v>593</v>
       </c>
       <c r="J331" s="3" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15493,13 +15499,13 @@
         <v>11</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="G332" s="2" t="s">
         <v>14</v>
@@ -15511,10 +15517,10 @@
         <v>593</v>
       </c>
       <c r="J332" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="333" spans="1:10">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15525,13 +15531,13 @@
         <v>11</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="G333" s="2" t="s">
         <v>14</v>
@@ -15543,10 +15549,10 @@
         <v>593</v>
       </c>
       <c r="J333" s="3" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="334" spans="1:10" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15557,13 +15563,13 @@
         <v>11</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>14</v>
@@ -15575,10 +15581,10 @@
         <v>593</v>
       </c>
       <c r="J334" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="335" spans="1:10">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="335" spans="1:10" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15589,13 +15595,13 @@
         <v>11</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="G335" s="2" t="s">
         <v>14</v>
@@ -15607,10 +15613,10 @@
         <v>593</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="336" spans="1:10">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="336" spans="1:10" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15621,13 +15627,13 @@
         <v>11</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E336" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="G336" s="2" t="s">
         <v>14</v>
@@ -15639,10 +15645,10 @@
         <v>593</v>
       </c>
       <c r="J336" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15653,13 +15659,13 @@
         <v>11</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="G337" s="2" t="s">
         <v>14</v>
@@ -15671,7 +15677,7 @@
         <v>593</v>
       </c>
       <c r="J337" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="338" spans="1:10" hidden="1">
@@ -15685,13 +15691,13 @@
         <v>11</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E338" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G338" s="2" t="s">
         <v>14</v>
@@ -15703,7 +15709,7 @@
         <v>593</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="339" spans="1:10" hidden="1">
@@ -15717,13 +15723,13 @@
         <v>11</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G339" s="2" t="s">
         <v>14</v>
@@ -15735,7 +15741,7 @@
         <v>593</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="340" spans="1:10" hidden="1">
@@ -15749,13 +15755,13 @@
         <v>11</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G340" s="2" t="s">
         <v>14</v>
@@ -15767,7 +15773,7 @@
         <v>593</v>
       </c>
       <c r="J340" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="341" spans="1:10" hidden="1">
@@ -15781,13 +15787,13 @@
         <v>11</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G341" s="2" t="s">
         <v>14</v>
@@ -15799,7 +15805,7 @@
         <v>593</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="342" spans="1:10" hidden="1">
@@ -15813,13 +15819,13 @@
         <v>11</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G342" s="2" t="s">
         <v>14</v>
@@ -15831,7 +15837,7 @@
         <v>593</v>
       </c>
       <c r="J342" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="343" spans="1:10" hidden="1">
@@ -15845,13 +15851,13 @@
         <v>11</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>14</v>
@@ -15863,7 +15869,7 @@
         <v>593</v>
       </c>
       <c r="J343" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="344" spans="1:10" hidden="1">
@@ -15915,7 +15921,7 @@
         <v>80</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="G345" s="14" t="s">
         <v>14</v>
@@ -15927,7 +15933,7 @@
         <v>593</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="346" spans="1:10" hidden="1">
@@ -15941,7 +15947,7 @@
         <v>11</v>
       </c>
       <c r="D346" s="38" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>80</v>
@@ -15959,7 +15965,7 @@
         <v>593</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="347" spans="1:10" hidden="1">
@@ -15973,7 +15979,7 @@
         <v>11</v>
       </c>
       <c r="D347" s="38" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>80</v>
@@ -15991,7 +15997,7 @@
         <v>593</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="348" spans="1:10" hidden="1">
@@ -16005,13 +16011,13 @@
         <v>11</v>
       </c>
       <c r="D348" s="38" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>14</v>
@@ -16023,7 +16029,7 @@
         <v>593</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="349" spans="1:10" hidden="1">
@@ -16037,13 +16043,13 @@
         <v>11</v>
       </c>
       <c r="D349" s="38" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>14</v>
@@ -16055,7 +16061,7 @@
         <v>593</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="350" spans="1:10" hidden="1">
@@ -16069,13 +16075,13 @@
         <v>11</v>
       </c>
       <c r="D350" s="38" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G350" s="2" t="s">
         <v>14</v>
@@ -16087,7 +16093,7 @@
         <v>593</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="351" spans="1:10" hidden="1">
@@ -16101,13 +16107,13 @@
         <v>11</v>
       </c>
       <c r="D351" s="38" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G351" s="2" t="s">
         <v>14</v>
@@ -16119,7 +16125,7 @@
         <v>593</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="352" spans="1:10" hidden="1">
@@ -16133,25 +16139,25 @@
         <v>11</v>
       </c>
       <c r="D352" s="38" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>25</v>
+        <v>839</v>
       </c>
       <c r="G352" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H352" s="23">
-        <v>45946</v>
+      <c r="H352" s="9">
+        <v>45947</v>
       </c>
       <c r="I352" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>993</v>
+        <v>912</v>
       </c>
     </row>
     <row r="353" spans="1:10" hidden="1">
@@ -16165,25 +16171,25 @@
         <v>11</v>
       </c>
       <c r="D353" s="38" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F353" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="G353" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H353" s="23">
+        <v>45946</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J353" s="3" t="s">
         <v>841</v>
-      </c>
-      <c r="G353" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H353" s="9">
-        <v>45947</v>
-      </c>
-      <c r="I353" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="J353" s="3" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="354" spans="1:10" hidden="1">
@@ -16197,25 +16203,25 @@
         <v>11</v>
       </c>
       <c r="D354" s="38" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
       <c r="G354" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H354" s="23">
-        <v>45946</v>
+        <v>45945</v>
       </c>
       <c r="I354" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
     </row>
     <row r="355" spans="1:10" hidden="1">
@@ -16229,25 +16235,25 @@
         <v>11</v>
       </c>
       <c r="D355" s="38" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>828</v>
+        <v>697</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H355" s="23">
-        <v>45945</v>
+        <v>45942</v>
       </c>
       <c r="I355" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>829</v>
+        <v>806</v>
       </c>
     </row>
     <row r="356" spans="1:10" hidden="1">
@@ -16267,19 +16273,19 @@
         <v>80</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>698</v>
+        <v>837</v>
       </c>
       <c r="G356" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H356" s="23">
-        <v>45942</v>
+        <v>45946</v>
       </c>
       <c r="I356" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>808</v>
+        <v>840</v>
       </c>
     </row>
     <row r="357" spans="1:10" hidden="1">
@@ -16293,13 +16299,13 @@
         <v>11</v>
       </c>
       <c r="D357" s="38" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="G357" s="2" t="s">
         <v>14</v>
@@ -16311,7 +16317,7 @@
         <v>593</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="358" spans="1:10" hidden="1">
@@ -16325,25 +16331,25 @@
         <v>11</v>
       </c>
       <c r="D358" s="38" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>836</v>
+        <v>802</v>
       </c>
       <c r="G358" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H358" s="23">
-        <v>45946</v>
+        <v>45942</v>
       </c>
       <c r="I358" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>837</v>
+        <v>807</v>
       </c>
     </row>
     <row r="359" spans="1:10" hidden="1">
@@ -16357,25 +16363,25 @@
         <v>11</v>
       </c>
       <c r="D359" s="38" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>804</v>
+        <v>974</v>
       </c>
       <c r="G359" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H359" s="23">
-        <v>45942</v>
+        <v>45945</v>
       </c>
       <c r="I359" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J359" s="3" t="s">
-        <v>809</v>
+        <v>901</v>
       </c>
     </row>
     <row r="360" spans="1:10" hidden="1">
@@ -16389,25 +16395,25 @@
         <v>11</v>
       </c>
       <c r="D360" s="38" t="s">
-        <v>740</v>
+        <v>918</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>976</v>
+        <v>509</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H360" s="23">
-        <v>45945</v>
+        <v>46036</v>
       </c>
       <c r="I360" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>903</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="361" spans="1:10" hidden="1">
@@ -16421,25 +16427,25 @@
         <v>11</v>
       </c>
       <c r="D361" s="38" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>509</v>
+        <v>961</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H361" s="23">
-        <v>46036</v>
+        <v>45968</v>
       </c>
       <c r="I361" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>1025</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="362" spans="1:10" hidden="1">
@@ -16453,25 +16459,25 @@
         <v>11</v>
       </c>
       <c r="D362" s="38" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H362" s="23">
-        <v>45968</v>
+        <v>45994</v>
       </c>
       <c r="I362" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>1015</v>
+        <v>966</v>
       </c>
     </row>
     <row r="363" spans="1:10" hidden="1">
@@ -16485,25 +16491,25 @@
         <v>11</v>
       </c>
       <c r="D363" s="38" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H363" s="23">
-        <v>45994</v>
+        <v>45968</v>
       </c>
       <c r="I363" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="364" spans="1:10" hidden="1">
@@ -16517,13 +16523,13 @@
         <v>11</v>
       </c>
       <c r="D364" s="38" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>970</v>
+        <v>1140</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>14</v>
@@ -16532,10 +16538,10 @@
         <v>45968</v>
       </c>
       <c r="I364" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
     </row>
     <row r="365" spans="1:10" hidden="1">
@@ -16549,13 +16555,13 @@
         <v>11</v>
       </c>
       <c r="D365" s="38" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>1143</v>
+        <v>943</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>14</v>
@@ -16564,10 +16570,10 @@
         <v>45968</v>
       </c>
       <c r="I365" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="366" spans="1:10" hidden="1">
@@ -16581,13 +16587,13 @@
         <v>11</v>
       </c>
       <c r="D366" s="38" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>945</v>
+        <v>1194</v>
       </c>
       <c r="G366" s="2" t="s">
         <v>14</v>
@@ -16596,13 +16602,13 @@
         <v>45968</v>
       </c>
       <c r="I366" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16613,13 +16619,13 @@
         <v>11</v>
       </c>
       <c r="D367" s="38" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F367" s="1" t="s">
-        <v>1197</v>
+        <v>822</v>
       </c>
       <c r="G367" s="2" t="s">
         <v>14</v>
@@ -16628,10 +16634,10 @@
         <v>45968</v>
       </c>
       <c r="I367" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
     </row>
     <row r="368" spans="1:10" hidden="1">
@@ -16645,13 +16651,13 @@
         <v>11</v>
       </c>
       <c r="D368" s="38" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>824</v>
+        <v>1195</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>14</v>
@@ -16660,13 +16666,13 @@
         <v>45968</v>
       </c>
       <c r="I368" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="369" spans="1:10">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="369" spans="1:10" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16680,19 +16686,19 @@
         <v>928</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>1198</v>
+        <v>712</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H369" s="23">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J369" s="3" t="s">
         <v>929</v>
@@ -16702,52 +16708,52 @@
       <c r="A370" s="4">
         <v>369</v>
       </c>
-      <c r="B370" s="30" t="s">
-        <v>425</v>
+      <c r="B370" s="25" t="s">
+        <v>740</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D370" s="38" t="s">
-        <v>930</v>
+        <v>741</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>713</v>
+        <v>1196</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H370" s="23">
-        <v>45971</v>
+        <v>45945</v>
       </c>
       <c r="I370" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" hidden="1">
       <c r="A371" s="4">
         <v>370</v>
       </c>
       <c r="B371" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D371" s="38" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>71</v>
+        <v>359</v>
       </c>
       <c r="F371" s="1" t="s">
-        <v>1199</v>
+        <v>574</v>
       </c>
       <c r="G371" s="2" t="s">
         <v>14</v>
@@ -16759,7 +16765,7 @@
         <v>593</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>1035</v>
+        <v>898</v>
       </c>
     </row>
     <row r="372" spans="1:10" hidden="1">
@@ -16767,19 +16773,19 @@
         <v>371</v>
       </c>
       <c r="B372" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D372" s="38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>574</v>
+        <v>1221</v>
       </c>
       <c r="G372" s="2" t="s">
         <v>14</v>
@@ -16791,7 +16797,7 @@
         <v>593</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>900</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="373" spans="1:10" hidden="1">
@@ -16799,31 +16805,31 @@
         <v>372</v>
       </c>
       <c r="B373" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D373" s="38" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F373" s="1" t="s">
-        <v>1224</v>
+        <v>880</v>
       </c>
       <c r="G373" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H373" s="23">
-        <v>45945</v>
+        <v>45992</v>
       </c>
       <c r="I373" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>1225</v>
+        <v>960</v>
       </c>
     </row>
     <row r="374" spans="1:10" hidden="1">
@@ -16831,93 +16837,93 @@
         <v>373</v>
       </c>
       <c r="B374" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D374" s="38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>882</v>
+        <v>763</v>
       </c>
       <c r="G374" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H374" s="23">
-        <v>45992</v>
+        <v>45945</v>
       </c>
       <c r="I374" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J374" s="3" t="s">
-        <v>962</v>
-      </c>
+      <c r="J374" s="24"/>
     </row>
     <row r="375" spans="1:10" hidden="1">
       <c r="A375" s="4">
         <v>374</v>
       </c>
       <c r="B375" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D375" s="38" t="s">
-        <v>747</v>
+      <c r="D375" s="39" t="s">
+        <v>746</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>23</v>
+        <v>359</v>
       </c>
       <c r="F375" s="1" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="G375" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H375" s="23">
-        <v>45945</v>
+        <v>45941</v>
       </c>
       <c r="I375" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J375" s="24"/>
+      <c r="J375" s="3" t="s">
+        <v>766</v>
+      </c>
     </row>
     <row r="376" spans="1:10" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
       <c r="B376" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D376" s="39" t="s">
-        <v>748</v>
+      <c r="D376" s="38" t="s">
+        <v>747</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>757</v>
+        <v>1223</v>
       </c>
       <c r="G376" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H376" s="23">
-        <v>45941</v>
+        <v>45945</v>
       </c>
       <c r="I376" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>768</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="377" spans="1:10" hidden="1">
@@ -16925,31 +16931,31 @@
         <v>376</v>
       </c>
       <c r="B377" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D377" s="38" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F377" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G377" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H377" s="23">
+        <v>46098</v>
+      </c>
+      <c r="I377" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J377" s="3" t="s">
         <v>1226</v>
-      </c>
-      <c r="G377" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H377" s="23">
-        <v>45945</v>
-      </c>
-      <c r="I377" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="J377" s="3" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="378" spans="1:10" hidden="1">
@@ -16957,31 +16963,31 @@
         <v>377</v>
       </c>
       <c r="B378" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D378" s="38" t="s">
-        <v>750</v>
+      <c r="D378" s="39" t="s">
+        <v>749</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>1228</v>
+        <v>767</v>
       </c>
       <c r="G378" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H378" s="23">
-        <v>46098</v>
+        <v>45941</v>
       </c>
       <c r="I378" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>1229</v>
+        <v>768</v>
       </c>
     </row>
     <row r="379" spans="1:10" hidden="1">
@@ -16989,19 +16995,19 @@
         <v>378</v>
       </c>
       <c r="B379" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D379" s="39" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="G379" s="2" t="s">
         <v>14</v>
@@ -17013,7 +17019,7 @@
         <v>593</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="380" spans="1:10" hidden="1">
@@ -17021,31 +17027,31 @@
         <v>379</v>
       </c>
       <c r="B380" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D380" s="39" t="s">
-        <v>752</v>
+      <c r="D380" s="38" t="s">
+        <v>751</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>763</v>
+        <v>1227</v>
       </c>
       <c r="G380" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H380" s="23">
-        <v>45941</v>
+        <v>45952</v>
       </c>
       <c r="I380" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>773</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="381" spans="1:10" hidden="1">
@@ -17053,31 +17059,31 @@
         <v>380</v>
       </c>
       <c r="B381" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D381" s="38" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F381" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G381" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H381" s="23">
+        <v>45950</v>
+      </c>
+      <c r="I381" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="J381" s="3" t="s">
         <v>1230</v>
-      </c>
-      <c r="G381" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H381" s="23">
-        <v>45952</v>
-      </c>
-      <c r="I381" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="J381" s="3" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="382" spans="1:10" hidden="1">
@@ -17085,95 +17091,95 @@
         <v>381</v>
       </c>
       <c r="B382" s="25" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D382" s="38" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1232</v>
+        <v>1184</v>
       </c>
       <c r="G382" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H382" s="23">
-        <v>45950</v>
+        <v>45996</v>
       </c>
       <c r="I382" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="383" spans="1:10">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="383" spans="1:10" hidden="1">
       <c r="A383" s="4">
         <v>382</v>
       </c>
-      <c r="B383" s="25" t="s">
-        <v>742</v>
+      <c r="B383" s="26" t="s">
+        <v>740</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D383" s="38" t="s">
-        <v>755</v>
+      <c r="D383" s="39" t="s">
+        <v>754</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>71</v>
+        <v>359</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>1187</v>
+        <v>769</v>
       </c>
       <c r="G383" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H383" s="23">
-        <v>45996</v>
+      <c r="H383" s="9">
+        <v>45941</v>
       </c>
       <c r="I383" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>983</v>
+        <v>770</v>
       </c>
     </row>
     <row r="384" spans="1:10" hidden="1">
       <c r="A384" s="4">
         <v>383</v>
       </c>
-      <c r="B384" s="26" t="s">
-        <v>742</v>
+      <c r="B384" s="27" t="s">
+        <v>40</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D384" s="39" t="s">
-        <v>756</v>
+        <v>11</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>833</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>359</v>
+        <v>13</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>771</v>
+        <v>98</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H384" s="9">
-        <v>45941</v>
+      <c r="H384" s="23">
+        <v>45946</v>
       </c>
       <c r="I384" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>772</v>
+        <v>843</v>
       </c>
     </row>
     <row r="385" spans="1:10" hidden="1">
@@ -17187,25 +17193,25 @@
         <v>11</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>835</v>
+        <v>866</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>98</v>
+        <v>1210</v>
       </c>
       <c r="G385" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H385" s="23">
-        <v>45946</v>
+        <v>45952</v>
       </c>
       <c r="I385" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>845</v>
+        <v>897</v>
       </c>
     </row>
     <row r="386" spans="1:10" hidden="1">
@@ -17219,25 +17225,25 @@
         <v>11</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>868</v>
+        <v>896</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1213</v>
+        <v>1011</v>
       </c>
       <c r="G386" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H386" s="23">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="I386" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>899</v>
+        <v>945</v>
       </c>
     </row>
     <row r="387" spans="1:10" hidden="1">
@@ -17251,28 +17257,28 @@
         <v>11</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>627</v>
+        <v>1155</v>
       </c>
       <c r="G387" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H387" s="23">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="I387" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="388" spans="1:10">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17283,28 +17289,28 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>913</v>
+        <v>1048</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1014</v>
+        <v>1197</v>
       </c>
       <c r="G388" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H388" s="23">
-        <v>45960</v>
+        <v>45945</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17315,13 +17321,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>1200</v>
+        <v>72</v>
       </c>
       <c r="G389" s="2" t="s">
         <v>14</v>
@@ -17333,10 +17339,10 @@
         <v>593</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17347,13 +17353,13 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>72</v>
+        <v>1198</v>
       </c>
       <c r="G390" s="2" t="s">
         <v>14</v>
@@ -17365,10 +17371,10 @@
         <v>593</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17379,13 +17385,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G391" s="2" t="s">
         <v>14</v>
@@ -17397,10 +17403,10 @@
         <v>593</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17411,13 +17417,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="G392" s="2" t="s">
         <v>14</v>
@@ -17429,39 +17435,39 @@
         <v>593</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="393" spans="1:10">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10" hidden="1">
       <c r="A393" s="4">
         <v>392</v>
       </c>
-      <c r="B393" s="27" t="s">
-        <v>40</v>
+      <c r="B393" s="28" t="s">
+        <v>764</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D393" s="2" t="s">
-        <v>1061</v>
+      <c r="D393" s="5" t="s">
+        <v>779</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>71</v>
+        <v>359</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>1203</v>
+        <v>781</v>
       </c>
       <c r="G393" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H393" s="23">
-        <v>45945</v>
+        <v>45940</v>
       </c>
       <c r="I393" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J393" s="3" t="s">
-        <v>1062</v>
+        <v>794</v>
       </c>
     </row>
     <row r="394" spans="1:10" hidden="1">
@@ -17469,19 +17475,19 @@
         <v>393</v>
       </c>
       <c r="B394" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G394" s="2" t="s">
         <v>14</v>
@@ -17492,8 +17498,8 @@
       <c r="I394" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J394" s="3" t="s">
-        <v>796</v>
+      <c r="J394" s="24" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="395" spans="1:10" hidden="1">
@@ -17501,19 +17507,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>14</v>
@@ -17524,8 +17530,8 @@
       <c r="I395" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J395" s="24" t="s">
-        <v>796</v>
+      <c r="J395" s="3" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="396" spans="1:10" hidden="1">
@@ -17533,7 +17539,7 @@
         <v>395</v>
       </c>
       <c r="B396" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>11</v>
@@ -17551,7 +17557,7 @@
         <v>14</v>
       </c>
       <c r="H396" s="23">
-        <v>45940</v>
+        <v>45939</v>
       </c>
       <c r="I396" s="4" t="s">
         <v>593</v>
@@ -17565,19 +17571,19 @@
         <v>396</v>
       </c>
       <c r="B397" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>14</v>
@@ -17588,8 +17594,8 @@
       <c r="I397" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J397" s="3" t="s">
-        <v>799</v>
+      <c r="J397" s="24" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="398" spans="1:10" hidden="1">
@@ -17597,7 +17603,7 @@
         <v>397</v>
       </c>
       <c r="B398" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>11</v>
@@ -17609,19 +17615,19 @@
         <v>359</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H398" s="23">
-        <v>45939</v>
+        <v>45938</v>
       </c>
       <c r="I398" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J398" s="24" t="s">
-        <v>799</v>
+      <c r="J398" s="3" t="s">
+        <v>798</v>
       </c>
     </row>
     <row r="399" spans="1:10" hidden="1">
@@ -17629,7 +17635,7 @@
         <v>398</v>
       </c>
       <c r="B399" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>11</v>
@@ -17641,7 +17647,7 @@
         <v>359</v>
       </c>
       <c r="F399" s="1" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>14</v>
@@ -17653,7 +17659,7 @@
         <v>593</v>
       </c>
       <c r="J399" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="400" spans="1:10" hidden="1">
@@ -17661,31 +17667,31 @@
         <v>399</v>
       </c>
       <c r="B400" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D400" s="5" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="G400" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H400" s="23">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="I400" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
     </row>
     <row r="401" spans="1:10" hidden="1">
@@ -17693,7 +17699,7 @@
         <v>400</v>
       </c>
       <c r="B401" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>11</v>
@@ -17717,7 +17723,7 @@
         <v>593</v>
       </c>
       <c r="J401" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="402" spans="1:10" hidden="1">
@@ -17725,31 +17731,31 @@
         <v>401</v>
       </c>
       <c r="B402" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>812</v>
+        <v>952</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>813</v>
+        <v>953</v>
       </c>
       <c r="G402" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H402" s="23">
-        <v>45939</v>
+        <v>45985</v>
       </c>
       <c r="I402" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J402" s="3" t="s">
-        <v>815</v>
+        <v>954</v>
       </c>
     </row>
     <row r="403" spans="1:10" hidden="1">
@@ -17757,31 +17763,31 @@
         <v>402</v>
       </c>
       <c r="B403" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F403" s="1" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
       <c r="G403" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H403" s="23">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="I403" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J403" s="3" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
     </row>
     <row r="404" spans="1:10" hidden="1">
@@ -17789,31 +17795,31 @@
         <v>403</v>
       </c>
       <c r="B404" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>965</v>
+        <v>975</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="G404" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H404" s="23">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="I404" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J404" s="3" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
     </row>
     <row r="405" spans="1:10" hidden="1">
@@ -17821,19 +17827,19 @@
         <v>404</v>
       </c>
       <c r="B405" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F405" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>14</v>
@@ -17845,7 +17851,7 @@
         <v>593</v>
       </c>
       <c r="J405" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="406" spans="1:10" hidden="1">
@@ -17853,63 +17859,63 @@
         <v>405</v>
       </c>
       <c r="B406" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>980</v>
+        <v>1003</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F406" s="1" t="s">
-        <v>981</v>
+        <v>1004</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H406" s="23">
-        <v>45996</v>
+        <v>45985</v>
       </c>
       <c r="I406" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>982</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="407" spans="1:10" hidden="1">
       <c r="A407" s="4">
         <v>406</v>
       </c>
-      <c r="B407" s="28" t="s">
-        <v>766</v>
+      <c r="B407" s="29" t="s">
+        <v>765</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1006</v>
+        <v>773</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="F407" s="1" t="s">
-        <v>1007</v>
+        <v>775</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H407" s="23">
-        <v>45985</v>
+        <v>45940</v>
       </c>
       <c r="I407" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J407" s="3" t="s">
-        <v>1040</v>
+        <v>796</v>
       </c>
     </row>
     <row r="408" spans="1:10" hidden="1">
@@ -17917,13 +17923,13 @@
         <v>407</v>
       </c>
       <c r="B408" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C408" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>359</v>
@@ -17941,7 +17947,7 @@
         <v>593</v>
       </c>
       <c r="J408" s="3" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="409" spans="1:10" hidden="1">
@@ -17949,19 +17955,19 @@
         <v>408</v>
       </c>
       <c r="B409" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C409" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F409" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G409" s="2" t="s">
         <v>14</v>
@@ -17973,7 +17979,7 @@
         <v>593</v>
       </c>
       <c r="J409" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="410" spans="1:10" hidden="1">
@@ -17981,31 +17987,31 @@
         <v>409</v>
       </c>
       <c r="B410" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>776</v>
+        <v>823</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F410" s="1" t="s">
-        <v>780</v>
+        <v>824</v>
       </c>
       <c r="G410" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H410" s="23">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="I410" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J410" s="3" t="s">
-        <v>803</v>
+        <v>825</v>
       </c>
     </row>
     <row r="411" spans="1:10" hidden="1">
@@ -18013,31 +18019,31 @@
         <v>410</v>
       </c>
       <c r="B411" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>826</v>
+        <v>850</v>
       </c>
       <c r="G411" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H411" s="23">
-        <v>45945</v>
+        <v>45950</v>
       </c>
       <c r="I411" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J411" s="3" t="s">
-        <v>827</v>
+        <v>862</v>
       </c>
     </row>
     <row r="412" spans="1:10" hidden="1">
@@ -18045,19 +18051,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C412" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G412" s="2" t="s">
         <v>14</v>
@@ -18069,7 +18075,7 @@
         <v>593</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="413" spans="1:10" hidden="1">
@@ -18077,31 +18083,31 @@
         <v>412</v>
       </c>
       <c r="B413" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C413" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F413" s="1" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="G413" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H413" s="23">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="I413" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J413" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="414" spans="1:10" hidden="1">
@@ -18109,19 +18115,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C414" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G414" s="2" t="s">
         <v>14</v>
@@ -18133,7 +18139,7 @@
         <v>593</v>
       </c>
       <c r="J414" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="415" spans="1:10" hidden="1">
@@ -18141,31 +18147,31 @@
         <v>414</v>
       </c>
       <c r="B415" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D415" s="5" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>862</v>
+        <v>1235</v>
       </c>
       <c r="G415" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H415" s="23">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="I415" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>867</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="416" spans="1:10" hidden="1">
@@ -18173,31 +18179,31 @@
         <v>415</v>
       </c>
       <c r="B416" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C416" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D416" s="5" t="s">
-        <v>886</v>
+        <v>956</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>1238</v>
+        <v>941</v>
       </c>
       <c r="G416" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H416" s="23">
-        <v>45960</v>
+        <v>45992</v>
       </c>
       <c r="I416" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>1239</v>
+        <v>967</v>
       </c>
     </row>
     <row r="417" spans="1:10" hidden="1">
@@ -18205,7 +18211,7 @@
         <v>416</v>
       </c>
       <c r="B417" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>11</v>
@@ -18217,7 +18223,7 @@
         <v>80</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G417" s="2" t="s">
         <v>14</v>
@@ -18229,7 +18235,7 @@
         <v>593</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
     </row>
     <row r="418" spans="1:10" hidden="1">
@@ -18237,31 +18243,31 @@
         <v>417</v>
       </c>
       <c r="B418" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>944</v>
+        <v>973</v>
       </c>
       <c r="G418" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H418" s="23">
-        <v>45992</v>
+        <v>45975</v>
       </c>
       <c r="I418" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J418" s="3" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
     </row>
     <row r="419" spans="1:10" hidden="1">
@@ -18269,19 +18275,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C419" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>975</v>
+        <v>985</v>
       </c>
       <c r="G419" s="2" t="s">
         <v>14</v>
@@ -18293,7 +18299,7 @@
         <v>593</v>
       </c>
       <c r="J419" s="3" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
     </row>
     <row r="420" spans="1:10" hidden="1">
@@ -18301,19 +18307,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G420" s="2" t="s">
         <v>14</v>
@@ -18325,7 +18331,7 @@
         <v>593</v>
       </c>
       <c r="J420" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="421" spans="1:10" hidden="1">
@@ -18333,31 +18339,31 @@
         <v>420</v>
       </c>
       <c r="B421" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>989</v>
+        <v>1006</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>990</v>
+        <v>1007</v>
       </c>
       <c r="G421" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H421" s="23">
-        <v>45975</v>
+        <v>46001</v>
       </c>
       <c r="I421" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="422" spans="1:10" hidden="1">
@@ -18365,31 +18371,31 @@
         <v>421</v>
       </c>
       <c r="B422" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C422" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>1010</v>
+        <v>940</v>
       </c>
       <c r="G422" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H422" s="23">
-        <v>46001</v>
+        <v>46036</v>
       </c>
       <c r="I422" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="423" spans="1:10" hidden="1">
@@ -18397,7 +18403,7 @@
         <v>422</v>
       </c>
       <c r="B423" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>11</v>
@@ -18409,16 +18415,16 @@
         <v>80</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>942</v>
+        <v>970</v>
       </c>
       <c r="G423" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H423" s="23">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="I423" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J423" s="3" t="s">
         <v>1027</v>
@@ -18429,81 +18435,81 @@
         <v>423</v>
       </c>
       <c r="B424" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>972</v>
+        <v>1031</v>
       </c>
       <c r="G424" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H424" s="23">
-        <v>46037</v>
+        <v>46001</v>
       </c>
       <c r="I424" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="J424" s="3" t="s">
-        <v>1030</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="J424" s="24"/>
     </row>
     <row r="425" spans="1:10" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
       <c r="B425" s="29" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>1034</v>
+        <v>838</v>
       </c>
       <c r="G425" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H425" s="23">
-        <v>46001</v>
+        <v>46041</v>
       </c>
       <c r="I425" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J425" s="24"/>
+      <c r="J425" s="3" t="s">
+        <v>1035</v>
+      </c>
     </row>
     <row r="426" spans="1:10" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
-      <c r="B426" s="29" t="s">
-        <v>767</v>
+      <c r="B426" s="40" t="s">
+        <v>885</v>
       </c>
       <c r="C426" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1037</v>
+        <v>886</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>80</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>840</v>
+        <v>804</v>
       </c>
       <c r="G426" s="2" t="s">
         <v>14</v>
@@ -18515,7 +18521,7 @@
         <v>593</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="427" spans="1:10" hidden="1">
@@ -18523,31 +18529,31 @@
         <v>426</v>
       </c>
       <c r="B427" s="40" t="s">
+        <v>885</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D427" s="5" t="s">
         <v>887</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D427" s="5" t="s">
-        <v>888</v>
-      </c>
       <c r="E427" s="1" t="s">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>806</v>
+        <v>913</v>
       </c>
       <c r="G427" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H427" s="23">
-        <v>46041</v>
+        <v>45957</v>
       </c>
       <c r="I427" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1039</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="428" spans="1:10" hidden="1">
@@ -18555,31 +18561,31 @@
         <v>427</v>
       </c>
       <c r="B428" s="40" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>915</v>
+        <v>1018</v>
       </c>
       <c r="G428" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H428" s="23">
-        <v>45957</v>
+        <v>46034</v>
       </c>
       <c r="I428" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1072</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="429" spans="1:10" hidden="1">
@@ -18587,95 +18593,95 @@
         <v>428</v>
       </c>
       <c r="B429" s="40" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>890</v>
+        <v>1053</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1021</v>
+        <v>1201</v>
       </c>
       <c r="G429" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H429" s="23">
-        <v>46034</v>
+        <v>45957</v>
       </c>
       <c r="I429" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
       <c r="B430" s="40" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>1056</v>
+        <v>889</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>1204</v>
+        <v>876</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H430" s="23">
-        <v>45957</v>
+        <v>46036</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1057</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="431" spans="1:10" hidden="1">
       <c r="A431" s="4">
         <v>430</v>
       </c>
-      <c r="B431" s="40" t="s">
-        <v>887</v>
+      <c r="B431" s="31" t="s">
+        <v>870</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D431" s="5" t="s">
-        <v>891</v>
+      <c r="D431" s="2" t="s">
+        <v>1044</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>878</v>
+        <v>722</v>
       </c>
       <c r="G431" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H431" s="23">
-        <v>46036</v>
+        <v>45950</v>
       </c>
       <c r="I431" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1028</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="432" spans="1:10" hidden="1">
@@ -18683,19 +18689,19 @@
         <v>431</v>
       </c>
       <c r="B432" s="31" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>723</v>
+        <v>783</v>
       </c>
       <c r="G432" s="2" t="s">
         <v>32</v>
@@ -18707,7 +18713,7 @@
         <v>593</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="433" spans="1:10" hidden="1">
@@ -18715,31 +18721,31 @@
         <v>432</v>
       </c>
       <c r="B433" s="31" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1045</v>
+        <v>1061</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>785</v>
+        <v>1065</v>
       </c>
       <c r="G433" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H433" s="23">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="I433" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1046</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="434" spans="1:10" hidden="1">
@@ -18747,31 +18753,31 @@
         <v>433</v>
       </c>
       <c r="B434" s="31" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G434" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H434" s="23">
-        <v>45952</v>
+        <v>46048</v>
       </c>
       <c r="I434" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="435" spans="1:10" hidden="1">
@@ -18779,95 +18785,95 @@
         <v>434</v>
       </c>
       <c r="B435" s="31" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>359</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="G435" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H435" s="23">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="I435" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1066</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="436" spans="1:10" hidden="1">
       <c r="A436" s="4">
         <v>435</v>
       </c>
-      <c r="B436" s="31" t="s">
-        <v>872</v>
+      <c r="B436" s="52" t="s">
+        <v>668</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1073</v>
+        <v>669</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>359</v>
+        <v>663</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>1078</v>
+        <v>382</v>
       </c>
       <c r="G436" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H436" s="23">
-        <v>46050</v>
+      <c r="H436" s="15">
+        <v>45918</v>
       </c>
       <c r="I436" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J436" s="3" t="s">
-        <v>1074</v>
+        <v>671</v>
       </c>
     </row>
     <row r="437" spans="1:10" hidden="1">
       <c r="A437" s="4">
         <v>436</v>
       </c>
-      <c r="B437" s="52" t="s">
-        <v>669</v>
+      <c r="B437" s="53" t="s">
+        <v>1111</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>670</v>
+        <v>1113</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>664</v>
+        <v>19</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>382</v>
+        <v>857</v>
       </c>
       <c r="G437" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H437" s="15">
-        <v>45918</v>
+      <c r="H437" s="23">
+        <v>45712</v>
       </c>
       <c r="I437" s="4" t="s">
         <v>593</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>672</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="438" spans="1:10" hidden="1">
@@ -18875,51 +18881,49 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>859</v>
+        <v>626</v>
       </c>
       <c r="G438" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H438" s="23">
-        <v>45712</v>
+        <v>46063</v>
       </c>
       <c r="I438" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="J438" s="3" t="s">
-        <v>1150</v>
-      </c>
+      <c r="J438" s="24"/>
     </row>
     <row r="439" spans="1:10" hidden="1">
       <c r="A439" s="4">
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>32</v>
@@ -18937,19 +18941,19 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>32</v>
@@ -18967,7 +18971,7 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
@@ -18979,7 +18983,7 @@
         <v>23</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G441" s="2" t="s">
         <v>32</v>
@@ -18997,28 +19001,28 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1123</v>
+        <v>1216</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>627</v>
+        <v>1217</v>
       </c>
       <c r="G442" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H442" s="23">
-        <v>46063</v>
+        <v>46104</v>
       </c>
       <c r="I442" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J442" s="24"/>
     </row>
@@ -19027,19 +19031,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>32</v>
@@ -19048,7 +19052,7 @@
         <v>46104</v>
       </c>
       <c r="I443" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J443" s="24"/>
     </row>
@@ -19057,28 +19061,28 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1218</v>
+        <v>552</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1221</v>
+        <v>626</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H444" s="23">
-        <v>46104</v>
+        <v>46081</v>
       </c>
       <c r="I444" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J444" s="24"/>
     </row>
@@ -19087,7 +19091,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19099,7 +19103,7 @@
         <v>23</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G445" s="2" t="s">
         <v>32</v>
@@ -19117,7 +19121,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19129,7 +19133,7 @@
         <v>23</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>32</v>
@@ -19146,29 +19150,29 @@
       <c r="A447" s="4">
         <v>446</v>
       </c>
-      <c r="B447" s="53" t="s">
-        <v>1114</v>
+      <c r="B447" s="52" t="s">
+        <v>1112</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>552</v>
+        <v>1132</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>627</v>
+        <v>1133</v>
       </c>
       <c r="G447" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H447" s="23">
-        <v>46081</v>
+        <v>46091</v>
       </c>
       <c r="I447" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J447" s="24"/>
     </row>
@@ -19177,28 +19181,28 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="G448" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H448" s="23">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="I448" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J448" s="24"/>
     </row>
@@ -19207,25 +19211,25 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1146</v>
+        <v>1202</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1145</v>
+        <v>1090</v>
       </c>
       <c r="G449" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H449" s="23">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="I449" s="4" t="s">
         <v>593</v>
@@ -19237,19 +19241,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1093</v>
+        <v>1204</v>
       </c>
       <c r="G450" s="2" t="s">
         <v>32</v>
@@ -19267,19 +19271,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G451" s="2" t="s">
         <v>32</v>
@@ -19288,7 +19292,7 @@
         <v>46099</v>
       </c>
       <c r="I451" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J451" s="24"/>
     </row>
@@ -19297,13 +19301,13 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
@@ -19318,7 +19322,7 @@
         <v>46099</v>
       </c>
       <c r="I452" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J452" s="24"/>
     </row>
@@ -19327,28 +19331,28 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="G453" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H453" s="23">
-        <v>46099</v>
+        <v>46081</v>
       </c>
       <c r="I453" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J453" s="24"/>
     </row>
@@ -19357,28 +19361,28 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1217</v>
+        <v>1126</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H454" s="23">
-        <v>46081</v>
+        <v>46105</v>
       </c>
       <c r="I454" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J454" s="24"/>
     </row>
@@ -19387,19 +19391,19 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G455" s="2" t="s">
         <v>32</v>
@@ -19408,7 +19412,7 @@
         <v>46105</v>
       </c>
       <c r="I455" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J455" s="24"/>
     </row>
@@ -19417,28 +19421,28 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1128</v>
+        <v>1233</v>
       </c>
       <c r="G456" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H456" s="23">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="I456" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J456" s="24"/>
     </row>
@@ -19447,19 +19451,19 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G457" s="2" t="s">
         <v>32</v>
@@ -19468,7 +19472,7 @@
         <v>46108</v>
       </c>
       <c r="I457" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J457" s="24"/>
     </row>
@@ -19477,28 +19481,28 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G458" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H458" s="23">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="I458" s="4" t="s">
-        <v>671</v>
+        <v>593</v>
       </c>
       <c r="J458" s="24"/>
     </row>
@@ -19507,28 +19511,28 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>552</v>
+        <v>1239</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>627</v>
+        <v>1240</v>
       </c>
       <c r="G459" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H459" s="23">
-        <v>46081</v>
+        <v>46113</v>
       </c>
       <c r="I459" s="4" t="s">
-        <v>593</v>
+        <v>670</v>
       </c>
       <c r="J459" s="24"/>
     </row>
@@ -19537,7 +19541,7 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
@@ -19549,7 +19553,7 @@
         <v>23</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>32</v>
@@ -19567,7 +19571,7 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
@@ -19579,7 +19583,7 @@
         <v>23</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G461" s="2" t="s">
         <v>32</v>
@@ -19597,7 +19601,7 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
@@ -19609,7 +19613,7 @@
         <v>23</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G462" s="2" t="s">
         <v>32</v>
@@ -19627,7 +19631,7 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
@@ -19639,7 +19643,7 @@
         <v>23</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G463" s="2" t="s">
         <v>32</v>
@@ -19657,7 +19661,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19669,7 +19673,7 @@
         <v>23</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G464" s="2" t="s">
         <v>32</v>
@@ -19687,7 +19691,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19699,7 +19703,7 @@
         <v>23</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G465" s="2" t="s">
         <v>32</v>
@@ -19717,7 +19721,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19729,7 +19733,7 @@
         <v>23</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G466" s="2" t="s">
         <v>32</v>
@@ -19747,7 +19751,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19759,7 +19763,7 @@
         <v>23</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G467" s="2" t="s">
         <v>32</v>
@@ -19777,7 +19781,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19789,7 +19793,7 @@
         <v>23</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G468" s="2" t="s">
         <v>32</v>
@@ -19807,7 +19811,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19819,7 +19823,7 @@
         <v>23</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G469" s="2" t="s">
         <v>32</v>
@@ -19837,7 +19841,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19849,7 +19853,7 @@
         <v>23</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G470" s="2" t="s">
         <v>32</v>
@@ -19867,7 +19871,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19879,7 +19883,7 @@
         <v>23</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G471" s="2" t="s">
         <v>32</v>
@@ -19897,7 +19901,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19909,7 +19913,7 @@
         <v>23</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G472" s="2" t="s">
         <v>32</v>
@@ -19927,7 +19931,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19939,7 +19943,7 @@
         <v>23</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G473" s="2" t="s">
         <v>32</v>
@@ -19957,7 +19961,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19969,7 +19973,7 @@
         <v>23</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G474" s="2" t="s">
         <v>32</v>
@@ -19987,7 +19991,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -19999,7 +20003,7 @@
         <v>23</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G475" s="2" t="s">
         <v>32</v>
@@ -20017,7 +20021,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20029,7 +20033,7 @@
         <v>23</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G476" s="2" t="s">
         <v>32</v>
@@ -20047,7 +20051,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20059,7 +20063,7 @@
         <v>23</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G477" s="2" t="s">
         <v>32</v>
@@ -20077,7 +20081,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20089,7 +20093,7 @@
         <v>23</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G478" s="2" t="s">
         <v>32</v>
@@ -20107,7 +20111,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20119,7 +20123,7 @@
         <v>23</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G479" s="2" t="s">
         <v>32</v>
@@ -20137,7 +20141,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20149,7 +20153,7 @@
         <v>23</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G480" s="2" t="s">
         <v>32</v>
@@ -20167,7 +20171,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20179,7 +20183,7 @@
         <v>23</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G481" s="2" t="s">
         <v>32</v>
@@ -20197,7 +20201,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20209,7 +20213,7 @@
         <v>23</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G482" s="2" t="s">
         <v>32</v>
@@ -20227,7 +20231,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20239,7 +20243,7 @@
         <v>23</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>32</v>
@@ -20257,7 +20261,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20269,7 +20273,7 @@
         <v>23</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G484" s="2" t="s">
         <v>32</v>
@@ -20287,25 +20291,25 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>552</v>
+        <v>1121</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G485" s="2" t="s">
         <v>32</v>
       </c>
       <c r="H485" s="23">
-        <v>46081</v>
+        <v>46063</v>
       </c>
       <c r="I485" s="4" t="s">
         <v>593</v>
@@ -20317,19 +20321,19 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G486" s="2" t="s">
         <v>32</v>
@@ -20341,36 +20345,6 @@
         <v>593</v>
       </c>
       <c r="J486" s="24"/>
-    </row>
-    <row r="487" spans="1:10" hidden="1">
-      <c r="A487" s="4">
-        <v>486</v>
-      </c>
-      <c r="B487" s="52" t="s">
-        <v>1115</v>
-      </c>
-      <c r="C487" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D487" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E487" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="G487" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H487" s="23">
-        <v>46063</v>
-      </c>
-      <c r="I487" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="J487" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -20388,7 +20362,7 @@
   <conditionalFormatting sqref="D345">
     <cfRule type="duplicateValues" dxfId="24" priority="89"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D437 D2:D345">
+  <conditionalFormatting sqref="D436 D2:D345">
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E236 G194 E238:E1048576">
@@ -20465,19 +20439,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C2" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="D2" s="43" t="s">
+        <v>930</v>
+      </c>
+      <c r="E2" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>932</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F2" s="46">
         <v>22</v>
@@ -20485,19 +20459,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C3" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="D3" s="43" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>933</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F3" s="46">
         <v>5</v>
@@ -20505,19 +20479,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C4" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="D4" s="43" t="s">
+        <v>932</v>
+      </c>
+      <c r="E4" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>934</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F4" s="46">
         <v>1</v>
@@ -20525,19 +20499,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="D5" s="43" t="s">
+        <v>933</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C5" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>935</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F5" s="46">
         <v>3</v>
@@ -20545,19 +20519,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C6" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="D6" s="43" t="s">
+        <v>934</v>
+      </c>
+      <c r="E6" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C6" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>936</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F6" s="46">
         <v>3</v>
@@ -20565,19 +20539,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="42" t="s">
+        <v>902</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>903</v>
+      </c>
+      <c r="C7" s="42" t="s">
         <v>904</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="D7" s="44" t="s">
+        <v>935</v>
+      </c>
+      <c r="E7" s="44" t="s">
         <v>905</v>
-      </c>
-      <c r="C7" s="42" t="s">
-        <v>906</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>937</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>907</v>
       </c>
       <c r="F7" s="46">
         <v>6</v>
@@ -21084,10 +21058,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E1" t="s">
         <v>717</v>
-      </c>
-      <c r="E1" t="s">
-        <v>718</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -21096,13 +21070,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I1" t="s">
         <v>719</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>720</v>
-      </c>
-      <c r="J1" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -21110,16 +21084,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>382</v>
@@ -21134,7 +21108,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -21142,16 +21116,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D3" s="1">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>382</v>
@@ -21166,7 +21140,7 @@
         <v>15</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -21174,16 +21148,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>382</v>
@@ -21198,7 +21172,7 @@
         <v>15</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -21206,16 +21180,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>382</v>
@@ -21230,7 +21204,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -21238,16 +21212,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>382</v>
@@ -21262,7 +21236,7 @@
         <v>15</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -21270,16 +21244,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>382</v>
@@ -21294,7 +21268,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -21302,16 +21276,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>382</v>
@@ -21326,7 +21300,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -21334,16 +21308,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>382</v>
@@ -21358,7 +21332,7 @@
         <v>15</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -21366,16 +21340,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D10" s="1">
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>382</v>
@@ -21390,7 +21364,7 @@
         <v>15</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -21398,16 +21372,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>382</v>
@@ -21422,7 +21396,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -21430,16 +21404,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D12" s="1">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="D12" s="1">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>382</v>
@@ -21454,7 +21428,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -21462,16 +21436,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>382</v>
@@ -21486,7 +21460,7 @@
         <v>15</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -21494,16 +21468,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>382</v>
@@ -21518,7 +21492,7 @@
         <v>15</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -21526,16 +21500,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D15" s="1">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>663</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="D15" s="1">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>664</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>382</v>
@@ -21550,7 +21524,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -21558,16 +21532,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D16" s="1">
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>382</v>
@@ -21582,7 +21556,7 @@
         <v>15</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -21590,16 +21564,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>382</v>
@@ -21614,7 +21588,7 @@
         <v>15</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -21622,16 +21596,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>382</v>
@@ -21646,7 +21620,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -21654,16 +21628,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D19" s="1">
         <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>382</v>
@@ -21678,7 +21652,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -21686,16 +21660,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D20" s="1">
         <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>382</v>
@@ -21710,7 +21684,7 @@
         <v>15</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -21718,16 +21692,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>382</v>
@@ -21742,7 +21716,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -21750,16 +21724,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D22" s="1">
         <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>382</v>
@@ -21774,7 +21748,7 @@
         <v>15</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -21782,16 +21756,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D23" s="1">
         <v>22</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>382</v>
@@ -21806,7 +21780,7 @@
         <v>15</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -21814,16 +21788,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D24" s="1">
         <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>382</v>
@@ -21838,7 +21812,7 @@
         <v>15</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -21846,10 +21820,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D25" s="1">
         <v>24</v>
@@ -21858,7 +21832,7 @@
         <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>32</v>
@@ -21876,10 +21850,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D26" s="1">
         <v>25</v>
@@ -21888,7 +21862,7 @@
         <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>32</v>
@@ -21906,10 +21880,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D27" s="1">
         <v>26</v>
@@ -21918,7 +21892,7 @@
         <v>23</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>32</v>
@@ -21936,10 +21910,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D28" s="1">
         <v>27</v>
@@ -21948,7 +21922,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>32</v>
@@ -21966,10 +21940,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D29" s="1">
         <v>28</v>
@@ -21978,7 +21952,7 @@
         <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>32</v>
@@ -21996,10 +21970,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D30" s="1">
         <v>29</v>
@@ -22008,7 +21982,7 @@
         <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -22026,10 +22000,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D31" s="1">
         <v>30</v>
@@ -22038,7 +22012,7 @@
         <v>23</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -22056,10 +22030,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D32" s="1">
         <v>31</v>
@@ -22068,7 +22042,7 @@
         <v>23</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>32</v>
@@ -22086,10 +22060,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D33" s="1">
         <v>32</v>
@@ -22098,7 +22072,7 @@
         <v>23</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>32</v>
@@ -22116,10 +22090,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D34" s="1">
         <v>33</v>
@@ -22128,7 +22102,7 @@
         <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>32</v>
@@ -22146,10 +22120,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D35" s="1">
         <v>34</v>
@@ -22158,7 +22132,7 @@
         <v>23</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>32</v>
@@ -22176,10 +22150,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D36" s="1">
         <v>35</v>
@@ -22188,7 +22162,7 @@
         <v>23</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>32</v>
@@ -22206,10 +22180,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D37" s="1">
         <v>36</v>
@@ -22218,7 +22192,7 @@
         <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>32</v>
@@ -22236,10 +22210,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D38" s="1">
         <v>37</v>
@@ -22248,7 +22222,7 @@
         <v>23</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>32</v>
@@ -22266,19 +22240,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>675</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>32</v>
@@ -22296,19 +22270,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -22326,16 +22300,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>382</v>
@@ -22356,19 +22330,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C42" s="47" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G42" t="s">
         <v>32</v>
@@ -22385,19 +22359,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E43" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
@@ -22409,7 +22383,7 @@
         <v>15</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -22417,19 +22391,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D44" s="33">
         <v>101</v>
       </c>
       <c r="E44" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F44" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G44" t="s">
         <v>32</v>
@@ -22441,7 +22415,7 @@
         <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -22449,10 +22423,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D45" s="33">
         <v>102</v>
@@ -22461,7 +22435,7 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G45" t="s">
         <v>32</v>
@@ -22478,10 +22452,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C46" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D46">
         <v>201</v>
@@ -22490,7 +22464,7 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G46" t="s">
         <v>32</v>
@@ -22507,10 +22481,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C47" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D47">
         <v>202</v>
@@ -22519,7 +22493,7 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G47" t="s">
         <v>32</v>
@@ -22536,10 +22510,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C48" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D48">
         <v>203</v>
@@ -22548,7 +22522,7 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G48" t="s">
         <v>32</v>
@@ -22565,10 +22539,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C49" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D49">
         <v>204</v>
@@ -22577,7 +22551,7 @@
         <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="G49" t="s">
         <v>32</v>
@@ -22594,10 +22568,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C50" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D50">
         <v>205</v>
@@ -22606,7 +22580,7 @@
         <v>13</v>
       </c>
       <c r="F50" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G50" t="s">
         <v>32</v>
@@ -22618,7 +22592,7 @@
         <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -22626,10 +22600,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="D51">
         <v>206</v>
@@ -22638,7 +22612,7 @@
         <v>13</v>
       </c>
       <c r="F51" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G51" t="s">
         <v>32</v>
@@ -22650,7 +22624,7 @@
         <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1">
@@ -22658,13 +22632,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>881</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>71</v>
@@ -22682,7 +22656,7 @@
         <v>593</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1">
@@ -22690,10 +22664,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="D53" s="14">
         <v>22011316</v>
@@ -22702,7 +22676,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -22714,7 +22688,7 @@
         <v>593</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="54" spans="1:10">

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53FC9D7-91B4-47AE-9F6C-85A62599FBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45B6159-D22D-410F-A651-93AFD9647488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="1245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4266" uniqueCount="1248">
   <si>
     <t>INDICE</t>
   </si>
@@ -3334,9 +3334,6 @@
     <t>E.M. FERNANDO DE CARVALHO</t>
   </si>
   <si>
-    <t>E.M. MAESTRO KIKO</t>
-  </si>
-  <si>
     <t>E.M. JOAQUINA DE OLIVEIRA RANGEL</t>
   </si>
   <si>
@@ -3773,6 +3770,18 @@
   </si>
   <si>
     <t>M-15-02-2025; M-31/03/2026;</t>
+  </si>
+  <si>
+    <t>XC75051318</t>
+  </si>
+  <si>
+    <t>E.M.E. FRANCISCO JOSE DE MARINS KIKO</t>
+  </si>
+  <si>
+    <t>XC75051319</t>
+  </si>
+  <si>
+    <t>E.M.VER. EDEMUNDO P. DE SA CARVALHO</t>
   </si>
 </sst>
 </file>
@@ -3838,7 +3847,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3905,12 +3914,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -3958,7 +3961,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4100,10 +4103,7 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4404,91 +4404,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4572,7 +4487,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4724,6 +4639,91 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4764,22 +4764,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J486" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J486" tableType="queryTable" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
   <autoFilter ref="A1:J486" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J27">
     <sortCondition ref="A13"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="52"/>
-    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="51"/>
-    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{F8E3D681-C494-47F2-8429-052381C12AF1}" uniqueName="1" name="INDICE" queryTableFieldId="1" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{EE2E8FA5-A99D-4573-9868-408DB8FD4417}" uniqueName="2" name="MODELO" queryTableFieldId="2" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{CB5196C0-CCA1-4329-825F-D71E0948A542}" uniqueName="11" name="TIPO" queryTableFieldId="16390" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{27BC8F35-CC2C-44A1-BAF7-B0390B09477F}" uniqueName="3" name="NUMERO DE SERIE" queryTableFieldId="3" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{552F7A6E-6277-4DC1-9CDA-EA7FDCCE8E36}" uniqueName="4" name="LOCALIZAÇÃO" queryTableFieldId="4" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{4C8345F1-6E01-4566-9030-039665486C03}" uniqueName="5" name="SETOR" queryTableFieldId="5" dataDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{10436F87-F6F1-46C4-A81A-8D144AC72FDF}" uniqueName="9" name="EMPRESA" queryTableFieldId="16389" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{B7941BA2-3E1C-476B-A3C7-BA155A35A2D0}" uniqueName="6" name="ATUALIZADO" queryTableFieldId="6" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{4338F703-CE4B-4443-8A10-74F64ED8CD42}" uniqueName="7" name="PRINTWAY" queryTableFieldId="16391" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{02B7C1FB-8EA9-4F22-BCCF-3D1809FFEDCC}" uniqueName="8" name="OBSERVAÇÃO" queryTableFieldId="8" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4794,26 +4794,26 @@
     <tableColumn id="3" xr3:uid="{95A3DCD3-FE19-4A74-9940-661D6BB94B25}" name="MODELO"/>
     <tableColumn id="4" xr3:uid="{521C03E5-7FA9-4789-8198-9E0781F3ABC7}" name="DESCRIÇÃO"/>
     <tableColumn id="5" xr3:uid="{579D81F0-AA4C-4609-BF35-AF838B2B149B}" name="COR"/>
-    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{19487D13-EF31-43DA-89CA-4AA1E1029C34}" name="QUANTIDADE" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}" name="Tabela4" displayName="Tabela4" ref="A1:J51" insertRowShift="1" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:J51" xr:uid="{FBC7B6D1-65BC-435E-B4FF-CC495249D6BD}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{A3ABFE90-9D3C-42DA-8CF0-D71D91CAB9BB}" name="INDICE" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{A733301C-FC8A-4542-8BA2-BBEA67F3D424}" name="MODELO" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{C6E07CD7-A3F4-4433-BB55-99FA29AE99FA}" name="TIPO" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{007A788B-09E3-480D-A6BC-6718BD4566C1}" name="SERIAL" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{ACA8BAA3-86EA-4046-9E8D-0C6E6216A0B1}" name="LOCALIDADE" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{D2E86C5C-2786-4CA5-9B36-02C6270BDE33}" name="SETOR" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{3F4C4914-DB98-431A-AD17-7760541C7F42}" name="EMPRESA" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{4F681722-ADFE-4A58-BC0F-8623348ECD33}" name="DATA" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{13FFF32F-FC49-429E-BD6E-76ADCE6F7534}" name="MONIT." dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{F4255CFF-6FAD-434F-93D8-3A0C54269527}" name="DETALHES" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5125,8 +5125,8 @@
     <col min="4" max="4" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="255.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="3"/>
@@ -5151,7 +5151,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -5183,7 +5183,7 @@
       <c r="F2" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="6">
@@ -5215,7 +5215,7 @@
       <c r="F3" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="6">
@@ -5247,7 +5247,7 @@
       <c r="F4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="6">
@@ -5279,7 +5279,7 @@
       <c r="F5" s="4" t="s">
         <v>817</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="6">
@@ -5311,7 +5311,7 @@
       <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="6">
@@ -5343,7 +5343,7 @@
       <c r="F7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="6">
@@ -5375,7 +5375,7 @@
       <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H8" s="6">
@@ -5407,7 +5407,7 @@
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="6">
@@ -5437,7 +5437,7 @@
       <c r="F10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H10" s="6">
@@ -5467,7 +5467,7 @@
       <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="9">
@@ -5499,7 +5499,7 @@
       <c r="F12" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="9">
@@ -5531,7 +5531,7 @@
       <c r="F13" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="9">
@@ -5563,7 +5563,7 @@
       <c r="F14" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H14" s="9">
@@ -5595,7 +5595,7 @@
       <c r="F15" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H15" s="9">
@@ -5625,9 +5625,9 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G16" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H16" s="9">
@@ -5656,7 +5656,7 @@
       <c r="F17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H17" s="9">
@@ -5688,7 +5688,7 @@
       <c r="F18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="9">
@@ -5720,7 +5720,7 @@
       <c r="F19" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H19" s="9">
@@ -5752,7 +5752,7 @@
       <c r="F20" s="4" t="s">
         <v>1091</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="9">
@@ -5784,7 +5784,7 @@
       <c r="F21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H21" s="9">
@@ -5816,7 +5816,7 @@
       <c r="F22" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H22" s="9">
@@ -5848,7 +5848,7 @@
       <c r="F23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H23" s="9">
@@ -5880,7 +5880,7 @@
       <c r="F24" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H24" s="9">
@@ -5912,7 +5912,7 @@
       <c r="F25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H25" s="9">
@@ -5944,7 +5944,7 @@
       <c r="F26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H26" s="9">
@@ -5973,7 +5973,7 @@
       <c r="F27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H27" s="9">
@@ -6002,7 +6002,7 @@
       <c r="F28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H28" s="9">
@@ -6034,7 +6034,7 @@
       <c r="F29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H29" s="9">
@@ -6066,7 +6066,7 @@
       <c r="F30" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H30" s="9">
@@ -6098,7 +6098,7 @@
       <c r="F31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H31" s="9">
@@ -6130,7 +6130,7 @@
       <c r="F32" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H32" s="9">
@@ -6162,7 +6162,7 @@
       <c r="F33" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H33" s="9">
@@ -6194,7 +6194,7 @@
       <c r="F34" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H34" s="9">
@@ -6226,7 +6226,7 @@
       <c r="F35" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H35" s="9">
@@ -6258,7 +6258,7 @@
       <c r="F36" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H36" s="9">
@@ -6290,7 +6290,7 @@
       <c r="F37" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H37" s="9">
@@ -6319,7 +6319,7 @@
       <c r="F38" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H38" s="9">
@@ -6351,7 +6351,7 @@
       <c r="F39" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H39" s="9">
@@ -6383,7 +6383,7 @@
       <c r="F40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H40" s="9">
@@ -6415,7 +6415,7 @@
       <c r="F41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H41" s="9">
@@ -6447,7 +6447,7 @@
       <c r="F42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H42" s="9">
@@ -6479,7 +6479,7 @@
       <c r="F43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H43" s="9">
@@ -6511,7 +6511,7 @@
       <c r="F44" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="9">
@@ -6543,7 +6543,7 @@
       <c r="F45" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H45" s="9">
@@ -6572,7 +6572,7 @@
       <c r="F46" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H46" s="9">
@@ -6604,7 +6604,7 @@
       <c r="F47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="5" t="s">
+      <c r="G47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H47" s="9">
@@ -6636,7 +6636,7 @@
       <c r="F48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H48" s="9">
@@ -6668,7 +6668,7 @@
       <c r="F49" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H49" s="9">
@@ -6697,7 +6697,7 @@
       <c r="F50" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H50" s="9">
@@ -6726,7 +6726,7 @@
       <c r="F51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G51" s="5" t="s">
+      <c r="G51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H51" s="9">
@@ -6758,7 +6758,7 @@
       <c r="F52" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H52" s="15">
@@ -6790,7 +6790,7 @@
       <c r="F53" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H53" s="9">
@@ -6820,9 +6820,9 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G54" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>71</v>
       </c>
       <c r="H54" s="23">
@@ -6854,7 +6854,7 @@
       <c r="F55" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H55" s="9">
@@ -6883,7 +6883,7 @@
       <c r="F56" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H56" s="9">
@@ -6912,7 +6912,7 @@
       <c r="F57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G57" s="5" t="s">
+      <c r="G57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H57" s="9">
@@ -6941,7 +6941,7 @@
       <c r="F58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H58" s="9">
@@ -6970,7 +6970,7 @@
       <c r="F59" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H59" s="9">
@@ -6999,7 +6999,7 @@
       <c r="F60" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H60" s="9">
@@ -7028,7 +7028,7 @@
       <c r="F61" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H61" s="9">
@@ -7060,7 +7060,7 @@
       <c r="F62" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H62" s="9">
@@ -7092,7 +7092,7 @@
       <c r="F63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H63" s="9">
@@ -7121,7 +7121,7 @@
       <c r="F64" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H64" s="9">
@@ -7153,7 +7153,7 @@
       <c r="F65" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="G65" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H65" s="9">
@@ -7182,7 +7182,7 @@
       <c r="F66" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="9">
@@ -7211,7 +7211,7 @@
       <c r="F67" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="9">
@@ -7240,7 +7240,7 @@
       <c r="F68" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H68" s="9">
@@ -7269,7 +7269,7 @@
       <c r="F69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H69" s="9">
@@ -7301,7 +7301,7 @@
       <c r="F70" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H70" s="9">
@@ -7333,7 +7333,7 @@
       <c r="F71" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="G71" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H71" s="9">
@@ -7357,12 +7357,12 @@
         <v>149</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G72" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H72" s="9">
@@ -7394,7 +7394,7 @@
       <c r="F73" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G73" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H73" s="9">
@@ -7426,7 +7426,7 @@
       <c r="F74" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H74" s="9">
@@ -7458,7 +7458,7 @@
       <c r="F75" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H75" s="9">
@@ -7487,7 +7487,7 @@
       <c r="F76" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H76" s="9">
@@ -7519,7 +7519,7 @@
       <c r="F77" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G77" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H77" s="9">
@@ -7551,7 +7551,7 @@
       <c r="F78" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H78" s="9">
@@ -7583,7 +7583,7 @@
       <c r="F79" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H79" s="9">
@@ -7615,7 +7615,7 @@
       <c r="F80" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H80" s="9">
@@ -7647,7 +7647,7 @@
       <c r="F81" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H81" s="9">
@@ -7679,7 +7679,7 @@
       <c r="F82" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I82" s="4" t="s">
@@ -7705,7 +7705,7 @@
       <c r="F83" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G83" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I83" s="4" t="s">
@@ -7731,7 +7731,7 @@
       <c r="F84" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I84" s="4" t="s">
@@ -7757,7 +7757,7 @@
       <c r="F85" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="G85" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H85" s="9">
@@ -7789,7 +7789,7 @@
       <c r="F86" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G86" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H86" s="9">
@@ -7812,8 +7812,8 @@
       <c r="C87" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D87" s="54" t="s">
-        <v>1243</v>
+      <c r="D87" s="2" t="s">
+        <v>1242</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>23</v>
@@ -7821,7 +7821,7 @@
       <c r="F87" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="G87" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H87" s="9">
@@ -7831,7 +7831,7 @@
         <v>591</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -7853,7 +7853,7 @@
       <c r="F88" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G88" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="9">
@@ -7885,7 +7885,7 @@
       <c r="F89" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I89" s="4" t="s">
@@ -7912,9 +7912,9 @@
         <v>997</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G90" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G90" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H90" s="9">
@@ -7946,7 +7946,7 @@
       <c r="F91" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H91" s="9">
@@ -7978,7 +7978,7 @@
       <c r="F92" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I92" s="4" t="s">
@@ -8004,7 +8004,7 @@
       <c r="F93" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="G93" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I93" s="4" t="s">
@@ -8030,7 +8030,7 @@
       <c r="F94" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="G94" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H94" s="9">
@@ -8062,7 +8062,7 @@
       <c r="F95" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I95" s="4" t="s">
@@ -8091,7 +8091,7 @@
       <c r="F96" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="G96" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H96" s="9">
@@ -8120,7 +8120,7 @@
       <c r="F97" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="G97" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H97" s="9">
@@ -8149,7 +8149,7 @@
       <c r="F98" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G98" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H98" s="9">
@@ -8178,7 +8178,7 @@
       <c r="F99" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H99" s="9">
@@ -8210,7 +8210,7 @@
       <c r="F100" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H100" s="9">
@@ -8242,7 +8242,7 @@
       <c r="F101" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="9">
@@ -8272,9 +8272,9 @@
         <v>80</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1138</v>
-      </c>
-      <c r="G102" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G102" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H102" s="9">
@@ -8306,7 +8306,7 @@
       <c r="F103" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="9">
@@ -8338,7 +8338,7 @@
       <c r="F104" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H104" s="9">
@@ -8370,7 +8370,7 @@
       <c r="F105" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H105" s="9">
@@ -8402,7 +8402,7 @@
       <c r="F106" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H106" s="9">
@@ -8434,7 +8434,7 @@
       <c r="F107" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H107" s="9">
@@ -8466,7 +8466,7 @@
       <c r="F108" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H108" s="23"/>
@@ -8494,7 +8494,7 @@
       <c r="F109" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H109" s="9">
@@ -8526,7 +8526,7 @@
       <c r="F110" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H110" s="9">
@@ -8558,7 +8558,7 @@
       <c r="F111" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H111" s="9">
@@ -8590,7 +8590,7 @@
       <c r="F112" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H112" s="9">
@@ -8622,7 +8622,7 @@
       <c r="F113" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H113" s="9">
@@ -8654,7 +8654,7 @@
       <c r="F114" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H114" s="9">
@@ -8686,7 +8686,7 @@
       <c r="F115" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G115" s="5" t="s">
+      <c r="G115" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H115" s="9">
@@ -8718,7 +8718,7 @@
       <c r="F116" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="G116" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H116" s="9">
@@ -8750,7 +8750,7 @@
       <c r="F117" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G117" s="5" t="s">
+      <c r="G117" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H117" s="9">
@@ -8782,7 +8782,7 @@
       <c r="F118" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H118" s="9">
@@ -8814,7 +8814,7 @@
       <c r="F119" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="G119" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H119" s="9">
@@ -8846,7 +8846,7 @@
       <c r="F120" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="G120" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H120" s="9">
@@ -8878,7 +8878,7 @@
       <c r="F121" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G121" s="5" t="s">
+      <c r="G121" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H121" s="9">
@@ -8910,7 +8910,7 @@
       <c r="F122" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G122" s="5" t="s">
+      <c r="G122" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H122" s="9">
@@ -8940,9 +8940,9 @@
         <v>71</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="G123" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G123" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H123" s="9">
@@ -8969,9 +8969,9 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="G124" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H124" s="9">
@@ -9003,7 +9003,7 @@
       <c r="F125" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G125" s="5" t="s">
+      <c r="G125" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H125" s="9">
@@ -9033,9 +9033,9 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="G126" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G126" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H126" s="9">
@@ -9067,7 +9067,7 @@
       <c r="F127" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="G127" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H127" s="9">
@@ -9099,7 +9099,7 @@
       <c r="F128" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H128" s="9">
@@ -9131,7 +9131,7 @@
       <c r="F129" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="G129" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H129" s="9">
@@ -9163,7 +9163,7 @@
       <c r="F130" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="G130" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H130" s="9">
@@ -9195,7 +9195,7 @@
       <c r="F131" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G131" s="5" t="s">
+      <c r="G131" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H131" s="9">
@@ -9225,9 +9225,9 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G132" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G132" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H132" s="9">
@@ -9259,7 +9259,7 @@
       <c r="F133" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="G133" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H133" s="9">
@@ -9289,9 +9289,9 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G134" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G134" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H134" s="9">
@@ -9321,9 +9321,9 @@
         <v>80</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="G135" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G135" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H135" s="9">
@@ -9333,7 +9333,7 @@
         <v>591</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9353,9 +9353,9 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G136" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G136" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H136" s="9">
@@ -9387,7 +9387,7 @@
       <c r="F137" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G137" s="5" t="s">
+      <c r="G137" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H137" s="9">
@@ -9419,7 +9419,7 @@
       <c r="F138" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="G138" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H138" s="9">
@@ -9451,7 +9451,7 @@
       <c r="F139" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="G139" s="5" t="s">
+      <c r="G139" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H139" s="9">
@@ -9461,7 +9461,7 @@
         <v>668</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -9483,7 +9483,7 @@
       <c r="F140" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="G140" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H140" s="9">
@@ -9513,9 +9513,9 @@
         <v>80</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G141" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G141" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H141" s="9">
@@ -9545,9 +9545,9 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G142" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G142" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H142" s="9">
@@ -9579,7 +9579,7 @@
       <c r="F143" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="G143" s="5" t="s">
+      <c r="G143" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H143" s="9">
@@ -9611,7 +9611,7 @@
       <c r="F144" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="G144" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H144" s="9">
@@ -9641,9 +9641,9 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1176</v>
-      </c>
-      <c r="G145" s="14" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G145" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H145" s="15">
@@ -9673,9 +9673,9 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G146" s="14" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G146" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H146" s="15">
@@ -9705,9 +9705,9 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="G147" s="14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G147" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H147" s="15">
@@ -9737,9 +9737,9 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G148" s="14" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G148" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H148" s="15">
@@ -9771,7 +9771,7 @@
       <c r="F149" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="G149" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H149" s="9">
@@ -9803,7 +9803,7 @@
       <c r="F150" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H150" s="9">
@@ -9835,7 +9835,7 @@
       <c r="F151" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G151" s="5" t="s">
+      <c r="G151" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H151" s="9">
@@ -9865,9 +9865,9 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="G152" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G152" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H152" s="9">
@@ -9877,7 +9877,7 @@
         <v>591</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -9899,7 +9899,7 @@
       <c r="F153" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G153" s="5" t="s">
+      <c r="G153" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H153" s="9">
@@ -9931,7 +9931,7 @@
       <c r="F154" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="G154" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H154" s="6">
@@ -9963,7 +9963,7 @@
       <c r="F155" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H155" s="9">
@@ -9995,7 +9995,7 @@
       <c r="F156" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G156" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H156" s="9">
@@ -10024,7 +10024,7 @@
       <c r="F157" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G157" s="5" t="s">
+      <c r="G157" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H157" s="9">
@@ -10053,7 +10053,7 @@
       <c r="F158" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G158" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H158" s="4"/>
@@ -10078,9 +10078,9 @@
         <v>358</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G159" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G159" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H159" s="9">
@@ -10090,7 +10090,7 @@
         <v>591</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -10112,7 +10112,7 @@
       <c r="F160" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G160" s="5" t="s">
+      <c r="G160" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H160" s="9">
@@ -10141,7 +10141,7 @@
       <c r="F161" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G161" s="5" t="s">
+      <c r="G161" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H161" s="6">
@@ -10173,7 +10173,7 @@
       <c r="F162" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G162" s="5" t="s">
+      <c r="G162" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H162" s="6">
@@ -10205,7 +10205,7 @@
       <c r="F163" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G163" s="5" t="s">
+      <c r="G163" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H163" s="9">
@@ -10215,7 +10215,7 @@
         <v>591</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -10237,7 +10237,7 @@
       <c r="F164" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G164" s="5" t="s">
+      <c r="G164" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H164" s="9">
@@ -10269,7 +10269,7 @@
       <c r="F165" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G165" s="2" t="s">
+      <c r="G165" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H165" s="9">
@@ -10298,7 +10298,7 @@
       <c r="F166" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="G166" s="5" t="s">
+      <c r="G166" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H166" s="9">
@@ -10327,7 +10327,7 @@
       <c r="F167" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="G167" s="5" t="s">
+      <c r="G167" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H167" s="6">
@@ -10359,7 +10359,7 @@
       <c r="F168" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="G168" s="5" t="s">
+      <c r="G168" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I168" s="4" t="s">
@@ -10385,7 +10385,7 @@
       <c r="F169" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="G169" s="5" t="s">
+      <c r="G169" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H169" s="23">
@@ -10415,7 +10415,7 @@
       <c r="F170" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="G170" s="5" t="s">
+      <c r="G170" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H170" s="9">
@@ -10425,7 +10425,7 @@
         <v>591</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -10447,7 +10447,7 @@
       <c r="F171" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="G171" s="5" t="s">
+      <c r="G171" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H171" s="9">
@@ -10476,7 +10476,7 @@
       <c r="F172" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="G172" s="5" t="s">
+      <c r="G172" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H172" s="9">
@@ -10505,7 +10505,7 @@
       <c r="F173" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G173" s="5" t="s">
+      <c r="G173" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H173" s="9">
@@ -10534,7 +10534,7 @@
       <c r="F174" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="G174" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H174" s="9">
@@ -10563,7 +10563,7 @@
       <c r="F175" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G175" s="5" t="s">
+      <c r="G175" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H175" s="9">
@@ -10592,7 +10592,7 @@
       <c r="F176" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G176" s="5" t="s">
+      <c r="G176" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H176" s="9">
@@ -10621,7 +10621,7 @@
       <c r="F177" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G177" s="5" t="s">
+      <c r="G177" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H177" s="9">
@@ -10650,7 +10650,7 @@
       <c r="F178" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G178" s="5" t="s">
+      <c r="G178" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H178" s="9">
@@ -10679,7 +10679,7 @@
       <c r="F179" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G179" s="5" t="s">
+      <c r="G179" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H179" s="9">
@@ -10708,7 +10708,7 @@
       <c r="F180" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G180" s="5" t="s">
+      <c r="G180" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H180" s="9">
@@ -10737,7 +10737,7 @@
       <c r="F181" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G181" s="5" t="s">
+      <c r="G181" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H181" s="9">
@@ -10766,7 +10766,7 @@
       <c r="F182" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G182" s="5" t="s">
+      <c r="G182" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H182" s="9">
@@ -10795,7 +10795,7 @@
       <c r="F183" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G183" s="5" t="s">
+      <c r="G183" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H183" s="9">
@@ -10824,7 +10824,7 @@
       <c r="F184" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="G184" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H184" s="9">
@@ -10853,7 +10853,7 @@
       <c r="F185" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G185" s="5" t="s">
+      <c r="G185" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H185" s="9">
@@ -10882,7 +10882,7 @@
       <c r="F186" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G186" s="5" t="s">
+      <c r="G186" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H186" s="9">
@@ -10911,7 +10911,7 @@
       <c r="F187" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G187" s="5" t="s">
+      <c r="G187" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H187" s="9">
@@ -10940,7 +10940,7 @@
       <c r="F188" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G188" s="5" t="s">
+      <c r="G188" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H188" s="9">
@@ -10969,7 +10969,7 @@
       <c r="F189" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G189" s="5" t="s">
+      <c r="G189" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H189" s="9">
@@ -10998,7 +10998,7 @@
       <c r="F190" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G190" s="5" t="s">
+      <c r="G190" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H190" s="9">
@@ -11027,7 +11027,7 @@
       <c r="F191" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G191" s="5" t="s">
+      <c r="G191" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H191" s="9">
@@ -11056,7 +11056,7 @@
       <c r="F192" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G192" s="5" t="s">
+      <c r="G192" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H192" s="9">
@@ -11085,7 +11085,7 @@
       <c r="F193" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="G193" s="5" t="s">
+      <c r="G193" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H193" s="9">
@@ -11114,7 +11114,7 @@
       <c r="F194" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G194" s="2" t="s">
+      <c r="G194" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H194" s="9">
@@ -11143,7 +11143,7 @@
       <c r="F195" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G195" s="5" t="s">
+      <c r="G195" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H195" s="9">
@@ -11175,7 +11175,7 @@
       <c r="F196" s="4" t="s">
         <v>989</v>
       </c>
-      <c r="G196" s="5" t="s">
+      <c r="G196" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H196" s="6">
@@ -11207,7 +11207,7 @@
       <c r="F197" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G197" s="5" t="s">
+      <c r="G197" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H197" s="6">
@@ -11239,7 +11239,7 @@
       <c r="F198" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G198" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H198" s="6">
@@ -11271,7 +11271,7 @@
       <c r="F199" s="4" t="s">
         <v>989</v>
       </c>
-      <c r="G199" s="5" t="s">
+      <c r="G199" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H199" s="6">
@@ -11301,9 +11301,9 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G200" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G200" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H200" s="9">
@@ -11335,7 +11335,7 @@
       <c r="F201" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="G201" s="5" t="s">
+      <c r="G201" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H201" s="9">
@@ -11367,7 +11367,7 @@
       <c r="F202" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G202" s="5" t="s">
+      <c r="G202" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H202" s="6">
@@ -11399,7 +11399,7 @@
       <c r="F203" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="G203" s="5" t="s">
+      <c r="G203" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H203" s="9">
@@ -11431,7 +11431,7 @@
       <c r="F204" s="1" t="s">
         <v>1093</v>
       </c>
-      <c r="G204" s="2" t="s">
+      <c r="G204" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H204" s="9">
@@ -11463,7 +11463,7 @@
       <c r="F205" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G205" s="2" t="s">
+      <c r="G205" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H205" s="9">
@@ -11495,7 +11495,7 @@
       <c r="F206" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G206" s="5" t="s">
+      <c r="G206" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H206" s="9">
@@ -11527,7 +11527,7 @@
       <c r="F207" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="G207" s="5" t="s">
+      <c r="G207" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H207" s="9">
@@ -11559,7 +11559,7 @@
       <c r="F208" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="G208" s="5" t="s">
+      <c r="G208" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H208" s="9">
@@ -11589,9 +11589,9 @@
         <v>80</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G209" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G209" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H209" s="9">
@@ -11623,7 +11623,7 @@
       <c r="F210" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="G210" s="5" t="s">
+      <c r="G210" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H210" s="9">
@@ -11655,7 +11655,7 @@
       <c r="F211" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G211" s="5" t="s">
+      <c r="G211" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H211" s="9">
@@ -11687,7 +11687,7 @@
       <c r="F212" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G212" s="5" t="s">
+      <c r="G212" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H212" s="9">
@@ -11719,7 +11719,7 @@
       <c r="F213" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G213" s="5" t="s">
+      <c r="G213" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H213" s="9">
@@ -11751,7 +11751,7 @@
       <c r="F214" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G214" s="5" t="s">
+      <c r="G214" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H214" s="9">
@@ -11783,7 +11783,7 @@
       <c r="F215" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G215" s="5" t="s">
+      <c r="G215" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H215" s="9">
@@ -11815,7 +11815,7 @@
       <c r="F216" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="G216" s="5" t="s">
+      <c r="G216" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H216" s="9">
@@ -11847,7 +11847,7 @@
       <c r="F217" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G217" s="5" t="s">
+      <c r="G217" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H217" s="9">
@@ -11877,9 +11877,9 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G218" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G218" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H218" s="9">
@@ -11909,9 +11909,9 @@
         <v>19</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G219" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G219" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H219" s="9">
@@ -11941,9 +11941,9 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G220" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G220" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H220" s="9">
@@ -11953,7 +11953,7 @@
         <v>591</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -11973,9 +11973,9 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G221" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G221" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H221" s="9">
@@ -12007,7 +12007,7 @@
       <c r="F222" s="4" t="s">
         <v>1092</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H222" s="9">
@@ -12037,9 +12037,9 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G223" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G223" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H223" s="9">
@@ -12071,7 +12071,7 @@
       <c r="F224" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H224" s="9">
@@ -12103,7 +12103,7 @@
       <c r="F225" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="G225" s="5" t="s">
+      <c r="G225" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H225" s="9">
@@ -12135,7 +12135,7 @@
       <c r="F226" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H226" s="9">
@@ -12167,7 +12167,7 @@
       <c r="F227" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="G227" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H227" s="9">
@@ -12199,7 +12199,7 @@
       <c r="F228" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H228" s="9">
@@ -12231,7 +12231,7 @@
       <c r="F229" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="G229" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H229" s="6">
@@ -12241,7 +12241,7 @@
         <v>591</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -12261,9 +12261,9 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="G230" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G230" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H230" s="6">
@@ -12295,7 +12295,7 @@
       <c r="F231" s="50" t="s">
         <v>1074</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="G231" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H231" s="6">
@@ -12325,9 +12325,9 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G232" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G232" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H232" s="9">
@@ -12359,7 +12359,7 @@
       <c r="F233" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="G233" s="5" t="s">
+      <c r="G233" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H233" s="9">
@@ -12391,7 +12391,7 @@
       <c r="F234" s="41" t="s">
         <v>1096</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H234" s="6">
@@ -12423,7 +12423,7 @@
       <c r="F235" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="G235" s="14" t="s">
+      <c r="G235" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H235" s="15">
@@ -12455,7 +12455,7 @@
       <c r="F236" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="G236" s="2" t="s">
+      <c r="G236" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H236" s="15">
@@ -12485,7 +12485,7 @@
       <c r="F237" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G237" s="14" t="s">
+      <c r="G237" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H237" s="15">
@@ -12517,7 +12517,7 @@
       <c r="F238" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H238" s="9">
@@ -12549,7 +12549,7 @@
       <c r="F239" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="G239" s="5" t="s">
+      <c r="G239" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H239" s="9">
@@ -12579,9 +12579,9 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1151</v>
-      </c>
-      <c r="G240" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G240" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H240" s="9">
@@ -12613,7 +12613,7 @@
       <c r="F241" s="1" t="s">
         <v>1097</v>
       </c>
-      <c r="G241" s="2" t="s">
+      <c r="G241" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H241" s="9">
@@ -12645,7 +12645,7 @@
       <c r="F242" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G242" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H242" s="9">
@@ -12674,7 +12674,7 @@
       <c r="F243" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="G243" s="5" t="s">
+      <c r="G243" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H243" s="9">
@@ -12706,7 +12706,7 @@
       <c r="F244" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G244" s="2" t="s">
+      <c r="G244" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H244" s="9">
@@ -12738,7 +12738,7 @@
       <c r="F245" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G245" s="5" t="s">
+      <c r="G245" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H245" s="9">
@@ -12770,7 +12770,7 @@
       <c r="F246" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="G246" s="2" t="s">
+      <c r="G246" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I246" s="4" t="s">
@@ -12799,7 +12799,7 @@
       <c r="F247" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="G247" s="2" t="s">
+      <c r="G247" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H247" s="9">
@@ -12831,7 +12831,7 @@
       <c r="F248" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G248" s="2" t="s">
+      <c r="G248" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H248" s="9">
@@ -12860,7 +12860,7 @@
       <c r="F249" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G249" s="2" t="s">
+      <c r="G249" s="1" t="s">
         <v>32</v>
       </c>
       <c r="I249" s="4" t="s">
@@ -12889,7 +12889,7 @@
       <c r="F250" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G250" s="2" t="s">
+      <c r="G250" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H250" s="15">
@@ -12921,7 +12921,7 @@
       <c r="F251" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G251" s="5" t="s">
+      <c r="G251" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H251" s="9">
@@ -12931,7 +12931,7 @@
         <v>591</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -12953,7 +12953,7 @@
       <c r="F252" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="G252" s="5" t="s">
+      <c r="G252" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H252" s="9">
@@ -12983,9 +12983,9 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G253" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G253" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H253" s="9">
@@ -13017,7 +13017,7 @@
       <c r="F254" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G254" s="5" t="s">
+      <c r="G254" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H254" s="9">
@@ -13049,7 +13049,7 @@
       <c r="F255" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G255" s="5" t="s">
+      <c r="G255" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H255" s="9">
@@ -13081,7 +13081,7 @@
       <c r="F256" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="G256" s="5" t="s">
+      <c r="G256" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H256" s="9">
@@ -13091,7 +13091,7 @@
         <v>591</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -13113,7 +13113,7 @@
       <c r="F257" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G257" s="5" t="s">
+      <c r="G257" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H257" s="9">
@@ -13145,7 +13145,7 @@
       <c r="F258" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G258" s="5" t="s">
+      <c r="G258" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H258" s="9">
@@ -13177,7 +13177,7 @@
       <c r="F259" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G259" s="5" t="s">
+      <c r="G259" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H259" s="9">
@@ -13209,7 +13209,7 @@
       <c r="F260" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G260" s="5" t="s">
+      <c r="G260" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H260" s="9">
@@ -13241,7 +13241,7 @@
       <c r="F261" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G261" s="5" t="s">
+      <c r="G261" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H261" s="9">
@@ -13251,7 +13251,7 @@
         <v>591</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -13273,7 +13273,7 @@
       <c r="F262" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G262" s="5" t="s">
+      <c r="G262" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H262" s="9">
@@ -13305,7 +13305,7 @@
       <c r="F263" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G263" s="5" t="s">
+      <c r="G263" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H263" s="9">
@@ -13337,7 +13337,7 @@
       <c r="F264" s="4" t="s">
         <v>1014</v>
       </c>
-      <c r="G264" s="5" t="s">
+      <c r="G264" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H264" s="9">
@@ -13369,7 +13369,7 @@
       <c r="F265" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G265" s="5" t="s">
+      <c r="G265" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H265" s="9">
@@ -13401,7 +13401,7 @@
       <c r="F266" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G266" s="2" t="s">
+      <c r="G266" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H266" s="9">
@@ -13433,7 +13433,7 @@
       <c r="F267" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G267" s="2" t="s">
+      <c r="G267" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H267" s="9">
@@ -13465,7 +13465,7 @@
       <c r="F268" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G268" s="2" t="s">
+      <c r="G268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H268" s="9">
@@ -13495,9 +13495,9 @@
         <v>358</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G269" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G269" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H269" s="9">
@@ -13507,7 +13507,7 @@
         <v>591</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -13527,9 +13527,9 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G270" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G270" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H270" s="9">
@@ -13559,9 +13559,9 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G271" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G271" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H271" s="9">
@@ -13591,9 +13591,9 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G272" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G272" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H272" s="9">
@@ -13623,9 +13623,9 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G273" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G273" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H273" s="9">
@@ -13655,9 +13655,9 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G274" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G274" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H274" s="9">
@@ -13687,9 +13687,9 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G275" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G275" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H275" s="9">
@@ -13721,7 +13721,7 @@
       <c r="F276" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="G276" s="2" t="s">
+      <c r="G276" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H276" s="9">
@@ -13753,7 +13753,7 @@
       <c r="F277" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="G277" s="2" t="s">
+      <c r="G277" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H277" s="9">
@@ -13783,9 +13783,9 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="G278" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G278" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H278" s="9">
@@ -13815,9 +13815,9 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G279" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G279" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H279" s="9">
@@ -13847,9 +13847,9 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G280" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G280" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H280" s="9">
@@ -13879,9 +13879,9 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G281" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G281" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H281" s="9">
@@ -13911,9 +13911,9 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G282" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G282" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H282" s="9">
@@ -13945,7 +13945,7 @@
       <c r="F283" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="G283" s="2" t="s">
+      <c r="G283" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H283" s="9">
@@ -13975,9 +13975,9 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G284" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G284" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H284" s="9">
@@ -14007,9 +14007,9 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1164</v>
-      </c>
-      <c r="G285" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G285" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H285" s="9">
@@ -14039,9 +14039,9 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G286" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G286" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H286" s="9">
@@ -14071,9 +14071,9 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G287" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G287" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H287" s="9">
@@ -14105,7 +14105,7 @@
       <c r="F288" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="G288" s="2" t="s">
+      <c r="G288" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H288" s="9">
@@ -14137,7 +14137,7 @@
       <c r="F289" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G289" s="2" t="s">
+      <c r="G289" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H289" s="9">
@@ -14169,7 +14169,7 @@
       <c r="F290" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="G290" s="2" t="s">
+      <c r="G290" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H290" s="9">
@@ -14201,7 +14201,7 @@
       <c r="F291" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="G291" s="2" t="s">
+      <c r="G291" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H291" s="9">
@@ -14233,7 +14233,7 @@
       <c r="F292" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="G292" s="2" t="s">
+      <c r="G292" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H292" s="9">
@@ -14265,7 +14265,7 @@
       <c r="F293" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="G293" s="2" t="s">
+      <c r="G293" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H293" s="9">
@@ -14297,7 +14297,7 @@
       <c r="F294" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="G294" s="2" t="s">
+      <c r="G294" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H294" s="9">
@@ -14329,7 +14329,7 @@
       <c r="F295" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="G295" s="2" t="s">
+      <c r="G295" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H295" s="9">
@@ -14361,7 +14361,7 @@
       <c r="F296" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="G296" s="2" t="s">
+      <c r="G296" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H296" s="9">
@@ -14393,7 +14393,7 @@
       <c r="F297" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="G297" s="2" t="s">
+      <c r="G297" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H297" s="9">
@@ -14425,7 +14425,7 @@
       <c r="F298" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="G298" s="2" t="s">
+      <c r="G298" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H298" s="9">
@@ -14457,7 +14457,7 @@
       <c r="F299" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="G299" s="2" t="s">
+      <c r="G299" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H299" s="9">
@@ -14489,7 +14489,7 @@
       <c r="F300" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="G300" s="2" t="s">
+      <c r="G300" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H300" s="9">
@@ -14521,7 +14521,7 @@
       <c r="F301" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="G301" s="2" t="s">
+      <c r="G301" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H301" s="9">
@@ -14553,7 +14553,7 @@
       <c r="F302" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="G302" s="2" t="s">
+      <c r="G302" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H302" s="9">
@@ -14585,7 +14585,7 @@
       <c r="F303" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="G303" s="2" t="s">
+      <c r="G303" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H303" s="9">
@@ -14615,9 +14615,9 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G304" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G304" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H304" s="9">
@@ -14649,7 +14649,7 @@
       <c r="F305" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="G305" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H305" s="9">
@@ -14681,7 +14681,7 @@
       <c r="F306" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="G306" s="2" t="s">
+      <c r="G306" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H306" s="9">
@@ -14713,7 +14713,7 @@
       <c r="F307" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="G307" s="2" t="s">
+      <c r="G307" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H307" s="9">
@@ -14745,7 +14745,7 @@
       <c r="F308" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="G308" s="2" t="s">
+      <c r="G308" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H308" s="9">
@@ -14777,7 +14777,7 @@
       <c r="F309" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G309" s="2" t="s">
+      <c r="G309" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H309" s="9">
@@ -14809,7 +14809,7 @@
       <c r="F310" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G310" s="2" t="s">
+      <c r="G310" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H310" s="9">
@@ -14839,9 +14839,9 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G311" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G311" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H311" s="9">
@@ -14873,7 +14873,7 @@
       <c r="F312" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="G312" s="2" t="s">
+      <c r="G312" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H312" s="9">
@@ -14905,7 +14905,7 @@
       <c r="F313" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="G313" s="2" t="s">
+      <c r="G313" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H313" s="9">
@@ -14937,7 +14937,7 @@
       <c r="F314" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G314" s="2" t="s">
+      <c r="G314" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H314" s="9">
@@ -14967,9 +14967,9 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G315" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G315" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H315" s="9">
@@ -14999,9 +14999,9 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G316" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G316" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H316" s="9">
@@ -15031,9 +15031,9 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G317" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G317" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H317" s="9">
@@ -15063,9 +15063,9 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G318" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G318" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H318" s="9">
@@ -15095,9 +15095,9 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G319" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G319" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H319" s="9">
@@ -15127,9 +15127,9 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1174</v>
-      </c>
-      <c r="G320" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G320" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H320" s="9">
@@ -15159,9 +15159,9 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G321" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G321" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H321" s="9">
@@ -15191,9 +15191,9 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="G322" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G322" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H322" s="9">
@@ -15223,9 +15223,9 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G323" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G323" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H323" s="9">
@@ -15255,9 +15255,9 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G324" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G324" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H324" s="9">
@@ -15287,9 +15287,9 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G325" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G325" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H325" s="9">
@@ -15319,9 +15319,9 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G326" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G326" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H326" s="9">
@@ -15353,7 +15353,7 @@
       <c r="F327" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G327" s="2" t="s">
+      <c r="G327" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H327" s="9">
@@ -15363,7 +15363,7 @@
         <v>591</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -15383,9 +15383,9 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1174</v>
-      </c>
-      <c r="G328" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G328" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H328" s="9">
@@ -15415,9 +15415,9 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="G329" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G329" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H329" s="9">
@@ -15447,9 +15447,9 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G330" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G330" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H330" s="9">
@@ -15481,7 +15481,7 @@
       <c r="F331" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="G331" s="2" t="s">
+      <c r="G331" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H331" s="9">
@@ -15511,9 +15511,9 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1186</v>
-      </c>
-      <c r="G332" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G332" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H332" s="9">
@@ -15543,9 +15543,9 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G333" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G333" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H333" s="9">
@@ -15575,9 +15575,9 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G334" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G334" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H334" s="9">
@@ -15607,9 +15607,9 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G335" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G335" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H335" s="9">
@@ -15639,9 +15639,9 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1190</v>
-      </c>
-      <c r="G336" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G336" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H336" s="9">
@@ -15673,7 +15673,7 @@
       <c r="F337" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="G337" s="2" t="s">
+      <c r="G337" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H337" s="9">
@@ -15705,7 +15705,7 @@
       <c r="F338" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="G338" s="2" t="s">
+      <c r="G338" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H338" s="9">
@@ -15737,7 +15737,7 @@
       <c r="F339" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="G339" s="2" t="s">
+      <c r="G339" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H339" s="9">
@@ -15769,7 +15769,7 @@
       <c r="F340" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="G340" s="2" t="s">
+      <c r="G340" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H340" s="9">
@@ -15801,7 +15801,7 @@
       <c r="F341" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="G341" s="2" t="s">
+      <c r="G341" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H341" s="9">
@@ -15833,7 +15833,7 @@
       <c r="F342" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="G342" s="2" t="s">
+      <c r="G342" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H342" s="9">
@@ -15865,7 +15865,7 @@
       <c r="F343" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="G343" s="2" t="s">
+      <c r="G343" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H343" s="9">
@@ -15897,7 +15897,7 @@
       <c r="F344" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G344" s="14" t="s">
+      <c r="G344" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H344" s="15">
@@ -15929,7 +15929,7 @@
       <c r="F345" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="G345" s="14" t="s">
+      <c r="G345" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H345" s="15">
@@ -15961,7 +15961,7 @@
       <c r="F346" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G346" s="2" t="s">
+      <c r="G346" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H346" s="9">
@@ -15993,7 +15993,7 @@
       <c r="F347" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G347" s="2" t="s">
+      <c r="G347" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H347" s="9">
@@ -16025,7 +16025,7 @@
       <c r="F348" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="G348" s="2" t="s">
+      <c r="G348" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H348" s="9">
@@ -16057,7 +16057,7 @@
       <c r="F349" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="G349" s="2" t="s">
+      <c r="G349" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H349" s="23">
@@ -16089,7 +16089,7 @@
       <c r="F350" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G350" s="2" t="s">
+      <c r="G350" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H350" s="23">
@@ -16121,7 +16121,7 @@
       <c r="F351" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G351" s="2" t="s">
+      <c r="G351" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H351" s="23">
@@ -16153,7 +16153,7 @@
       <c r="F352" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="G352" s="2" t="s">
+      <c r="G352" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H352" s="9">
@@ -16185,7 +16185,7 @@
       <c r="F353" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="G353" s="2" t="s">
+      <c r="G353" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H353" s="23">
@@ -16217,7 +16217,7 @@
       <c r="F354" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G354" s="2" t="s">
+      <c r="G354" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H354" s="23">
@@ -16249,7 +16249,7 @@
       <c r="F355" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G355" s="2" t="s">
+      <c r="G355" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H355" s="23">
@@ -16281,7 +16281,7 @@
       <c r="F356" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="G356" s="2" t="s">
+      <c r="G356" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H356" s="23">
@@ -16313,7 +16313,7 @@
       <c r="F357" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="G357" s="2" t="s">
+      <c r="G357" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H357" s="23">
@@ -16345,7 +16345,7 @@
       <c r="F358" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="G358" s="2" t="s">
+      <c r="G358" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H358" s="23">
@@ -16377,7 +16377,7 @@
       <c r="F359" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="G359" s="2" t="s">
+      <c r="G359" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H359" s="23">
@@ -16409,7 +16409,7 @@
       <c r="F360" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="G360" s="2" t="s">
+      <c r="G360" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H360" s="23">
@@ -16441,7 +16441,7 @@
       <c r="F361" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="G361" s="2" t="s">
+      <c r="G361" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H361" s="23">
@@ -16473,7 +16473,7 @@
       <c r="F362" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="G362" s="2" t="s">
+      <c r="G362" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H362" s="23">
@@ -16505,7 +16505,7 @@
       <c r="F363" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="G363" s="2" t="s">
+      <c r="G363" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H363" s="23">
@@ -16535,9 +16535,9 @@
         <v>80</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G364" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G364" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H364" s="23">
@@ -16569,7 +16569,7 @@
       <c r="F365" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="G365" s="2" t="s">
+      <c r="G365" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H365" s="23">
@@ -16599,9 +16599,9 @@
         <v>71</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G366" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G366" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H366" s="23">
@@ -16633,7 +16633,7 @@
       <c r="F367" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="G367" s="2" t="s">
+      <c r="G367" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H367" s="23">
@@ -16663,9 +16663,9 @@
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G368" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G368" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H368" s="23">
@@ -16697,7 +16697,7 @@
       <c r="F369" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="G369" s="2" t="s">
+      <c r="G369" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H369" s="23">
@@ -16727,9 +16727,9 @@
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G370" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G370" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H370" s="23">
@@ -16761,7 +16761,7 @@
       <c r="F371" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="G371" s="2" t="s">
+      <c r="G371" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H371" s="23">
@@ -16791,9 +16791,9 @@
         <v>80</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G372" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G372" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H372" s="23">
@@ -16803,7 +16803,7 @@
         <v>591</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -16825,7 +16825,7 @@
       <c r="F373" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="G373" s="2" t="s">
+      <c r="G373" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H373" s="23">
@@ -16857,7 +16857,7 @@
       <c r="F374" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="G374" s="2" t="s">
+      <c r="G374" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H374" s="23">
@@ -16887,7 +16887,7 @@
       <c r="F375" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="G375" s="2" t="s">
+      <c r="G375" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H375" s="23">
@@ -16917,9 +16917,9 @@
         <v>80</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="G376" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G376" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H376" s="23">
@@ -16929,7 +16929,7 @@
         <v>591</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -16949,9 +16949,9 @@
         <v>80</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G377" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G377" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H377" s="23">
@@ -16961,7 +16961,7 @@
         <v>591</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -16983,7 +16983,7 @@
       <c r="F378" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="G378" s="2" t="s">
+      <c r="G378" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H378" s="23">
@@ -17015,7 +17015,7 @@
       <c r="F379" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="G379" s="2" t="s">
+      <c r="G379" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H379" s="23">
@@ -17045,9 +17045,9 @@
         <v>80</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="G380" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G380" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H380" s="23">
@@ -17057,7 +17057,7 @@
         <v>591</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -17077,9 +17077,9 @@
         <v>80</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="G381" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G381" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H381" s="23">
@@ -17089,7 +17089,7 @@
         <v>591</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -17109,9 +17109,9 @@
         <v>71</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G382" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G382" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H382" s="23">
@@ -17143,7 +17143,7 @@
       <c r="F383" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G383" s="2" t="s">
+      <c r="G383" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H383" s="9">
@@ -17175,7 +17175,7 @@
       <c r="F384" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G384" s="2" t="s">
+      <c r="G384" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H384" s="23">
@@ -17205,9 +17205,9 @@
         <v>19</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G385" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G385" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H385" s="23">
@@ -17239,7 +17239,7 @@
       <c r="F386" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="G386" s="2" t="s">
+      <c r="G386" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H386" s="23">
@@ -17269,9 +17269,9 @@
         <v>71</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="G387" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G387" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H387" s="23">
@@ -17301,9 +17301,9 @@
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G388" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G388" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H388" s="23">
@@ -17335,7 +17335,7 @@
       <c r="F389" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G389" s="2" t="s">
+      <c r="G389" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H389" s="23">
@@ -17365,9 +17365,9 @@
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G390" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G390" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H390" s="23">
@@ -17397,9 +17397,9 @@
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G391" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G391" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H391" s="23">
@@ -17429,9 +17429,9 @@
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G392" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G392" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H392" s="23">
@@ -17463,7 +17463,7 @@
       <c r="F393" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G393" s="2" t="s">
+      <c r="G393" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H393" s="23">
@@ -17495,7 +17495,7 @@
       <c r="F394" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="G394" s="2" t="s">
+      <c r="G394" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H394" s="23">
@@ -17527,7 +17527,7 @@
       <c r="F395" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="G395" s="2" t="s">
+      <c r="G395" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H395" s="23">
@@ -17559,7 +17559,7 @@
       <c r="F396" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="G396" s="2" t="s">
+      <c r="G396" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H396" s="23">
@@ -17591,7 +17591,7 @@
       <c r="F397" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="G397" s="2" t="s">
+      <c r="G397" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H397" s="23">
@@ -17623,7 +17623,7 @@
       <c r="F398" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="G398" s="2" t="s">
+      <c r="G398" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H398" s="23">
@@ -17655,7 +17655,7 @@
       <c r="F399" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="G399" s="2" t="s">
+      <c r="G399" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H399" s="23">
@@ -17687,7 +17687,7 @@
       <c r="F400" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="G400" s="2" t="s">
+      <c r="G400" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H400" s="23">
@@ -17719,7 +17719,7 @@
       <c r="F401" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G401" s="2" t="s">
+      <c r="G401" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H401" s="23">
@@ -17751,7 +17751,7 @@
       <c r="F402" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="G402" s="2" t="s">
+      <c r="G402" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H402" s="23">
@@ -17783,7 +17783,7 @@
       <c r="F403" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="G403" s="2" t="s">
+      <c r="G403" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H403" s="23">
@@ -17815,7 +17815,7 @@
       <c r="F404" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="G404" s="2" t="s">
+      <c r="G404" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H404" s="23">
@@ -17847,7 +17847,7 @@
       <c r="F405" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="G405" s="2" t="s">
+      <c r="G405" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H405" s="23">
@@ -17879,7 +17879,7 @@
       <c r="F406" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="G406" s="2" t="s">
+      <c r="G406" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H406" s="23">
@@ -17911,7 +17911,7 @@
       <c r="F407" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G407" s="2" t="s">
+      <c r="G407" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H407" s="23">
@@ -17943,7 +17943,7 @@
       <c r="F408" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="G408" s="2" t="s">
+      <c r="G408" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H408" s="23">
@@ -17975,7 +17975,7 @@
       <c r="F409" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="G409" s="2" t="s">
+      <c r="G409" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H409" s="23">
@@ -18007,7 +18007,7 @@
       <c r="F410" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="G410" s="2" t="s">
+      <c r="G410" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H410" s="23">
@@ -18039,7 +18039,7 @@
       <c r="F411" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="G411" s="2" t="s">
+      <c r="G411" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H411" s="23">
@@ -18071,7 +18071,7 @@
       <c r="F412" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G412" s="2" t="s">
+      <c r="G412" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H412" s="23">
@@ -18103,7 +18103,7 @@
       <c r="F413" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="G413" s="2" t="s">
+      <c r="G413" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H413" s="23">
@@ -18135,7 +18135,7 @@
       <c r="F414" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="G414" s="2" t="s">
+      <c r="G414" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H414" s="23">
@@ -18165,9 +18165,9 @@
         <v>80</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G415" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G415" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H415" s="23">
@@ -18177,7 +18177,7 @@
         <v>668</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -18199,7 +18199,7 @@
       <c r="F416" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="G416" s="2" t="s">
+      <c r="G416" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H416" s="23">
@@ -18231,7 +18231,7 @@
       <c r="F417" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="G417" s="2" t="s">
+      <c r="G417" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H417" s="23">
@@ -18263,7 +18263,7 @@
       <c r="F418" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="G418" s="2" t="s">
+      <c r="G418" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H418" s="23">
@@ -18295,7 +18295,7 @@
       <c r="F419" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="G419" s="2" t="s">
+      <c r="G419" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H419" s="23">
@@ -18327,7 +18327,7 @@
       <c r="F420" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="G420" s="2" t="s">
+      <c r="G420" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H420" s="23">
@@ -18359,7 +18359,7 @@
       <c r="F421" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="G421" s="2" t="s">
+      <c r="G421" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H421" s="23">
@@ -18391,7 +18391,7 @@
       <c r="F422" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="G422" s="2" t="s">
+      <c r="G422" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H422" s="23">
@@ -18423,7 +18423,7 @@
       <c r="F423" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="G423" s="2" t="s">
+      <c r="G423" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H423" s="23">
@@ -18455,7 +18455,7 @@
       <c r="F424" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="G424" s="2" t="s">
+      <c r="G424" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H424" s="23">
@@ -18485,7 +18485,7 @@
       <c r="F425" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="G425" s="2" t="s">
+      <c r="G425" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H425" s="23">
@@ -18517,7 +18517,7 @@
       <c r="F426" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="G426" s="2" t="s">
+      <c r="G426" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H426" s="23">
@@ -18549,7 +18549,7 @@
       <c r="F427" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="G427" s="2" t="s">
+      <c r="G427" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H427" s="23">
@@ -18581,7 +18581,7 @@
       <c r="F428" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="G428" s="2" t="s">
+      <c r="G428" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H428" s="23">
@@ -18611,9 +18611,9 @@
         <v>71</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="G429" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G429" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H429" s="23">
@@ -18645,7 +18645,7 @@
       <c r="F430" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="G430" s="2" t="s">
+      <c r="G430" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H430" s="23">
@@ -18677,7 +18677,7 @@
       <c r="F431" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G431" s="2" t="s">
+      <c r="G431" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H431" s="23">
@@ -18709,7 +18709,7 @@
       <c r="F432" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="G432" s="2" t="s">
+      <c r="G432" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H432" s="23">
@@ -18741,7 +18741,7 @@
       <c r="F433" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="G433" s="2" t="s">
+      <c r="G433" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H433" s="23">
@@ -18773,7 +18773,7 @@
       <c r="F434" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="G434" s="2" t="s">
+      <c r="G434" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H434" s="23">
@@ -18805,7 +18805,7 @@
       <c r="F435" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="G435" s="2" t="s">
+      <c r="G435" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H435" s="23">
@@ -18837,7 +18837,7 @@
       <c r="F436" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="G436" s="2" t="s">
+      <c r="G436" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H436" s="15">
@@ -18855,13 +18855,13 @@
         <v>436</v>
       </c>
       <c r="B437" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>19</v>
@@ -18869,7 +18869,7 @@
       <c r="F437" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="G437" s="2" t="s">
+      <c r="G437" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H437" s="23">
@@ -18879,7 +18879,7 @@
         <v>591</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -18887,21 +18887,21 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G438" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G438" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H438" s="23">
@@ -18917,21 +18917,21 @@
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G439" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G439" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H439" s="23">
@@ -18947,21 +18947,21 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G440" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G440" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H440" s="23">
@@ -18977,21 +18977,21 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G441" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G441" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H441" s="23">
@@ -19007,21 +19007,21 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1214</v>
-      </c>
-      <c r="G442" s="2" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G442" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H442" s="23">
@@ -19037,21 +19037,21 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G443" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G443" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H443" s="23">
@@ -19067,7 +19067,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>88</v>
@@ -19079,9 +19079,9 @@
         <v>23</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G444" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G444" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H444" s="23">
@@ -19097,7 +19097,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>88</v>
@@ -19109,9 +19109,9 @@
         <v>23</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G445" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G445" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H445" s="23">
@@ -19127,7 +19127,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>88</v>
@@ -19139,9 +19139,9 @@
         <v>23</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G446" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G446" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H446" s="23">
@@ -19157,21 +19157,21 @@
         <v>446</v>
       </c>
       <c r="B447" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G447" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G447" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H447" s="23">
@@ -19187,21 +19187,21 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G448" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G448" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H448" s="23">
@@ -19217,13 +19217,13 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
@@ -19231,7 +19231,7 @@
       <c r="F449" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="G449" s="2" t="s">
+      <c r="G449" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H449" s="23">
@@ -19247,21 +19247,21 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G450" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G450" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H450" s="23">
@@ -19277,21 +19277,21 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G451" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G451" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H451" s="23">
@@ -19307,21 +19307,21 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="G452" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G452" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H452" s="23">
@@ -19337,21 +19337,21 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G453" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G453" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H453" s="23">
@@ -19367,21 +19367,21 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G454" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G454" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H454" s="23">
@@ -19397,21 +19397,21 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G455" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G455" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H455" s="23">
@@ -19427,21 +19427,21 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="G456" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G456" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H456" s="23">
@@ -19457,21 +19457,21 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G457" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G457" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H457" s="23">
@@ -19487,21 +19487,21 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G458" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G458" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H458" s="23">
@@ -19517,21 +19517,21 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G459" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="G459" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H459" s="23">
@@ -19547,21 +19547,21 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1240</v>
-      </c>
-      <c r="G460" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G460" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H460" s="23">
@@ -19577,21 +19577,21 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G461" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G461" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H461" s="23">
@@ -19607,28 +19607,28 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>550</v>
+        <v>1244</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G462" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G462" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H462" s="23">
-        <v>46081</v>
+        <v>46118</v>
       </c>
       <c r="I462" s="4" t="s">
-        <v>591</v>
+        <v>668</v>
       </c>
       <c r="J462" s="24"/>
     </row>
@@ -19637,28 +19637,28 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>550</v>
+        <v>1246</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G463" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G463" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H463" s="23">
-        <v>46081</v>
+        <v>46119</v>
       </c>
       <c r="I463" s="4" t="s">
-        <v>591</v>
+        <v>668</v>
       </c>
       <c r="J463" s="24"/>
     </row>
@@ -19667,7 +19667,7 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
@@ -19679,9 +19679,9 @@
         <v>23</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G464" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G464" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H464" s="23">
@@ -19697,7 +19697,7 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
@@ -19709,9 +19709,9 @@
         <v>23</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G465" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G465" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H465" s="23">
@@ -19727,7 +19727,7 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
@@ -19739,9 +19739,9 @@
         <v>23</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G466" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G466" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H466" s="23">
@@ -19757,7 +19757,7 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
@@ -19769,9 +19769,9 @@
         <v>23</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G467" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G467" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H467" s="23">
@@ -19787,7 +19787,7 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
@@ -19799,9 +19799,9 @@
         <v>23</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G468" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G468" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H468" s="23">
@@ -19817,7 +19817,7 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
@@ -19829,9 +19829,9 @@
         <v>23</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G469" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G469" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H469" s="23">
@@ -19847,7 +19847,7 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
@@ -19859,9 +19859,9 @@
         <v>23</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G470" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G470" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H470" s="23">
@@ -19877,7 +19877,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19889,9 +19889,9 @@
         <v>23</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G471" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G471" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H471" s="23">
@@ -19907,7 +19907,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19919,9 +19919,9 @@
         <v>23</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G472" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G472" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H472" s="23">
@@ -19937,7 +19937,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19949,9 +19949,9 @@
         <v>23</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G473" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G473" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H473" s="23">
@@ -19967,7 +19967,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -19979,9 +19979,9 @@
         <v>23</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G474" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G474" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H474" s="23">
@@ -19997,7 +19997,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -20009,9 +20009,9 @@
         <v>23</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G475" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G475" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H475" s="23">
@@ -20027,7 +20027,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20039,9 +20039,9 @@
         <v>23</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G476" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G476" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H476" s="23">
@@ -20057,7 +20057,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20069,9 +20069,9 @@
         <v>23</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G477" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G477" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H477" s="23">
@@ -20087,7 +20087,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20099,9 +20099,9 @@
         <v>23</v>
       </c>
       <c r="F478" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G478" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G478" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H478" s="23">
@@ -20117,7 +20117,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20129,9 +20129,9 @@
         <v>23</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G479" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G479" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H479" s="23">
@@ -20147,7 +20147,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20159,9 +20159,9 @@
         <v>23</v>
       </c>
       <c r="F480" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G480" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G480" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H480" s="23">
@@ -20177,7 +20177,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20189,9 +20189,9 @@
         <v>23</v>
       </c>
       <c r="F481" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G481" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G481" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H481" s="23">
@@ -20207,7 +20207,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20219,9 +20219,9 @@
         <v>23</v>
       </c>
       <c r="F482" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G482" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G482" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H482" s="23">
@@ -20237,7 +20237,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20249,9 +20249,9 @@
         <v>23</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G483" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G483" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H483" s="23">
@@ -20267,7 +20267,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20279,9 +20279,9 @@
         <v>23</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G484" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G484" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H484" s="23">
@@ -20297,21 +20297,21 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G485" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G485" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H485" s="23">
@@ -20327,21 +20327,21 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="G486" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G486" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H486" s="23">
@@ -22682,7 +22682,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D51DD45-C7C3-4254-B0D5-32193DE7B78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C3E068-497D-4957-8FBD-6C9126A734FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4267" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4267" uniqueCount="1263">
   <si>
     <t>INDICE</t>
   </si>
@@ -3049,9 +3049,6 @@
     <t>UPA PEDIATRICA - ADM</t>
   </si>
   <si>
-    <t>INSTALADA 06/01/2026 UPA PEDIATRICA;</t>
-  </si>
-  <si>
     <t>PROGE 02</t>
   </si>
   <si>
@@ -3800,6 +3797,36 @@
   </si>
   <si>
     <t xml:space="preserve">PAÇO - DIVIDA ATIVA - ADM </t>
+  </si>
+  <si>
+    <t>XC75051324</t>
+  </si>
+  <si>
+    <t>E.M. PROF. RAYMUNDO MAGNO CAMARÃO</t>
+  </si>
+  <si>
+    <t>XC75051326</t>
+  </si>
+  <si>
+    <t>N.E.E.M. PREF. ALTEVIR V. BARRETO</t>
+  </si>
+  <si>
+    <t>XC75051304</t>
+  </si>
+  <si>
+    <t>P.E.M. MARCOS HERON CORREIA</t>
+  </si>
+  <si>
+    <t>XC75051803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M. JERONIMO CARLOS DO NASCIMENTO </t>
+  </si>
+  <si>
+    <t>VIGILANCIA SANITARIA</t>
+  </si>
+  <si>
+    <t>INSTALADA 06/01/2026 UPA PEDIATRICA; INSTALADA NA VIGILANCIA SANITARIA 14/04/2026</t>
   </si>
 </sst>
 </file>
@@ -4142,16 +4169,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4338,6 +4355,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4786,7 +4813,7 @@
   <autoFilter ref="A1:J486" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
     <filterColumn colId="4">
       <filters>
-        <filter val="PAÇO"/>
+        <filter val="SAÚDE"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5148,7 +5175,7 @@
     <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -5501,7 +5528,7 @@
         <v>590</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="12" spans="1:10" hidden="1">
@@ -5632,7 +5659,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -5649,7 +5676,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>14</v>
@@ -5774,7 +5801,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -5786,7 +5813,7 @@
         <v>590</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="21" spans="1:10" hidden="1">
@@ -5838,7 +5865,7 @@
         <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>14</v>
@@ -5850,10 +5877,10 @@
         <v>590</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" hidden="1">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -5867,10 +5894,10 @@
         <v>57</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>25</v>
+        <v>1002</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>14</v>
@@ -6763,7 +6790,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -6795,7 +6822,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" hidden="1">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -6827,7 +6854,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" hidden="1">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -6844,7 +6871,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>71</v>
@@ -7381,10 +7408,10 @@
         <v>148</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>25</v>
+        <v>1108</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>14</v>
@@ -7837,7 +7864,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>23</v>
@@ -7855,7 +7882,7 @@
         <v>590</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="88" spans="1:10" hidden="1">
@@ -7936,7 +7963,7 @@
         <v>995</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>32</v>
@@ -8279,7 +8306,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1">
+    <row r="102" spans="1:10">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8296,7 +8323,7 @@
         <v>79</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -8308,7 +8335,7 @@
         <v>590</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="103" spans="1:10" hidden="1">
@@ -8482,7 +8509,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -8947,7 +8974,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" hidden="1">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -8976,10 +9003,10 @@
         <v>590</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -8996,7 +9023,7 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>32</v>
@@ -9011,7 +9038,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" hidden="1">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -9028,7 +9055,7 @@
         <v>71</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9040,7 +9067,7 @@
         <v>590</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="126" spans="1:10" hidden="1">
@@ -9060,7 +9087,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>32</v>
@@ -9252,7 +9279,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9284,7 +9311,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>14</v>
@@ -9296,7 +9323,7 @@
         <v>590</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="134" spans="1:10" hidden="1">
@@ -9316,7 +9343,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9331,7 +9358,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1">
+    <row r="135" spans="1:10">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9348,7 +9375,7 @@
         <v>79</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>14</v>
@@ -9360,7 +9387,7 @@
         <v>590</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="136" spans="1:10" hidden="1">
@@ -9380,7 +9407,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>14</v>
@@ -9444,7 +9471,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>14</v>
@@ -9456,7 +9483,7 @@
         <v>590</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="139" spans="1:10" hidden="1">
@@ -9488,7 +9515,7 @@
         <v>666</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="140" spans="1:10" hidden="1">
@@ -9523,7 +9550,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1">
+    <row r="141" spans="1:10">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9540,7 +9567,7 @@
         <v>79</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>14</v>
@@ -9555,7 +9582,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" hidden="1">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -9572,7 +9599,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
@@ -9587,7 +9614,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" hidden="1">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -9604,7 +9631,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>14</v>
@@ -9616,10 +9643,10 @@
         <v>590</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" hidden="1">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9630,13 +9657,13 @@
         <v>87</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G144" s="4" t="s">
         <v>14</v>
@@ -9648,10 +9675,10 @@
         <v>590</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" hidden="1">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -9668,7 +9695,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G145" s="13" t="s">
         <v>14</v>
@@ -9683,7 +9710,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" hidden="1">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -9700,7 +9727,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>14</v>
@@ -9715,7 +9742,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" hidden="1">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -9732,7 +9759,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>14</v>
@@ -9747,7 +9774,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" hidden="1">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -9764,7 +9791,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>14</v>
@@ -9875,7 +9902,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" hidden="1">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -9892,7 +9919,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>14</v>
@@ -9904,7 +9931,7 @@
         <v>590</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="153" spans="1:10" hidden="1">
@@ -10105,7 +10132,7 @@
         <v>357</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>14</v>
@@ -10117,7 +10144,7 @@
         <v>590</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="160" spans="1:10" hidden="1">
@@ -10242,7 +10269,7 @@
         <v>590</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="164" spans="1:10" hidden="1">
@@ -10423,7 +10450,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10" hidden="1">
+    <row r="170" spans="1:10">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10452,7 +10479,7 @@
         <v>590</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="171" spans="1:10" hidden="1">
@@ -11276,7 +11303,7 @@
         <v>590</v>
       </c>
       <c r="J198" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="199" spans="1:10" hidden="1">
@@ -11328,7 +11355,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>14</v>
@@ -11360,7 +11387,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>14</v>
@@ -11372,7 +11399,7 @@
         <v>590</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="202" spans="1:10" hidden="1">
@@ -11456,7 +11483,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>32</v>
@@ -11500,7 +11527,7 @@
         <v>590</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="206" spans="1:10" hidden="1">
@@ -11552,7 +11579,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>14</v>
@@ -11564,7 +11591,7 @@
         <v>590</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="208" spans="1:10" hidden="1">
@@ -11584,7 +11611,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>14</v>
@@ -11599,7 +11626,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1">
+    <row r="209" spans="1:10">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11616,7 +11643,7 @@
         <v>79</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>14</v>
@@ -11628,7 +11655,7 @@
         <v>590</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="210" spans="1:10" hidden="1">
@@ -11820,7 +11847,7 @@
         <v>590</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="216" spans="1:10" hidden="1">
@@ -11840,7 +11867,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>14</v>
@@ -11852,7 +11879,7 @@
         <v>590</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="217" spans="1:10" hidden="1">
@@ -11904,7 +11931,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>14</v>
@@ -11933,10 +11960,10 @@
         <v>349</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>1099</v>
+        <v>25</v>
       </c>
       <c r="G219" s="4" t="s">
         <v>14</v>
@@ -11968,7 +11995,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>14</v>
@@ -11980,7 +12007,7 @@
         <v>590</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="221" spans="1:10" hidden="1">
@@ -12000,7 +12027,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>14</v>
@@ -12032,7 +12059,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>14</v>
@@ -12047,7 +12074,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" hidden="1">
       <c r="A223" s="4">
         <v>222</v>
       </c>
@@ -12064,7 +12091,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>14</v>
@@ -12192,7 +12219,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>14</v>
@@ -12204,7 +12231,7 @@
         <v>590</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="228" spans="1:10" hidden="1">
@@ -12268,7 +12295,7 @@
         <v>590</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="230" spans="1:10" hidden="1">
@@ -12288,7 +12315,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1109</v>
+        <v>1098</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>14</v>
@@ -12320,7 +12347,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>14</v>
@@ -12332,7 +12359,7 @@
         <v>590</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="232" spans="1:10" hidden="1">
@@ -12352,7 +12379,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>14</v>
@@ -12364,7 +12391,7 @@
         <v>666</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="233" spans="1:10" hidden="1">
@@ -12384,7 +12411,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>14</v>
@@ -12416,7 +12443,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>14</v>
@@ -12428,7 +12455,7 @@
         <v>590</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="235" spans="1:10" hidden="1">
@@ -12460,7 +12487,7 @@
         <v>590</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="236" spans="1:10" hidden="1">
@@ -12589,7 +12616,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" hidden="1">
       <c r="A240" s="4">
         <v>239</v>
       </c>
@@ -12606,7 +12633,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>14</v>
@@ -12638,7 +12665,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>19</v>
@@ -12958,7 +12985,7 @@
         <v>590</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="252" spans="1:10" hidden="1">
@@ -12993,7 +13020,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -13010,7 +13037,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>14</v>
@@ -13118,7 +13145,7 @@
         <v>590</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="257" spans="1:10" hidden="1">
@@ -13278,7 +13305,7 @@
         <v>590</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="262" spans="1:10" hidden="1">
@@ -13362,7 +13389,7 @@
         <v>986</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G264" s="4" t="s">
         <v>14</v>
@@ -13522,7 +13549,7 @@
         <v>357</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>14</v>
@@ -13534,10 +13561,10 @@
         <v>590</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="270" spans="1:10">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" hidden="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -13554,7 +13581,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>14</v>
@@ -13569,7 +13596,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" hidden="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -13586,7 +13613,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>14</v>
@@ -13601,7 +13628,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" hidden="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -13618,7 +13645,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>14</v>
@@ -13633,7 +13660,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" hidden="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -13650,7 +13677,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>14</v>
@@ -13665,7 +13692,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" hidden="1">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -13682,7 +13709,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>14</v>
@@ -13697,7 +13724,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" hidden="1">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -13714,7 +13741,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>14</v>
@@ -13729,7 +13756,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" hidden="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -13746,7 +13773,7 @@
         <v>71</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>14</v>
@@ -13761,7 +13788,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" hidden="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -13778,7 +13805,7 @@
         <v>71</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>14</v>
@@ -13793,7 +13820,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" hidden="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -13810,7 +13837,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>14</v>
@@ -13825,7 +13852,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" hidden="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -13842,7 +13869,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>14</v>
@@ -13857,7 +13884,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" hidden="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -13874,7 +13901,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>14</v>
@@ -13889,7 +13916,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" hidden="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -13906,7 +13933,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>14</v>
@@ -13921,7 +13948,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" hidden="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -13938,7 +13965,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>14</v>
@@ -13953,7 +13980,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1">
+    <row r="283" spans="1:10">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13970,7 +13997,7 @@
         <v>79</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>14</v>
@@ -13982,10 +14009,10 @@
         <v>666</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="284" spans="1:10">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" hidden="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -14002,7 +14029,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>14</v>
@@ -14017,7 +14044,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" hidden="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -14034,7 +14061,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>14</v>
@@ -14049,7 +14076,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" hidden="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -14066,7 +14093,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>14</v>
@@ -14081,7 +14108,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" hidden="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -14098,7 +14125,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>14</v>
@@ -14529,7 +14556,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="301" spans="1:10" hidden="1">
+    <row r="301" spans="1:10">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14561,7 +14588,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="302" spans="1:10" hidden="1">
+    <row r="302" spans="1:10">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14590,10 +14617,10 @@
         <v>590</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" hidden="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14625,7 +14652,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" hidden="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -14642,7 +14669,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>14</v>
@@ -14657,7 +14684,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="305" spans="1:10" hidden="1">
+    <row r="305" spans="1:10">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14686,7 +14713,7 @@
         <v>590</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="306" spans="1:10" hidden="1">
@@ -14849,7 +14876,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" hidden="1">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -14866,7 +14893,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>14</v>
@@ -14977,7 +15004,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" hidden="1">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -14994,7 +15021,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>14</v>
@@ -15009,7 +15036,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" hidden="1">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -15026,7 +15053,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>14</v>
@@ -15041,7 +15068,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" hidden="1">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -15058,7 +15085,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>14</v>
@@ -15073,7 +15100,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" hidden="1">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -15090,7 +15117,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>14</v>
@@ -15105,7 +15132,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" hidden="1">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -15122,7 +15149,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>14</v>
@@ -15137,7 +15164,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" hidden="1">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -15154,7 +15181,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>14</v>
@@ -15169,7 +15196,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" hidden="1">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -15186,7 +15213,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>14</v>
@@ -15201,7 +15228,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" hidden="1">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -15218,7 +15245,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>14</v>
@@ -15233,7 +15260,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" hidden="1">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -15250,7 +15277,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>14</v>
@@ -15265,7 +15292,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" hidden="1">
       <c r="A324" s="4">
         <v>323</v>
       </c>
@@ -15282,7 +15309,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>14</v>
@@ -15297,7 +15324,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" hidden="1">
       <c r="A325" s="4">
         <v>324</v>
       </c>
@@ -15314,7 +15341,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>14</v>
@@ -15329,7 +15356,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" hidden="1">
       <c r="A326" s="4">
         <v>325</v>
       </c>
@@ -15346,7 +15373,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>14</v>
@@ -15390,10 +15417,10 @@
         <v>590</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" hidden="1">
       <c r="A328" s="4">
         <v>327</v>
       </c>
@@ -15410,7 +15437,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>14</v>
@@ -15425,7 +15452,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" hidden="1">
       <c r="A329" s="4">
         <v>328</v>
       </c>
@@ -15442,7 +15469,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>14</v>
@@ -15457,7 +15484,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" hidden="1">
       <c r="A330" s="4">
         <v>329</v>
       </c>
@@ -15474,7 +15501,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>14</v>
@@ -15489,7 +15516,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1">
+    <row r="331" spans="1:10">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15521,7 +15548,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" hidden="1">
       <c r="A332" s="4">
         <v>331</v>
       </c>
@@ -15538,7 +15565,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>14</v>
@@ -15553,7 +15580,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" hidden="1">
       <c r="A333" s="4">
         <v>332</v>
       </c>
@@ -15570,7 +15597,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>14</v>
@@ -15585,7 +15612,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" hidden="1">
       <c r="A334" s="4">
         <v>333</v>
       </c>
@@ -15602,7 +15629,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>14</v>
@@ -15617,7 +15644,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" hidden="1">
       <c r="A335" s="4">
         <v>334</v>
       </c>
@@ -15634,7 +15661,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>14</v>
@@ -15649,7 +15676,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" hidden="1">
       <c r="A336" s="4">
         <v>335</v>
       </c>
@@ -15666,7 +15693,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>14</v>
@@ -15681,7 +15708,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" hidden="1">
       <c r="A337" s="4">
         <v>336</v>
       </c>
@@ -15698,7 +15725,7 @@
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>14</v>
@@ -15713,7 +15740,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="338" spans="1:10" hidden="1">
+    <row r="338" spans="1:10">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15745,7 +15772,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="339" spans="1:10" hidden="1">
+    <row r="339" spans="1:10">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15777,7 +15804,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="340" spans="1:10" hidden="1">
+    <row r="340" spans="1:10">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15809,7 +15836,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="341" spans="1:10" hidden="1">
+    <row r="341" spans="1:10">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15841,7 +15868,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="342" spans="1:10" hidden="1">
+    <row r="342" spans="1:10">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15937,7 +15964,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="345" spans="1:10" hidden="1">
+    <row r="345" spans="1:10">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15954,7 +15981,7 @@
         <v>79</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G345" s="13" t="s">
         <v>14</v>
@@ -15966,10 +15993,10 @@
         <v>590</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" hidden="1">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -16001,7 +16028,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="347" spans="1:10" hidden="1">
+    <row r="347" spans="1:10">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -16033,7 +16060,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="348" spans="1:10" hidden="1">
+    <row r="348" spans="1:10">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -16065,7 +16092,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="349" spans="1:10" hidden="1">
+    <row r="349" spans="1:10">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16097,7 +16124,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="350" spans="1:10" hidden="1">
+    <row r="350" spans="1:10">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16129,7 +16156,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="351" spans="1:10" hidden="1">
+    <row r="351" spans="1:10">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16161,7 +16188,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="352" spans="1:10" hidden="1">
+    <row r="352" spans="1:10">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16193,7 +16220,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="353" spans="1:10" hidden="1">
+    <row r="353" spans="1:10">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16225,7 +16252,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="354" spans="1:10" hidden="1">
+    <row r="354" spans="1:10">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16257,7 +16284,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="355" spans="1:10" hidden="1">
+    <row r="355" spans="1:10">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16289,7 +16316,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="356" spans="1:10" hidden="1">
+    <row r="356" spans="1:10">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16321,7 +16348,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="357" spans="1:10" hidden="1">
+    <row r="357" spans="1:10">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16353,7 +16380,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="358" spans="1:10" hidden="1">
+    <row r="358" spans="1:10">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16385,7 +16412,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="359" spans="1:10" hidden="1">
+    <row r="359" spans="1:10">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16417,7 +16444,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="360" spans="1:10" hidden="1">
+    <row r="360" spans="1:10">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16446,10 +16473,10 @@
         <v>590</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" hidden="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16478,10 +16505,10 @@
         <v>590</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" hidden="1">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16513,7 +16540,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="363" spans="1:10" hidden="1">
+    <row r="363" spans="1:10">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16545,7 +16572,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="364" spans="1:10" hidden="1">
+    <row r="364" spans="1:10">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16562,7 +16589,7 @@
         <v>79</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>14</v>
@@ -16577,7 +16604,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="365" spans="1:10" hidden="1">
+    <row r="365" spans="1:10">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16609,7 +16636,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" hidden="1">
       <c r="A366" s="4">
         <v>365</v>
       </c>
@@ -16626,7 +16653,7 @@
         <v>71</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>14</v>
@@ -16641,7 +16668,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="367" spans="1:10" hidden="1">
+    <row r="367" spans="1:10">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16673,7 +16700,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" hidden="1">
       <c r="A368" s="4">
         <v>367</v>
       </c>
@@ -16690,7 +16717,7 @@
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>14</v>
@@ -16705,7 +16732,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="369" spans="1:10" hidden="1">
+    <row r="369" spans="1:10">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16737,7 +16764,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" hidden="1">
       <c r="A370" s="4">
         <v>369</v>
       </c>
@@ -16754,7 +16781,7 @@
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>14</v>
@@ -16766,7 +16793,7 @@
         <v>590</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="371" spans="1:10" hidden="1">
@@ -16801,7 +16828,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="372" spans="1:10" hidden="1">
+    <row r="372" spans="1:10">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16818,7 +16845,7 @@
         <v>79</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>14</v>
@@ -16830,10 +16857,10 @@
         <v>590</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10" hidden="1">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16927,7 +16954,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="376" spans="1:10" hidden="1">
+    <row r="376" spans="1:10">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16944,7 +16971,7 @@
         <v>79</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>14</v>
@@ -16956,10 +16983,10 @@
         <v>590</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10" hidden="1">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -16976,7 +17003,7 @@
         <v>79</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>14</v>
@@ -16988,7 +17015,7 @@
         <v>590</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="378" spans="1:10" hidden="1">
@@ -17055,7 +17082,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="380" spans="1:10" hidden="1">
+    <row r="380" spans="1:10">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -17072,7 +17099,7 @@
         <v>79</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>14</v>
@@ -17084,10 +17111,10 @@
         <v>590</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" hidden="1">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -17104,7 +17131,7 @@
         <v>79</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>14</v>
@@ -17116,10 +17143,10 @@
         <v>590</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="382" spans="1:10">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="382" spans="1:10" hidden="1">
       <c r="A382" s="4">
         <v>381</v>
       </c>
@@ -17136,7 +17163,7 @@
         <v>71</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>14</v>
@@ -17232,7 +17259,7 @@
         <v>19</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>14</v>
@@ -17247,7 +17274,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" hidden="1">
       <c r="A386" s="4">
         <v>385</v>
       </c>
@@ -17264,7 +17291,7 @@
         <v>71</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>14</v>
@@ -17279,7 +17306,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" hidden="1">
       <c r="A387" s="4">
         <v>386</v>
       </c>
@@ -17296,7 +17323,7 @@
         <v>71</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>14</v>
@@ -17311,7 +17338,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" hidden="1">
       <c r="A388" s="4">
         <v>387</v>
       </c>
@@ -17322,13 +17349,13 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17340,10 +17367,10 @@
         <v>590</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10" hidden="1">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17354,7 +17381,7 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>23</v>
@@ -17372,10 +17399,10 @@
         <v>590</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" hidden="1">
       <c r="A390" s="4">
         <v>389</v>
       </c>
@@ -17386,13 +17413,13 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>14</v>
@@ -17404,10 +17431,10 @@
         <v>590</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" hidden="1">
       <c r="A391" s="4">
         <v>390</v>
       </c>
@@ -17418,13 +17445,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>14</v>
@@ -17436,10 +17463,10 @@
         <v>590</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" hidden="1">
       <c r="A392" s="4">
         <v>391</v>
       </c>
@@ -17450,13 +17477,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
@@ -17468,7 +17495,7 @@
         <v>590</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="393" spans="1:10" hidden="1">
@@ -17759,7 +17786,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="402" spans="1:10" hidden="1">
+    <row r="402" spans="1:10">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17791,7 +17818,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="403" spans="1:10" hidden="1">
+    <row r="403" spans="1:10">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17823,7 +17850,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="404" spans="1:10" hidden="1">
+    <row r="404" spans="1:10">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17855,7 +17882,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="405" spans="1:10" hidden="1">
+    <row r="405" spans="1:10">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17887,7 +17914,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="406" spans="1:10" hidden="1">
+    <row r="406" spans="1:10">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17916,7 +17943,7 @@
         <v>590</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="407" spans="1:10" hidden="1">
@@ -18175,7 +18202,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="415" spans="1:10" hidden="1">
+    <row r="415" spans="1:10">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18192,7 +18219,7 @@
         <v>79</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>14</v>
@@ -18204,10 +18231,10 @@
         <v>666</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10" hidden="1">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18239,7 +18266,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="417" spans="1:10" hidden="1">
+    <row r="417" spans="1:10">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18271,7 +18298,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="418" spans="1:10" hidden="1">
+    <row r="418" spans="1:10">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18303,7 +18330,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="419" spans="1:10" hidden="1">
+    <row r="419" spans="1:10">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18335,7 +18362,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="420" spans="1:10" hidden="1">
+    <row r="420" spans="1:10">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18367,7 +18394,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="421" spans="1:10" hidden="1">
+    <row r="421" spans="1:10">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18384,7 +18411,7 @@
         <v>79</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1002</v>
+        <v>1261</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>14</v>
@@ -18396,10 +18423,10 @@
         <v>590</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10" hidden="1">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18410,7 +18437,7 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>79</v>
@@ -18428,10 +18455,10 @@
         <v>590</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10" hidden="1">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18442,7 +18469,7 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>79</v>
@@ -18460,10 +18487,10 @@
         <v>666</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10" hidden="1">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18474,13 +18501,13 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>14</v>
@@ -18493,7 +18520,7 @@
       </c>
       <c r="J424" s="24"/>
     </row>
-    <row r="425" spans="1:10" hidden="1">
+    <row r="425" spans="1:10">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18504,7 +18531,7 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>79</v>
@@ -18522,10 +18549,10 @@
         <v>590</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10" hidden="1">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18554,7 +18581,7 @@
         <v>590</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="427" spans="1:10" hidden="1">
@@ -18586,10 +18613,10 @@
         <v>590</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10" hidden="1">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18606,7 +18633,7 @@
         <v>79</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>14</v>
@@ -18618,10 +18645,10 @@
         <v>590</v>
       </c>
       <c r="J428" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="429" spans="1:10">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="429" spans="1:10" hidden="1">
       <c r="A429" s="4">
         <v>428</v>
       </c>
@@ -18632,13 +18659,13 @@
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>14</v>
@@ -18650,10 +18677,10 @@
         <v>590</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" hidden="1">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18682,7 +18709,7 @@
         <v>590</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="431" spans="1:10" hidden="1">
@@ -18696,7 +18723,7 @@
         <v>11</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>357</v>
@@ -18714,7 +18741,7 @@
         <v>590</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="432" spans="1:10" hidden="1">
@@ -18728,7 +18755,7 @@
         <v>11</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>357</v>
@@ -18746,7 +18773,7 @@
         <v>590</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="433" spans="1:10" hidden="1">
@@ -18760,13 +18787,13 @@
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>32</v>
@@ -18778,7 +18805,7 @@
         <v>590</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="434" spans="1:10" hidden="1">
@@ -18792,13 +18819,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>32</v>
@@ -18810,7 +18837,7 @@
         <v>590</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="435" spans="1:10" hidden="1">
@@ -18824,13 +18851,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>32</v>
@@ -18842,7 +18869,7 @@
         <v>590</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="436" spans="1:10" hidden="1">
@@ -18882,13 +18909,13 @@
         <v>436</v>
       </c>
       <c r="B437" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>19</v>
@@ -18906,7 +18933,7 @@
         <v>590</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="438" spans="1:10" hidden="1">
@@ -18914,13 +18941,13 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>23</v>
@@ -18944,13 +18971,13 @@
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -18974,13 +19001,13 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -19004,13 +19031,13 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -19034,19 +19061,19 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>32</v>
@@ -19064,19 +19091,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>32</v>
@@ -19094,7 +19121,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>87</v>
@@ -19124,7 +19151,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>87</v>
@@ -19154,7 +19181,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>87</v>
@@ -19184,19 +19211,19 @@
         <v>446</v>
       </c>
       <c r="B447" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>32</v>
@@ -19214,19 +19241,19 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>32</v>
@@ -19244,19 +19271,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>32</v>
@@ -19274,19 +19301,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>32</v>
@@ -19304,19 +19331,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>32</v>
@@ -19334,19 +19361,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>32</v>
@@ -19364,19 +19391,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>32</v>
@@ -19394,19 +19421,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>32</v>
@@ -19424,19 +19451,19 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>32</v>
@@ -19454,19 +19481,19 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>32</v>
@@ -19484,19 +19511,19 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>32</v>
@@ -19514,19 +19541,19 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>32</v>
@@ -19544,19 +19571,19 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>32</v>
@@ -19574,19 +19601,19 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>32</v>
@@ -19604,19 +19631,19 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>32</v>
@@ -19634,19 +19661,19 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>32</v>
@@ -19664,19 +19691,19 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>32</v>
@@ -19694,19 +19721,19 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>32</v>
@@ -19724,19 +19751,19 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>32</v>
@@ -19754,19 +19781,19 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>32</v>
@@ -19784,25 +19811,25 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>549</v>
+        <v>1253</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>758</v>
+        <v>1254</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H467" s="23">
-        <v>46081</v>
+        <v>46121</v>
       </c>
       <c r="I467" s="4" t="s">
         <v>590</v>
@@ -19814,25 +19841,25 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>549</v>
+        <v>1259</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>758</v>
+        <v>1260</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H468" s="23">
-        <v>46081</v>
+        <v>46126</v>
       </c>
       <c r="I468" s="4" t="s">
         <v>590</v>
@@ -19844,25 +19871,25 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>549</v>
+        <v>1255</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>758</v>
+        <v>1256</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H469" s="23">
-        <v>46081</v>
+        <v>46126</v>
       </c>
       <c r="I469" s="4" t="s">
         <v>590</v>
@@ -19874,25 +19901,25 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>549</v>
+        <v>1257</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>758</v>
+        <v>1258</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H470" s="23">
-        <v>46081</v>
+        <v>46126</v>
       </c>
       <c r="I470" s="4" t="s">
         <v>590</v>
@@ -19904,7 +19931,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19934,7 +19961,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19964,7 +19991,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -19994,7 +20021,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -20024,7 +20051,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -20054,7 +20081,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20084,7 +20111,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20114,7 +20141,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20144,7 +20171,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20174,7 +20201,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20204,7 +20231,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20234,7 +20261,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20264,7 +20291,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20294,7 +20321,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20324,13 +20351,13 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>23</v>
@@ -20354,13 +20381,13 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20399,34 +20426,34 @@
     <cfRule type="duplicateValues" dxfId="23" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E236 G194 E238:E1048576">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E344:E345">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F230 F232:F233 F235:F1048576">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F344">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22709,7 +22736,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -22825,51 +22852,51 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="D2:D51">
-    <cfRule type="duplicateValues" dxfId="15" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E51">
-    <cfRule type="cellIs" dxfId="10" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E52:E53">
-    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F51">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="17" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="20" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F53">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"DOADORA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"DEPOSITO SOLAGOS"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C3E068-497D-4957-8FBD-6C9126A734FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804E73B1-AA65-4B68-96F0-C102FD3BAEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="COMPUTER" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$486</definedName>
+    <definedName name="DadosExternos_1" localSheetId="0" hidden="1">PRINTERS_INVENTORY!$A$1:$J$487</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4267" uniqueCount="1263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4273" uniqueCount="1265">
   <si>
     <t>INDICE</t>
   </si>
@@ -3085,9 +3085,6 @@
     <t>IMPRESSORA INSTALADA EM 22/11/2024 - SUBSTITUIU RICOH 501; BROTHER 5512 QUEIMOU A PLACA FONTE COM PICO LUZ QUE TEVE NO HOSPITAL 04/01/2025; Reparada e colocada Pam 16/06/2025; VEIO REPARADA WP INSTALADA SESAU RH;</t>
   </si>
   <si>
-    <t>ESCOLA TERRA PROMETIDA</t>
-  </si>
-  <si>
     <t>INSTALAÇÃO FEITA HOSPITAL SÃO VICENTE 14/01/2026;</t>
   </si>
   <si>
@@ -3827,6 +3824,15 @@
   </si>
   <si>
     <t>INSTALADA 06/01/2026 UPA PEDIATRICA; INSTALADA NA VIGILANCIA SANITARIA 14/04/2026</t>
+  </si>
+  <si>
+    <t>X6QM040322</t>
+  </si>
+  <si>
+    <t>OKI ES8473</t>
+  </si>
+  <si>
+    <t>ESCOLA TERRA PROMETIDA - LEGACY</t>
   </si>
 </sst>
 </file>
@@ -4006,7 +4012,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4149,6 +4155,25 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4809,11 +4834,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J486" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
-  <autoFilter ref="A1:J486" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}" name="Controle_Inventario_Impressoras" displayName="Controle_Inventario_Impressoras" ref="A1:J487" tableType="queryTable" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+  <autoFilter ref="A1:J487" xr:uid="{C244623C-48DE-4D05-852C-6EFDD885ABE2}">
     <filterColumn colId="4">
       <filters>
-        <filter val="SAÚDE"/>
+        <filter val="PARTICULAR"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5167,7 +5192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD39631B-97B8-405A-AA43-14CDFBC77F92}">
-  <dimension ref="A1:J486"/>
+  <dimension ref="A1:J487"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.109375" style="1" bestFit="1" customWidth="1"/>
@@ -5215,7 +5240,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1">
+    <row r="2" spans="1:10">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5247,7 +5272,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1">
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5311,7 +5336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5528,7 +5553,7 @@
         <v>590</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="12" spans="1:10" hidden="1">
@@ -5676,7 +5701,7 @@
         <v>71</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>14</v>
@@ -5801,7 +5826,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>14</v>
@@ -5813,7 +5838,7 @@
         <v>590</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="21" spans="1:10" hidden="1">
@@ -5848,7 +5873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -5862,10 +5887,10 @@
         <v>56</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1015</v>
+        <v>25</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>14</v>
@@ -5877,10 +5902,10 @@
         <v>590</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -6162,7 +6187,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1">
+    <row r="32" spans="1:10">
       <c r="A32" s="4">
         <v>31</v>
       </c>
@@ -6194,7 +6219,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1">
+    <row r="33" spans="1:10">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -6226,7 +6251,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1">
+    <row r="34" spans="1:10">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -6322,7 +6347,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1">
+    <row r="37" spans="1:10">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -6871,7 +6896,7 @@
         <v>71</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>71</v>
@@ -7411,7 +7436,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>14</v>
@@ -7864,7 +7889,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>23</v>
@@ -7882,7 +7907,7 @@
         <v>590</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="88" spans="1:10" hidden="1">
@@ -7963,7 +7988,7 @@
         <v>995</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>32</v>
@@ -8306,7 +8331,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -8323,7 +8348,7 @@
         <v>79</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -8335,7 +8360,7 @@
         <v>590</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="103" spans="1:10" hidden="1">
@@ -8509,7 +8534,7 @@
         <v>11</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>23</v>
@@ -9003,7 +9028,7 @@
         <v>590</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="124" spans="1:10" hidden="1">
@@ -9023,7 +9048,7 @@
         <v>71</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>32</v>
@@ -9055,7 +9080,7 @@
         <v>71</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9067,7 +9092,7 @@
         <v>590</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="126" spans="1:10" hidden="1">
@@ -9087,7 +9112,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>32</v>
@@ -9279,7 +9304,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9311,7 +9336,7 @@
         <v>19</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G133" s="4" t="s">
         <v>14</v>
@@ -9323,7 +9348,7 @@
         <v>590</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="134" spans="1:10" hidden="1">
@@ -9343,7 +9368,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9358,7 +9383,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" hidden="1">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -9375,7 +9400,7 @@
         <v>79</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>14</v>
@@ -9387,7 +9412,7 @@
         <v>590</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="136" spans="1:10" hidden="1">
@@ -9407,7 +9432,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G136" s="4" t="s">
         <v>14</v>
@@ -9471,7 +9496,7 @@
         <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>14</v>
@@ -9483,10 +9508,10 @@
         <v>590</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" hidden="1">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -9515,7 +9540,7 @@
         <v>666</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="140" spans="1:10" hidden="1">
@@ -9550,7 +9575,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" hidden="1">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -9567,7 +9592,7 @@
         <v>79</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G141" s="4" t="s">
         <v>14</v>
@@ -9599,7 +9624,7 @@
         <v>71</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G142" s="4" t="s">
         <v>14</v>
@@ -9631,7 +9656,7 @@
         <v>71</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G143" s="4" t="s">
         <v>14</v>
@@ -9643,10 +9668,10 @@
         <v>590</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" hidden="1">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -9695,7 +9720,7 @@
         <v>71</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G145" s="13" t="s">
         <v>14</v>
@@ -9727,7 +9752,7 @@
         <v>71</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G146" s="13" t="s">
         <v>14</v>
@@ -9759,7 +9784,7 @@
         <v>71</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G147" s="13" t="s">
         <v>14</v>
@@ -9791,7 +9816,7 @@
         <v>71</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G148" s="13" t="s">
         <v>14</v>
@@ -9919,7 +9944,7 @@
         <v>71</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G152" s="4" t="s">
         <v>14</v>
@@ -9931,7 +9956,7 @@
         <v>590</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="153" spans="1:10" hidden="1">
@@ -9966,7 +9991,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1">
+    <row r="154" spans="1:10">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -10030,7 +10055,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1">
+    <row r="156" spans="1:10">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -10059,7 +10084,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1">
+    <row r="157" spans="1:10">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -10088,7 +10113,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1">
+    <row r="158" spans="1:10">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -10132,7 +10157,7 @@
         <v>357</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G159" s="4" t="s">
         <v>14</v>
@@ -10144,10 +10169,10 @@
         <v>590</v>
       </c>
       <c r="J159" s="3" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" hidden="1">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -10269,10 +10294,10 @@
         <v>590</v>
       </c>
       <c r="J163" s="3" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" hidden="1">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -10333,7 +10358,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1">
+    <row r="166" spans="1:10">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -10362,7 +10387,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1">
+    <row r="167" spans="1:10">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -10431,13 +10456,13 @@
         <v>87</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>839</v>
+        <v>1262</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>986</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="G169" s="4" t="s">
         <v>14</v>
@@ -10450,7 +10475,7 @@
       </c>
       <c r="J169" s="24"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" hidden="1">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -10479,7 +10504,7 @@
         <v>590</v>
       </c>
       <c r="J170" s="3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="171" spans="1:10" hidden="1">
@@ -10496,10 +10521,10 @@
         <v>291</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>986</v>
+        <v>23</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>989</v>
+        <v>25</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>14</v>
@@ -11355,7 +11380,7 @@
         <v>19</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G200" s="4" t="s">
         <v>14</v>
@@ -11387,7 +11412,7 @@
         <v>19</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G201" s="4" t="s">
         <v>14</v>
@@ -11399,7 +11424,7 @@
         <v>590</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="202" spans="1:10" hidden="1">
@@ -11483,7 +11508,7 @@
         <v>19</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>32</v>
@@ -11527,7 +11552,7 @@
         <v>590</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="206" spans="1:10" hidden="1">
@@ -11579,7 +11604,7 @@
         <v>19</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G207" s="4" t="s">
         <v>14</v>
@@ -11591,7 +11616,7 @@
         <v>590</v>
       </c>
       <c r="J207" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="208" spans="1:10" hidden="1">
@@ -11611,7 +11636,7 @@
         <v>19</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G208" s="4" t="s">
         <v>14</v>
@@ -11626,7 +11651,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" hidden="1">
       <c r="A209" s="4">
         <v>208</v>
       </c>
@@ -11643,7 +11668,7 @@
         <v>79</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G209" s="4" t="s">
         <v>14</v>
@@ -11655,10 +11680,10 @@
         <v>590</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="210" spans="1:10" hidden="1">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
       <c r="A210" s="4">
         <v>209</v>
       </c>
@@ -11847,7 +11872,7 @@
         <v>590</v>
       </c>
       <c r="J215" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="216" spans="1:10" hidden="1">
@@ -11867,7 +11892,7 @@
         <v>19</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G216" s="4" t="s">
         <v>14</v>
@@ -11879,7 +11904,7 @@
         <v>590</v>
       </c>
       <c r="J216" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="217" spans="1:10" hidden="1">
@@ -11931,7 +11956,7 @@
         <v>19</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G218" s="4" t="s">
         <v>14</v>
@@ -11995,7 +12020,7 @@
         <v>19</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G220" s="4" t="s">
         <v>14</v>
@@ -12007,7 +12032,7 @@
         <v>590</v>
       </c>
       <c r="J220" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="221" spans="1:10" hidden="1">
@@ -12027,7 +12052,7 @@
         <v>19</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G221" s="4" t="s">
         <v>14</v>
@@ -12059,7 +12084,7 @@
         <v>19</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G222" s="4" t="s">
         <v>14</v>
@@ -12091,7 +12116,7 @@
         <v>71</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G223" s="4" t="s">
         <v>14</v>
@@ -12219,7 +12244,7 @@
         <v>19</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>14</v>
@@ -12231,7 +12256,7 @@
         <v>590</v>
       </c>
       <c r="J227" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="228" spans="1:10" hidden="1">
@@ -12295,7 +12320,7 @@
         <v>590</v>
       </c>
       <c r="J229" s="7" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="230" spans="1:10" hidden="1">
@@ -12315,7 +12340,7 @@
         <v>19</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G230" s="4" t="s">
         <v>14</v>
@@ -12347,7 +12372,7 @@
         <v>19</v>
       </c>
       <c r="F231" s="50" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G231" s="4" t="s">
         <v>14</v>
@@ -12359,7 +12384,7 @@
         <v>590</v>
       </c>
       <c r="J231" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="232" spans="1:10" hidden="1">
@@ -12379,7 +12404,7 @@
         <v>19</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G232" s="4" t="s">
         <v>14</v>
@@ -12391,7 +12416,7 @@
         <v>666</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="233" spans="1:10" hidden="1">
@@ -12411,7 +12436,7 @@
         <v>19</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G233" s="4" t="s">
         <v>14</v>
@@ -12443,7 +12468,7 @@
         <v>19</v>
       </c>
       <c r="F234" s="41" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G234" s="4" t="s">
         <v>14</v>
@@ -12455,7 +12480,7 @@
         <v>590</v>
       </c>
       <c r="J234" s="8" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="235" spans="1:10" hidden="1">
@@ -12487,7 +12512,7 @@
         <v>590</v>
       </c>
       <c r="J235" s="8" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="236" spans="1:10" hidden="1">
@@ -12633,7 +12658,7 @@
         <v>71</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G240" s="4" t="s">
         <v>14</v>
@@ -12665,7 +12690,7 @@
         <v>19</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>19</v>
@@ -12985,7 +13010,7 @@
         <v>590</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="252" spans="1:10" hidden="1">
@@ -13037,7 +13062,7 @@
         <v>71</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G253" s="4" t="s">
         <v>14</v>
@@ -13145,7 +13170,7 @@
         <v>590</v>
       </c>
       <c r="J256" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="257" spans="1:10" hidden="1">
@@ -13305,7 +13330,7 @@
         <v>590</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="262" spans="1:10" hidden="1">
@@ -13549,7 +13574,7 @@
         <v>357</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>14</v>
@@ -13561,7 +13586,7 @@
         <v>590</v>
       </c>
       <c r="J269" s="3" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="270" spans="1:10" hidden="1">
@@ -13581,7 +13606,7 @@
         <v>71</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>14</v>
@@ -13613,7 +13638,7 @@
         <v>71</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>14</v>
@@ -13645,7 +13670,7 @@
         <v>71</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>14</v>
@@ -13677,7 +13702,7 @@
         <v>71</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>14</v>
@@ -13709,7 +13734,7 @@
         <v>71</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>14</v>
@@ -13741,7 +13766,7 @@
         <v>71</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>14</v>
@@ -13837,7 +13862,7 @@
         <v>71</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>14</v>
@@ -13869,7 +13894,7 @@
         <v>71</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>14</v>
@@ -13901,7 +13926,7 @@
         <v>71</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>14</v>
@@ -13933,7 +13958,7 @@
         <v>71</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>14</v>
@@ -13965,7 +13990,7 @@
         <v>71</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>14</v>
@@ -13980,7 +14005,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" hidden="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -13997,7 +14022,7 @@
         <v>79</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>14</v>
@@ -14009,7 +14034,7 @@
         <v>666</v>
       </c>
       <c r="J283" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="284" spans="1:10" hidden="1">
@@ -14029,7 +14054,7 @@
         <v>71</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>14</v>
@@ -14061,7 +14086,7 @@
         <v>71</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>14</v>
@@ -14093,7 +14118,7 @@
         <v>71</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>14</v>
@@ -14125,7 +14150,7 @@
         <v>71</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>14</v>
@@ -14556,7 +14581,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" hidden="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -14588,7 +14613,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" hidden="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -14620,7 +14645,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" hidden="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -14669,7 +14694,7 @@
         <v>71</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G304" s="1" t="s">
         <v>14</v>
@@ -14684,7 +14709,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" hidden="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -14713,7 +14738,7 @@
         <v>590</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="306" spans="1:10" hidden="1">
@@ -14893,7 +14918,7 @@
         <v>71</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G311" s="1" t="s">
         <v>14</v>
@@ -15021,7 +15046,7 @@
         <v>71</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G315" s="1" t="s">
         <v>14</v>
@@ -15053,7 +15078,7 @@
         <v>71</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G316" s="1" t="s">
         <v>14</v>
@@ -15085,7 +15110,7 @@
         <v>71</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G317" s="1" t="s">
         <v>14</v>
@@ -15117,7 +15142,7 @@
         <v>71</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G318" s="1" t="s">
         <v>14</v>
@@ -15149,7 +15174,7 @@
         <v>71</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G319" s="1" t="s">
         <v>14</v>
@@ -15181,7 +15206,7 @@
         <v>71</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G320" s="1" t="s">
         <v>14</v>
@@ -15213,7 +15238,7 @@
         <v>71</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G321" s="1" t="s">
         <v>14</v>
@@ -15245,7 +15270,7 @@
         <v>71</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G322" s="1" t="s">
         <v>14</v>
@@ -15277,7 +15302,7 @@
         <v>71</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G323" s="1" t="s">
         <v>14</v>
@@ -15309,7 +15334,7 @@
         <v>71</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G324" s="1" t="s">
         <v>14</v>
@@ -15341,7 +15366,7 @@
         <v>71</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G325" s="1" t="s">
         <v>14</v>
@@ -15373,7 +15398,7 @@
         <v>71</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G326" s="1" t="s">
         <v>14</v>
@@ -15417,7 +15442,7 @@
         <v>590</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="328" spans="1:10" hidden="1">
@@ -15437,7 +15462,7 @@
         <v>71</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G328" s="1" t="s">
         <v>14</v>
@@ -15469,7 +15494,7 @@
         <v>71</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G329" s="1" t="s">
         <v>14</v>
@@ -15501,7 +15526,7 @@
         <v>71</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G330" s="1" t="s">
         <v>14</v>
@@ -15516,7 +15541,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" hidden="1">
       <c r="A331" s="4">
         <v>330</v>
       </c>
@@ -15565,7 +15590,7 @@
         <v>71</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G332" s="1" t="s">
         <v>14</v>
@@ -15597,7 +15622,7 @@
         <v>71</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G333" s="1" t="s">
         <v>14</v>
@@ -15629,7 +15654,7 @@
         <v>71</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G334" s="1" t="s">
         <v>14</v>
@@ -15661,7 +15686,7 @@
         <v>71</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G335" s="1" t="s">
         <v>14</v>
@@ -15693,7 +15718,7 @@
         <v>71</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G336" s="1" t="s">
         <v>14</v>
@@ -15725,7 +15750,7 @@
         <v>71</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G337" s="1" t="s">
         <v>14</v>
@@ -15740,7 +15765,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" hidden="1">
       <c r="A338" s="4">
         <v>337</v>
       </c>
@@ -15772,7 +15797,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" hidden="1">
       <c r="A339" s="4">
         <v>338</v>
       </c>
@@ -15804,7 +15829,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" hidden="1">
       <c r="A340" s="4">
         <v>339</v>
       </c>
@@ -15836,7 +15861,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" hidden="1">
       <c r="A341" s="4">
         <v>340</v>
       </c>
@@ -15868,7 +15893,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" hidden="1">
       <c r="A342" s="4">
         <v>341</v>
       </c>
@@ -15900,7 +15925,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="343" spans="1:10" hidden="1">
+    <row r="343" spans="1:10">
       <c r="A343" s="4">
         <v>342</v>
       </c>
@@ -15964,7 +15989,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" s="4">
         <v>344</v>
       </c>
@@ -15981,7 +16006,7 @@
         <v>79</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="G345" s="13" t="s">
         <v>14</v>
@@ -15993,10 +16018,10 @@
         <v>590</v>
       </c>
       <c r="J345" s="3" t="s">
-        <v>1035</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" s="4">
         <v>345</v>
       </c>
@@ -16028,7 +16053,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" s="4">
         <v>346</v>
       </c>
@@ -16060,7 +16085,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" s="4">
         <v>347</v>
       </c>
@@ -16092,7 +16117,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" hidden="1">
       <c r="A349" s="4">
         <v>348</v>
       </c>
@@ -16124,7 +16149,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" hidden="1">
       <c r="A350" s="4">
         <v>349</v>
       </c>
@@ -16156,7 +16181,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" hidden="1">
       <c r="A351" s="4">
         <v>350</v>
       </c>
@@ -16188,7 +16213,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" hidden="1">
       <c r="A352" s="4">
         <v>351</v>
       </c>
@@ -16220,7 +16245,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" hidden="1">
       <c r="A353" s="4">
         <v>352</v>
       </c>
@@ -16252,7 +16277,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" hidden="1">
       <c r="A354" s="4">
         <v>353</v>
       </c>
@@ -16284,7 +16309,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" hidden="1">
       <c r="A355" s="4">
         <v>354</v>
       </c>
@@ -16316,7 +16341,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" hidden="1">
       <c r="A356" s="4">
         <v>355</v>
       </c>
@@ -16348,7 +16373,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" hidden="1">
       <c r="A357" s="4">
         <v>356</v>
       </c>
@@ -16380,7 +16405,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" hidden="1">
       <c r="A358" s="4">
         <v>357</v>
       </c>
@@ -16412,7 +16437,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" hidden="1">
       <c r="A359" s="4">
         <v>358</v>
       </c>
@@ -16444,7 +16469,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" hidden="1">
       <c r="A360" s="4">
         <v>359</v>
       </c>
@@ -16473,10 +16498,10 @@
         <v>590</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" hidden="1">
       <c r="A361" s="4">
         <v>360</v>
       </c>
@@ -16508,7 +16533,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" hidden="1">
       <c r="A362" s="4">
         <v>361</v>
       </c>
@@ -16540,7 +16565,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" hidden="1">
       <c r="A363" s="4">
         <v>362</v>
       </c>
@@ -16572,7 +16597,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" hidden="1">
       <c r="A364" s="4">
         <v>363</v>
       </c>
@@ -16589,7 +16614,7 @@
         <v>79</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G364" s="1" t="s">
         <v>14</v>
@@ -16604,7 +16629,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" hidden="1">
       <c r="A365" s="4">
         <v>364</v>
       </c>
@@ -16653,7 +16678,7 @@
         <v>71</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G366" s="1" t="s">
         <v>14</v>
@@ -16668,7 +16693,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" hidden="1">
       <c r="A367" s="4">
         <v>366</v>
       </c>
@@ -16717,7 +16742,7 @@
         <v>71</v>
       </c>
       <c r="F368" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G368" s="1" t="s">
         <v>14</v>
@@ -16732,7 +16757,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" hidden="1">
       <c r="A369" s="4">
         <v>368</v>
       </c>
@@ -16781,7 +16806,7 @@
         <v>71</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G370" s="1" t="s">
         <v>14</v>
@@ -16793,7 +16818,7 @@
         <v>590</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="371" spans="1:10" hidden="1">
@@ -16828,7 +16853,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" hidden="1">
       <c r="A372" s="4">
         <v>371</v>
       </c>
@@ -16845,7 +16870,7 @@
         <v>79</v>
       </c>
       <c r="F372" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G372" s="1" t="s">
         <v>14</v>
@@ -16857,10 +16882,10 @@
         <v>590</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="373" spans="1:10">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="373" spans="1:10" hidden="1">
       <c r="A373" s="4">
         <v>372</v>
       </c>
@@ -16954,7 +16979,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" hidden="1">
       <c r="A376" s="4">
         <v>375</v>
       </c>
@@ -16971,7 +16996,7 @@
         <v>79</v>
       </c>
       <c r="F376" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G376" s="1" t="s">
         <v>14</v>
@@ -16983,10 +17008,10 @@
         <v>590</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="377" spans="1:10">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="377" spans="1:10" hidden="1">
       <c r="A377" s="4">
         <v>376</v>
       </c>
@@ -17003,7 +17028,7 @@
         <v>79</v>
       </c>
       <c r="F377" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G377" s="1" t="s">
         <v>14</v>
@@ -17015,7 +17040,7 @@
         <v>590</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="378" spans="1:10" hidden="1">
@@ -17082,7 +17107,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" hidden="1">
       <c r="A380" s="4">
         <v>379</v>
       </c>
@@ -17099,7 +17124,7 @@
         <v>79</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G380" s="1" t="s">
         <v>14</v>
@@ -17111,10 +17136,10 @@
         <v>590</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" hidden="1">
       <c r="A381" s="4">
         <v>380</v>
       </c>
@@ -17131,7 +17156,7 @@
         <v>79</v>
       </c>
       <c r="F381" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G381" s="1" t="s">
         <v>14</v>
@@ -17143,7 +17168,7 @@
         <v>590</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="382" spans="1:10" hidden="1">
@@ -17163,7 +17188,7 @@
         <v>71</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G382" s="1" t="s">
         <v>14</v>
@@ -17210,7 +17235,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="384" spans="1:10" hidden="1">
+    <row r="384" spans="1:10">
       <c r="A384" s="4">
         <v>383</v>
       </c>
@@ -17259,7 +17284,7 @@
         <v>19</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G385" s="1" t="s">
         <v>14</v>
@@ -17323,7 +17348,7 @@
         <v>71</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G387" s="1" t="s">
         <v>14</v>
@@ -17349,13 +17374,13 @@
         <v>11</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G388" s="1" t="s">
         <v>14</v>
@@ -17367,10 +17392,10 @@
         <v>590</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="389" spans="1:10" hidden="1">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
       <c r="A389" s="4">
         <v>388</v>
       </c>
@@ -17381,13 +17406,13 @@
         <v>11</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>25</v>
+        <v>1264</v>
       </c>
       <c r="G389" s="1" t="s">
         <v>14</v>
@@ -17399,7 +17424,7 @@
         <v>590</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="390" spans="1:10" hidden="1">
@@ -17413,13 +17438,13 @@
         <v>11</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G390" s="1" t="s">
         <v>14</v>
@@ -17431,7 +17456,7 @@
         <v>590</v>
       </c>
       <c r="J390" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="391" spans="1:10" hidden="1">
@@ -17445,13 +17470,13 @@
         <v>11</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G391" s="1" t="s">
         <v>14</v>
@@ -17463,7 +17488,7 @@
         <v>590</v>
       </c>
       <c r="J391" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="392" spans="1:10" hidden="1">
@@ -17477,13 +17502,13 @@
         <v>11</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G392" s="1" t="s">
         <v>14</v>
@@ -17495,7 +17520,7 @@
         <v>590</v>
       </c>
       <c r="J392" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="393" spans="1:10" hidden="1">
@@ -17786,7 +17811,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" hidden="1">
       <c r="A402" s="4">
         <v>401</v>
       </c>
@@ -17818,7 +17843,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" hidden="1">
       <c r="A403" s="4">
         <v>402</v>
       </c>
@@ -17850,7 +17875,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" hidden="1">
       <c r="A404" s="4">
         <v>403</v>
       </c>
@@ -17882,7 +17907,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" hidden="1">
       <c r="A405" s="4">
         <v>404</v>
       </c>
@@ -17914,7 +17939,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" hidden="1">
       <c r="A406" s="4">
         <v>405</v>
       </c>
@@ -17943,7 +17968,7 @@
         <v>590</v>
       </c>
       <c r="J406" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="407" spans="1:10" hidden="1">
@@ -18202,7 +18227,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" hidden="1">
       <c r="A415" s="4">
         <v>414</v>
       </c>
@@ -18219,7 +18244,7 @@
         <v>79</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>14</v>
@@ -18231,10 +18256,10 @@
         <v>666</v>
       </c>
       <c r="J415" s="3" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" hidden="1">
       <c r="A416" s="4">
         <v>415</v>
       </c>
@@ -18266,7 +18291,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" hidden="1">
       <c r="A417" s="4">
         <v>416</v>
       </c>
@@ -18298,7 +18323,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" hidden="1">
       <c r="A418" s="4">
         <v>417</v>
       </c>
@@ -18330,7 +18355,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" hidden="1">
       <c r="A419" s="4">
         <v>418</v>
       </c>
@@ -18362,7 +18387,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" hidden="1">
       <c r="A420" s="4">
         <v>419</v>
       </c>
@@ -18394,7 +18419,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" hidden="1">
       <c r="A421" s="4">
         <v>420</v>
       </c>
@@ -18411,7 +18436,7 @@
         <v>79</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>14</v>
@@ -18423,10 +18448,10 @@
         <v>590</v>
       </c>
       <c r="J421" s="3" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="422" spans="1:10">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="422" spans="1:10" hidden="1">
       <c r="A422" s="4">
         <v>421</v>
       </c>
@@ -18437,7 +18462,7 @@
         <v>11</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>79</v>
@@ -18455,10 +18480,10 @@
         <v>590</v>
       </c>
       <c r="J422" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="423" spans="1:10">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="423" spans="1:10" hidden="1">
       <c r="A423" s="4">
         <v>422</v>
       </c>
@@ -18469,7 +18494,7 @@
         <v>11</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>79</v>
@@ -18487,10 +18512,10 @@
         <v>666</v>
       </c>
       <c r="J423" s="3" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="424" spans="1:10">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="424" spans="1:10" hidden="1">
       <c r="A424" s="4">
         <v>423</v>
       </c>
@@ -18501,13 +18526,13 @@
         <v>11</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>79</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>14</v>
@@ -18520,7 +18545,7 @@
       </c>
       <c r="J424" s="24"/>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" hidden="1">
       <c r="A425" s="4">
         <v>424</v>
       </c>
@@ -18531,7 +18556,7 @@
         <v>11</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>79</v>
@@ -18549,10 +18574,10 @@
         <v>590</v>
       </c>
       <c r="J425" s="3" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="426" spans="1:10">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="426" spans="1:10" hidden="1">
       <c r="A426" s="4">
         <v>425</v>
       </c>
@@ -18581,7 +18606,7 @@
         <v>590</v>
       </c>
       <c r="J426" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="427" spans="1:10" hidden="1">
@@ -18613,10 +18638,10 @@
         <v>590</v>
       </c>
       <c r="J427" s="3" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="428" spans="1:10">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="428" spans="1:10" hidden="1">
       <c r="A428" s="4">
         <v>427</v>
       </c>
@@ -18659,13 +18684,13 @@
         <v>11</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>71</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>14</v>
@@ -18677,10 +18702,10 @@
         <v>590</v>
       </c>
       <c r="J429" s="3" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" hidden="1">
       <c r="A430" s="4">
         <v>429</v>
       </c>
@@ -18709,7 +18734,7 @@
         <v>590</v>
       </c>
       <c r="J430" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="431" spans="1:10" hidden="1">
@@ -18723,7 +18748,7 @@
         <v>11</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>357</v>
@@ -18741,7 +18766,7 @@
         <v>590</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="432" spans="1:10" hidden="1">
@@ -18755,7 +18780,7 @@
         <v>11</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>357</v>
@@ -18773,7 +18798,7 @@
         <v>590</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="433" spans="1:10" hidden="1">
@@ -18787,13 +18812,13 @@
         <v>11</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>32</v>
@@ -18805,7 +18830,7 @@
         <v>590</v>
       </c>
       <c r="J433" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="434" spans="1:10" hidden="1">
@@ -18819,13 +18844,13 @@
         <v>11</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>32</v>
@@ -18837,7 +18862,7 @@
         <v>590</v>
       </c>
       <c r="J434" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="435" spans="1:10" hidden="1">
@@ -18851,13 +18876,13 @@
         <v>11</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>32</v>
@@ -18869,7 +18894,7 @@
         <v>590</v>
       </c>
       <c r="J435" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="436" spans="1:10" hidden="1">
@@ -18909,13 +18934,13 @@
         <v>436</v>
       </c>
       <c r="B437" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>19</v>
@@ -18933,7 +18958,7 @@
         <v>590</v>
       </c>
       <c r="J437" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="438" spans="1:10" hidden="1">
@@ -18941,13 +18966,13 @@
         <v>437</v>
       </c>
       <c r="B438" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>23</v>
@@ -18971,13 +18996,13 @@
         <v>438</v>
       </c>
       <c r="B439" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>23</v>
@@ -19001,13 +19026,13 @@
         <v>439</v>
       </c>
       <c r="B440" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>23</v>
@@ -19031,13 +19056,13 @@
         <v>440</v>
       </c>
       <c r="B441" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>23</v>
@@ -19061,19 +19086,19 @@
         <v>441</v>
       </c>
       <c r="B442" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>32</v>
@@ -19091,19 +19116,19 @@
         <v>442</v>
       </c>
       <c r="B443" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>87</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G443" s="1" t="s">
         <v>32</v>
@@ -19121,7 +19146,7 @@
         <v>443</v>
       </c>
       <c r="B444" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C444" s="1" t="s">
         <v>87</v>
@@ -19151,7 +19176,7 @@
         <v>444</v>
       </c>
       <c r="B445" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>87</v>
@@ -19181,7 +19206,7 @@
         <v>445</v>
       </c>
       <c r="B446" s="53" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>87</v>
@@ -19211,19 +19236,19 @@
         <v>446</v>
       </c>
       <c r="B447" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>32</v>
@@ -19241,19 +19266,19 @@
         <v>447</v>
       </c>
       <c r="B448" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>32</v>
@@ -19271,19 +19296,19 @@
         <v>448</v>
       </c>
       <c r="B449" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>32</v>
@@ -19301,19 +19326,19 @@
         <v>449</v>
       </c>
       <c r="B450" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>32</v>
@@ -19331,19 +19356,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>32</v>
@@ -19361,19 +19386,19 @@
         <v>451</v>
       </c>
       <c r="B452" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G452" s="1" t="s">
         <v>32</v>
@@ -19391,19 +19416,19 @@
         <v>452</v>
       </c>
       <c r="B453" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>32</v>
@@ -19421,19 +19446,19 @@
         <v>453</v>
       </c>
       <c r="B454" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G454" s="1" t="s">
         <v>32</v>
@@ -19451,19 +19476,19 @@
         <v>454</v>
       </c>
       <c r="B455" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>32</v>
@@ -19481,19 +19506,19 @@
         <v>455</v>
       </c>
       <c r="B456" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>32</v>
@@ -19511,19 +19536,19 @@
         <v>456</v>
       </c>
       <c r="B457" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>32</v>
@@ -19541,19 +19566,19 @@
         <v>457</v>
       </c>
       <c r="B458" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>32</v>
@@ -19571,19 +19596,19 @@
         <v>458</v>
       </c>
       <c r="B459" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C459" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F459" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G459" s="1" t="s">
         <v>32</v>
@@ -19601,19 +19626,19 @@
         <v>459</v>
       </c>
       <c r="B460" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C460" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G460" s="1" t="s">
         <v>32</v>
@@ -19631,19 +19656,19 @@
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>32</v>
@@ -19661,19 +19686,19 @@
         <v>461</v>
       </c>
       <c r="B462" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>32</v>
@@ -19691,19 +19716,19 @@
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>32</v>
@@ -19721,19 +19746,19 @@
         <v>463</v>
       </c>
       <c r="B464" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>32</v>
@@ -19751,19 +19776,19 @@
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>32</v>
@@ -19781,19 +19806,19 @@
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>32</v>
@@ -19811,19 +19836,19 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>32</v>
@@ -19841,19 +19866,19 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>32</v>
@@ -19871,19 +19896,19 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>32</v>
@@ -19901,19 +19926,19 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G470" s="1" t="s">
         <v>32</v>
@@ -19931,7 +19956,7 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>11</v>
@@ -19961,7 +19986,7 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>11</v>
@@ -19991,7 +20016,7 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>11</v>
@@ -20021,7 +20046,7 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>11</v>
@@ -20051,7 +20076,7 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>11</v>
@@ -20081,7 +20106,7 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>11</v>
@@ -20111,7 +20136,7 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>11</v>
@@ -20141,7 +20166,7 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>11</v>
@@ -20171,7 +20196,7 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>11</v>
@@ -20201,7 +20226,7 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C480" s="1" t="s">
         <v>11</v>
@@ -20231,7 +20256,7 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>11</v>
@@ -20261,7 +20286,7 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>11</v>
@@ -20291,7 +20316,7 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>11</v>
@@ -20321,7 +20346,7 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>11</v>
@@ -20351,13 +20376,13 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D485" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>23</v>
@@ -20381,13 +20406,13 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D486" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>23</v>
@@ -20405,6 +20430,34 @@
         <v>590</v>
       </c>
       <c r="J486" s="24"/>
+    </row>
+    <row r="487" spans="1:10" hidden="1">
+      <c r="A487" s="54">
+        <v>486</v>
+      </c>
+      <c r="B487" s="60" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C487" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="D487" s="55"/>
+      <c r="E487" s="58" t="s">
+        <v>986</v>
+      </c>
+      <c r="F487" s="54" t="s">
+        <v>988</v>
+      </c>
+      <c r="G487" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="H487" s="56">
+        <v>46063</v>
+      </c>
+      <c r="I487" s="59" t="s">
+        <v>590</v>
+      </c>
+      <c r="J487" s="57"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -20435,7 +20488,7 @@
       <formula>"SOLAGOS DEPOSITO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F230 F232:F233 F235:F1048576">
+  <conditionalFormatting sqref="F232:F233 F235:F1048576 F1:F230">
     <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"MANUTENÇÃO"</formula>
     </cfRule>
@@ -22736,7 +22789,7 @@
         <v>71</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>

--- a/data_printer.xlsx
+++ b/data_printer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erick\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C44BBB5-F52F-478A-B9CF-022DE4D13BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B96353-0E8D-4765-BB32-A02333772F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A8AA41B5-7AA1-4FF7-A9B8-54B8A4E1AF28}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4326" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4327" uniqueCount="1289">
   <si>
     <t>INDICE</t>
   </si>
@@ -3241,9 +3241,6 @@
     <t>E.M. JOÃO BRITO SOUZA</t>
   </si>
   <si>
-    <t>E.M. PEDRO PAULO</t>
-  </si>
-  <si>
     <t>E.M. PARATI</t>
   </si>
   <si>
@@ -3307,9 +3304,6 @@
     <t>XBJZ043841</t>
   </si>
   <si>
-    <t>XC75036979</t>
-  </si>
-  <si>
     <t>XC75047651</t>
   </si>
   <si>
@@ -3847,18 +3841,9 @@
     <t>X3</t>
   </si>
   <si>
-    <t>X4</t>
-  </si>
-  <si>
-    <t>X5</t>
-  </si>
-  <si>
     <t>AL77042430DO</t>
   </si>
   <si>
-    <t>C.R.E.I.M. LACY FERREIRA DO AMARAL</t>
-  </si>
-  <si>
     <t>PAÇO - ADMINISTRAÇÃO - SECRETARIA</t>
   </si>
   <si>
@@ -3904,7 +3889,22 @@
     <t>ESTAVA NA CONTABILIDADE PAÇO; INSTALAÇÃO PAÇO SECRETARIA DE TRANSPORTE ADM 12/10/2025; INSTALAÇÃO UBS MORRO GRANDE 14/11/2025; RETIRATA UBS MORRO GRANDE 15/01/2026;</t>
   </si>
   <si>
-    <t>xx</t>
+    <t>XAABS33328</t>
+  </si>
+  <si>
+    <t>INSTALAÇÃO 08-06-26 IMPRESSORA NA CAIXA INSTALAÇÃO CRECHE SÃO MAXIMILIANO;</t>
+  </si>
+  <si>
+    <t>XAABR75680</t>
+  </si>
+  <si>
+    <t>CRECHE - C.R.E.I.M. LACY FER. DO AMARAL</t>
+  </si>
+  <si>
+    <t>CRECHE - M. VER. CIRALDO FER. DA SILVA</t>
+  </si>
+  <si>
+    <t>CRECHE - M. SÃO MAXIMILIANO M. KOLBE</t>
   </si>
 </sst>
 </file>
@@ -5420,7 +5420,7 @@
         <v>577</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5672,7 +5672,7 @@
         <v>577</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5704,7 +5704,7 @@
         <v>577</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5768,7 +5768,7 @@
         <v>577</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5788,7 +5788,7 @@
         <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>14</v>
@@ -5989,7 +5989,7 @@
         <v>577</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6983,7 +6983,7 @@
         <v>68</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>68</v>
@@ -7535,7 +7535,7 @@
         <v>577</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -7976,7 +7976,7 @@
         <v>11</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>21</v>
@@ -7994,7 +7994,7 @@
         <v>577</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -8075,7 +8075,7 @@
         <v>974</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>30</v>
@@ -8435,7 +8435,7 @@
         <v>76</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G102" s="4" t="s">
         <v>14</v>
@@ -9115,7 +9115,7 @@
         <v>577</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -9135,7 +9135,7 @@
         <v>68</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>30</v>
@@ -9167,7 +9167,7 @@
         <v>68</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G125" s="4" t="s">
         <v>14</v>
@@ -9179,7 +9179,7 @@
         <v>577</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -9199,7 +9199,7 @@
         <v>19</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>30</v>
@@ -9391,7 +9391,7 @@
         <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>14</v>
@@ -9435,7 +9435,7 @@
         <v>577</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -9455,7 +9455,7 @@
         <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G134" s="4" t="s">
         <v>14</v>
@@ -9487,7 +9487,7 @@
         <v>76</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G135" s="4" t="s">
         <v>14</v>
@@ -9499,7 +9499,7 @@
         <v>577</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -9519,7 +9519,7 @@
         <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G136" s="4" t="s">
         <v